--- a/otzyvy_halyk.xlsx
+++ b/otzyvy_halyk.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3213,6 +3213,1154 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>46253.51787037037</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>App Store</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Ужасное приложение банка</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Еле грузит, колл-центр типа с искусственными интеллектом который тупо молчит! Куда звонить!? Пишу в поддержку ответы тоже ии без решения проблемы. Вам до Каспи банка далеко!</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Злая 1479(</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>7.15.0</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>14446617149</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>46254.38908564814</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>5</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Класс!</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Laiosh Tolnai</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>a2b1475d0a4636044e411f96</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>46254.37627314815</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>5</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>очень удобно оплачивать ком услуги ну и все остальное</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Анаргуль Есенгалиева</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0d69e28794204a7ebc123308</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>46254.37443287037</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>5</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>все хорошо. спасибо</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Кайрат Маусымхан</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>7d68f1ac71d4d9fa0e6e7239</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>46254.36811342592</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>5</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Пока всё отлично! Просто, удобно.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Наталья Энзе</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>ebfe0c1582b6e0efd21a9304</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>46254.29225694444</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>5</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>👍👍👍</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Serikkali Moldahmetov</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>8f08456f1f7037ddfc48fb40</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>46254.26644675926</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>5</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Спасибо!Быстро и качественно.</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Фарит Абдуллин</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4bc036aaba61bf9681d0c2f8</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>46254.23796296296</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>4</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Очень удобный сервис!!!</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Камшат Есентаева</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>6ce3a6058942a3a52ea23739</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46254.18957175926</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>5</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Рахмет очень удобно пользоваться</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Мария Кулёва</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>974572017a25b0123bd5f57c</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>46254.15381944444</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>5</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>хорошо спасибо</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Elmurat Bayanov</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>abd0fd54964a3ac6c73eaf28</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>46254.12082175926</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>5</v>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>люблю халык банк</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Береза График</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>6147099de51977f68610bbdc</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>46254.10601851852</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>5</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>супер</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Бахтыгуль Алдажарова</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>af62592e2b234acc94cae3c7</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
+        <v>46254.0353587963</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>5</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Халык Алакан тоже сделайте, чтобы рукой можно было оплачивать</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Бауыржан Джаримбетов</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3bf98a3770b05e9be2c430cb</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>46253.99089120371</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>5</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>отлично</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Гульмира Тащанова</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>915995320029b26e5b7f6f0a</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46253.94253472222</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>довольно часто не работает приложение</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Зарина Султанова</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>0ed11d36c4bb48b15370e5e2</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>46253.93590277778</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>5</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>очень очень приятно</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Асхат Ногайбаев</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>a4b69efb01fca2c81b220ec9</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>46253.92797453704</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>5</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>очень удобное и нужное приложение.</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Adai</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>c2834899d00d38c54b8deb58</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>46253.91368055555</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>5</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>күшті</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Марат Газизович</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>4451aeedc50f456c670fa41c</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n">
+        <v>46253.91197916667</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>5</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>отличное приложение</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Kaiyrzhan Makhanov</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>534dacc61d02bb38aa52d612</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46253.89833333333</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>мало функции , те которые есть не совсем просто использовать , можно сделать проще и доступнее . Очень мало интернет магазинов ...</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Dos Dosanov</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>a4e57b2dff2e9988d2957d0d</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n">
+        <v>46253.87689814815</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>5</v>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>удобно</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Aisar Atabek</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>c9e20cbacf740c765c59a66c</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>46253.85269675926</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>4</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>иногда не могу найти историю платежа в приложении. например когда оплачиваешь проезд на автобус, когда выходишь не сможешь найти, а там реклама</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Багила Берниязова</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>27532977d33acaf460206cc3</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>46253.85040509259</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Ешқандай техподержка операторға хабарласақ тек обновит етіп қойдықтан басқасын аитпайды оператор сойлем аяқталмай телефонды өшіріп тастайды</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Сапармурат Абдуллаев</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>9c8033c621be3a2064bb1efc</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>46253.83737268519</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>5</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Super</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Данияр Мусаев</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>cae9951351f128d20380f025</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>46253.83456018518</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>бежать нужно с этого банка</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>виталий Шабалин</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>17b166bf83abe143eadce261</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>46253.77180555555</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>пОлучать сообщения опополнении</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Живой Некромант</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>4c30970474e4542378188c99</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/otzyvy_halyk.xlsx
+++ b/otzyvy_halyk.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3278,7 +3278,6 @@
       <c r="D63" t="n">
         <v>5</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>Класс!</t>
@@ -3322,7 +3321,6 @@
       <c r="D64" t="n">
         <v>5</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>очень удобно оплачивать ком услуги ну и все остальное</t>
@@ -3366,7 +3364,6 @@
       <c r="D65" t="n">
         <v>5</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>все хорошо. спасибо</t>
@@ -3410,7 +3407,6 @@
       <c r="D66" t="n">
         <v>5</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>Пока всё отлично! Просто, удобно.</t>
@@ -3454,7 +3450,6 @@
       <c r="D67" t="n">
         <v>5</v>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>👍👍👍</t>
@@ -3498,7 +3493,6 @@
       <c r="D68" t="n">
         <v>5</v>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>Спасибо!Быстро и качественно.</t>
@@ -3542,7 +3536,6 @@
       <c r="D69" t="n">
         <v>4</v>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>Очень удобный сервис!!!</t>
@@ -3586,7 +3579,6 @@
       <c r="D70" t="n">
         <v>5</v>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>Рахмет очень удобно пользоваться</t>
@@ -3630,7 +3622,6 @@
       <c r="D71" t="n">
         <v>5</v>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>хорошо спасибо</t>
@@ -3674,7 +3665,6 @@
       <c r="D72" t="n">
         <v>5</v>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>люблю халык банк</t>
@@ -3718,7 +3708,6 @@
       <c r="D73" t="n">
         <v>5</v>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>супер</t>
@@ -3762,7 +3751,6 @@
       <c r="D74" t="n">
         <v>5</v>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>Халык Алакан тоже сделайте, чтобы рукой можно было оплачивать</t>
@@ -3806,7 +3794,6 @@
       <c r="D75" t="n">
         <v>5</v>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -3894,7 +3881,6 @@
       <c r="D77" t="n">
         <v>5</v>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>очень очень приятно</t>
@@ -3938,7 +3924,6 @@
       <c r="D78" t="n">
         <v>5</v>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>очень удобное и нужное приложение.</t>
@@ -3982,7 +3967,6 @@
       <c r="D79" t="n">
         <v>5</v>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>күшті</t>
@@ -4026,7 +4010,6 @@
       <c r="D80" t="n">
         <v>5</v>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>отличное приложение</t>
@@ -4114,7 +4097,6 @@
       <c r="D82" t="n">
         <v>5</v>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>удобно</t>
@@ -4158,7 +4140,6 @@
       <c r="D83" t="n">
         <v>4</v>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>иногда не могу найти историю платежа в приложении. например когда оплачиваешь проезд на автобус, когда выходишь не сможешь найти, а там реклама</t>
@@ -4246,7 +4227,6 @@
       <c r="D85" t="n">
         <v>5</v>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>Super</t>
@@ -4358,6 +4338,1326 @@
       <c r="J87" s="2" t="inlineStr">
         <is>
           <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="n">
+        <v>46254.18469907407</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>5</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>самый лучший народ банк</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Айгуль Ахбаева</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2864ff427c1ec5b7a38a8ddc</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>46254.18075231482</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>5</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Класс!</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Laiosh Tolnai</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>fb0de02efe8d94f0fb464c70</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="n">
+        <v>46254.16793981481</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>5</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>очень удобно оплачивать ком услуги ну и все остальное</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Анаргуль Есенгалиева</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>a4b2e3adb13ad921414a6635</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>46254.16609953704</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>5</v>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>все хорошо. спасибо</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Кайрат Маусымхан</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>b66e41f33b3bb3375f4102bf</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n">
+        <v>46254.1597800926</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>5</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Пока всё отлично! Просто, удобно.</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Наталья Энзе</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>9d3a50aeb9a1be0e6401d30e</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>46254.08392361111</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>5</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>👍👍👍</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Serikkali Moldahmetov</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>fa70e056db59bff38e51054d</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n">
+        <v>46254.05811342593</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>5</v>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Спасибо!Быстро и качественно.</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Фарит Абдуллин</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>4f573c9546e98bc36e801317</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>46254.02962962963</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>4</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Очень удобный сервис!!!</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Камшат Есентаева</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>3ac78723f6934b7b7064559a</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="n">
+        <v>46253.98123842593</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>5</v>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Рахмет очень удобно пользоваться</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Мария Кулёва</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>016e6615c024070673bf537b</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n">
+        <v>46253.94548611111</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>5</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>хорошо спасибо</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Elmurat Bayanov</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>689bc9a55e1557b43da704d4</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="n">
+        <v>46253.91248842593</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>5</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>люблю халык банк</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Береза График</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>512494d0ed24072778dc9b83</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n">
+        <v>46253.89768518518</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>5</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>супер</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Бахтыгуль Алдажарова</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>bfdd751eb68d7c3bf8b7b130</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="n">
+        <v>46253.82702546296</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>5</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Халык Алакан тоже сделайте, чтобы рукой можно было оплачивать</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Бауыржан Джаримбетов</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1e0e140cbee81ea399bf2644</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>46253.78255787037</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>5</v>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>отлично</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Гульмира Тащанова</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>372cdfcf76255e31517f6e0a</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>46253.73420138889</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>довольно часто не работает приложение</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Зарина Султанова</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>c20dea8a5bacede13b8afe33</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n">
+        <v>46253.72756944445</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>5</v>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>очень очень приятно</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Асхат Ногайбаев</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>a20f62e75c4af9a4c89e6d16</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="n">
+        <v>46253.7196412037</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>5</v>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>очень удобное и нужное приложение.</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Adai</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>104605b9b756332baf327e20</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n">
+        <v>46253.70534722223</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>5</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>күшті</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Марат Газизович</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>f3caae2f5188c908e275e625</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n">
+        <v>46253.70364583333</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>5</v>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>отличное приложение</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Kaiyrzhan Makhanov</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>f73004388c6bc0250cc98d77</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>46253.69</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>мало функции , те которые есть не совсем просто использовать , можно сделать проще и доступнее . Очень мало интернет магазинов ...</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Dos Dosanov</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>9c1a2ea1ebbae7ec6973f028</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="n">
+        <v>46253.66856481481</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>5</v>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>удобно</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Aisar Atabek</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>c5bc570e86452296eeb6d4f6</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n">
+        <v>46253.64436342593</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>4</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>иногда не могу найти историю платежа в приложении. например когда оплачиваешь проезд на автобус, когда выходишь не сможешь найти, а там реклама</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Багила Берниязова</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>dfba5d63bd0015f0f6d282f6</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46253.64207175926</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Ешқандай техподержка операторға хабарласақ тек обновит етіп қойдықтан басқасын аитпайды оператор сойлем аяқталмай телефонды өшіріп тастайды</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Сапармурат Абдуллаев</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>0ea255c3e4d314ea782118e0</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n">
+        <v>46253.62903935185</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>5</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Super</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Данияр Мусаев</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>64dfc5192927ee9ff24e2692</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>46253.62622685185</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>бежать нужно с этого банка</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>виталий Шабалин</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>3afd299cae8695256dd5cc72</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>46253.56347222222</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>пОлучать сообщения опополнении</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Живой Некромант</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>6bf82710f4d2bb9d737675b8</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46253.56259259259</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>постоянно вылетает. предлагает постоянно обновляться. ненадежное приложение, в дороге подведет 100%.</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Али Исмаилов</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>9f2f384e2276d0b3d10a54f7</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n">
+        <v>46253.56158564815</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>5</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>круто</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Эльбек Равшанбеков</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>b051e59cd8b157f39c2e4384</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="n">
+        <v>46253.55957175926</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>4</v>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>медленно работает</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Ренат Сапаров</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2e4b3b335fa83f743650e470</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n">
+        <v>46253.54431712963</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>5</v>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>отлично</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Galim Alimbaev</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2eeb7fde5021868ee0939984</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>

--- a/otzyvy_halyk.xlsx
+++ b/otzyvy_halyk.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4358,7 +4358,6 @@
       <c r="D88" t="n">
         <v>5</v>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>самый лучший народ банк</t>
@@ -4402,7 +4401,6 @@
       <c r="D89" t="n">
         <v>5</v>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>Класс!</t>
@@ -4446,7 +4444,6 @@
       <c r="D90" t="n">
         <v>5</v>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>очень удобно оплачивать ком услуги ну и все остальное</t>
@@ -4490,7 +4487,6 @@
       <c r="D91" t="n">
         <v>5</v>
       </c>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>все хорошо. спасибо</t>
@@ -4534,7 +4530,6 @@
       <c r="D92" t="n">
         <v>5</v>
       </c>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>Пока всё отлично! Просто, удобно.</t>
@@ -4578,7 +4573,6 @@
       <c r="D93" t="n">
         <v>5</v>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>👍👍👍</t>
@@ -4622,7 +4616,6 @@
       <c r="D94" t="n">
         <v>5</v>
       </c>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>Спасибо!Быстро и качественно.</t>
@@ -4666,7 +4659,6 @@
       <c r="D95" t="n">
         <v>4</v>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>Очень удобный сервис!!!</t>
@@ -4710,7 +4702,6 @@
       <c r="D96" t="n">
         <v>5</v>
       </c>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>Рахмет очень удобно пользоваться</t>
@@ -4754,7 +4745,6 @@
       <c r="D97" t="n">
         <v>5</v>
       </c>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>хорошо спасибо</t>
@@ -4798,7 +4788,6 @@
       <c r="D98" t="n">
         <v>5</v>
       </c>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>люблю халык банк</t>
@@ -4842,7 +4831,6 @@
       <c r="D99" t="n">
         <v>5</v>
       </c>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>супер</t>
@@ -4886,7 +4874,6 @@
       <c r="D100" t="n">
         <v>5</v>
       </c>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>Халык Алакан тоже сделайте, чтобы рукой можно было оплачивать</t>
@@ -4930,7 +4917,6 @@
       <c r="D101" t="n">
         <v>5</v>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -5018,7 +5004,6 @@
       <c r="D103" t="n">
         <v>5</v>
       </c>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>очень очень приятно</t>
@@ -5062,7 +5047,6 @@
       <c r="D104" t="n">
         <v>5</v>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>очень удобное и нужное приложение.</t>
@@ -5106,7 +5090,6 @@
       <c r="D105" t="n">
         <v>5</v>
       </c>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>күшті</t>
@@ -5150,7 +5133,6 @@
       <c r="D106" t="n">
         <v>5</v>
       </c>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>отличное приложение</t>
@@ -5238,7 +5220,6 @@
       <c r="D108" t="n">
         <v>5</v>
       </c>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>удобно</t>
@@ -5282,7 +5263,6 @@
       <c r="D109" t="n">
         <v>4</v>
       </c>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>иногда не могу найти историю платежа в приложении. например когда оплачиваешь проезд на автобус, когда выходишь не сможешь найти, а там реклама</t>
@@ -5370,7 +5350,6 @@
       <c r="D111" t="n">
         <v>5</v>
       </c>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>Super</t>
@@ -5546,7 +5525,6 @@
       <c r="D115" t="n">
         <v>5</v>
       </c>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>круто</t>
@@ -5590,7 +5568,6 @@
       <c r="D116" t="n">
         <v>4</v>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>медленно работает</t>
@@ -5634,7 +5611,6 @@
       <c r="D117" t="n">
         <v>5</v>
       </c>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -5656,6 +5632,50 @@
         </is>
       </c>
       <c r="J117" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="n">
+        <v>46254.19555555555</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>5</v>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>все отлично работает рекомендую 🔥</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Самир Бабенов</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>46c7507e70c1d2dcc78dcc77</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
         <is>
           <t>нет</t>
         </is>

--- a/otzyvy_halyk.xlsx
+++ b/otzyvy_halyk.xlsx
@@ -5654,7 +5654,6 @@
       <c r="D118" t="n">
         <v>5</v>
       </c>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>все отлично работает рекомендую 🔥</t>

--- a/otzyvy_halyk.xlsx
+++ b/otzyvy_halyk.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J120"/>
+  <dimension ref="A1:J150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46254.40388888889</v>
+        <v>46255.20873842593</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -499,22 +499,18 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>все отлично работает рекомендую 🔥</t>
+          <t>Мне почему то не одобряет кредит? Почему?</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Самир Бабенов</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>7.14.0</t>
-        </is>
-      </c>
+          <t>Назым Медетбекова</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1d706399a1a41e9d88bace0a</t>
+          <t>5cf847481dbc9620da12c414</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -525,7 +521,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>46254.39303240741</v>
+        <v>46255.2072800926</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -543,12 +539,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>самый лучший народ банк</t>
+          <t>удобное приложение</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Айгуль Ахбаева</t>
+          <t>Rashida Gabitova</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -558,7 +554,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>902a4c325bd87cb378424e29</t>
+          <t>fa23f3fb60c751836c8f9c5a</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -569,7 +565,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46254.38908564814</v>
+        <v>46255.20168981481</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -584,24 +580,25 @@
       <c r="D4" t="n">
         <v>5</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Класс!</t>
+          <t>Ең керемет банк</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Laiosh Tolnai</t>
+          <t>Меирамкул Курманалиева</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.13.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>a2b1475d0a4636044e411f96</t>
+          <t>97790e1e18a0850e97295caa</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -612,7 +609,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46254.37627314815</v>
+        <v>46255.18505787037</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -627,24 +624,21 @@
       <c r="D5" t="n">
         <v>5</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>очень удобно оплачивать ком услуги ну и все остальное</t>
+          <t>отлично</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Анаргуль Есенгалиева</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>7.15.2</t>
-        </is>
-      </c>
+          <t>Айбар Жантлеуов</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0d69e28794204a7ebc123308</t>
+          <t>9790d3324f980775058dee07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -655,7 +649,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46254.37443287037</v>
+        <v>46255.18493055556</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -668,16 +662,17 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>все хорошо. спасибо</t>
+          <t>👍👍👍</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Кайрат Маусымхан</t>
+          <t>Алмагуль Балтаева</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -687,7 +682,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7d68f1ac71d4d9fa0e6e7239</t>
+          <t>803e45eee322d30bebf059ed</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -698,7 +693,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46254.36811342592</v>
+        <v>46255.17663194444</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -713,14 +708,15 @@
       <c r="D7" t="n">
         <v>5</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Пока всё отлично! Просто, удобно.</t>
+          <t>мне нравится, единственная только,что не можем заказывать продукты в Магнум, смолл...через приложение, а так все на отлично</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Наталья Энзе</t>
+          <t>Кульсара Куатбайкызы КульСара</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -730,7 +726,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ebfe0c1582b6e0efd21a9304</t>
+          <t>c6fadabdb81d7d5302855f26</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -741,7 +737,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46254.29225694444</v>
+        <v>46255.16217592593</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -756,24 +752,25 @@
       <c r="D8" t="n">
         <v>5</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>👍👍👍</t>
+          <t>Всё отлично 👌</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Serikkali Moldahmetov</t>
+          <t>Viktor Boiko</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8f08456f1f7037ddfc48fb40</t>
+          <t>81d33296827e492996ecd6e0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -784,7 +781,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46254.26644675926</v>
+        <v>46254.8696875</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -799,78 +796,80 @@
       <c r="D9" t="n">
         <v>5</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Спасибо!Быстро и качественно.</t>
+          <t>удобно</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Фарит Абдуллин</t>
+          <t>Алимаш Абишева</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>b08cf092cec14373fc514b8a</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46254.74541666666</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>перевод на абонента каждый раз надо набирать, повторить не возможно</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Мурат Маткеримов</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4bc036aaba61bf9681d0c2f8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>46254.23796296296</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Очень удобный сервис!!!</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Камшат Есентаева</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>7.14.0</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6ce3a6058942a3a52ea23739</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>91bd44e2d2d7e691e8d6cbff</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46254.19555555555</v>
+        <v>46254.74200231482</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -885,24 +884,25 @@
       <c r="D11" t="n">
         <v>5</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>все отлично работает рекомендую 🔥</t>
+          <t>отлично</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Самир Бабенов</t>
+          <t>Галымбек Абжанов</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>46c7507e70c1d2dcc78dcc77</t>
+          <t>2c562ffefb82d242c72d750a</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -913,7 +913,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46254.18957175926</v>
+        <v>46254.72582175926</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -928,24 +928,25 @@
       <c r="D12" t="n">
         <v>5</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Рахмет очень удобно пользоваться</t>
+          <t>все нужное в одном приложении</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Мария Кулёва</t>
+          <t>Azamat Azamatov</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.10.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>974572017a25b0123bd5f57c</t>
+          <t>aa7eb7c3883776ebed41a267</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -956,7 +957,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46254.18469907407</v>
+        <v>46254.67237268519</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -971,14 +972,15 @@
       <c r="D13" t="n">
         <v>5</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>самый лучший народ банк</t>
+          <t>Классное приложение</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Айгуль Ахбаева</t>
+          <t>Куаныш Адам</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -988,7 +990,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2864ff427c1ec5b7a38a8ddc</t>
+          <t>a612b01c975adbcde2ac3f7b</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -998,51 +1000,52 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>46254.18075231482</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Класс!</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Laiosh Tolnai</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="A14" s="1" t="n">
+        <v>46254.64497685185</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>пишет удалите приложение, загрузите с официального источника</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Maxim Balashov</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>fb0de02efe8d94f0fb464c70</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1f95a099d22c142607b9f342</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46254.16793981481</v>
+        <v>46254.61626157408</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1057,14 +1060,15 @@
       <c r="D15" t="n">
         <v>5</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>очень удобно оплачивать ком услуги ну и все остальное</t>
+          <t>здравствуйте, банк очень хороший, на все вопросы можно получить быстрый и профессиональный ответ, операторы очень вежливые и грамотные, спасибо!!!</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Анаргуль Есенгалиева</t>
+          <t>Андрей Макаров</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1074,7 +1078,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>a4b2e3adb13ad921414a6635</t>
+          <t>a9d8e91c4657493dd304c4c4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1085,7 +1089,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46254.16609953704</v>
+        <v>46254.60901620371</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1100,14 +1104,15 @@
       <c r="D16" t="n">
         <v>5</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>все хорошо. спасибо</t>
+          <t>спасибо</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Кайрат Маусымхан</t>
+          <t>Евгения Кизильбашева</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1117,7 +1122,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>b66e41f33b3bb3375f4102bf</t>
+          <t>754322021db55b561edd5fba</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1128,7 +1133,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46254.1597800926</v>
+        <v>46254.59369212963</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1143,24 +1148,25 @@
       <c r="D17" t="n">
         <v>5</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Пока всё отлично! Просто, удобно.</t>
+          <t>Интернет слабыи</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Наталья Энзе</t>
+          <t>Елубаи Исабаев</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.13.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9d3a50aeb9a1be0e6401d30e</t>
+          <t>eb3dd17a5338aa923ae7b590</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1171,7 +1177,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46254.15381944444</v>
+        <v>46254.5825462963</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1186,14 +1192,15 @@
       <c r="D18" t="n">
         <v>5</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>хорошо спасибо</t>
+          <t>Большое спасибо, всё нравиться, удачи вам в вашей работе!!!</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Elmurat Bayanov</t>
+          <t>Надежда</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1203,7 +1210,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>abd0fd54964a3ac6c73eaf28</t>
+          <t>d89f143961b7c54d67186eb9</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1214,7 +1221,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46254.12082175926</v>
+        <v>46254.57494212963</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1229,14 +1236,15 @@
       <c r="D19" t="n">
         <v>5</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>люблю халык банк</t>
+          <t>Народный банк самый лучший!</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Береза График</t>
+          <t>Abai Hakimov</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1246,7 +1254,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6147099de51977f68610bbdc</t>
+          <t>5e89bf7d0445a6d4c56a03ca</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1257,7 +1265,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46254.10601851852</v>
+        <v>46254.57232638889</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1270,26 +1278,27 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>супер</t>
+          <t>Приложение хорошее. Но нужно доработать многое и увеличить сферы услуг как на Камри банк. И вот программа очень долго думает при работе с клиентами. А в остальном все хорошо.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Бахтыгуль Алдажарова</t>
+          <t>Бейбут Мапитов</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>af62592e2b234acc94cae3c7</t>
+          <t>2eb752646789d9b4757248c0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1300,7 +1309,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46254.08392361111</v>
+        <v>46254.53262731482</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1315,14 +1324,15 @@
       <c r="D21" t="n">
         <v>5</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>👍👍👍</t>
+          <t>все хорошо!!</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Serikkali Moldahmetov</t>
+          <t>Сауле</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1332,7 +1342,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>fa70e056db59bff38e51054d</t>
+          <t>8db3d3391197733724486294</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1343,7 +1353,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46254.05811342593</v>
+        <v>46254.50099537037</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1358,14 +1368,15 @@
       <c r="D22" t="n">
         <v>5</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Спасибо!Быстро и качественно.</t>
+          <t>отлично</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Фарит Абдуллин</t>
+          <t>Бахытгуль Машауова</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1375,7 +1386,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4f573c9546e98bc36e801317</t>
+          <t>41ce544ddd314bb43102ad3c</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1386,7 +1397,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46254.0353587963</v>
+        <v>46254.49489583333</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1401,24 +1412,25 @@
       <c r="D23" t="n">
         <v>5</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Халык Алакан тоже сделайте, чтобы рукой можно было оплачивать</t>
+          <t>хороший приложение</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Бауыржан Джаримбетов</t>
+          <t>Жасылан Мустафин</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3bf98a3770b05e9be2c430cb</t>
+          <t>05fd972f45b29f751ad0c7e2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1429,7 +1441,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46254.02962962963</v>
+        <v>46254.49033564814</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1442,26 +1454,27 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Очень удобный сервис!!!</t>
+          <t>благодарю за труд.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Камшат Есентаева</t>
+          <t>Ринат Абдулин</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3ac78723f6934b7b7064559a</t>
+          <t>8da80f96b67bcea577ac6da1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1472,7 +1485,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46253.99089120371</v>
+        <v>46254.47194444444</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1487,24 +1500,25 @@
       <c r="D25" t="n">
         <v>5</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>отлично</t>
+          <t>жақсы</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Гульмира Тащанова</t>
+          <t>Куралай искен</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>915995320029b26e5b7f6f0a</t>
+          <t>57b87dd718575213574108a1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1515,7 +1529,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46253.98123842593</v>
+        <v>46254.46241898148</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1530,24 +1544,25 @@
       <c r="D26" t="n">
         <v>5</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Рахмет очень удобно пользоваться</t>
+          <t>Все устраивает. Halyk работает хорошо.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Мария Кулёва</t>
+          <t>Наталья Шеина</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>016e6615c024070673bf537b</t>
+          <t>16954a1d03ed6273ebdaff39</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1558,7 +1573,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46253.94548611111</v>
+        <v>46254.45520833333</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1573,14 +1588,15 @@
       <c r="D27" t="n">
         <v>5</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>хорошо спасибо</t>
+          <t>Отлично</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Elmurat Bayanov</t>
+          <t>Серик Толыбаев</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1590,7 +1606,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>689bc9a55e1557b43da704d4</t>
+          <t>857538ba251754a59756c996</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1601,7 +1617,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46253.94253472222</v>
+        <v>46254.45472222222</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
@@ -1614,27 +1630,27 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>довольно часто не работает приложение</t>
+          <t>Из всех банковских приложений это самое убогое.Заходишь пишут обновить, заходишь в плей маркет ,обновления нет .Удаляешь ,заново скачиваю опять тоже самое.Вы разработчики издеваетесь 😡😡😡</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Зарина Султанова</t>
+          <t>Alex Nord</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0ed11d36c4bb48b15370e5e2</t>
+          <t>f0e15c297aaa467375c1f44d</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -1645,7 +1661,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46253.93590277778</v>
+        <v>46254.44621527778</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1660,14 +1676,15 @@
       <c r="D29" t="n">
         <v>5</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>очень очень приятно</t>
+          <t>все хорошо</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Асхат Ногайбаев</t>
+          <t>Сауле Шуйкенова</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1677,7 +1694,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>a4b69efb01fca2c81b220ec9</t>
+          <t>34c8dbd8f4db6ced0bc667a6</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1687,51 +1704,52 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>46253.92797453704</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>5</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>очень удобное и нужное приложение.</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Adai</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="A30" s="1" t="n">
+        <v>46254.43652777778</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>почему удержали 1 тыс тенге</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Шалкар Казжанов</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>c2834899d00d38c54b8deb58</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1aa4118e55ac6e7359b7dd74</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46253.91368055555</v>
+        <v>46254.43355324074</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1746,24 +1764,25 @@
       <c r="D31" t="n">
         <v>5</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>күшті</t>
+          <t>удобно</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Марат Газизович</t>
+          <t>Кайролла</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.13.0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4451aeedc50f456c670fa41c</t>
+          <t>3a01546a2ff51ef0067d39e3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1774,7 +1793,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46253.91248842593</v>
+        <v>46254.40388888889</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1791,22 +1810,22 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>люблю халык банк</t>
+          <t>все отлично работает рекомендую 🔥</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Береза График</t>
+          <t>Самир Бабенов</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>512494d0ed24072778dc9b83</t>
+          <t>1d706399a1a41e9d88bace0a</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1817,7 +1836,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46253.91197916667</v>
+        <v>46254.39303240741</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1834,12 +1853,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>отличное приложение</t>
+          <t>самый лучший народ банк</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Kaiyrzhan Makhanov</t>
+          <t>Айгуль Ахбаева</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1849,7 +1868,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>534dacc61d02bb38aa52d612</t>
+          <t>902a4c325bd87cb378424e29</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1859,52 +1878,51 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>46253.89833333333</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>мало функции , те которые есть не совсем просто использовать , можно сделать проще и доступнее . Очень мало интернет магазинов ...</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Dos Dosanov</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="A34" s="3" t="n">
+        <v>46254.38908564814</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Класс!</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Laiosh Tolnai</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>a4e57b2dff2e9988d2957d0d</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>a2b1475d0a4636044e411f96</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46253.89768518518</v>
+        <v>46254.37627314815</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1921,22 +1939,22 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>супер</t>
+          <t>очень удобно оплачивать ком услуги ну и все остальное</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Бахтыгуль Алдажарова</t>
+          <t>Анаргуль Есенгалиева</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>bfdd751eb68d7c3bf8b7b130</t>
+          <t>0d69e28794204a7ebc123308</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1947,7 +1965,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46253.87689814815</v>
+        <v>46254.37443287037</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1964,22 +1982,22 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>удобно</t>
+          <t>все хорошо. спасибо</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Aisar Atabek</t>
+          <t>Кайрат Маусымхан</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>c9e20cbacf740c765c59a66c</t>
+          <t>7d68f1ac71d4d9fa0e6e7239</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1990,7 +2008,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46253.85269675926</v>
+        <v>46254.36811342592</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2003,81 +2021,80 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>иногда не могу найти историю платежа в приложении. например когда оплачиваешь проезд на автобус, когда выходишь не сможешь найти, а там реклама</t>
+          <t>Пока всё отлично! Просто, удобно.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Багила Берниязова</t>
+          <t>Наталья Энзе</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ebfe0c1582b6e0efd21a9304</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>46254.29225694444</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>👍👍👍</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Serikkali Moldahmetov</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>27532977d33acaf460206cc3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>46253.85040509259</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Ешқандай техподержка операторға хабарласақ тек обновит етіп қойдықтан басқасын аитпайды оператор сойлем аяқталмай телефонды өшіріп тастайды</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Сапармурат Абдуллаев</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>7.15.2</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>9c8033c621be3a2064bb1efc</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>8f08456f1f7037ddfc48fb40</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46253.83737268519</v>
+        <v>46254.26644675926</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2094,12 +2111,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Super</t>
+          <t>Спасибо!Быстро и качественно.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Данияр Мусаев</t>
+          <t>Фарит Абдуллин</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2109,7 +2126,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>cae9951351f128d20380f025</t>
+          <t>4bc036aaba61bf9681d0c2f8</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2119,52 +2136,51 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>46253.83456018518</v>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>бежать нужно с этого банка</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>виталий Шабалин</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="A40" s="3" t="n">
+        <v>46254.23796296296</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Очень удобный сервис!!!</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Камшат Есентаева</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>17b166bf83abe143eadce261</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6ce3a6058942a3a52ea23739</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46253.82702546296</v>
+        <v>46254.19555555555</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2181,22 +2197,22 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Халык Алакан тоже сделайте, чтобы рукой можно было оплачивать</t>
+          <t>все отлично работает рекомендую 🔥</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Бауыржан Джаримбетов</t>
+          <t>Самир Бабенов</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1e0e140cbee81ea399bf2644</t>
+          <t>46c7507e70c1d2dcc78dcc77</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2207,7 +2223,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46253.78255787037</v>
+        <v>46254.18957175926</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2224,121 +2240,119 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>отлично</t>
+          <t>Рахмет очень удобно пользоваться</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Гульмира Тащанова</t>
+          <t>Мария Кулёва</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>974572017a25b0123bd5f57c</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>46254.18469907407</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>самый лучший народ банк</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Айгуль Ахбаева</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>372cdfcf76255e31517f6e0a</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>46253.77180555555</v>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>пОлучать сообщения опополнении</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Живой Некромант</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>7.14.0</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>4c30970474e4542378188c99</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2864ff427c1ec5b7a38a8ddc</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>46253.77092592593</v>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>постоянно вылетает. предлагает постоянно обновляться. ненадежное приложение, в дороге подведет 100%.</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Али Исмаилов</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="A44" s="3" t="n">
+        <v>46254.18075231482</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Класс!</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Laiosh Tolnai</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>9b6472222913528ab39424db</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>fb0de02efe8d94f0fb464c70</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46253.76991898148</v>
+        <v>46254.16793981481</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2355,12 +2369,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>круто</t>
+          <t>очень удобно оплачивать ком услуги ну и все остальное</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Эльбек Равшанбеков</t>
+          <t>Анаргуль Есенгалиева</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2370,7 +2384,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>7ecde1d490bd0dfc3f3cb0f3</t>
+          <t>a4b2e3adb13ad921414a6635</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2381,7 +2395,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46253.76790509259</v>
+        <v>46254.16609953704</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2394,26 +2408,26 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>медленно работает</t>
+          <t>все хорошо. спасибо</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ренат Сапаров</t>
+          <t>Кайрат Маусымхан</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>c2404043e825d2060f4d5fd5</t>
+          <t>b66e41f33b3bb3375f4102bf</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2424,7 +2438,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46253.75265046296</v>
+        <v>46254.1597800926</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2441,12 +2455,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>отлично</t>
+          <t>Пока всё отлично! Просто, удобно.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Galim Alimbaev</t>
+          <t>Наталья Энзе</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2456,7 +2470,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>16b0ed98238aa2c416ad337f</t>
+          <t>9d3a50aeb9a1be0e6401d30e</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2466,52 +2480,51 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>46253.73420138889</v>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E48" s="2" t="n"/>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>довольно часто не работает приложение</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Зарина Султанова</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>7.14.0</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>c20dea8a5bacede13b8afe33</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="A48" s="3" t="n">
+        <v>46254.15381944444</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>хорошо спасибо</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Elmurat Bayanov</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>abd0fd54964a3ac6c73eaf28</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46253.73025462963</v>
+        <v>46254.12082175926</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2528,12 +2541,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>просто супер</t>
+          <t>люблю халык банк</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Манарбек Сундетов</t>
+          <t>Береза График</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2543,7 +2556,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>ffb6dba62e8c0cd009c9c61f</t>
+          <t>6147099de51977f68610bbdc</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2554,7 +2567,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46253.72756944445</v>
+        <v>46254.10601851852</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2571,12 +2584,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>очень очень приятно</t>
+          <t>супер</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Асхат Ногайбаев</t>
+          <t>Бахтыгуль Алдажарова</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2586,7 +2599,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>a20f62e75c4af9a4c89e6d16</t>
+          <t>af62592e2b234acc94cae3c7</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2597,7 +2610,7 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46253.7196412037</v>
+        <v>46254.08392361111</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2614,22 +2627,22 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>очень удобное и нужное приложение.</t>
+          <t>👍👍👍</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Adai</t>
+          <t>Serikkali Moldahmetov</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>104605b9b756332baf327e20</t>
+          <t>fa70e056db59bff38e51054d</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2639,52 +2652,51 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>46253.71857638889</v>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>как обновлять приложение? раз два в месяц просят обновить,а кнопки обновить нет. Приходится удалять и заново регистрироваться. в плэй маркет тоже написано либо открыть либо удалить приложение.</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Дана Нуралбаева</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>7.15.2</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>485dcc361736176a994fa708</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="A52" s="3" t="n">
+        <v>46254.05811342593</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Спасибо!Быстро и качественно.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Фарит Абдуллин</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4f573c9546e98bc36e801317</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46253.70534722223</v>
+        <v>46254.0353587963</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2701,22 +2713,22 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>күшті</t>
+          <t>Халык Алакан тоже сделайте, чтобы рукой можно было оплачивать</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Марат Газизович</t>
+          <t>Бауыржан Джаримбетов</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>f3caae2f5188c908e275e625</t>
+          <t>3bf98a3770b05e9be2c430cb</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2727,7 +2739,7 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46253.70364583333</v>
+        <v>46254.02962962963</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2740,26 +2752,26 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>отличное приложение</t>
+          <t>Очень удобный сервис!!!</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Kaiyrzhan Makhanov</t>
+          <t>Камшат Есентаева</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>f73004388c6bc0250cc98d77</t>
+          <t>3ac78723f6934b7b7064559a</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2770,7 +2782,7 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46253.70266203704</v>
+        <v>46253.99089120371</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2787,77 +2799,76 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>просто после каждой покупки есть бонусы люблю этот банк</t>
+          <t>отлично</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Milka</t>
+          <t>Гульмира Тащанова</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>915995320029b26e5b7f6f0a</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>46253.98123842593</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Рахмет очень удобно пользоваться</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Мария Кулёва</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>60fdf22787e9bc58fff13ee8</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>46253.69</v>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>мало функции , те которые есть не совсем просто использовать , можно сделать проще и доступнее . Очень мало интернет магазинов ...</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Dos Dosanov</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>7.15.2</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>9c1a2ea1ebbae7ec6973f028</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>016e6615c024070673bf537b</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46253.66856481481</v>
+        <v>46253.94548611111</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2874,12 +2885,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>удобно</t>
+          <t>хорошо спасибо</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Aisar Atabek</t>
+          <t>Elmurat Bayanov</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2889,7 +2900,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>c5bc570e86452296eeb6d4f6</t>
+          <t>689bc9a55e1557b43da704d4</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2899,95 +2910,95 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
-        <v>46253.66216435185</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>5</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>спасибо</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Гульфия Баянова</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
+      <c r="A58" s="1" t="n">
+        <v>46253.94253472222</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>довольно часто не работает приложение</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Зарина Султанова</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>fecedf3dff791736f089b6d2</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>0ed11d36c4bb48b15370e5e2</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>46253.64832175926</v>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="2" t="n"/>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>Ассалаумағалайкум! Өте жаман банк, маған рефинансирования бермеген және бонус, жеңілдік ешқашан жасамайсыздар, тек өз қалтасын ойлаған банк, ещё аты халық деп қойған, өзгертіңіздер.</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Ербулан Кабенов</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="A59" s="3" t="n">
+        <v>46253.93590277778</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>очень очень приятно</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Асхат Ногайбаев</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
         <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>14953e8c80868af9144af552</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>a4b69efb01fca2c81b220ec9</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46253.64436342593</v>
+        <v>46253.92797453704</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3000,81 +3011,80 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>иногда не могу найти историю платежа в приложении. например когда оплачиваешь проезд на автобус, когда выходишь не сможешь найти, а там реклама</t>
+          <t>очень удобное и нужное приложение.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Багила Берниязова</t>
+          <t>Adai</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>c2834899d00d38c54b8deb58</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>46253.91368055555</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>5</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>күшті</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Марат Газизович</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>dfba5d63bd0015f0f6d282f6</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>46253.64207175926</v>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="2" t="n"/>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Ешқандай техподержка операторға хабарласақ тек обновит етіп қойдықтан басқасын аитпайды оператор сойлем аяқталмай телефонды өшіріп тастайды</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Сапармурат Абдуллаев</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>7.15.2</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>0ea255c3e4d314ea782118e0</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>4451aeedc50f456c670fa41c</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46253.63549768519</v>
+        <v>46253.91248842593</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3091,22 +3101,22 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Супер</t>
+          <t>люблю халык банк</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nurgul Saduakasova</t>
+          <t>Береза График</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>dd777fb21421f322c1754e84</t>
+          <t>512494d0ed24072778dc9b83</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3117,7 +3127,7 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46253.62903935185</v>
+        <v>46253.91197916667</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3134,22 +3144,22 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Super</t>
+          <t>отличное приложение</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Данияр Мусаев</t>
+          <t>Kaiyrzhan Makhanov</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>64dfc5192927ee9ff24e2692</t>
+          <t>534dacc61d02bb38aa52d612</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3160,7 +3170,7 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46253.62622685185</v>
+        <v>46253.89833333333</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
@@ -3173,27 +3183,27 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" s="2" t="n"/>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>бежать нужно с этого банка</t>
+          <t>мало функции , те которые есть не совсем просто использовать , можно сделать проще и доступнее . Очень мало интернет магазинов ...</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>виталий Шабалин</t>
+          <t>Dos Dosanov</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>3afd299cae8695256dd5cc72</t>
+          <t>a4e57b2dff2e9988d2957d0d</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -3204,7 +3214,7 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46253.61278935185</v>
+        <v>46253.89768518518</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3221,22 +3231,22 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>хорошо</t>
+          <t>супер</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Smarysam</t>
+          <t>Бахтыгуль Алдажарова</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>7.13.0</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>753ffb6cc20c0b9b5de215f8</t>
+          <t>bfdd751eb68d7c3bf8b7b130</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3247,7 +3257,7 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46253.60559027778</v>
+        <v>46253.87689814815</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3264,22 +3274,22 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>все круто мне нравится удобно быстро</t>
+          <t>удобно</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sania Sania</t>
+          <t>Aisar Atabek</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>7.13.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>97a88caa8bec831663f6eed7</t>
+          <t>c9e20cbacf740c765c59a66c</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3290,7 +3300,7 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46253.59975694444</v>
+        <v>46253.85269675926</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3303,26 +3313,26 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>удобно</t>
+          <t>иногда не могу найти историю платежа в приложении. например когда оплачиваешь проезд на автобус, когда выходишь не сможешь найти, а там реклама</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Galina Messerle</t>
+          <t>Багила Берниязова</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1b46d6fd93e72ddea1708603</t>
+          <t>27532977d33acaf460206cc3</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3333,7 +3343,7 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46253.58292824074</v>
+        <v>46253.85040509259</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
@@ -3351,22 +3361,22 @@
       <c r="E68" s="2" t="n"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>неге қайта қайта жаңарту сұрай береді оны істесем ашпайды ғой</t>
+          <t>Ешқандай техподержка операторға хабарласақ тек обновит етіп қойдықтан басқасын аитпайды оператор сойлем аяқталмай телефонды өшіріп тастайды</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Нурсултан мусаев</t>
+          <t>Сапармурат Абдуллаев</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>5.34.50</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>d03bffd4cdbb16375542e553</t>
+          <t>9c8033c621be3a2064bb1efc</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -3376,48 +3386,51 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
-        <v>46253.57615740741</v>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="2" t="n"/>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>плохо уменя халык инвест не откырется</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Шукурилло Абдуллаев</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="n"/>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>9a1e407dd83600d41de4a4f1</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="A69" s="3" t="n">
+        <v>46253.83737268519</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>5</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Super</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Данияр Мусаев</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>cae9951351f128d20380f025</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46253.56730324074</v>
+        <v>46253.83456018518</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
@@ -3435,207 +3448,207 @@
       <c r="E70" s="2" t="n"/>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>не открываются доступ.блокируют на ровном месте.</t>
+          <t>бежать нужно с этого банка</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Лилия Серткая</t>
+          <t>виталий Шабалин</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>17b166bf83abe143eadce261</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>46253.82702546296</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Халык Алакан тоже сделайте, чтобы рукой можно было оплачивать</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Бауыржан Джаримбетов</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>49a460d74550e23b1f7545c8</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1e0e140cbee81ea399bf2644</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>46253.78255787037</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>отлично</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Гульмира Тащанова</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>372cdfcf76255e31517f6e0a</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46253.77180555555</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>пОлучать сообщения опополнении</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Живой Некромант</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>4c30970474e4542378188c99</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="1" t="n">
-        <v>46253.56347222222</v>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E71" s="2" t="n"/>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>пОлучать сообщения опополнении</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Живой Некромант</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>7.14.0</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>6bf82710f4d2bb9d737675b8</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46253.77092592593</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>постоянно вылетает. предлагает постоянно обновляться. ненадежное приложение, в дороге подведет 100%.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Али Исмаилов</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>9b6472222913528ab39424db</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>да</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="n">
-        <v>46253.56259259259</v>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="2" t="n"/>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>постоянно вылетает. предлагает постоянно обновляться. ненадежное приложение, в дороге подведет 100%.</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Али Исмаилов</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>7.15.2</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>9f2f384e2276d0b3d10a54f7</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="n">
-        <v>46253.56158564815</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>5</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>круто</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Эльбек Равшанбеков</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>7.15.2</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>b051e59cd8b157f39c2e4384</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="n">
-        <v>46253.55957175926</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>4</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>медленно работает</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Ренат Сапаров</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>7.15.2</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2e4b3b335fa83f743650e470</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46253.55112268519</v>
+        <v>46253.76991898148</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -3652,12 +3665,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>удобно, просто и доступно</t>
+          <t>круто</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Феруза Вагизова</t>
+          <t>Эльбек Равшанбеков</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3667,7 +3680,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>88955cff6ec34b9e14618d22</t>
+          <t>7ecde1d490bd0dfc3f3cb0f3</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3678,7 +3691,7 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46253.54431712963</v>
+        <v>46253.76790509259</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3691,128 +3704,124 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
+          <t>медленно работает</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Ренат Сапаров</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>c2404043e825d2060f4d5fd5</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>46253.75265046296</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>5</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>отлично</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Galim Alimbaev</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2eeb7fde5021868ee0939984</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="n">
-        <v>46253.51787037037</v>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>App Store</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>Ужасное приложение банка</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>Еле грузит, колл-центр типа с искусственными интеллектом который тупо молчит! Куда звонить!? Пишу в поддержку ответы тоже ии без решения проблемы. Вам до Каспи банка далеко!</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>Злая 1479(</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>7.15.0</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>14446617149</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>16b0ed98238aa2c416ad337f</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46253.73420138889</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>довольно часто не работает приложение</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Зарина Султанова</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>c20dea8a5bacede13b8afe33</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
         <is>
           <t>да</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="n">
-        <v>46253.48809027778</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>5</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>приложение нравиться</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Жанылдык Куандыкова</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>7.14.0</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>76ebeb3b52fa6d65470bce15</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46253.47815972222</v>
+        <v>46253.73025462963</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3829,12 +3838,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Удобное к использованию. Спасибо разработчикам!</t>
+          <t>просто супер</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Владимир Малобродский</t>
+          <t>Манарбек Сундетов</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3844,7 +3853,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>9d83be8eca2e8b573ad54496</t>
+          <t>ffb6dba62e8c0cd009c9c61f</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3855,7 +3864,7 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46253.47572916667</v>
+        <v>46253.72756944445</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3872,12 +3881,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>мықты банк😘😍🥰</t>
+          <t>очень очень приятно</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Алмира Каппасова</t>
+          <t>Асхат Ногайбаев</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3887,7 +3896,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>cde496c4de6df1d45db6e66d</t>
+          <t>a20f62e75c4af9a4c89e6d16</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3898,7 +3907,7 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46253.47311342593</v>
+        <v>46253.7196412037</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3915,22 +3924,22 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Супер хорошо</t>
+          <t>очень удобное и нужное приложение.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Нуралы Арыстанов</t>
+          <t>Adai</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>ee139e99f791411d77f2a9ce</t>
+          <t>104605b9b756332baf327e20</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3940,51 +3949,52 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n">
-        <v>46253.45833333334</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>4</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Приложение мне нравится спасибо я доволен.</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Владислав Мироненко</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>7.14.0</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>a6940b0e122f3fb5b10a9620</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="A82" s="1" t="n">
+        <v>46253.71857638889</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>как обновлять приложение? раз два в месяц просят обновить,а кнопки обновить нет. Приходится удалять и заново регистрироваться. в плэй маркет тоже написано либо открыть либо удалить приложение.</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Дана Нуралбаева</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>485dcc361736176a994fa708</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46253.43320601852</v>
+        <v>46253.70534722223</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -4001,17 +4011,22 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Отличное обслуживание!</t>
+          <t>күшті</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Марат Тутенбаева</t>
+          <t>Марат Газизович</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>212c27f2d06ff94438b31822</t>
+          <t>f3caae2f5188c908e275e625</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4022,7 +4037,7 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46253.42391203704</v>
+        <v>46253.70364583333</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -4039,12 +4054,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Супер</t>
+          <t>отличное приложение</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Лидия Запольская</t>
+          <t>Kaiyrzhan Makhanov</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4054,7 +4069,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>681f5ee0cddd7fbeffec2f67</t>
+          <t>f73004388c6bc0250cc98d77</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4065,7 +4080,7 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46253.42209490741</v>
+        <v>46253.70266203704</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -4082,12 +4097,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>мне нравится это приложение мне удобно им пользоваться всё понятно и доступно обслуживание очень культурное и уважительное спасибо вам!</t>
+          <t>просто после каждой покупки есть бонусы люблю этот банк</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Любовь Михайловна</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4097,7 +4112,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>b5214e8e4b5b537ccc662a4f</t>
+          <t>60fdf22787e9bc58fff13ee8</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4107,95 +4122,95 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n">
-        <v>46253.40755787037</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>5</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>для меня удобно х/банк когда работала зарплату получала, теперь пенсия получаю пользуясь ком.услаги оплачиваю.</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Гулжамал Есенгариева</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
+      <c r="A86" s="1" t="n">
+        <v>46253.69</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>мало функции , те которые есть не совсем просто использовать , можно сделать проще и доступнее . Очень мало интернет магазинов ...</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Dos Dosanov</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>2a10f4ba2e6bec1e8c856108</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>9c1a2ea1ebbae7ec6973f028</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
-        <v>46253.39053240741</v>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="2" t="n"/>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>Дорого...</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>Бекжан Анашбаев</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="A87" s="3" t="n">
+        <v>46253.66856481481</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>5</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>удобно</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Aisar Atabek</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>dee49c20714e3b8fc9b67d27</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>c5bc570e86452296eeb6d4f6</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46253.37592592592</v>
+        <v>46253.66216435185</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -4212,12 +4227,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>хорошо</t>
+          <t>спасибо</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Марат Жакупов</t>
+          <t>Гульфия Баянова</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4227,7 +4242,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>914b5d137fb7ea72d31bde28</t>
+          <t>fecedf3dff791736f089b6d2</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4237,51 +4252,52 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
-        <v>46253.36215277778</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>5</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Керемеи</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Салтанат Сулейменова</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
+      <c r="A89" s="1" t="n">
+        <v>46253.64832175926</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Ассалаумағалайкум! Өте жаман банк, маған рефинансирования бермеген және бонус, жеңілдік ешқашан жасамайсыздар, тек өз қалтасын ойлаған банк, ещё аты халық деп қойған, өзгертіңіздер.</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Ербулан Кабенов</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>626de18e1a86299500598b91</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>14953e8c80868af9144af552</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46253.3578125</v>
+        <v>46253.64436342593</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -4294,16 +4310,16 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Алла өзі қолдасын</t>
+          <t>иногда не могу найти историю платежа в приложении. например когда оплачиваешь проезд на автобус, когда выходишь не сможешь найти, а там реклама</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ali Kanatbai</t>
+          <t>Багила Берниязова</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4313,7 +4329,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>653bbcd21fcefcd62836fbca</t>
+          <t>dfba5d63bd0015f0f6d282f6</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -4324,11 +4340,11 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46252.29043981482</v>
+        <v>46253.64207175926</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>App Store</t>
+          <t>Google Play</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -4339,12 +4355,1306 @@
       <c r="D91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E91" s="2" t="n"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Ешқандай техподержка операторға хабарласақ тек обновит етіп қойдықтан басқасын аитпайды оператор сойлем аяқталмай телефонды өшіріп тастайды</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Сапармурат Абдуллаев</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>0ea255c3e4d314ea782118e0</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n">
+        <v>46253.63549768519</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>5</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Супер</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Nurgul Saduakasova</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>dd777fb21421f322c1754e84</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>46253.62903935185</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>5</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Super</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Данияр Мусаев</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>64dfc5192927ee9ff24e2692</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>46253.62622685185</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>бежать нужно с этого банка</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>виталий Шабалин</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>3afd299cae8695256dd5cc72</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>46253.61278935185</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>5</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>хорошо</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Smarysam</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>7.13.0</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>753ffb6cc20c0b9b5de215f8</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="n">
+        <v>46253.60559027778</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>5</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>все круто мне нравится удобно быстро</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Sania Sania</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>7.13.0</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>97a88caa8bec831663f6eed7</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n">
+        <v>46253.59975694444</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>5</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>удобно</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Galina Messerle</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1b46d6fd93e72ddea1708603</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>46253.58292824074</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="2" t="n"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>неге қайта қайта жаңарту сұрай береді оны істесем ашпайды ғой</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Нурсултан мусаев</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>5.34.50</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>d03bffd4cdbb16375542e553</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>46253.57615740741</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="2" t="n"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>плохо уменя халык инвест не откырется</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Шукурилло Абдуллаев</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="n"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>9a1e407dd83600d41de4a4f1</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>46253.56730324074</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="2" t="n"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>не открываются доступ.блокируют на ровном месте.</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Лилия Серткая</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>49a460d74550e23b1f7545c8</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>46253.56347222222</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E101" s="2" t="n"/>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>пОлучать сообщения опополнении</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Живой Некромант</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>6bf82710f4d2bb9d737675b8</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>46253.56259259259</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="2" t="n"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>постоянно вылетает. предлагает постоянно обновляться. ненадежное приложение, в дороге подведет 100%.</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Али Исмаилов</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>9f2f384e2276d0b3d10a54f7</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n">
+        <v>46253.56158564815</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>5</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>круто</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Эльбек Равшанбеков</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>b051e59cd8b157f39c2e4384</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="n">
+        <v>46253.55957175926</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>4</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>медленно работает</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Ренат Сапаров</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2e4b3b335fa83f743650e470</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n">
+        <v>46253.55112268519</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>5</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>удобно, просто и доступно</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Феруза Вагизова</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>88955cff6ec34b9e14618d22</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n">
+        <v>46253.54431712963</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>5</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>отлично</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Galim Alimbaev</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2eeb7fde5021868ee0939984</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>46253.51787037037</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>App Store</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Ужасное приложение банка</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Еле грузит, колл-центр типа с искусственными интеллектом который тупо молчит! Куда звонить!? Пишу в поддержку ответы тоже ии без решения проблемы. Вам до Каспи банка далеко!</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Злая 1479(</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>7.15.0</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>14446617149</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="n">
+        <v>46253.48809027778</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>5</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>приложение нравиться</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Жанылдык Куандыкова</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>76ebeb3b52fa6d65470bce15</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n">
+        <v>46253.47815972222</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>5</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Удобное к использованию. Спасибо разработчикам!</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Владимир Малобродский</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>9d83be8eca2e8b573ad54496</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="n">
+        <v>46253.47572916667</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>5</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>мықты банк😘😍🥰</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Алмира Каппасова</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>cde496c4de6df1d45db6e66d</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n">
+        <v>46253.47311342593</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>5</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Супер хорошо</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Нуралы Арыстанов</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>ee139e99f791411d77f2a9ce</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="n">
+        <v>46253.45833333334</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>4</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Приложение мне нравится спасибо я доволен.</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Владислав Мироненко</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>a6940b0e122f3fb5b10a9620</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n">
+        <v>46253.43320601852</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>5</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Отличное обслуживание!</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Марат Тутенбаева</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>212c27f2d06ff94438b31822</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="n">
+        <v>46253.42391203704</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>5</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Супер</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Лидия Запольская</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>681f5ee0cddd7fbeffec2f67</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n">
+        <v>46253.42209490741</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>5</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>мне нравится это приложение мне удобно им пользоваться всё понятно и доступно обслуживание очень культурное и уважительное спасибо вам!</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Любовь Михайловна</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>b5214e8e4b5b537ccc662a4f</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="n">
+        <v>46253.40755787037</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>5</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>для меня удобно х/банк когда работала зарплату получала, теперь пенсия получаю пользуясь ком.услаги оплачиваю.</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Гулжамал Есенгариева</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2a10f4ba2e6bec1e8c856108</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>46253.39053240741</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="2" t="n"/>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Дорого...</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Бекжан Анашбаев</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>dee49c20714e3b8fc9b67d27</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="n">
+        <v>46253.37592592592</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>5</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>хорошо</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Марат Жакупов</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>914b5d137fb7ea72d31bde28</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="n">
+        <v>46253.36215277778</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>5</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Керемеи</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Салтанат Сулейменова</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>626de18e1a86299500598b91</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="n">
+        <v>46253.3578125</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>5</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Алла өзі қолдасын</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Ali Kanatbai</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>653bbcd21fcefcd62836fbca</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46252.29043981482</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>App Store</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Вечные баги</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>1. Хотел добавить в страховку водителя, 3 дня парился добавил еле как.
 2. Коплю бонусы но почему то при оплате некоторых услуг не могу использовать, смешная система если честно.
@@ -4352,1417 +5662,1417 @@
 В общем решайте сами хотите себя мучать этим банком или нет.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>just_aidos</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr">
         <is>
           <t>14441741585</t>
         </is>
       </c>
-      <c r="J91" s="2" t="inlineStr">
+      <c r="J121" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="1" t="n">
+    <row r="122">
+      <c r="A122" s="1" t="n">
         <v>46251.58487268518</v>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="n">
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Жазылмай тұр вечно тормоз Халық банк</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Тормоз</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>Вечно тормоз халық банк</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr">
         <is>
           <t>14438910422</t>
         </is>
       </c>
-      <c r="J92" s="2" t="inlineStr">
+      <c r="J122" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="1" t="n">
+    <row r="123">
+      <c r="A123" s="1" t="n">
         <v>46250.45633101852</v>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="n">
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Дизайн приложения</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>UI/UX приложения немножко неудобный для такого популярного сервиса. Почему в разделе «Блокировки» выключенное состояние означает, что блокировка стоит? Нелогичный интерфейс.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>kamgamjamieee</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
+      <c r="I123" s="2" t="inlineStr">
         <is>
           <t>14434327048</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr">
+      <c r="J123" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="1" t="n">
+    <row r="124">
+      <c r="A124" s="1" t="n">
         <v>46249.21795138889</v>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="n">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Сұрағым бойынша</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Желіге тез қосылып сұрағыма жауап алдым🫶🏻</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>Жаази</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr">
         <is>
           <t>14429492941</t>
         </is>
       </c>
-      <c r="J94" s="2" t="inlineStr">
+      <c r="J124" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="3" t="n">
+    <row r="125">
+      <c r="A125" s="3" t="n">
         <v>46248.41894675926</v>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>5</v>
-      </c>
-      <c r="E95" t="inlineStr">
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>5</v>
+      </c>
+      <c r="E125" t="inlineStr">
         <is>
           <t>Отлично</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>От</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>Тттт07</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H125" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="I125" t="inlineStr">
         <is>
           <t>14426122877</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
         <v>46248.3246875</v>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="n">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Жалоба</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Это недоработанное приложение, на мой взгляд. Если разработчики что-то подсматривают у конкурентов и хотят реализовать, то пусть научатся делать это профессионально. Менеджеры банка недостаточно квалифицированы, опять-таки на мой взгляд, а об операторах колл-центра я лучше промолчу. Они все время что-то уточняют и звонок длится по полчаса. Жалобы рассматривают 15 р.б. , что говорит о многочисленных жалобах или супер ограниченном персонале обратной связи. Мне стыдно, что один из крупнейших банков Казахстана, ведет такую деятельность.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>Абылайбек</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr">
         <is>
           <t>14425781397</t>
         </is>
       </c>
-      <c r="J96" s="2" t="inlineStr">
+      <c r="J126" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="3" t="n">
+    <row r="127">
+      <c r="A127" s="3" t="n">
         <v>46248.28721064814</v>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>5</v>
-      </c>
-      <c r="E97" t="inlineStr">
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>5</v>
+      </c>
+      <c r="E127" t="inlineStr">
         <is>
           <t>Спасибо вам большое Халык банк</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>Самый лучший из лучших</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>Мама особенного и многодетного</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="I127" t="inlineStr">
         <is>
           <t>14425654331</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="n">
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="n">
         <v>46247.61267361111</v>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>5</v>
-      </c>
-      <c r="E98" t="inlineStr">
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>5</v>
+      </c>
+      <c r="E128" t="inlineStr">
         <is>
           <t>Кэшбек</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>Вечер добрый Халык банк. Сможете внедрить кэшбек за ком услуги (квартплата). Было бы отлично. Спасибо за ранее. Это в ваших силах.</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>Метис_79</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H128" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I128" t="inlineStr">
         <is>
           <t>14422975248</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="n">
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="n">
         <v>46246.42810185185</v>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>5</v>
-      </c>
-      <c r="E99" t="inlineStr">
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>5</v>
+      </c>
+      <c r="E129" t="inlineStr">
         <is>
           <t>Банк #1 в Казахстане</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>На данный момент лучший из лучших по всем параметрам! Конечно есть над чем работать, но пока Halyk ни разу не подводил!</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>Alex von Metz</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t>14418072605</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="n">
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="n">
         <v>46245.29766203704</v>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>5</v>
-      </c>
-      <c r="E100" t="inlineStr">
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>5</v>
+      </c>
+      <c r="E130" t="inlineStr">
         <is>
           <t>Халык!</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>Өте керемет!</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>Нурсат!</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="H130" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="I130" t="inlineStr">
         <is>
           <t>14413495571</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
         <v>46245.14422453703</v>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="n">
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Насильно на работе</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Добровольно/принудительно  на работе заставляют перейти в этот банк</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>Whisper spirit</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr">
+      <c r="I131" s="2" t="inlineStr">
         <is>
           <t>14412986159</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr">
+      <c r="J131" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="1" t="n">
+    <row r="132">
+      <c r="A132" s="1" t="n">
         <v>46242.868125</v>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="n">
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Ужас</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Ужасное обслуживание долго и много всего ужасссс</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>Ас!’ж</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr">
         <is>
           <t>14404184832</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr">
+      <c r="J132" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="3" t="n">
+    <row r="133">
+      <c r="A133" s="3" t="n">
         <v>46242.58256944444</v>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>5</v>
-      </c>
-      <c r="E103" t="inlineStr">
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>5</v>
+      </c>
+      <c r="E133" t="inlineStr">
         <is>
           <t>Comfortable App, BUT</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>Everything in your hand, but please add dark theme, sometimes white theme is so bright that hurts your eyes. Also, can you expand Halyk finance tools, like adding Kazakhstan governmental obligations like МЕКАМ/МЕУКАМ?</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>Nedkz</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I133" t="inlineStr">
         <is>
           <t>14402924703</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="n">
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="n">
         <v>46241.24402777778</v>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>5</v>
-      </c>
-      <c r="E104" t="inlineStr">
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>5</v>
+      </c>
+      <c r="E134" t="inlineStr">
         <is>
           <t>Керемет</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>Лучший банк</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>Жаке9094</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="H134" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I134" t="inlineStr">
         <is>
           <t>14397744425</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="n">
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="n">
         <v>46241.24172453704</v>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>5</v>
-      </c>
-      <c r="E105" t="inlineStr">
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>5</v>
+      </c>
+      <c r="E135" t="inlineStr">
         <is>
           <t>👍👍👍👍</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>Все классно</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>Чина 1991</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="H135" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="I135" t="inlineStr">
         <is>
           <t>14397736894</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
         <v>46240.56204861111</v>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="n">
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Так себе</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Зависает, неудобно</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>VK-apl</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr">
         <is>
           <t>14394977482</t>
         </is>
       </c>
-      <c r="J106" s="2" t="inlineStr">
+      <c r="J136" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="1" t="n">
+    <row r="137">
+      <c r="A137" s="1" t="n">
         <v>46240.51398148148</v>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="n">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Не вернули деньги</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Самый худший банк</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>Nike420-</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr">
         <is>
           <t>14394747340</t>
         </is>
       </c>
-      <c r="J107" s="2" t="inlineStr">
+      <c r="J137" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="1" t="n">
+    <row r="138">
+      <c r="A138" s="1" t="n">
         <v>46240.46083333333</v>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="n">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Приограма</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Многа тупит програм  увидомление нету каждый перевод камисся 200 тг 
 На ограничения 1000 тенге это все денги</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>Жаль но тупит много</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr">
         <is>
           <t>14394515666</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr">
+      <c r="J138" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="3" t="n">
+    <row r="139">
+      <c r="A139" s="3" t="n">
         <v>46240.36375</v>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>5</v>
-      </c>
-      <c r="E109" t="inlineStr">
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>5</v>
+      </c>
+      <c r="E139" t="inlineStr">
         <is>
           <t>Очень удобный</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>Очень удобный особенно когда ипотеку хочешь через предложение можешь смело падать</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t>Пожарный спасатель</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="H139" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="I139" t="inlineStr">
         <is>
           <t>14394154800</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="n">
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="n">
         <v>46240.20215277778</v>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
         <v>4</v>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E140" t="inlineStr">
         <is>
           <t>Добавьте возможность настройки размера шрифта</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>Слишком маленькие иконки и надписи. Вашим приложение пользуются взрослые люди и пенсионеры. Увеличьте шрифт или дайте возможность в настройках</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t>Altyn.0170</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="H140" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="I140" t="inlineStr">
         <is>
           <t>14393615835</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="n">
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="n">
         <v>46240.16615740741</v>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
         <v>4</v>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>Хорошее приложение</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>Нравится функционал и комиссии, но приложение зачастую не срабатывает при оплате QR в магазине или не заходит сразу</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t>Ruslan_Dv</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="H141" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="I141" t="inlineStr">
         <is>
           <t>14393494230</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="n">
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="n">
         <v>46240.12107638889</v>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>5</v>
-      </c>
-      <c r="E112" t="inlineStr">
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>5</v>
+      </c>
+      <c r="E142" t="inlineStr">
         <is>
           <t>Халық</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>Супер приложение</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="G142" t="inlineStr">
         <is>
           <t>Ukiltik</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="H142" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="I142" t="inlineStr">
         <is>
           <t>14393332099</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="n">
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="n">
         <v>46240.07537037037</v>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>5</v>
-      </c>
-      <c r="E113" t="inlineStr">
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>5</v>
+      </c>
+      <c r="E143" t="inlineStr">
         <is>
           <t>Маған рефенансирования жасауға одобрение шықса қатты қуанар едім!</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>Маған рефенансирование жасауға одобрение шықса қуанар едім!</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>Дұрыс жолға қойылған!</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="I143" t="inlineStr">
         <is>
           <t>14393158873</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
         <v>46239.76517361111</v>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="n">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Обновляйте сразу страницу, чтоб не приходилось каждый раз выходить из приложения и заходить обратно</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Почему после того как сделал перевод между своими счетами, не обновляется сразу страница, а приходится выходить с приложения и заходить обратно, закрыв его</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>Хочу обновку в прилодений</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr">
         <is>
           <t>14391948907</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr">
+      <c r="J144" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="1" t="n">
+    <row r="145">
+      <c r="A145" s="1" t="n">
         <v>46239.67016203704</v>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="n">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>.</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Ішіндегі ақшаларды жеп қоя береді, операторлар дұрыс айта алмайды, зп түскенде 5-10к болдмайды, қазірдің өзіңде 7к ақшамды базада тұр дейді, но менде жоқ</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>………7878</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr">
         <is>
           <t>14391503836</t>
         </is>
       </c>
-      <c r="J115" s="2" t="inlineStr">
+      <c r="J145" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="1" t="n">
+    <row r="146">
+      <c r="A146" s="1" t="n">
         <v>46239.52751157407</v>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="n">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Очень торомозит</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Очень плохо работает долго загружается показывает ошибку на ровном месте тормозит в день зарплаты вообще нет слов тормозы</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>Askar Maratulu</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr">
         <is>
           <t>14390778116</t>
         </is>
       </c>
-      <c r="J116" s="2" t="inlineStr">
+      <c r="J146" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="1" t="n">
+    <row r="147">
+      <c r="A147" s="1" t="n">
         <v>46239.44670138889</v>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="n">
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Dark theme, wheeen??</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Когда добавите темную тему?</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>001qr</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr">
         <is>
           <t>14390422067</t>
         </is>
       </c>
-      <c r="J117" s="2" t="inlineStr">
+      <c r="J147" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="1" t="n">
+    <row r="148">
+      <c r="A148" s="1" t="n">
         <v>46238.41152777777</v>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="n">
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Лаги, Баги</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Приложение работает ужасно. В строке поиск не чего не прописывается, только первая буква. В поддержку не пробиться везде боты. Пишу тут</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>Qwerty Still</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr">
         <is>
           <t>14386194340</t>
         </is>
       </c>
-      <c r="J118" s="2" t="inlineStr">
+      <c r="J148" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="1" t="n">
+    <row r="149">
+      <c r="A149" s="1" t="n">
         <v>46236.67026620371</v>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="n">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Карта Halyk Bonus</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>К работе приложения или самого банка, мобильного банкинга вопросов нет. 
 Негативный опыт вызывает политика банка к клиентам. 
 Приходит сообщение, что будет взиматься комиссия за выпуск карты Halyk bonus, спустя 2 года с момента выпуска самой карты в картомате. Как бы не жалко, но выпуск карты думаю должен быть бесплатным, а за её обслуживание комиссия взимается ежемесячно.</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>Просто Алл</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr">
         <is>
           <t>14379216532</t>
         </is>
       </c>
-      <c r="J119" s="2" t="inlineStr">
+      <c r="J149" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="3" t="n">
+    <row r="150">
+      <c r="A150" s="3" t="n">
         <v>46235.76702546296</v>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
         <v>4</v>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="E150" t="inlineStr">
         <is>
           <t>Тема</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F150" t="inlineStr">
         <is>
           <t>Добавьте темную тему</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="G150" t="inlineStr">
         <is>
           <t>Storm077</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="H150" t="inlineStr">
         <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="I150" t="inlineStr">
         <is>
           <t>14375681489</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
+      <c r="J150" t="inlineStr">
         <is>
           <t>нет</t>
         </is>

--- a/otzyvy_halyk.xlsx
+++ b/otzyvy_halyk.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J150"/>
+  <dimension ref="A1:J180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46255.20873842593</v>
+        <v>46256.21930555555</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -499,18 +499,22 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Мне почему то не одобряет кредит? Почему?</t>
+          <t>всё устраивает</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Назым Медетбекова</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Лидия Гончаренко</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5cf847481dbc9620da12c414</t>
+          <t>3b87fc88d9b83d6e73070456</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -520,52 +524,52 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>46255.2072800926</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>удобное приложение</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Rashida Gabitova</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>46256.21482638889</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>слишком долгая проверка при регистрации</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Egor</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>fa23f3fb60c751836c8f9c5a</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>bded4a6cf691bdeca5714128</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46255.20168981481</v>
+        <v>46256.17756944444</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -583,22 +587,22 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ең керемет банк</t>
+          <t>отлично</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Меирамкул Курманалиева</t>
+          <t>Аяулым</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7.13.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>97790e1e18a0850e97295caa</t>
+          <t>b30b0ebc6ddcdbdfb7922b26</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -609,7 +613,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46255.18505787037</v>
+        <v>46256.15180555556</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -627,18 +631,22 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>отлично</t>
+          <t>всё хорошо!!!!!</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Айбар Жантлеуов</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Николай</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9790d3324f980775058dee07</t>
+          <t>f980d7ce5826760b7805b77e</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -648,52 +656,52 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>46255.18493055556</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>👍👍👍</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Алмагуль Балтаева</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>7.14.0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>803e45eee322d30bebf059ed</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="A6" s="1" t="n">
+        <v>46255.84675925926</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Отвратительная работа маркета. Обратной связи 0. Извинений 0. Лояльности к клиентам 0. Пока сам не напишешь 10 раз ответов нет. Если по ошибке приложения приложения внёс меньше платёж по рассрочке (не хватало менее 1 тенге) НАКЛАДЫВАЮТ АРЕСТ НА СЧЁТ. Не рекомендую. раздел инвест криво работает. При просмотре акций списком открыв интересующую бумагу и при возвращении к списку приходится листать с самого начала. Когда нажимаешь кнопку назад возвращает на главный экран приложения. Итогневместился</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Владимир Трембак</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7c84fe10ea3f269147aa320e</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46255.17663194444</v>
+        <v>46255.70204861111</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -711,22 +719,22 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>мне нравится, единственная только,что не можем заказывать продукты в Магнум, смолл...через приложение, а так все на отлично</t>
+          <t>отличный банк</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Кульсара Куатбайкызы КульСара</t>
+          <t>Мунир Ахматзянов</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>c6fadabdb81d7d5302855f26</t>
+          <t>0f643a1c2337aa952e204a35</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -737,7 +745,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46255.16217592593</v>
+        <v>46255.60697916667</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -755,77 +763,77 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Всё отлично 👌</t>
+          <t>Быстрота и Качество</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Viktor Boiko</t>
+          <t>Татьяна Косовцова</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>14132f35ca6f1a542114aed0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46255.59869212963</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Проблемы с возвратом для клиентов, очень не удобно. Если клиент взял вчера, сегодня пришёл с возвратом, а на счёте нет денег за сегодня, возврат не доступен, клиент недоволен. Происходит недопонимание. Печально</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Светлана Скубакова</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>81d33296827e492996ecd6e0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>46254.8696875</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>удобно</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Алимаш Абишева</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>7.15.2</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>b08cf092cec14373fc514b8a</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>f8a7cec848983e5637ec730d</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46254.74541666666</v>
+        <v>46255.59763888889</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -838,27 +846,27 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>перевод на абонента каждый раз надо набирать, повторить не возможно</t>
+          <t>не удобный сервис, не user-friendly... кнопки должны быть так расположены, чтобы не приходилось по 10 раз нажимать</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Мурат Маткеримов</t>
+          <t>Natalya Goryushina</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91bd44e2d2d7e691e8d6cbff</t>
+          <t>6b8a1fbaa22ea124c1075d19</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -869,7 +877,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46254.74200231482</v>
+        <v>46255.59282407408</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -882,27 +890,27 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>отлично</t>
+          <t>Функция перевода денег на другой банк не удобно.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Галымбек Абжанов</t>
+          <t>Ероха Ероха</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2c562ffefb82d242c72d750a</t>
+          <t>58af67dd841ef8ba703ccabd</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -913,7 +921,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46254.72582175926</v>
+        <v>46255.57083333333</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -926,27 +934,27 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>все нужное в одном приложении</t>
+          <t>1. скорость. 2. почему нет бонусов</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Azamat Azamatov</t>
+          <t>Разия Алишева</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.10.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>aa7eb7c3883776ebed41a267</t>
+          <t>d5408a0044ac8c339cb5e111</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -957,7 +965,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46254.67237268519</v>
+        <v>46255.56806712963</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -975,12 +983,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Классное приложение</t>
+          <t>❤️❤️❤️</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Куаныш Адам</t>
+          <t>Полат</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -990,7 +998,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>a612b01c975adbcde2ac3f7b</t>
+          <t>800cde14c6a22c4b158a7220</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1000,52 +1008,52 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>46254.64497685185</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>пишет удалите приложение, загрузите с официального источника</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Maxim Balashov</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7.15.2</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1f95a099d22c142607b9f342</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="A14" s="3" t="n">
+        <v>46255.54769675926</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Приложение народного банка всегда мне очень нравится. Пользуюсь свыше 15 лет.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Rahnama Rahimova</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>435bd9dc7f9af2fd75a4a34a</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46254.61626157408</v>
+        <v>46255.5429050926</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1063,22 +1071,22 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>здравствуйте, банк очень хороший, на все вопросы можно получить быстрый и профессиональный ответ, операторы очень вежливые и грамотные, спасибо!!!</t>
+          <t>спасибо, хорошо!</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Андрей Макаров</t>
+          <t>Фаузия</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.13.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>a9d8e91c4657493dd304c4c4</t>
+          <t>e3d4e5bb24bdf44e56da5725</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1089,7 +1097,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46254.60901620371</v>
+        <v>46255.52001157407</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1107,22 +1115,22 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>спасибо</t>
+          <t>Рақмет</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Евгения Кизильбашева</t>
+          <t>Перизат Садырбаева</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>754322021db55b561edd5fba</t>
+          <t>99348d2e80e13da0049f6aa6</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1132,52 +1140,52 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46254.59369212963</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Интернет слабыи</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Елубаи Исабаев</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>7.13.0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>eb3dd17a5338aa923ae7b590</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="A17" s="1" t="n">
+        <v>46255.49870370371</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Приложение обновлено, но требует обновление. Бред полнейший</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Phil Pirelli</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>cf01bc7ce06b88624e04e748</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46254.5825462963</v>
+        <v>46255.48660879629</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1195,12 +1203,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Большое спасибо, всё нравиться, удачи вам в вашей работе!!!</t>
+          <t>всю жизнь ха́лык банком всё отлично</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Надежда</t>
+          <t>Юрий Нурсадыков</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1210,7 +1218,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>d89f143961b7c54d67186eb9</t>
+          <t>7801049a4cc7ba4ed2e25a39</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1220,52 +1228,52 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>46254.57494212963</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>5</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Народный банк самый лучший!</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Abai Hakimov</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="A19" s="1" t="n">
+        <v>46255.48552083333</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Оптимизируйте свое глючное приложение.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Zhandos Ashim</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5e89bf7d0445a6d4c56a03ca</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3710d7fb575516f59aac61b9</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46254.57232638889</v>
+        <v>46255.48532407408</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1283,12 +1291,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Приложение хорошее. Но нужно доработать многое и увеличить сферы услуг как на Камри банк. И вот программа очень долго думает при работе с клиентами. А в остальном все хорошо.</t>
+          <t>за минуту открыл карту . Но ребят. На главной сломалась локализация: вместо нормального текста отображаются ключи ресурсов — "searchTrigger.placeholder", "reesBlocks.forYou", "order.toBasket", "productTeaser.badges.original", "productTeaser.review.count" и т.д. Похоже, приложение не находит/не подгружает нужные переводы и показывает fallback в виде ключей. Проверьте i18n resources/bundle для текущей локали и соответствие ключей. И ещё вопрос: почему это вообще доходит до UI?</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Бейбут Мапитов</t>
+          <t>Spale</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1298,7 +1306,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2eb752646789d9b4757248c0</t>
+          <t>1153dfa1b52fa39f561b2f97</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1309,7 +1317,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46254.53262731482</v>
+        <v>46255.48186342593</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1327,22 +1335,22 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>все хорошо!!</t>
+          <t>Отлично</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Сауле</t>
+          <t>Валерий</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8db3d3391197733724486294</t>
+          <t>bf38366e53bd32ea0518c41c</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1352,52 +1360,52 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>46254.50099537037</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>5</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>отлично</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Бахытгуль Машауова</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>7.14.0</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>41ce544ddd314bb43102ad3c</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="A22" s="1" t="n">
+        <v>46255.47111111111</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>на складных устроистыах цифры не видны так себе теперь авторизоваться не могу звонил толку нет</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Isanayman Marat</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3341162ccafc084d2801611c</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46254.49489583333</v>
+        <v>46255.46608796297</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1415,22 +1423,22 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>хороший приложение</t>
+          <t>Отлично</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Жасылан Мустафин</t>
+          <t>Karim</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>05fd972f45b29f751ad0c7e2</t>
+          <t>c8af2c6e4b3183b62746849b</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1441,7 +1449,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46254.49033564814</v>
+        <v>46255.44545138889</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1459,77 +1467,77 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>благодарю за труд.</t>
+          <t>классный банк и удобный</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ринат Абдулин</t>
+          <t>Хасият Турдиева</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>7c72d823b887287ff296246e</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46255.42751157407</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Просто зависает постоянно, ничего невозможно сделать!</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>8da80f96b67bcea577ac6da1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>46254.47194444444</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>5</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>жақсы</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Куралай искен</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>7.14.0</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>57b87dd718575213574108a1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>cde533336ffbd9b98b80d9d6</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46254.46241898148</v>
+        <v>46255.39885416667</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1547,22 +1555,22 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Все устраивает. Halyk работает хорошо.</t>
+          <t>керемет жақсы банк сіздер</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Наталья Шеина</t>
+          <t>Камажай Екибасыва</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.13.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>16954a1d03ed6273ebdaff39</t>
+          <t>a406f378c4a7c676fe15d8e4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1573,7 +1581,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46254.45520833333</v>
+        <v>46255.39174768519</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1591,12 +1599,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Отлично</t>
+          <t>приложение удобное, хорошо работает</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Серик Толыбаев</t>
+          <t>Светлана Калашникова</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1606,7 +1614,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>857538ba251754a59756c996</t>
+          <t>9fbc50b1de643e284496e60b</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1616,52 +1624,52 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>46254.45472222222</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Из всех банковских приложений это самое убогое.Заходишь пишут обновить, заходишь в плей маркет ,обновления нет .Удаляешь ,заново скачиваю опять тоже самое.Вы разработчики издеваетесь 😡😡😡</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Alex Nord</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="n">
+        <v>46255.3869212963</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>хороший банк</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Айгуль Габдуллина</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>f0e15c297aaa467375c1f44d</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>013a3c4c5fcc851a6737db98</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46254.44621527778</v>
+        <v>46255.37782407407</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1679,12 +1687,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>все хорошо</t>
+          <t>Молодцы!</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Сауле Шуйкенова</t>
+          <t>Влад</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1694,7 +1702,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>34c8dbd8f4db6ced0bc667a6</t>
+          <t>769e88113c488d7223deb70e</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1704,96 +1712,96 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>46254.43652777778</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>почему удержали 1 тыс тенге</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Шалкар Казжанов</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="n">
+        <v>46255.36329861111</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>хорошо</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Асқат Бейбітбай</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20af977f4dcd64187b523736</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46255.35756944444</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Невозможно зайти в приложение.Приложение требует обновиться,но обновлений нет.Переустановка помогает не надолго.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Игорь Е.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>1aa4118e55ac6e7359b7dd74</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>3a4be50f2e8e07e1c09ce8a6</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>да</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>46254.43355324074</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>5</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>удобно</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Кайролла</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>7.13.0</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3a01546a2ff51ef0067d39e3</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46254.40388888889</v>
+        <v>46255.20873842593</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1810,22 +1818,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>все отлично работает рекомендую 🔥</t>
+          <t>Мне почему то не одобряет кредит? Почему?</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Самир Бабенов</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>7.14.0</t>
+          <t>Назым Медетбекова</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1d706399a1a41e9d88bace0a</t>
+          <t>5cf847481dbc9620da12c414</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1836,7 +1839,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46254.39303240741</v>
+        <v>46255.2072800926</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1853,12 +1856,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>самый лучший народ банк</t>
+          <t>удобное приложение</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Айгуль Ахбаева</t>
+          <t>Rashida Gabitova</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1868,7 +1871,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>902a4c325bd87cb378424e29</t>
+          <t>fa23f3fb60c751836c8f9c5a</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1879,7 +1882,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46254.38908564814</v>
+        <v>46255.20168981481</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1896,22 +1899,22 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Класс!</t>
+          <t>Ең керемет банк</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Laiosh Tolnai</t>
+          <t>Меирамкул Курманалиева</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.13.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>a2b1475d0a4636044e411f96</t>
+          <t>97790e1e18a0850e97295caa</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1922,7 +1925,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46254.37627314815</v>
+        <v>46255.18505787037</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1939,22 +1942,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>очень удобно оплачивать ком услуги ну и все остальное</t>
+          <t>отлично</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Анаргуль Есенгалиева</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>7.15.2</t>
+          <t>Айбар Жантлеуов</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0d69e28794204a7ebc123308</t>
+          <t>9790d3324f980775058dee07</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1965,7 +1963,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46254.37443287037</v>
+        <v>46255.18493055556</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1978,16 +1976,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>все хорошо. спасибо</t>
+          <t>👍👍👍</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Кайрат Маусымхан</t>
+          <t>Алмагуль Балтаева</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1997,7 +1995,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>7d68f1ac71d4d9fa0e6e7239</t>
+          <t>803e45eee322d30bebf059ed</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2008,7 +2006,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46254.36811342592</v>
+        <v>46255.17663194444</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2025,12 +2023,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Пока всё отлично! Просто, удобно.</t>
+          <t>мне нравится, единственная только,что не можем заказывать продукты в Магнум, смолл...через приложение, а так все на отлично</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Наталья Энзе</t>
+          <t>Кульсара Куатбайкызы КульСара</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2040,7 +2038,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ebfe0c1582b6e0efd21a9304</t>
+          <t>c6fadabdb81d7d5302855f26</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2051,7 +2049,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46254.29225694444</v>
+        <v>46255.16217592593</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2068,22 +2066,22 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>👍👍👍</t>
+          <t>Всё отлично 👌</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Serikkali Moldahmetov</t>
+          <t>Viktor Boiko</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8f08456f1f7037ddfc48fb40</t>
+          <t>81d33296827e492996ecd6e0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2094,7 +2092,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46254.26644675926</v>
+        <v>46254.8696875</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2111,76 +2109,77 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Спасибо!Быстро и качественно.</t>
+          <t>удобно</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Фарит Абдуллин</t>
+          <t>Алимаш Абишева</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>b08cf092cec14373fc514b8a</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46254.74541666666</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>перевод на абонента каждый раз надо набирать, повторить не возможно</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Мурат Маткеримов</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>4bc036aaba61bf9681d0c2f8</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="n">
-        <v>46254.23796296296</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>4</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Очень удобный сервис!!!</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Камшат Есентаева</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>7.14.0</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>6ce3a6058942a3a52ea23739</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>91bd44e2d2d7e691e8d6cbff</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46254.19555555555</v>
+        <v>46254.74200231482</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2197,22 +2196,22 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>все отлично работает рекомендую 🔥</t>
+          <t>отлично</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Самир Бабенов</t>
+          <t>Галымбек Абжанов</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>46c7507e70c1d2dcc78dcc77</t>
+          <t>2c562ffefb82d242c72d750a</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2223,7 +2222,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46254.18957175926</v>
+        <v>46254.72582175926</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2240,22 +2239,22 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Рахмет очень удобно пользоваться</t>
+          <t>все нужное в одном приложении</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Мария Кулёва</t>
+          <t>Azamat Azamatov</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.10.0</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>974572017a25b0123bd5f57c</t>
+          <t>aa7eb7c3883776ebed41a267</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2266,7 +2265,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46254.18469907407</v>
+        <v>46254.67237268519</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2283,12 +2282,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>самый лучший народ банк</t>
+          <t>Классное приложение</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Айгуль Ахбаева</t>
+          <t>Куаныш Адам</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2298,7 +2297,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2864ff427c1ec5b7a38a8ddc</t>
+          <t>a612b01c975adbcde2ac3f7b</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2308,51 +2307,52 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
-        <v>46254.18075231482</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>5</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Класс!</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Laiosh Tolnai</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
+      <c r="A44" s="1" t="n">
+        <v>46254.64497685185</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>пишет удалите приложение, загрузите с официального источника</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Maxim Balashov</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>fb0de02efe8d94f0fb464c70</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>1f95a099d22c142607b9f342</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46254.16793981481</v>
+        <v>46254.61626157408</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>очень удобно оплачивать ком услуги ну и все остальное</t>
+          <t>здравствуйте, банк очень хороший, на все вопросы можно получить быстрый и профессиональный ответ, операторы очень вежливые и грамотные, спасибо!!!</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Анаргуль Есенгалиева</t>
+          <t>Андрей Макаров</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>a4b2e3adb13ad921414a6635</t>
+          <t>a9d8e91c4657493dd304c4c4</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2395,7 +2395,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46254.16609953704</v>
+        <v>46254.60901620371</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2412,12 +2412,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>все хорошо. спасибо</t>
+          <t>спасибо</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Кайрат Маусымхан</t>
+          <t>Евгения Кизильбашева</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>b66e41f33b3bb3375f4102bf</t>
+          <t>754322021db55b561edd5fba</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2438,7 +2438,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46254.1597800926</v>
+        <v>46254.59369212963</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2455,22 +2455,22 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Пока всё отлично! Просто, удобно.</t>
+          <t>Интернет слабыи</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Наталья Энзе</t>
+          <t>Елубаи Исабаев</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.13.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>9d3a50aeb9a1be0e6401d30e</t>
+          <t>eb3dd17a5338aa923ae7b590</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2481,7 +2481,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46254.15381944444</v>
+        <v>46254.5825462963</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2498,12 +2498,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>хорошо спасибо</t>
+          <t>Большое спасибо, всё нравиться, удачи вам в вашей работе!!!</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Elmurat Bayanov</t>
+          <t>Надежда</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>abd0fd54964a3ac6c73eaf28</t>
+          <t>d89f143961b7c54d67186eb9</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2524,7 +2524,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46254.12082175926</v>
+        <v>46254.57494212963</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2541,12 +2541,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>люблю халык банк</t>
+          <t>Народный банк самый лучший!</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Береза График</t>
+          <t>Abai Hakimov</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6147099de51977f68610bbdc</t>
+          <t>5e89bf7d0445a6d4c56a03ca</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2567,7 +2567,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46254.10601851852</v>
+        <v>46254.57232638889</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2580,26 +2580,26 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>супер</t>
+          <t>Приложение хорошее. Но нужно доработать многое и увеличить сферы услуг как на Камри банк. И вот программа очень долго думает при работе с клиентами. А в остальном все хорошо.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Бахтыгуль Алдажарова</t>
+          <t>Бейбут Мапитов</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>af62592e2b234acc94cae3c7</t>
+          <t>2eb752646789d9b4757248c0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2610,7 +2610,7 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46254.08392361111</v>
+        <v>46254.53262731482</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>👍👍👍</t>
+          <t>все хорошо!!</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Serikkali Moldahmetov</t>
+          <t>Сауле</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>fa70e056db59bff38e51054d</t>
+          <t>8db3d3391197733724486294</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2653,7 +2653,7 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46254.05811342593</v>
+        <v>46254.50099537037</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Спасибо!Быстро и качественно.</t>
+          <t>отлично</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Фарит Абдуллин</t>
+          <t>Бахытгуль Машауова</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>4f573c9546e98bc36e801317</t>
+          <t>41ce544ddd314bb43102ad3c</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2696,7 +2696,7 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46254.0353587963</v>
+        <v>46254.49489583333</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2713,22 +2713,22 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Халык Алакан тоже сделайте, чтобы рукой можно было оплачивать</t>
+          <t>хороший приложение</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Бауыржан Джаримбетов</t>
+          <t>Жасылан Мустафин</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3bf98a3770b05e9be2c430cb</t>
+          <t>05fd972f45b29f751ad0c7e2</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2739,7 +2739,7 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46254.02962962963</v>
+        <v>46254.49033564814</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2752,26 +2752,26 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Очень удобный сервис!!!</t>
+          <t>благодарю за труд.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Камшат Есентаева</t>
+          <t>Ринат Абдулин</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3ac78723f6934b7b7064559a</t>
+          <t>8da80f96b67bcea577ac6da1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2782,7 +2782,7 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46253.99089120371</v>
+        <v>46254.47194444444</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2799,22 +2799,22 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>отлично</t>
+          <t>жақсы</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Гульмира Тащанова</t>
+          <t>Куралай искен</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>915995320029b26e5b7f6f0a</t>
+          <t>57b87dd718575213574108a1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -2825,7 +2825,7 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46253.98123842593</v>
+        <v>46254.46241898148</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2842,22 +2842,22 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Рахмет очень удобно пользоваться</t>
+          <t>Все устраивает. Halyk работает хорошо.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Мария Кулёва</t>
+          <t>Наталья Шеина</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>016e6615c024070673bf537b</t>
+          <t>16954a1d03ed6273ebdaff39</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -2868,7 +2868,7 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46253.94548611111</v>
+        <v>46254.45520833333</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>хорошо спасибо</t>
+          <t>Отлично</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Elmurat Bayanov</t>
+          <t>Серик Толыбаев</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>689bc9a55e1557b43da704d4</t>
+          <t>857538ba251754a59756c996</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2911,7 +2911,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46253.94253472222</v>
+        <v>46254.45472222222</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
@@ -2924,27 +2924,27 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" s="2" t="n"/>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>довольно часто не работает приложение</t>
+          <t>Из всех банковских приложений это самое убогое.Заходишь пишут обновить, заходишь в плей маркет ,обновления нет .Удаляешь ,заново скачиваю опять тоже самое.Вы разработчики издеваетесь 😡😡😡</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Зарина Султанова</t>
+          <t>Alex Nord</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>0ed11d36c4bb48b15370e5e2</t>
+          <t>f0e15c297aaa467375c1f44d</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -2955,7 +2955,7 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46253.93590277778</v>
+        <v>46254.44621527778</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2972,12 +2972,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>очень очень приятно</t>
+          <t>все хорошо</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Асхат Ногайбаев</t>
+          <t>Сауле Шуйкенова</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>a4b69efb01fca2c81b220ec9</t>
+          <t>34c8dbd8f4db6ced0bc667a6</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2997,51 +2997,52 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
-        <v>46253.92797453704</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>5</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>очень удобное и нужное приложение.</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Adai</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
+      <c r="A60" s="1" t="n">
+        <v>46254.43652777778</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>почему удержали 1 тыс тенге</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Шалкар Казжанов</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>c2834899d00d38c54b8deb58</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>1aa4118e55ac6e7359b7dd74</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46253.91368055555</v>
+        <v>46254.43355324074</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3058,22 +3059,22 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>күшті</t>
+          <t>удобно</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Марат Газизович</t>
+          <t>Кайролла</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.13.0</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>4451aeedc50f456c670fa41c</t>
+          <t>3a01546a2ff51ef0067d39e3</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3084,7 +3085,7 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46253.91248842593</v>
+        <v>46254.40388888889</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3101,22 +3102,22 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>люблю халык банк</t>
+          <t>все отлично работает рекомендую 🔥</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Береза График</t>
+          <t>Самир Бабенов</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>512494d0ed24072778dc9b83</t>
+          <t>1d706399a1a41e9d88bace0a</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3127,7 +3128,7 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46253.91197916667</v>
+        <v>46254.39303240741</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3144,12 +3145,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>отличное приложение</t>
+          <t>самый лучший народ банк</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Kaiyrzhan Makhanov</t>
+          <t>Айгуль Ахбаева</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3159,7 +3160,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>534dacc61d02bb38aa52d612</t>
+          <t>902a4c325bd87cb378424e29</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3169,52 +3170,51 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>46253.89833333333</v>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E64" s="2" t="n"/>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>мало функции , те которые есть не совсем просто использовать , можно сделать проще и доступнее . Очень мало интернет магазинов ...</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Dos Dosanov</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="A64" s="3" t="n">
+        <v>46254.38908564814</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Класс!</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Laiosh Tolnai</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
         <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>a4e57b2dff2e9988d2957d0d</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>a2b1475d0a4636044e411f96</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46253.89768518518</v>
+        <v>46254.37627314815</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3231,22 +3231,22 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>супер</t>
+          <t>очень удобно оплачивать ком услуги ну и все остальное</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Бахтыгуль Алдажарова</t>
+          <t>Анаргуль Есенгалиева</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>bfdd751eb68d7c3bf8b7b130</t>
+          <t>0d69e28794204a7ebc123308</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3257,7 +3257,7 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46253.87689814815</v>
+        <v>46254.37443287037</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3274,22 +3274,22 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>удобно</t>
+          <t>все хорошо. спасибо</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Aisar Atabek</t>
+          <t>Кайрат Маусымхан</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>c9e20cbacf740c765c59a66c</t>
+          <t>7d68f1ac71d4d9fa0e6e7239</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3300,7 +3300,7 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46253.85269675926</v>
+        <v>46254.36811342592</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3313,81 +3313,80 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>иногда не могу найти историю платежа в приложении. например когда оплачиваешь проезд на автобус, когда выходишь не сможешь найти, а там реклама</t>
+          <t>Пока всё отлично! Просто, удобно.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Багила Берниязова</t>
+          <t>Наталья Энзе</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>ebfe0c1582b6e0efd21a9304</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>46254.29225694444</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>5</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>👍👍👍</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Serikkali Moldahmetov</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>27532977d33acaf460206cc3</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>46253.85040509259</v>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="2" t="n"/>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Ешқандай техподержка операторға хабарласақ тек обновит етіп қойдықтан басқасын аитпайды оператор сойлем аяқталмай телефонды өшіріп тастайды</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Сапармурат Абдуллаев</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>7.15.2</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>9c8033c621be3a2064bb1efc</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>8f08456f1f7037ddfc48fb40</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46253.83737268519</v>
+        <v>46254.26644675926</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3404,12 +3403,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Super</t>
+          <t>Спасибо!Быстро и качественно.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Данияр Мусаев</t>
+          <t>Фарит Абдуллин</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3419,7 +3418,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>cae9951351f128d20380f025</t>
+          <t>4bc036aaba61bf9681d0c2f8</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3429,52 +3428,51 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
-        <v>46253.83456018518</v>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="2" t="n"/>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>бежать нужно с этого банка</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>виталий Шабалин</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="A70" s="3" t="n">
+        <v>46254.23796296296</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>4</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Очень удобный сервис!!!</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Камшат Есентаева</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
         <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>17b166bf83abe143eadce261</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>6ce3a6058942a3a52ea23739</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46253.82702546296</v>
+        <v>46254.19555555555</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -3491,22 +3489,22 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Халык Алакан тоже сделайте, чтобы рукой можно было оплачивать</t>
+          <t>все отлично работает рекомендую 🔥</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Бауыржан Джаримбетов</t>
+          <t>Самир Бабенов</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1e0e140cbee81ea399bf2644</t>
+          <t>46c7507e70c1d2dcc78dcc77</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3517,7 +3515,7 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46253.78255787037</v>
+        <v>46254.18957175926</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3534,121 +3532,119 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>отлично</t>
+          <t>Рахмет очень удобно пользоваться</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Гульмира Тащанова</t>
+          <t>Мария Кулёва</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>974572017a25b0123bd5f57c</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>46254.18469907407</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>5</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>самый лучший народ банк</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Айгуль Ахбаева</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>372cdfcf76255e31517f6e0a</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="n">
-        <v>46253.77180555555</v>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E73" s="2" t="n"/>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>пОлучать сообщения опополнении</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Живой Некромант</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>7.14.0</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>4c30970474e4542378188c99</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2864ff427c1ec5b7a38a8ddc</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
-        <v>46253.77092592593</v>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" s="2" t="n"/>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>постоянно вылетает. предлагает постоянно обновляться. ненадежное приложение, в дороге подведет 100%.</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>Али Исмаилов</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="A74" s="3" t="n">
+        <v>46254.18075231482</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>5</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Класс!</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Laiosh Tolnai</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
         <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>9b6472222913528ab39424db</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>fb0de02efe8d94f0fb464c70</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46253.76991898148</v>
+        <v>46254.16793981481</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -3665,12 +3661,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>круто</t>
+          <t>очень удобно оплачивать ком услуги ну и все остальное</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Эльбек Равшанбеков</t>
+          <t>Анаргуль Есенгалиева</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3680,7 +3676,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>7ecde1d490bd0dfc3f3cb0f3</t>
+          <t>a4b2e3adb13ad921414a6635</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3691,7 +3687,7 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46253.76790509259</v>
+        <v>46254.16609953704</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3704,26 +3700,26 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>медленно работает</t>
+          <t>все хорошо. спасибо</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ренат Сапаров</t>
+          <t>Кайрат Маусымхан</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>c2404043e825d2060f4d5fd5</t>
+          <t>b66e41f33b3bb3375f4102bf</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3734,7 +3730,7 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46253.75265046296</v>
+        <v>46254.1597800926</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3751,12 +3747,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>отлично</t>
+          <t>Пока всё отлично! Просто, удобно.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Galim Alimbaev</t>
+          <t>Наталья Энзе</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3766,7 +3762,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>16b0ed98238aa2c416ad337f</t>
+          <t>9d3a50aeb9a1be0e6401d30e</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3776,52 +3772,51 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
-        <v>46253.73420138889</v>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E78" s="2" t="n"/>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>довольно часто не работает приложение</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Зарина Султанова</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>7.14.0</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>c20dea8a5bacede13b8afe33</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="A78" s="3" t="n">
+        <v>46254.15381944444</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>5</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>хорошо спасибо</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Elmurat Bayanov</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>abd0fd54964a3ac6c73eaf28</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46253.73025462963</v>
+        <v>46254.12082175926</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3838,12 +3833,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>просто супер</t>
+          <t>люблю халык банк</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Манарбек Сундетов</t>
+          <t>Береза График</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3853,7 +3848,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>ffb6dba62e8c0cd009c9c61f</t>
+          <t>6147099de51977f68610bbdc</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3864,7 +3859,7 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46253.72756944445</v>
+        <v>46254.10601851852</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3881,12 +3876,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>очень очень приятно</t>
+          <t>супер</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Асхат Ногайбаев</t>
+          <t>Бахтыгуль Алдажарова</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3896,7 +3891,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>a20f62e75c4af9a4c89e6d16</t>
+          <t>af62592e2b234acc94cae3c7</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3907,7 +3902,7 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46253.7196412037</v>
+        <v>46254.08392361111</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3924,22 +3919,22 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>очень удобное и нужное приложение.</t>
+          <t>👍👍👍</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Adai</t>
+          <t>Serikkali Moldahmetov</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>104605b9b756332baf327e20</t>
+          <t>fa70e056db59bff38e51054d</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3949,52 +3944,51 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
-        <v>46253.71857638889</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" s="2" t="n"/>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>как обновлять приложение? раз два в месяц просят обновить,а кнопки обновить нет. Приходится удалять и заново регистрироваться. в плэй маркет тоже написано либо открыть либо удалить приложение.</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>Дана Нуралбаева</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>7.15.2</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>485dcc361736176a994fa708</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="A82" s="3" t="n">
+        <v>46254.05811342593</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>5</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Спасибо!Быстро и качественно.</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Фарит Абдуллин</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>4f573c9546e98bc36e801317</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46253.70534722223</v>
+        <v>46254.0353587963</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -4011,22 +4005,22 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>күшті</t>
+          <t>Халык Алакан тоже сделайте, чтобы рукой можно было оплачивать</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Марат Газизович</t>
+          <t>Бауыржан Джаримбетов</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>f3caae2f5188c908e275e625</t>
+          <t>3bf98a3770b05e9be2c430cb</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4037,7 +4031,7 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46253.70364583333</v>
+        <v>46254.02962962963</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -4050,26 +4044,26 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>отличное приложение</t>
+          <t>Очень удобный сервис!!!</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Kaiyrzhan Makhanov</t>
+          <t>Камшат Есентаева</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>f73004388c6bc0250cc98d77</t>
+          <t>3ac78723f6934b7b7064559a</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4080,7 +4074,7 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46253.70266203704</v>
+        <v>46253.99089120371</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -4097,77 +4091,76 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>просто после каждой покупки есть бонусы люблю этот банк</t>
+          <t>отлично</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Milka</t>
+          <t>Гульмира Тащанова</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>915995320029b26e5b7f6f0a</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="n">
+        <v>46253.98123842593</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>5</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Рахмет очень удобно пользоваться</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Мария Кулёва</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>60fdf22787e9bc58fff13ee8</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="n">
-        <v>46253.69</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E86" s="2" t="n"/>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>мало функции , те которые есть не совсем просто использовать , можно сделать проще и доступнее . Очень мало интернет магазинов ...</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>Dos Dosanov</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>7.15.2</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>9c1a2ea1ebbae7ec6973f028</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>016e6615c024070673bf537b</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46253.66856481481</v>
+        <v>46253.94548611111</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -4184,12 +4177,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>удобно</t>
+          <t>хорошо спасибо</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Aisar Atabek</t>
+          <t>Elmurat Bayanov</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4199,7 +4192,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>c5bc570e86452296eeb6d4f6</t>
+          <t>689bc9a55e1557b43da704d4</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4209,95 +4202,95 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n">
-        <v>46253.66216435185</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>5</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>спасибо</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Гульфия Баянова</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
+      <c r="A88" s="1" t="n">
+        <v>46253.94253472222</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>довольно часто не работает приложение</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Зарина Султанова</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>fecedf3dff791736f089b6d2</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>0ed11d36c4bb48b15370e5e2</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
-        <v>46253.64832175926</v>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="2" t="n"/>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>Ассалаумағалайкум! Өте жаман банк, маған рефинансирования бермеген және бонус, жеңілдік ешқашан жасамайсыздар, тек өз қалтасын ойлаған банк, ещё аты халық деп қойған, өзгертіңіздер.</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>Ербулан Кабенов</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="A89" s="3" t="n">
+        <v>46253.93590277778</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>очень очень приятно</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Асхат Ногайбаев</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
         <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>14953e8c80868af9144af552</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>a4b69efb01fca2c81b220ec9</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46253.64436342593</v>
+        <v>46253.92797453704</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -4310,81 +4303,80 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>иногда не могу найти историю платежа в приложении. например когда оплачиваешь проезд на автобус, когда выходишь не сможешь найти, а там реклама</t>
+          <t>очень удобное и нужное приложение.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Багила Берниязова</t>
+          <t>Adai</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>c2834899d00d38c54b8deb58</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>46253.91368055555</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>5</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>күшті</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Марат Газизович</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>dfba5d63bd0015f0f6d282f6</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>46253.64207175926</v>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" s="2" t="n"/>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>Ешқандай техподержка операторға хабарласақ тек обновит етіп қойдықтан басқасын аитпайды оператор сойлем аяқталмай телефонды өшіріп тастайды</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Сапармурат Абдуллаев</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>7.15.2</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>0ea255c3e4d314ea782118e0</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>4451aeedc50f456c670fa41c</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46253.63549768519</v>
+        <v>46253.91248842593</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -4401,22 +4393,22 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Супер</t>
+          <t>люблю халык банк</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nurgul Saduakasova</t>
+          <t>Береза График</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>dd777fb21421f322c1754e84</t>
+          <t>512494d0ed24072778dc9b83</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -4427,7 +4419,7 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46253.62903935185</v>
+        <v>46253.91197916667</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -4444,22 +4436,22 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Super</t>
+          <t>отличное приложение</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Данияр Мусаев</t>
+          <t>Kaiyrzhan Makhanov</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>64dfc5192927ee9ff24e2692</t>
+          <t>534dacc61d02bb38aa52d612</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4470,7 +4462,7 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46253.62622685185</v>
+        <v>46253.89833333333</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
@@ -4483,27 +4475,27 @@
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" s="2" t="n"/>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>бежать нужно с этого банка</t>
+          <t>мало функции , те которые есть не совсем просто использовать , можно сделать проще и доступнее . Очень мало интернет магазинов ...</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>виталий Шабалин</t>
+          <t>Dos Dosanov</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>3afd299cae8695256dd5cc72</t>
+          <t>a4e57b2dff2e9988d2957d0d</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -4514,7 +4506,7 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46253.61278935185</v>
+        <v>46253.89768518518</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -4531,22 +4523,22 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>хорошо</t>
+          <t>супер</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Smarysam</t>
+          <t>Бахтыгуль Алдажарова</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>7.13.0</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>753ffb6cc20c0b9b5de215f8</t>
+          <t>bfdd751eb68d7c3bf8b7b130</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -4557,7 +4549,7 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46253.60559027778</v>
+        <v>46253.87689814815</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -4574,22 +4566,22 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>все круто мне нравится удобно быстро</t>
+          <t>удобно</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sania Sania</t>
+          <t>Aisar Atabek</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>7.13.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>97a88caa8bec831663f6eed7</t>
+          <t>c9e20cbacf740c765c59a66c</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -4600,7 +4592,7 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46253.59975694444</v>
+        <v>46253.85269675926</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -4613,26 +4605,26 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>удобно</t>
+          <t>иногда не могу найти историю платежа в приложении. например когда оплачиваешь проезд на автобус, когда выходишь не сможешь найти, а там реклама</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Galina Messerle</t>
+          <t>Багила Берниязова</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>7.15.2</t>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1b46d6fd93e72ddea1708603</t>
+          <t>27532977d33acaf460206cc3</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -4643,7 +4635,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46253.58292824074</v>
+        <v>46253.85040509259</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
@@ -4661,22 +4653,22 @@
       <c r="E98" s="2" t="n"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>неге қайта қайта жаңарту сұрай береді оны істесем ашпайды ғой</t>
+          <t>Ешқандай техподержка операторға хабарласақ тек обновит етіп қойдықтан басқасын аитпайды оператор сойлем аяқталмай телефонды өшіріп тастайды</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Нурсултан мусаев</t>
+          <t>Сапармурат Абдуллаев</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>5.34.50</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>d03bffd4cdbb16375542e553</t>
+          <t>9c8033c621be3a2064bb1efc</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -4686,48 +4678,51 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
-        <v>46253.57615740741</v>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" s="2" t="n"/>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>плохо уменя халык инвест не откырется</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>Шукурилло Абдуллаев</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="n"/>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>9a1e407dd83600d41de4a4f1</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="A99" s="3" t="n">
+        <v>46253.83737268519</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>5</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Super</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Данияр Мусаев</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>cae9951351f128d20380f025</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46253.56730324074</v>
+        <v>46253.83456018518</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
@@ -4745,207 +4740,207 @@
       <c r="E100" s="2" t="n"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>не открываются доступ.блокируют на ровном месте.</t>
+          <t>бежать нужно с этого банка</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Лилия Серткая</t>
+          <t>виталий Шабалин</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>17b166bf83abe143eadce261</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>46253.82702546296</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>5</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Халык Алакан тоже сделайте, чтобы рукой можно было оплачивать</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Бауыржан Джаримбетов</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>49a460d74550e23b1f7545c8</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1e0e140cbee81ea399bf2644</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="n">
+        <v>46253.78255787037</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>5</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>отлично</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Гульмира Тащанова</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>372cdfcf76255e31517f6e0a</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46253.77180555555</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E103" s="2" t="n"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>пОлучать сообщения опополнении</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Живой Некромант</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>4c30970474e4542378188c99</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="1" t="n">
-        <v>46253.56347222222</v>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E101" s="2" t="n"/>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>пОлучать сообщения опополнении</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>Живой Некромант</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>7.14.0</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>6bf82710f4d2bb9d737675b8</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>46253.77092592593</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="2" t="n"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>постоянно вылетает. предлагает постоянно обновляться. ненадежное приложение, в дороге подведет 100%.</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Али Исмаилов</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>9b6472222913528ab39424db</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
         <is>
           <t>да</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="1" t="n">
-        <v>46253.56259259259</v>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" s="2" t="n"/>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>постоянно вылетает. предлагает постоянно обновляться. ненадежное приложение, в дороге подведет 100%.</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Али Исмаилов</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>7.15.2</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>9f2f384e2276d0b3d10a54f7</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="n">
-        <v>46253.56158564815</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>5</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>круто</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Эльбек Равшанбеков</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>7.15.2</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>b051e59cd8b157f39c2e4384</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="n">
-        <v>46253.55957175926</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>4</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>медленно работает</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Ренат Сапаров</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>7.15.2</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>2e4b3b335fa83f743650e470</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46253.55112268519</v>
+        <v>46253.76991898148</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -4962,12 +4957,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>удобно, просто и доступно</t>
+          <t>круто</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Феруза Вагизова</t>
+          <t>Эльбек Равшанбеков</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4977,7 +4972,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>88955cff6ec34b9e14618d22</t>
+          <t>7ecde1d490bd0dfc3f3cb0f3</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -4988,7 +4983,7 @@
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46253.54431712963</v>
+        <v>46253.76790509259</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -5001,128 +4996,124 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
+          <t>медленно работает</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Ренат Сапаров</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>c2404043e825d2060f4d5fd5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
+        <v>46253.75265046296</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>5</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t>отлично</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>Galim Alimbaev</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>2eeb7fde5021868ee0939984</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="1" t="n">
-        <v>46253.51787037037</v>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>App Store</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>Ужасное приложение банка</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>Еле грузит, колл-центр типа с искусственными интеллектом который тупо молчит! Куда звонить!? Пишу в поддержку ответы тоже ии без решения проблемы. Вам до Каспи банка далеко!</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>Злая 1479(</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>7.15.0</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>14446617149</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>16b0ed98238aa2c416ad337f</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>46253.73420138889</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E108" s="2" t="n"/>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>довольно часто не работает приложение</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Зарина Султанова</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>c20dea8a5bacede13b8afe33</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
         <is>
           <t>да</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="n">
-        <v>46253.48809027778</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>5</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>приложение нравиться</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Жанылдык Куандыкова</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>7.14.0</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>76ebeb3b52fa6d65470bce15</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46253.47815972222</v>
+        <v>46253.73025462963</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -5139,12 +5130,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Удобное к использованию. Спасибо разработчикам!</t>
+          <t>просто супер</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Владимир Малобродский</t>
+          <t>Манарбек Сундетов</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5154,7 +5145,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>9d83be8eca2e8b573ad54496</t>
+          <t>ffb6dba62e8c0cd009c9c61f</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -5165,7 +5156,7 @@
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46253.47572916667</v>
+        <v>46253.72756944445</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -5182,12 +5173,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>мықты банк😘😍🥰</t>
+          <t>очень очень приятно</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Алмира Каппасова</t>
+          <t>Асхат Ногайбаев</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5197,7 +5188,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>cde496c4de6df1d45db6e66d</t>
+          <t>a20f62e75c4af9a4c89e6d16</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -5208,7 +5199,7 @@
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46253.47311342593</v>
+        <v>46253.7196412037</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -5225,22 +5216,22 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Супер хорошо</t>
+          <t>очень удобное и нужное приложение.</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Нуралы Арыстанов</t>
+          <t>Adai</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>7.14.0</t>
+          <t>7.15.2</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>ee139e99f791411d77f2a9ce</t>
+          <t>104605b9b756332baf327e20</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -5250,51 +5241,52 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="n">
-        <v>46253.45833333334</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>4</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Приложение мне нравится спасибо я доволен.</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Владислав Мироненко</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>7.14.0</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>a6940b0e122f3fb5b10a9620</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="A112" s="1" t="n">
+        <v>46253.71857638889</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="2" t="n"/>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>как обновлять приложение? раз два в месяц просят обновить,а кнопки обновить нет. Приходится удалять и заново регистрироваться. в плэй маркет тоже написано либо открыть либо удалить приложение.</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Дана Нуралбаева</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>485dcc361736176a994fa708</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46253.43320601852</v>
+        <v>46253.70534722223</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -5311,17 +5303,22 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Отличное обслуживание!</t>
+          <t>күшті</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Марат Тутенбаева</t>
+          <t>Марат Газизович</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>212c27f2d06ff94438b31822</t>
+          <t>f3caae2f5188c908e275e625</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -5332,7 +5329,7 @@
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46253.42391203704</v>
+        <v>46253.70364583333</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -5349,12 +5346,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Супер</t>
+          <t>отличное приложение</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Лидия Запольская</t>
+          <t>Kaiyrzhan Makhanov</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5364,7 +5361,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>681f5ee0cddd7fbeffec2f67</t>
+          <t>f73004388c6bc0250cc98d77</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -5375,7 +5372,7 @@
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46253.42209490741</v>
+        <v>46253.70266203704</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -5392,12 +5389,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>мне нравится это приложение мне удобно им пользоваться всё понятно и доступно обслуживание очень культурное и уважительное спасибо вам!</t>
+          <t>просто после каждой покупки есть бонусы люблю этот банк</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Любовь Михайловна</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5407,7 +5404,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>b5214e8e4b5b537ccc662a4f</t>
+          <t>60fdf22787e9bc58fff13ee8</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -5417,95 +5414,95 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="n">
-        <v>46253.40755787037</v>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>5</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>для меня удобно х/банк когда работала зарплату получала, теперь пенсия получаю пользуясь ком.услаги оплачиваю.</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Гулжамал Есенгариева</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
+      <c r="A116" s="1" t="n">
+        <v>46253.69</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E116" s="2" t="n"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>мало функции , те которые есть не совсем просто использовать , можно сделать проще и доступнее . Очень мало интернет магазинов ...</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Dos Dosanov</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>2a10f4ba2e6bec1e8c856108</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>9c1a2ea1ebbae7ec6973f028</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
-        <v>46253.39053240741</v>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E117" s="2" t="n"/>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>Дорого...</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>Бекжан Анашбаев</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="A117" s="3" t="n">
+        <v>46253.66856481481</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>5</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>удобно</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Aisar Atabek</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
         <is>
           <t>7.15.2</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>dee49c20714e3b8fc9b67d27</t>
-        </is>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>c5bc570e86452296eeb6d4f6</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46253.37592592592</v>
+        <v>46253.66216435185</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -5522,12 +5519,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>хорошо</t>
+          <t>спасибо</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Марат Жакупов</t>
+          <t>Гульфия Баянова</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5537,7 +5534,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>914b5d137fb7ea72d31bde28</t>
+          <t>fecedf3dff791736f089b6d2</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -5547,51 +5544,52 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="n">
-        <v>46253.36215277778</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Google Play</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>5</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Керемеи</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Салтанат Сулейменова</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
+      <c r="A119" s="1" t="n">
+        <v>46253.64832175926</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="2" t="n"/>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Ассалаумағалайкум! Өте жаман банк, маған рефинансирования бермеген және бонус, жеңілдік ешқашан жасамайсыздар, тек өз қалтасын ойлаған банк, ещё аты халық деп қойған, өзгертіңіздер.</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Ербулан Кабенов</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>626de18e1a86299500598b91</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>14953e8c80868af9144af552</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46253.3578125</v>
+        <v>46253.64436342593</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -5604,16 +5602,16 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Алла өзі қолдасын</t>
+          <t>иногда не могу найти историю платежа в приложении. например когда оплачиваешь проезд на автобус, когда выходишь не сможешь найти, а там реклама</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ali Kanatbai</t>
+          <t>Багила Берниязова</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5623,7 +5621,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>653bbcd21fcefcd62836fbca</t>
+          <t>dfba5d63bd0015f0f6d282f6</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -5634,11 +5632,11 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46252.29043981482</v>
+        <v>46253.64207175926</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>App Store</t>
+          <t>Google Play</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -5649,12 +5647,1306 @@
       <c r="D121" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E121" s="2" t="n"/>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Ешқандай техподержка операторға хабарласақ тек обновит етіп қойдықтан басқасын аитпайды оператор сойлем аяқталмай телефонды өшіріп тастайды</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Сапармурат Абдуллаев</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>0ea255c3e4d314ea782118e0</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="n">
+        <v>46253.63549768519</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>5</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Супер</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Nurgul Saduakasova</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>dd777fb21421f322c1754e84</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="n">
+        <v>46253.62903935185</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>5</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Super</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Данияр Мусаев</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>64dfc5192927ee9ff24e2692</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46253.62622685185</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="2" t="n"/>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>бежать нужно с этого банка</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>виталий Шабалин</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>3afd299cae8695256dd5cc72</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="n">
+        <v>46253.61278935185</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>5</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>хорошо</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Smarysam</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>7.13.0</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>753ffb6cc20c0b9b5de215f8</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="n">
+        <v>46253.60559027778</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>5</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>все круто мне нравится удобно быстро</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Sania Sania</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>7.13.0</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>97a88caa8bec831663f6eed7</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="n">
+        <v>46253.59975694444</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>5</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>удобно</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Galina Messerle</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1b46d6fd93e72ddea1708603</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>46253.58292824074</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="2" t="n"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>неге қайта қайта жаңарту сұрай береді оны істесем ашпайды ғой</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Нурсултан мусаев</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>5.34.50</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>d03bffd4cdbb16375542e553</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>46253.57615740741</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" s="2" t="n"/>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>плохо уменя халык инвест не откырется</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Шукурилло Абдуллаев</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="n"/>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>9a1e407dd83600d41de4a4f1</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>46253.56730324074</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="2" t="n"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>не открываются доступ.блокируют на ровном месте.</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Лилия Серткая</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>49a460d74550e23b1f7545c8</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>46253.56347222222</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E131" s="2" t="n"/>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>пОлучать сообщения опополнении</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Живой Некромант</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>6bf82710f4d2bb9d737675b8</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>46253.56259259259</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" s="2" t="n"/>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>постоянно вылетает. предлагает постоянно обновляться. ненадежное приложение, в дороге подведет 100%.</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Али Исмаилов</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>9f2f384e2276d0b3d10a54f7</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="n">
+        <v>46253.56158564815</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>5</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>круто</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Эльбек Равшанбеков</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>b051e59cd8b157f39c2e4384</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="n">
+        <v>46253.55957175926</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>4</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>медленно работает</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Ренат Сапаров</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2e4b3b335fa83f743650e470</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="n">
+        <v>46253.55112268519</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>5</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>удобно, просто и доступно</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Феруза Вагизова</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>88955cff6ec34b9e14618d22</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="n">
+        <v>46253.54431712963</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>5</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>отлично</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Galim Alimbaev</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2eeb7fde5021868ee0939984</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>46253.51787037037</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>App Store</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Ужасное приложение банка</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Еле грузит, колл-центр типа с искусственными интеллектом который тупо молчит! Куда звонить!? Пишу в поддержку ответы тоже ии без решения проблемы. Вам до Каспи банка далеко!</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Злая 1479(</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>7.15.0</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>14446617149</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="n">
+        <v>46253.48809027778</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>5</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>приложение нравиться</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Жанылдык Куандыкова</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>76ebeb3b52fa6d65470bce15</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="n">
+        <v>46253.47815972222</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>5</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Удобное к использованию. Спасибо разработчикам!</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Владимир Малобродский</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>9d83be8eca2e8b573ad54496</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="n">
+        <v>46253.47572916667</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>5</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>мықты банк😘😍🥰</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Алмира Каппасова</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>cde496c4de6df1d45db6e66d</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="n">
+        <v>46253.47311342593</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>5</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Супер хорошо</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Нуралы Арыстанов</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>ee139e99f791411d77f2a9ce</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="n">
+        <v>46253.45833333334</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>4</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Приложение мне нравится спасибо я доволен.</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Владислав Мироненко</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>a6940b0e122f3fb5b10a9620</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="n">
+        <v>46253.43320601852</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>5</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Отличное обслуживание!</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Марат Тутенбаева</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>212c27f2d06ff94438b31822</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="n">
+        <v>46253.42391203704</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>5</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Супер</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Лидия Запольская</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>681f5ee0cddd7fbeffec2f67</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="n">
+        <v>46253.42209490741</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>5</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>мне нравится это приложение мне удобно им пользоваться всё понятно и доступно обслуживание очень культурное и уважительное спасибо вам!</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Любовь Михайловна</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>b5214e8e4b5b537ccc662a4f</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="n">
+        <v>46253.40755787037</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>5</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>для меня удобно х/банк когда работала зарплату получала, теперь пенсия получаю пользуясь ком.услаги оплачиваю.</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Гулжамал Есенгариева</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>2a10f4ba2e6bec1e8c856108</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>46253.39053240741</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" s="2" t="n"/>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Дорого...</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Бекжан Анашбаев</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>7.15.2</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>dee49c20714e3b8fc9b67d27</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="n">
+        <v>46253.37592592592</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>5</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>хорошо</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Марат Жакупов</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>914b5d137fb7ea72d31bde28</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n">
+        <v>46253.36215277778</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>5</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Керемеи</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Салтанат Сулейменова</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>626de18e1a86299500598b91</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="n">
+        <v>46253.3578125</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>5</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Алла өзі қолдасын</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Ali Kanatbai</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>7.14.0</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>653bbcd21fcefcd62836fbca</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>46252.29043981482</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>App Store</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Вечные баги</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>1. Хотел добавить в страховку водителя, 3 дня парился добавил еле как.
 2. Коплю бонусы но почему то при оплате некоторых услуг не могу использовать, смешная система если честно.
@@ -5662,1417 +6954,1417 @@
 В общем решайте сами хотите себя мучать этим банком или нет.</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>just_aidos</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr">
         <is>
           <t>14441741585</t>
         </is>
       </c>
-      <c r="J121" s="2" t="inlineStr">
+      <c r="J151" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="1" t="n">
+    <row r="152">
+      <c r="A152" s="1" t="n">
         <v>46251.58487268518</v>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="n">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Жазылмай тұр вечно тормоз Халық банк</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Тормоз</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>Вечно тормоз халық банк</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr">
         <is>
           <t>14438910422</t>
         </is>
       </c>
-      <c r="J122" s="2" t="inlineStr">
+      <c r="J152" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="1" t="n">
+    <row r="153">
+      <c r="A153" s="1" t="n">
         <v>46250.45633101852</v>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="n">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Дизайн приложения</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>UI/UX приложения немножко неудобный для такого популярного сервиса. Почему в разделе «Блокировки» выключенное состояние означает, что блокировка стоит? Нелогичный интерфейс.</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>kamgamjamieee</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr">
         <is>
           <t>14434327048</t>
         </is>
       </c>
-      <c r="J123" s="2" t="inlineStr">
+      <c r="J153" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="1" t="n">
+    <row r="154">
+      <c r="A154" s="1" t="n">
         <v>46249.21795138889</v>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="n">
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Сұрағым бойынша</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Желіге тез қосылып сұрағыма жауап алдым🫶🏻</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>Жаази</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr">
         <is>
           <t>14429492941</t>
         </is>
       </c>
-      <c r="J124" s="2" t="inlineStr">
+      <c r="J154" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="3" t="n">
+    <row r="155">
+      <c r="A155" s="3" t="n">
         <v>46248.41894675926</v>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>5</v>
-      </c>
-      <c r="E125" t="inlineStr">
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>5</v>
+      </c>
+      <c r="E155" t="inlineStr">
         <is>
           <t>Отлично</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>От</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t>Тттт07</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="H155" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="I155" t="inlineStr">
         <is>
           <t>14426122877</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
         <v>46248.3246875</v>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="n">
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Жалоба</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Это недоработанное приложение, на мой взгляд. Если разработчики что-то подсматривают у конкурентов и хотят реализовать, то пусть научатся делать это профессионально. Менеджеры банка недостаточно квалифицированы, опять-таки на мой взгляд, а об операторах колл-центра я лучше промолчу. Они все время что-то уточняют и звонок длится по полчаса. Жалобы рассматривают 15 р.б. , что говорит о многочисленных жалобах или супер ограниченном персонале обратной связи. Мне стыдно, что один из крупнейших банков Казахстана, ведет такую деятельность.</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>Абылайбек</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr">
         <is>
           <t>14425781397</t>
         </is>
       </c>
-      <c r="J126" s="2" t="inlineStr">
+      <c r="J156" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="3" t="n">
+    <row r="157">
+      <c r="A157" s="3" t="n">
         <v>46248.28721064814</v>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>5</v>
-      </c>
-      <c r="E127" t="inlineStr">
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>5</v>
+      </c>
+      <c r="E157" t="inlineStr">
         <is>
           <t>Спасибо вам большое Халык банк</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F157" t="inlineStr">
         <is>
           <t>Самый лучший из лучших</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G157" t="inlineStr">
         <is>
           <t>Мама особенного и многодетного</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="H157" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="I157" t="inlineStr">
         <is>
           <t>14425654331</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="3" t="n">
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n">
         <v>46247.61267361111</v>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>5</v>
-      </c>
-      <c r="E128" t="inlineStr">
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>5</v>
+      </c>
+      <c r="E158" t="inlineStr">
         <is>
           <t>Кэшбек</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F158" t="inlineStr">
         <is>
           <t>Вечер добрый Халык банк. Сможете внедрить кэшбек за ком услуги (квартплата). Было бы отлично. Спасибо за ранее. Это в ваших силах.</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="G158" t="inlineStr">
         <is>
           <t>Метис_79</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="H158" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
+      <c r="I158" t="inlineStr">
         <is>
           <t>14422975248</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="3" t="n">
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
         <v>46246.42810185185</v>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>5</v>
-      </c>
-      <c r="E129" t="inlineStr">
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>5</v>
+      </c>
+      <c r="E159" t="inlineStr">
         <is>
           <t>Банк #1 в Казахстане</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t>На данный момент лучший из лучших по всем параметрам! Конечно есть над чем работать, но пока Halyk ни разу не подводил!</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t>Alex von Metz</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="H159" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
+      <c r="I159" t="inlineStr">
         <is>
           <t>14418072605</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="3" t="n">
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n">
         <v>46245.29766203704</v>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>5</v>
-      </c>
-      <c r="E130" t="inlineStr">
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>5</v>
+      </c>
+      <c r="E160" t="inlineStr">
         <is>
           <t>Халык!</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>Өте керемет!</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="G160" t="inlineStr">
         <is>
           <t>Нурсат!</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="H160" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
+      <c r="I160" t="inlineStr">
         <is>
           <t>14413495571</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
         <v>46245.14422453703</v>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="n">
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Насильно на работе</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Добровольно/принудительно  на работе заставляют перейти в этот банк</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>Whisper spirit</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr">
         <is>
           <t>14412986159</t>
         </is>
       </c>
-      <c r="J131" s="2" t="inlineStr">
+      <c r="J161" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="1" t="n">
+    <row r="162">
+      <c r="A162" s="1" t="n">
         <v>46242.868125</v>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="n">
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Ужас</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Ужасное обслуживание долго и много всего ужасссс</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>Ас!’ж</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr">
         <is>
           <t>14404184832</t>
         </is>
       </c>
-      <c r="J132" s="2" t="inlineStr">
+      <c r="J162" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="3" t="n">
+    <row r="163">
+      <c r="A163" s="3" t="n">
         <v>46242.58256944444</v>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>5</v>
-      </c>
-      <c r="E133" t="inlineStr">
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>5</v>
+      </c>
+      <c r="E163" t="inlineStr">
         <is>
           <t>Comfortable App, BUT</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F163" t="inlineStr">
         <is>
           <t>Everything in your hand, but please add dark theme, sometimes white theme is so bright that hurts your eyes. Also, can you expand Halyk finance tools, like adding Kazakhstan governmental obligations like МЕКАМ/МЕУКАМ?</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="G163" t="inlineStr">
         <is>
           <t>Nedkz</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="H163" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="I163" t="inlineStr">
         <is>
           <t>14402924703</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="3" t="n">
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
         <v>46241.24402777778</v>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>5</v>
-      </c>
-      <c r="E134" t="inlineStr">
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>5</v>
+      </c>
+      <c r="E164" t="inlineStr">
         <is>
           <t>Керемет</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F164" t="inlineStr">
         <is>
           <t>Лучший банк</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="G164" t="inlineStr">
         <is>
           <t>Жаке9094</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="H164" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
+      <c r="I164" t="inlineStr">
         <is>
           <t>14397744425</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="n">
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
         <v>46241.24172453704</v>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>5</v>
-      </c>
-      <c r="E135" t="inlineStr">
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>5</v>
+      </c>
+      <c r="E165" t="inlineStr">
         <is>
           <t>👍👍👍👍</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F165" t="inlineStr">
         <is>
           <t>Все классно</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="G165" t="inlineStr">
         <is>
           <t>Чина 1991</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
+      <c r="H165" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
+      <c r="I165" t="inlineStr">
         <is>
           <t>14397736894</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
         <v>46240.56204861111</v>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="n">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Так себе</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Зависает, неудобно</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>VK-apl</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr">
         <is>
           <t>14394977482</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr">
+      <c r="J166" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="1" t="n">
+    <row r="167">
+      <c r="A167" s="1" t="n">
         <v>46240.51398148148</v>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="n">
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Не вернули деньги</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Самый худший банк</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>Nike420-</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr">
         <is>
           <t>14394747340</t>
         </is>
       </c>
-      <c r="J137" s="2" t="inlineStr">
+      <c r="J167" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="1" t="n">
+    <row r="168">
+      <c r="A168" s="1" t="n">
         <v>46240.46083333333</v>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="n">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Приограма</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Многа тупит програм  увидомление нету каждый перевод камисся 200 тг 
 На ограничения 1000 тенге это все денги</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>Жаль но тупит много</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr">
         <is>
           <t>14394515666</t>
         </is>
       </c>
-      <c r="J138" s="2" t="inlineStr">
+      <c r="J168" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="3" t="n">
+    <row r="169">
+      <c r="A169" s="3" t="n">
         <v>46240.36375</v>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>5</v>
-      </c>
-      <c r="E139" t="inlineStr">
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>5</v>
+      </c>
+      <c r="E169" t="inlineStr">
         <is>
           <t>Очень удобный</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>Очень удобный особенно когда ипотеку хочешь через предложение можешь смело падать</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
+      <c r="G169" t="inlineStr">
         <is>
           <t>Пожарный спасатель</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
+      <c r="H169" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
+      <c r="I169" t="inlineStr">
         <is>
           <t>14394154800</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="3" t="n">
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n">
         <v>46240.20215277778</v>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B170" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
         <v>4</v>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="E170" t="inlineStr">
         <is>
           <t>Добавьте возможность настройки размера шрифта</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="F170" t="inlineStr">
         <is>
           <t>Слишком маленькие иконки и надписи. Вашим приложение пользуются взрослые люди и пенсионеры. Увеличьте шрифт или дайте возможность в настройках</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="G170" t="inlineStr">
         <is>
           <t>Altyn.0170</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
+      <c r="H170" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
+      <c r="I170" t="inlineStr">
         <is>
           <t>14393615835</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="3" t="n">
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n">
         <v>46240.16615740741</v>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
         <v>4</v>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E171" t="inlineStr">
         <is>
           <t>Хорошее приложение</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>Нравится функционал и комиссии, но приложение зачастую не срабатывает при оплате QR в магазине или не заходит сразу</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="G171" t="inlineStr">
         <is>
           <t>Ruslan_Dv</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="H171" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="I171" t="inlineStr">
         <is>
           <t>14393494230</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="3" t="n">
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n">
         <v>46240.12107638889</v>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>5</v>
-      </c>
-      <c r="E142" t="inlineStr">
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>5</v>
+      </c>
+      <c r="E172" t="inlineStr">
         <is>
           <t>Халық</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F172" t="inlineStr">
         <is>
           <t>Супер приложение</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="G172" t="inlineStr">
         <is>
           <t>Ukiltik</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="H172" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
+      <c r="I172" t="inlineStr">
         <is>
           <t>14393332099</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="3" t="n">
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="n">
         <v>46240.07537037037</v>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>5</v>
-      </c>
-      <c r="E143" t="inlineStr">
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>5</v>
+      </c>
+      <c r="E173" t="inlineStr">
         <is>
           <t>Маған рефенансирования жасауға одобрение шықса қатты қуанар едім!</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>Маған рефенансирование жасауға одобрение шықса қуанар едім!</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t>Дұрыс жолға қойылған!</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="H173" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
+      <c r="I173" t="inlineStr">
         <is>
           <t>14393158873</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
         <v>46239.76517361111</v>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="n">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Обновляйте сразу страницу, чтоб не приходилось каждый раз выходить из приложения и заходить обратно</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Почему после того как сделал перевод между своими счетами, не обновляется сразу страница, а приходится выходить с приложения и заходить обратно, закрыв его</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>Хочу обновку в прилодений</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr">
         <is>
           <t>14391948907</t>
         </is>
       </c>
-      <c r="J144" s="2" t="inlineStr">
+      <c r="J174" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="1" t="n">
+    <row r="175">
+      <c r="A175" s="1" t="n">
         <v>46239.67016203704</v>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="n">
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>.</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Ішіндегі ақшаларды жеп қоя береді, операторлар дұрыс айта алмайды, зп түскенде 5-10к болдмайды, қазірдің өзіңде 7к ақшамды базада тұр дейді, но менде жоқ</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>………7878</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr">
         <is>
           <t>14391503836</t>
         </is>
       </c>
-      <c r="J145" s="2" t="inlineStr">
+      <c r="J175" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="1" t="n">
+    <row r="176">
+      <c r="A176" s="1" t="n">
         <v>46239.52751157407</v>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="n">
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Очень торомозит</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Очень плохо работает долго загружается показывает ошибку на ровном месте тормозит в день зарплаты вообще нет слов тормозы</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>Askar Maratulu</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr">
         <is>
           <t>14390778116</t>
         </is>
       </c>
-      <c r="J146" s="2" t="inlineStr">
+      <c r="J176" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="1" t="n">
+    <row r="177">
+      <c r="A177" s="1" t="n">
         <v>46239.44670138889</v>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="n">
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Dark theme, wheeen??</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Когда добавите темную тему?</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>001qr</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>7.15.0</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr">
         <is>
           <t>14390422067</t>
         </is>
       </c>
-      <c r="J147" s="2" t="inlineStr">
+      <c r="J177" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="1" t="n">
+    <row r="178">
+      <c r="A178" s="1" t="n">
         <v>46238.41152777777</v>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="n">
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Лаги, Баги</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Приложение работает ужасно. В строке поиск не чего не прописывается, только первая буква. В поддержку не пробиться везде боты. Пишу тут</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>Qwerty Still</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr">
         <is>
           <t>14386194340</t>
         </is>
       </c>
-      <c r="J148" s="2" t="inlineStr">
+      <c r="J178" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="1" t="n">
+    <row r="179">
+      <c r="A179" s="1" t="n">
         <v>46236.67026620371</v>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="n">
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>Карта Halyk Bonus</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>К работе приложения или самого банка, мобильного банкинга вопросов нет. 
 Негативный опыт вызывает политика банка к клиентам. 
 Приходит сообщение, что будет взиматься комиссия за выпуск карты Halyk bonus, спустя 2 года с момента выпуска самой карты в картомате. Как бы не жалко, но выпуск карты думаю должен быть бесплатным, а за её обслуживание комиссия взимается ежемесячно.</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>Просто Алл</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr">
         <is>
           <t>14379216532</t>
         </is>
       </c>
-      <c r="J149" s="2" t="inlineStr">
+      <c r="J179" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="3" t="n">
+    <row r="180">
+      <c r="A180" s="3" t="n">
         <v>46235.76702546296</v>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>App Store</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>kz</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
         <v>4</v>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E180" t="inlineStr">
         <is>
           <t>Тема</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>Добавьте темную тему</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="G180" t="inlineStr">
         <is>
           <t>Storm077</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
+      <c r="H180" t="inlineStr">
         <is>
           <t>7.14.0</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
+      <c r="I180" t="inlineStr">
         <is>
           <t>14375681489</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr">
+      <c r="J180" t="inlineStr">
         <is>
           <t>нет</t>
         </is>

--- a/otzyvy_halyk.xlsx
+++ b/otzyvy_halyk.xlsx
@@ -2911,7 +2911,7 @@
       <c r="C66" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="n"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Отвратительная работа маркета. Обратной связи 0. Извинений 0. Лояльности к клиентам 0. Пока сам не напишешь 10 раз ответов нет. Если по ошибке приложения приложения внёс меньше платёж по рассрочке (не хватало менее 1 тенге) НАКЛАДЫВАЮТ АРЕСТ НА СЧЁТ. Не рекомендую. раздел инвест криво работает. При просмотре акций списком открыв интересующую бумагу и при возвращении к списку приходится листать с самого начала. Когда нажимаешь кнопку назад возвращает на главный экран приложения. Итогневместился</t>
@@ -2957,7 +2957,6 @@
       <c r="C68" t="n">
         <v>5</v>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>отличный банк</t>
@@ -3035,7 +3034,6 @@
       <c r="C70" t="n">
         <v>5</v>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>Быстрота и Качество</t>
@@ -3074,7 +3072,7 @@
       <c r="C71" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D71" s="2" t="inlineStr"/>
+      <c r="D71" s="2" t="n"/>
       <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Проблемы с возвратом для клиентов, очень не удобно. Если клиент взял вчера, сегодня пришёл с возвратом, а на счёте нет денег за сегодня, возврат не доступен, клиент недоволен. Происходит недопонимание. Печально</t>
@@ -3113,7 +3111,7 @@
       <c r="C72" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
           <t>не удобный сервис, не user-friendly... кнопки должны быть так расположены, чтобы не приходилось по 10 раз нажимать</t>
@@ -3152,7 +3150,6 @@
       <c r="C73" t="n">
         <v>4</v>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>Функция перевода денег на другой банк не удобно.</t>
@@ -3191,7 +3188,6 @@
       <c r="C74" t="n">
         <v>4</v>
       </c>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>1. скорость. 2. почему нет бонусов</t>
@@ -3230,7 +3226,6 @@
       <c r="C75" t="n">
         <v>5</v>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>❤️❤️❤️</t>
@@ -3269,7 +3264,6 @@
       <c r="C76" t="n">
         <v>5</v>
       </c>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>Приложение народного банка всегда мне очень нравится. Пользуюсь свыше 15 лет.</t>
@@ -3308,7 +3302,6 @@
       <c r="C77" t="n">
         <v>5</v>
       </c>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>спасибо, хорошо!</t>
@@ -3347,7 +3340,6 @@
       <c r="C78" t="n">
         <v>5</v>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Рақмет</t>
@@ -3386,7 +3378,7 @@
       <c r="C79" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Приложение обновлено, но требует обновление. Бред полнейший</t>
@@ -3463,7 +3455,6 @@
       <c r="C81" t="n">
         <v>5</v>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>всю жизнь ха́лык банком всё отлично</t>
@@ -3502,7 +3493,7 @@
       <c r="C82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Оптимизируйте свое глючное приложение.</t>
@@ -3541,7 +3532,6 @@
       <c r="C83" t="n">
         <v>4</v>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>за минуту открыл карту . Но ребят. На главной сломалась локализация: вместо нормального текста отображаются ключи ресурсов — "searchTrigger.placeholder", "reesBlocks.forYou", "order.toBasket", "productTeaser.badges.original", "productTeaser.review.count" и т.д. Похоже, приложение не находит/не подгружает нужные переводы и показывает fallback в виде ключей. Проверьте i18n resources/bundle для текущей локали и соответствие ключей. И ещё вопрос: почему это вообще доходит до UI?</t>
@@ -3580,7 +3570,6 @@
       <c r="C84" t="n">
         <v>5</v>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>Отлично</t>
@@ -3619,7 +3608,7 @@
       <c r="C85" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D85" s="2" t="inlineStr"/>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" s="2" t="inlineStr">
         <is>
           <t>на складных устроистыах цифры не видны так себе теперь авторизоваться не могу звонил толку нет</t>
@@ -3658,7 +3647,6 @@
       <c r="C86" t="n">
         <v>5</v>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>Отлично</t>
@@ -3697,7 +3685,6 @@
       <c r="C87" t="n">
         <v>5</v>
       </c>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>классный банк и удобный</t>
@@ -3736,7 +3723,7 @@
       <c r="C88" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D88" s="2" t="inlineStr"/>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Просто зависает постоянно, ничего невозможно сделать!</t>
@@ -3775,7 +3762,6 @@
       <c r="C89" t="n">
         <v>5</v>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>керемет жақсы банк сіздер</t>
@@ -3852,7 +3838,6 @@
       <c r="C91" t="n">
         <v>5</v>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>приложение удобное, хорошо работает</t>
@@ -3969,7 +3954,6 @@
       <c r="C94" t="n">
         <v>5</v>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>хороший банк</t>
@@ -4046,7 +4030,6 @@
       <c r="C96" t="n">
         <v>5</v>
       </c>
-      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>Молодцы!</t>
@@ -4085,7 +4068,6 @@
       <c r="C97" t="n">
         <v>5</v>
       </c>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>хорошо</t>
@@ -4200,7 +4182,7 @@
       <c r="C100" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D100" s="2" t="inlineStr"/>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Невозможно зайти в приложение.Приложение требует обновиться,но обновлений нет.Переустановка помогает не надолго.</t>
@@ -4315,7 +4297,6 @@
       <c r="C103" t="n">
         <v>5</v>
       </c>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>хороший банк</t>
@@ -4392,7 +4373,6 @@
       <c r="C105" t="n">
         <v>5</v>
       </c>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>керемет</t>
@@ -4431,7 +4411,6 @@
       <c r="C106" t="n">
         <v>5</v>
       </c>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>очень хорошая</t>
@@ -4509,7 +4488,6 @@
       <c r="C108" t="n">
         <v>5</v>
       </c>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>Очень удобное</t>
@@ -4740,7 +4718,6 @@
       <c r="C114" t="n">
         <v>5</v>
       </c>
-      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -4855,7 +4832,6 @@
       <c r="C117" t="n">
         <v>5</v>
       </c>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>Тамаша</t>
@@ -4933,7 +4909,6 @@
       <c r="C119" t="n">
         <v>5</v>
       </c>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>Мне почему то не одобряет кредит? Почему?</t>
@@ -4944,7 +4919,6 @@
           <t>Назым Медетбекова</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
           <t>f4cf507fc04b6f083f764e09</t>
@@ -4968,7 +4942,6 @@
       <c r="C120" t="n">
         <v>5</v>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>удобное приложение</t>
@@ -5007,7 +4980,6 @@
       <c r="C121" t="n">
         <v>5</v>
       </c>
-      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>Ең керемет банк</t>
@@ -5084,7 +5056,6 @@
       <c r="C123" t="n">
         <v>5</v>
       </c>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -5095,7 +5066,6 @@
           <t>Айбар Жантлеуов</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
           <t>dad947d5cbe62b7cb64e7509</t>
@@ -5119,7 +5089,6 @@
       <c r="C124" t="n">
         <v>4</v>
       </c>
-      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>👍👍👍</t>
@@ -5234,7 +5203,6 @@
       <c r="C127" t="n">
         <v>5</v>
       </c>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>мне нравится, единственная только,что не можем заказывать продукты в Магнум, смолл...через приложение, а так все на отлично</t>
@@ -5311,7 +5279,6 @@
       <c r="C129" t="n">
         <v>5</v>
       </c>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>Всё отлично 👌</t>
@@ -5683,7 +5650,6 @@
       <c r="C139" t="n">
         <v>5</v>
       </c>
-      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>удобно</t>
@@ -5729,7 +5695,7 @@
       <c r="C141" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D141" s="2" t="inlineStr"/>
+      <c r="D141" s="2" t="n"/>
       <c r="E141" s="2" t="inlineStr">
         <is>
           <t>перевод на абонента каждый раз надо набирать, повторить не возможно</t>
@@ -5768,7 +5734,6 @@
       <c r="C142" t="n">
         <v>5</v>
       </c>
-      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -5807,7 +5772,6 @@
       <c r="C143" t="n">
         <v>5</v>
       </c>
-      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>все нужное в одном приложении</t>
@@ -5846,7 +5810,6 @@
       <c r="C144" t="n">
         <v>5</v>
       </c>
-      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>Классное приложение</t>
@@ -5923,7 +5886,7 @@
       <c r="C146" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D146" s="2" t="inlineStr"/>
+      <c r="D146" s="2" t="n"/>
       <c r="E146" s="2" t="inlineStr">
         <is>
           <t>пишет удалите приложение, загрузите с официального источника</t>
@@ -5962,7 +5925,6 @@
       <c r="C147" t="n">
         <v>5</v>
       </c>
-      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>здравствуйте, банк очень хороший, на все вопросы можно получить быстрый и профессиональный ответ, операторы очень вежливые и грамотные, спасибо!!!</t>
@@ -6001,7 +5963,6 @@
       <c r="C148" t="n">
         <v>5</v>
       </c>
-      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>спасибо</t>
@@ -6040,7 +6001,6 @@
       <c r="C149" t="n">
         <v>5</v>
       </c>
-      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>Интернет слабыи</t>
@@ -6079,7 +6039,6 @@
       <c r="C150" t="n">
         <v>5</v>
       </c>
-      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>Большое спасибо, всё нравиться, удачи вам в вашей работе!!!</t>
@@ -6118,7 +6077,6 @@
       <c r="C151" t="n">
         <v>5</v>
       </c>
-      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>Народный банк самый лучший!</t>
@@ -6157,7 +6115,6 @@
       <c r="C152" t="n">
         <v>4</v>
       </c>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>Приложение хорошее. Но нужно доработать многое и увеличить сферы услуг как на Камри банк. И вот программа очень долго думает при работе с клиентами. А в остальном все хорошо.</t>
@@ -6273,7 +6230,6 @@
       <c r="C155" t="n">
         <v>5</v>
       </c>
-      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>все хорошо!!</t>
@@ -6350,7 +6306,6 @@
       <c r="C157" t="n">
         <v>5</v>
       </c>
-      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -6389,7 +6344,6 @@
       <c r="C158" t="n">
         <v>5</v>
       </c>
-      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>хороший приложение</t>
@@ -6428,7 +6382,6 @@
       <c r="C159" t="n">
         <v>5</v>
       </c>
-      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>благодарю за труд.</t>
@@ -6467,7 +6420,6 @@
       <c r="C160" t="n">
         <v>5</v>
       </c>
-      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>жақсы</t>
@@ -6544,7 +6496,6 @@
       <c r="C162" t="n">
         <v>5</v>
       </c>
-      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>Все устраивает. Halyk работает хорошо.</t>
@@ -6583,7 +6534,6 @@
       <c r="C163" t="n">
         <v>5</v>
       </c>
-      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>Отлично</t>
@@ -6622,7 +6572,7 @@
       <c r="C164" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D164" s="2" t="inlineStr"/>
+      <c r="D164" s="2" t="n"/>
       <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Из всех банковских приложений это самое убогое.Заходишь пишут обновить, заходишь в плей маркет ,обновления нет .Удаляешь ,заново скачиваю опять тоже самое.Вы разработчики издеваетесь 😡😡😡</t>
@@ -6661,7 +6611,6 @@
       <c r="C165" t="n">
         <v>5</v>
       </c>
-      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>все хорошо</t>
@@ -6739,7 +6688,7 @@
       <c r="C167" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D167" s="2" t="inlineStr"/>
+      <c r="D167" s="2" t="n"/>
       <c r="E167" s="2" t="inlineStr">
         <is>
           <t>почему удержали 1 тыс тенге</t>
@@ -6778,7 +6727,6 @@
       <c r="C168" t="n">
         <v>5</v>
       </c>
-      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>удобно</t>
@@ -6817,7 +6765,6 @@
       <c r="C169" t="n">
         <v>5</v>
       </c>
-      <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
           <t>Ыңғайлы</t>
@@ -6856,7 +6803,6 @@
       <c r="C170" t="n">
         <v>5</v>
       </c>
-      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>өте жақсы</t>
@@ -6895,7 +6841,6 @@
       <c r="C171" t="n">
         <v>5</v>
       </c>
-      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>В последнее время стали работать гораздо лучше, оперативнее! Спасибо!</t>
@@ -6934,7 +6879,6 @@
       <c r="C172" t="n">
         <v>5</v>
       </c>
-      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>очень удобно и быстро</t>
@@ -7011,7 +6955,6 @@
       <c r="C174" t="n">
         <v>5</v>
       </c>
-      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
           <t>👍👍👍</t>
@@ -7088,7 +7031,7 @@
       <c r="C176" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D176" s="2" t="inlineStr"/>
+      <c r="D176" s="2" t="n"/>
       <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Раньше было вполне себе приличное приложение. С начала августа вдруг перестало запускать меня в банк. Регистрацию через видео сделать не даёт. Колл центр 7111, говорит мне про недоверенный номер телефона. Хотя на egov и в другие банки я захожу по нему спокойно. В БМГ зарегистрирован. В общем после нескольких дней мучений со входом в это приложение, сделала перевод пенсии в другой более лояльный к клиентам. Ни это приложение, ни этот банк не рекомендую. Нервы без них целее будут.</t>
@@ -7099,7 +7042,7 @@
           <t>Любовь Малых</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
+      <c r="G176" s="2" t="n"/>
       <c r="H176" s="2" t="inlineStr">
         <is>
           <t>e85a1d5044a99973ee63b274</t>
@@ -7123,7 +7066,6 @@
       <c r="C177" t="n">
         <v>5</v>
       </c>
-      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>всё доступно</t>
@@ -7314,7 +7256,6 @@
       <c r="C182" t="n">
         <v>5</v>
       </c>
-      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
           <t>Очень удобно.</t>
@@ -7353,7 +7294,6 @@
       <c r="C183" t="n">
         <v>5</v>
       </c>
-      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>Отличное приложение для нас ленивых не вставая с дивана</t>
@@ -7392,7 +7332,6 @@
       <c r="C184" t="n">
         <v>5</v>
       </c>
-      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -7431,7 +7370,6 @@
       <c r="C185" t="n">
         <v>5</v>
       </c>
-      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
           <t>все, что мне нужно, есть в этом приложении</t>
@@ -7508,7 +7446,6 @@
       <c r="C187" t="n">
         <v>5</v>
       </c>
-      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
           <t>жаксы</t>
@@ -7547,7 +7484,6 @@
       <c r="C188" t="n">
         <v>5</v>
       </c>
-      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>Приложение мне нравится. Совмещение с электронным паркетом хорошо реализовано. Нравится быстрый процесс оплаты и доставки. Отличная работа.!</t>
@@ -7662,7 +7598,7 @@
       <c r="C191" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D191" s="2" t="inlineStr"/>
+      <c r="D191" s="2" t="n"/>
       <c r="E191" s="2" t="inlineStr">
         <is>
           <t>Постоянно просит удалить старое и установить новое приложение.... Уже месяц такая проблема не возможно работать...</t>
@@ -7673,7 +7609,7 @@
           <t>Si.Bat. Анатолий Батенев</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr"/>
+      <c r="G191" s="2" t="n"/>
       <c r="H191" s="2" t="inlineStr">
         <is>
           <t>0196b5da549aafeef7a7e046</t>
@@ -7735,7 +7671,6 @@
       <c r="C193" t="n">
         <v>5</v>
       </c>
-      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>хорошее приложение.</t>
@@ -7812,7 +7747,6 @@
       <c r="C195" t="n">
         <v>5</v>
       </c>
-      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
           <t>Ұнайды</t>
@@ -7851,7 +7785,6 @@
       <c r="C196" t="n">
         <v>5</v>
       </c>
-      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>Күшті керемет</t>
@@ -7890,7 +7823,7 @@
       <c r="C197" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D197" s="2" t="inlineStr"/>
+      <c r="D197" s="2" t="n"/>
       <c r="E197" s="2" t="inlineStr">
         <is>
           <t>теперь каждые пять дней обновляется</t>
@@ -7901,7 +7834,7 @@
           <t>Талгат Баимбет</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr"/>
+      <c r="G197" s="2" t="n"/>
       <c r="H197" s="2" t="inlineStr">
         <is>
           <t>036050352ab5b63457a0bacd</t>
@@ -7963,7 +7896,6 @@
       <c r="C199" t="n">
         <v>5</v>
       </c>
-      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
           <t>Отличное обслуживание</t>
@@ -8002,7 +7934,7 @@
       <c r="C200" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D200" s="2" t="inlineStr"/>
+      <c r="D200" s="2" t="n"/>
       <c r="E200" s="2" t="inlineStr">
         <is>
           <t>неудобно что в сообщениях не показывается сумма которая осталась после списания.</t>
@@ -8041,7 +7973,6 @@
       <c r="C201" t="n">
         <v>5</v>
       </c>
-      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>ОТЛИЧНО!!!</t>
@@ -8118,7 +8049,6 @@
       <c r="C203" t="n">
         <v>5</v>
       </c>
-      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
           <t>Надёжный банк.</t>
@@ -8196,7 +8126,6 @@
       <c r="C205" t="n">
         <v>5</v>
       </c>
-      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
           <t>Мне очень нравится приложение. Работает без сбоев. Все доступно и удобно.</t>
@@ -8350,7 +8279,6 @@
       <c r="C209" t="n">
         <v>5</v>
       </c>
-      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
           <t>Халық банкінің қызметкерлері мен басшыларына үлкен рақмет, барлығы ұнайды, жақсы</t>
@@ -8389,7 +8317,6 @@
       <c r="C210" t="n">
         <v>5</v>
       </c>
-      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
           <t>очень удобно пользоваться</t>
@@ -11829,7 +11756,7 @@
       <c r="C300" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D300" s="2" t="inlineStr"/>
+      <c r="D300" s="2" t="n"/>
       <c r="E300" s="2" t="inlineStr">
         <is>
           <t>Начиная с 17 августа приложение при запуске требует установить обновление из официального источника и закрывается. Переустановки и перезагрузки не помогают, очистка кэша тоже. Халык, скажите что делать?</t>
@@ -11868,7 +11795,6 @@
       <c r="C301" t="n">
         <v>5</v>
       </c>
-      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
           <t>камфортно</t>
@@ -11907,7 +11833,6 @@
       <c r="C302" t="n">
         <v>5</v>
       </c>
-      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr">
         <is>
           <t>удачи</t>
@@ -11960,7 +11885,6 @@
       <c r="C305" t="n">
         <v>5</v>
       </c>
-      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
           <t>Очень нужный и удобный банк! Мне нравится! Спасибо! Процветания!</t>
@@ -12043,7 +11967,6 @@
       <c r="C306" t="n">
         <v>5</v>
       </c>
-      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
           <t>удобно</t>
@@ -12082,7 +12005,6 @@
       <c r="C307" t="n">
         <v>5</v>
       </c>
-      <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
           <t>рақмет</t>
@@ -12121,7 +12043,6 @@
       <c r="C308" t="n">
         <v>5</v>
       </c>
-      <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
           <t>ужасный сервис</t>
@@ -12132,7 +12053,6 @@
           <t>Galina Gubaidullina</t>
         </is>
       </c>
-      <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr">
         <is>
           <t>3d69deeee8924c9334af3030</t>
@@ -12156,7 +12076,6 @@
       <c r="C309" t="n">
         <v>5</v>
       </c>
-      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -12195,7 +12114,6 @@
       <c r="C310" t="n">
         <v>5</v>
       </c>
-      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
           <t>приложение Халык банк супер удобно быстро качественно . переводы плотижи быстро. рекомендую.</t>
@@ -12234,7 +12152,6 @@
       <c r="C311" t="n">
         <v>5</v>
       </c>
-      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -12273,7 +12190,7 @@
       <c r="C312" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D312" s="2" t="inlineStr"/>
+      <c r="D312" s="2" t="n"/>
       <c r="E312" s="2" t="inlineStr">
         <is>
           <t>До каспи вам ещё далеко,деньги на счету не понятно исчезают и у вас очень долгое обслуживание</t>
@@ -12312,7 +12229,6 @@
       <c r="C313" t="n">
         <v>5</v>
       </c>
-      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
           <t>вы лучшие</t>
@@ -12351,7 +12267,6 @@
       <c r="C314" t="n">
         <v>5</v>
       </c>
-      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
           <t>не обновляется новое приложение и предыдущее приложение не открывается</t>
@@ -12390,7 +12305,7 @@
       <c r="C315" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D315" s="2" t="inlineStr"/>
+      <c r="D315" s="2" t="n"/>
       <c r="E315" s="2" t="inlineStr">
         <is>
           <t>Самое тупое приложение из существующих, чтобы зарегаться, пройти невозможно биометрику от слова НИКОГДА!!! Спасибо рукожопам айтишникам, что я не стал клиентом банка😃</t>
@@ -12401,7 +12316,7 @@
           <t>Серик</t>
         </is>
       </c>
-      <c r="G315" s="2" t="inlineStr"/>
+      <c r="G315" s="2" t="n"/>
       <c r="H315" s="2" t="inlineStr">
         <is>
           <t>2144906f4228d9e3e20df2d9</t>
@@ -12425,7 +12340,7 @@
       <c r="C316" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D316" s="2" t="inlineStr"/>
+      <c r="D316" s="2" t="n"/>
       <c r="E316" s="2" t="inlineStr">
         <is>
           <t>на Oppo A3 данный приложение не работает</t>
@@ -12436,7 +12351,7 @@
           <t>Nuraddin Baluanov</t>
         </is>
       </c>
-      <c r="G316" s="2" t="inlineStr"/>
+      <c r="G316" s="2" t="n"/>
       <c r="H316" s="2" t="inlineStr">
         <is>
           <t>0dda85866ca505829e6d0c2c</t>
@@ -12460,7 +12375,6 @@
       <c r="C317" t="n">
         <v>5</v>
       </c>
-      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
           <t>удобная</t>
@@ -12499,7 +12413,6 @@
       <c r="C318" t="n">
         <v>5</v>
       </c>
-      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -12538,7 +12451,7 @@
       <c r="C319" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D319" s="2" t="inlineStr"/>
+      <c r="D319" s="2" t="n"/>
       <c r="E319" s="2" t="inlineStr">
         <is>
           <t>банкомат древний век!!! шагайте в ногу с КаспиБанком!!!</t>
@@ -12577,7 +12490,6 @@
       <c r="C320" t="n">
         <v>5</v>
       </c>
-      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
           <t>Спасибо Вам! Мне всё нравится</t>
@@ -12616,7 +12528,6 @@
       <c r="C321" t="n">
         <v>5</v>
       </c>
-      <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
           <t>👍👍👍👍</t>
@@ -12655,7 +12566,6 @@
       <c r="C322" t="n">
         <v>5</v>
       </c>
-      <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
           <t>ок</t>
@@ -12694,7 +12604,6 @@
       <c r="C323" t="n">
         <v>5</v>
       </c>
-      <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
           <t>очень удобно и быстро</t>
@@ -12733,7 +12642,6 @@
       <c r="C324" t="n">
         <v>5</v>
       </c>
-      <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
           <t>Хорошее обслуживание</t>
@@ -12744,7 +12652,6 @@
           <t>Bolathan</t>
         </is>
       </c>
-      <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr">
         <is>
           <t>ee217fc76abbf58ea6abd79a</t>
@@ -12768,7 +12675,6 @@
       <c r="C325" t="n">
         <v>5</v>
       </c>
-      <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
           <t>приложение отличное</t>
@@ -12807,7 +12713,7 @@
       <c r="C326" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D326" s="2" t="inlineStr"/>
+      <c r="D326" s="2" t="n"/>
       <c r="E326" s="2" t="inlineStr">
         <is>
           <t>Ужасное приложение, видео проверку пройти невозможно, пробовали на разных устройствах и с разными людьми 💩💩💩</t>
@@ -12846,7 +12752,6 @@
       <c r="C327" t="n">
         <v>5</v>
       </c>
-      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
           <t>всегда пользуюсь и это очень удобно им пользоваться, всем советую тебе</t>
@@ -12857,7 +12762,6 @@
           <t>Ольга Абашева</t>
         </is>
       </c>
-      <c r="G327" t="inlineStr"/>
       <c r="H327" t="inlineStr">
         <is>
           <t>31982d73471267d3d11e32a0</t>
@@ -12881,7 +12785,7 @@
       <c r="C328" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D328" s="2" t="inlineStr"/>
+      <c r="D328" s="2" t="n"/>
       <c r="E328" s="2" t="inlineStr">
         <is>
           <t>Не нравится. Тормозит страшно. Благодаря этому на меня повесили 2 рассрочки. Спасибо вам. И продавцу мошеннику</t>
@@ -12920,7 +12824,7 @@
       <c r="C329" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D329" s="2" t="inlineStr"/>
+      <c r="D329" s="2" t="n"/>
       <c r="E329" s="2" t="inlineStr">
         <is>
           <t>нужно было срочно посмотреть баланс,не смогла! ваша проверка занимает много времени.</t>
@@ -12959,7 +12863,6 @@
       <c r="C330" t="n">
         <v>5</v>
       </c>
-      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
           <t>Все на высшем уровне</t>
@@ -12998,7 +12901,6 @@
       <c r="C331" t="n">
         <v>5</v>
       </c>
-      <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
           <t>Очень хорошо</t>
@@ -13037,7 +12939,6 @@
       <c r="C332" t="n">
         <v>5</v>
       </c>
-      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
           <t>как обновить приложение?</t>
@@ -13076,7 +12977,6 @@
       <c r="C333" t="n">
         <v>5</v>
       </c>
-      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
           <t>хорошее качество</t>
@@ -13115,7 +13015,7 @@
       <c r="C334" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D334" s="2" t="inlineStr"/>
+      <c r="D334" s="2" t="n"/>
       <c r="E334" s="2" t="inlineStr">
         <is>
           <t>вам бы улучшить производительность при снятии с депозита стоишь и обновляешь пока не подтвердится,нужно чтобы сразу снимались. пародия на каспи</t>
@@ -13154,7 +13054,6 @@
       <c r="C335" t="n">
         <v>5</v>
       </c>
-      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
           <t>Халық банк халыққа мінсіз қызмет жасайды. Еңбектеріңіз табысты болсын!</t>
@@ -13193,7 +13092,6 @@
       <c r="C336" t="n">
         <v>5</v>
       </c>
-      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
           <t>в принципе всё отлично работает, никаких нареканий к приложению нет. продолжайте в том же духе!</t>
@@ -13239,7 +13137,6 @@
       <c r="C338" t="n">
         <v>5</v>
       </c>
-      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
           <t>легко и просто, главное удобно</t>
@@ -13319,7 +13216,6 @@
       <c r="C339" t="n">
         <v>5</v>
       </c>
-      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
           <t>отличный банк</t>
@@ -13358,7 +13254,6 @@
       <c r="C340" t="n">
         <v>5</v>
       </c>
-      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
           <t>Супер</t>
@@ -13397,7 +13292,7 @@
       <c r="C341" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D341" s="2" t="inlineStr"/>
+      <c r="D341" s="2" t="n"/>
       <c r="E341" s="2" t="inlineStr">
         <is>
           <t>Являюсь вашим клиентом. Отправил сам себе перевод Western Union из Европы в Казахстан. Из-за смены номера телефона не могу подтвердить списание/получение в приложении Halyk Homebank, а пройти видео-идентификацию из-за границы не удается. Приложение выдает ошибку. ​В итоге 500 евро висят в системе, комиссия уплачена, а поддержка отвечает шаблонным «приходите в отделение». Приехать физически сейчас возможности нет. Прошу руководство/SMM-команду связаться со мной в LSI и помочь провести удаленную в</t>
@@ -13408,7 +13303,7 @@
           <t>Олег</t>
         </is>
       </c>
-      <c r="G341" s="2" t="inlineStr"/>
+      <c r="G341" s="2" t="n"/>
       <c r="H341" s="2" t="inlineStr">
         <is>
           <t>a87644aa13beeab26f672987</t>
@@ -13432,7 +13327,6 @@
       <c r="C342" t="n">
         <v>5</v>
       </c>
-      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
           <t>АЛЛА РАЗЫ БОЛСЫН рахмет сіздерге халық банкі ұжымдық кәсіби мамандарына.</t>
@@ -13471,7 +13365,6 @@
       <c r="C343" t="n">
         <v>5</v>
       </c>
-      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
           <t>отличное приложение и обслуживание</t>
@@ -13510,7 +13403,6 @@
       <c r="C344" t="n">
         <v>5</v>
       </c>
-      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
           <t>тема</t>
@@ -13549,7 +13441,6 @@
       <c r="C345" t="n">
         <v>5</v>
       </c>
-      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -13588,7 +13479,7 @@
       <c r="C346" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D346" s="2" t="inlineStr"/>
+      <c r="D346" s="2" t="n"/>
       <c r="E346" s="2" t="inlineStr">
         <is>
           <t>Добавьте возможность удаления неактуальных гос номеров автомобилей в выпадающем списке при оплате парковки итп. Понимаю, что для вас это архисложно, но вы уж как-нибудь постарайтесь или спросите у тех, кто умеет.</t>
@@ -13627,7 +13518,6 @@
       <c r="C347" t="n">
         <v>5</v>
       </c>
-      <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
           <t>очень удобное приложение и вежливый персонал и оператор</t>
@@ -13666,7 +13556,6 @@
       <c r="C348" t="n">
         <v>5</v>
       </c>
-      <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
           <t>всё отлично</t>
@@ -13705,7 +13594,6 @@
       <c r="C349" t="n">
         <v>5</v>
       </c>
-      <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
           <t>балык банк ашылмай тұр</t>
@@ -13744,7 +13632,6 @@
       <c r="C350" t="n">
         <v>5</v>
       </c>
-      <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
           <t>всё хорошо</t>
@@ -13783,7 +13670,6 @@
       <c r="C351" t="n">
         <v>5</v>
       </c>
-      <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr">
         <is>
           <t>Все вопросы решаются на месте оперативно, спасибо</t>
@@ -13822,7 +13708,7 @@
       <c r="C352" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D352" s="2" t="inlineStr"/>
+      <c r="D352" s="2" t="n"/>
       <c r="E352" s="2" t="inlineStr">
         <is>
           <t>Ужасное в последнее время. потребовало обновления в связи с безопасностью, удаляешь, устанавливаешь, тольку ноль. Позвонила в тех.поддержку,ответили, что у меня устарела операционная система телефона,надо обновить. Когда стала проверять, все в порядке, стоит последняя версия ПО. Наверное в банке сами не понимают, что происходит. Охота закрыть здесь все счета.</t>
@@ -13833,7 +13719,7 @@
           <t>Софья Краузе</t>
         </is>
       </c>
-      <c r="G352" s="2" t="inlineStr"/>
+      <c r="G352" s="2" t="n"/>
       <c r="H352" s="2" t="inlineStr">
         <is>
           <t>f871da7b770688514f95bcd8</t>
@@ -13857,7 +13743,6 @@
       <c r="C353" t="n">
         <v>5</v>
       </c>
-      <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
           <t>ЕҢ СЕНІМДІ БАНК 🏦</t>
@@ -13896,7 +13781,7 @@
       <c r="C354" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D354" s="2" t="inlineStr"/>
+      <c r="D354" s="2" t="n"/>
       <c r="E354" s="2" t="inlineStr">
         <is>
           <t>Часто зависает. Но лучше работает, чем онлайн банк.</t>
@@ -13935,7 +13820,6 @@
       <c r="C355" t="n">
         <v>5</v>
       </c>
-      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
           <t>ең жақсы банк</t>
@@ -13974,7 +13858,6 @@
       <c r="C356" t="n">
         <v>5</v>
       </c>
-      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
           <t>позвоните через видео</t>
@@ -14013,7 +13896,7 @@
       <c r="C357" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D357" s="2" t="inlineStr"/>
+      <c r="D357" s="2" t="n"/>
       <c r="E357" s="2" t="inlineStr">
         <is>
           <t>Приложение ужасное , сохраняешь в частые карту от другого банка для быстрого перевода она слетает! хочешь повторить перевод тоже нельзя, надо искать карточку и вбивать все заного( отстой каспи в этом плане лучше</t>
@@ -14052,7 +13935,7 @@
       <c r="C358" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D358" s="2" t="inlineStr"/>
+      <c r="D358" s="2" t="n"/>
       <c r="E358" s="2" t="inlineStr">
         <is>
           <t>Приложение хорошее, но есть нюансы. не советую пользоваться сервисом Рестораны, так как если Ваш заказ не будет исполнен, Халык тут не причем, разбирайтесь сами. в Яндексе бы все решили за Вас, для Вас.</t>
@@ -14091,7 +13974,6 @@
       <c r="C359" t="n">
         <v>5</v>
       </c>
-      <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr">
         <is>
           <t>все хорошо 👍</t>
@@ -14130,7 +14012,6 @@
       <c r="C360" t="n">
         <v>5</v>
       </c>
-      <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
           <t>керемет</t>
@@ -14169,7 +14050,7 @@
       <c r="C361" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D361" s="2" t="inlineStr"/>
+      <c r="D361" s="2" t="n"/>
       <c r="E361" s="2" t="inlineStr">
         <is>
           <t>Бонус жүреді деген акцияға алданып қалдым, әйтпесе фридомнан алар едім ...</t>
@@ -14208,7 +14089,6 @@
       <c r="C362" t="n">
         <v>5</v>
       </c>
-      <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
           <t>Очень удобный приложение 🎖🏆💰🧿</t>
@@ -14247,7 +14127,6 @@
       <c r="C363" t="n">
         <v>5</v>
       </c>
-      <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
           <t>супер</t>
@@ -14286,7 +14165,6 @@
       <c r="C364" t="n">
         <v>5</v>
       </c>
-      <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
           <t>самое хорошее приложение им удобно пользоваться</t>
@@ -14325,7 +14203,7 @@
       <c r="C365" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D365" s="2" t="inlineStr"/>
+      <c r="D365" s="2" t="n"/>
       <c r="E365" s="2" t="inlineStr">
         <is>
           <t>не могу который день авторизоваться в приложении. сначала говорили версия андроида не подходит, после версия приложения. теперь 3 дня сказали ждать. версии все обновлены, но при авторизации направляет на запрос кредита.</t>
@@ -14364,7 +14242,6 @@
       <c r="C366" t="n">
         <v>5</v>
       </c>
-      <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
           <t>я боле 20 лет ползуес усугамй халық банка дайте мне пожалуста кредит хотябы 50 000 тг.</t>
@@ -14403,7 +14280,6 @@
       <c r="C367" t="n">
         <v>5</v>
       </c>
-      <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
           <t>хорошо</t>
@@ -14442,7 +14318,6 @@
       <c r="C368" t="n">
         <v>4</v>
       </c>
-      <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
           <t>все хорошо. только почему-то не приходят смс когда снимаешь наличку с карты .раньше приходили а теперь нет</t>
@@ -14481,7 +14356,6 @@
       <c r="C369" t="n">
         <v>5</v>
       </c>
-      <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
           <t>супер</t>
@@ -14520,7 +14394,7 @@
       <c r="C370" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D370" s="2" t="inlineStr"/>
+      <c r="D370" s="2" t="n"/>
       <c r="E370" s="2" t="inlineStr">
         <is>
           <t>Выходит модальное окно о необходимости установки новой версии приложения Халык банка, но отсутствует кнопка Обновить. В Googleplay выдаётся инфо о том, что приложение уже установлено и предлагается удалить установленное приложение для того, что иметь возможность установить новую версию. Разработчики, вы понимаете всю степень опасности установки данного банковского приложения не с официального источника??? Почему отсутствует кнопка Обновить? Почему нужно сначала удалить приложение?</t>
@@ -14559,7 +14433,6 @@
       <c r="C371" t="n">
         <v>5</v>
       </c>
-      <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
           <t>классное приложение!!!!</t>
@@ -14598,7 +14471,6 @@
       <c r="C372" t="n">
         <v>5</v>
       </c>
-      <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -14637,7 +14509,7 @@
       <c r="C373" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D373" s="2" t="inlineStr"/>
+      <c r="D373" s="2" t="n"/>
       <c r="E373" s="2" t="inlineStr">
         <is>
           <t>неудобное приложение, неудобное расположение функций, неудобно переводить деньги, надо сначала у себя между счетами переводить, потом уже куда-то, для чего тогда делать этот никчемный кошелёк? на него переводить можно, а с него нельзя. Ужасный дизайн, блёклый, невыразительный, глазу не за что зацепиться, сидишь ищешь вкладку. Пользуюсь им от силы 1 день в месяц, чтобы деньги с него отправить на другой банк и там уже пользоваться.</t>
@@ -14676,7 +14548,6 @@
       <c r="C374" t="n">
         <v>5</v>
       </c>
-      <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr">
         <is>
           <t>Отличное приложение, все работает.</t>
@@ -14715,7 +14586,6 @@
       <c r="C375" t="n">
         <v>5</v>
       </c>
-      <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr">
         <is>
           <t>Супер</t>
@@ -14754,7 +14624,7 @@
       <c r="C376" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D376" s="2" t="inlineStr"/>
+      <c r="D376" s="2" t="n"/>
       <c r="E376" s="2" t="inlineStr">
         <is>
           <t>доброе утро,уже несколько дней не могу зайти в приложение,пишет удалить и скачать новую версию,удалили с качала и тоже самое.что сделать?</t>
@@ -14765,7 +14635,7 @@
           <t>лариса орлова</t>
         </is>
       </c>
-      <c r="G376" s="2" t="inlineStr"/>
+      <c r="G376" s="2" t="n"/>
       <c r="H376" s="2" t="inlineStr">
         <is>
           <t>ea39ff26788190e8cf3ae9e2</t>
@@ -14789,7 +14659,6 @@
       <c r="C377" t="n">
         <v>5</v>
       </c>
-      <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
           <t>очень простой и удобный в использований</t>
@@ -14828,7 +14697,6 @@
       <c r="C378" t="n">
         <v>5</v>
       </c>
-      <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
           <t>👍</t>
@@ -14867,7 +14735,6 @@
       <c r="C379" t="n">
         <v>5</v>
       </c>
-      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
           <t>классно</t>
@@ -14906,7 +14773,6 @@
       <c r="C380" t="n">
         <v>5</v>
       </c>
-      <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
           <t>Очень удобно и лехко</t>
@@ -14945,7 +14811,7 @@
       <c r="C381" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D381" s="2" t="inlineStr"/>
+      <c r="D381" s="2" t="n"/>
       <c r="E381" s="2" t="inlineStr">
         <is>
           <t>өте жай істейді каспиге қарағанда және өте ыңғайсыз қанша ақша аударылғанын тексеру үшін қосымшадан шығып қайтпдан кіру керек.</t>
@@ -14984,7 +14850,7 @@
       <c r="C382" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D382" s="2" t="inlineStr"/>
+      <c r="D382" s="2" t="n"/>
       <c r="E382" s="2" t="inlineStr">
         <is>
           <t>почему приложение не открывается</t>
@@ -15023,7 +14889,6 @@
       <c r="C383" t="n">
         <v>5</v>
       </c>
-      <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr">
         <is>
           <t>Супер халық банк</t>
@@ -15062,7 +14927,6 @@
       <c r="C384" t="n">
         <v>5</v>
       </c>
-      <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr">
         <is>
           <t>супер</t>
@@ -15108,7 +14972,6 @@
       <c r="C386" t="n">
         <v>5</v>
       </c>
-      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr">
         <is>
           <t>👍</t>
@@ -15188,7 +15051,6 @@
       <c r="C387" t="n">
         <v>5</v>
       </c>
-      <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr">
         <is>
           <t>всё устраивает. срасибо</t>
@@ -15227,7 +15089,6 @@
       <c r="C388" t="n">
         <v>5</v>
       </c>
-      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr">
         <is>
           <t>Khoroshi Bank,</t>
@@ -15266,7 +15127,6 @@
       <c r="C389" t="n">
         <v>5</v>
       </c>
-      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr">
         <is>
           <t>очень классно пригодиться</t>
@@ -15277,7 +15137,6 @@
           <t>nuraly</t>
         </is>
       </c>
-      <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr">
         <is>
           <t>78ac57ca9f476cce3bd93f6a</t>
@@ -15301,7 +15160,6 @@
       <c r="C390" t="n">
         <v>5</v>
       </c>
-      <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr">
         <is>
           <t>👍</t>
@@ -15340,7 +15198,6 @@
       <c r="C391" t="n">
         <v>5</v>
       </c>
-      <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr">
         <is>
           <t>Отличный</t>
@@ -15379,7 +15236,6 @@
       <c r="C392" t="n">
         <v>5</v>
       </c>
-      <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr">
         <is>
           <t>спасибо за заботу и гарантию от неправомерных,неправильных или ошибочных действий</t>
@@ -15418,7 +15274,6 @@
       <c r="C393" t="n">
         <v>5</v>
       </c>
-      <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr">
         <is>
           <t>всё работает стабильно</t>
@@ -15457,7 +15312,6 @@
       <c r="C394" t="n">
         <v>5</v>
       </c>
-      <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr">
         <is>
           <t>😘❤️</t>
@@ -15496,7 +15350,6 @@
       <c r="C395" t="n">
         <v>5</v>
       </c>
-      <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr">
         <is>
           <t>керемет</t>
@@ -15535,7 +15388,6 @@
       <c r="C396" t="n">
         <v>5</v>
       </c>
-      <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr">
         <is>
           <t>избавьте от машенников</t>
@@ -15574,7 +15426,6 @@
       <c r="C397" t="n">
         <v>5</v>
       </c>
-      <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr">
         <is>
           <t>норма</t>
@@ -15613,7 +15464,7 @@
       <c r="C398" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D398" s="2" t="inlineStr"/>
+      <c r="D398" s="2" t="n"/>
       <c r="E398" s="2" t="inlineStr">
         <is>
           <t>Постоянно нужно удалять и скачивать заново. Самое худшее приложение из банковских.</t>
@@ -15624,7 +15475,7 @@
           <t>Евгений Дергилёв</t>
         </is>
       </c>
-      <c r="G398" s="2" t="inlineStr"/>
+      <c r="G398" s="2" t="n"/>
       <c r="H398" s="2" t="inlineStr">
         <is>
           <t>1b7aadc581b3b69886d93d01</t>
@@ -15648,7 +15499,6 @@
       <c r="C399" t="n">
         <v>5</v>
       </c>
-      <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr">
         <is>
           <t>оте кушти</t>
@@ -15659,7 +15509,6 @@
           <t>Абай Муратов</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr"/>
       <c r="H399" t="inlineStr">
         <is>
           <t>3865008f82af0ec3ed9e2f8a</t>
@@ -15683,7 +15532,6 @@
       <c r="C400" t="n">
         <v>5</v>
       </c>
-      <c r="D400" t="inlineStr"/>
       <c r="E400" t="inlineStr">
         <is>
           <t>Как надоело каждый день удалять. приложение и востонавливать</t>
@@ -15722,7 +15570,6 @@
       <c r="C401" t="n">
         <v>5</v>
       </c>
-      <c r="D401" t="inlineStr"/>
       <c r="E401" t="inlineStr">
         <is>
           <t>хороший банк меня устраивает.</t>
@@ -15761,7 +15608,6 @@
       <c r="C402" t="n">
         <v>5</v>
       </c>
-      <c r="D402" t="inlineStr"/>
       <c r="E402" t="inlineStr">
         <is>
           <t>Жабу емес,,,, қалу болуы керек</t>
@@ -15800,7 +15646,6 @@
       <c r="C403" t="n">
         <v>5</v>
       </c>
-      <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr">
         <is>
           <t>супер</t>
@@ -15839,7 +15684,6 @@
       <c r="C404" t="n">
         <v>5</v>
       </c>
-      <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr">
         <is>
           <t>классно 👍</t>
@@ -15878,7 +15722,7 @@
       <c r="C405" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D405" s="2" t="inlineStr"/>
+      <c r="D405" s="2" t="n"/>
       <c r="E405" s="2" t="inlineStr">
         <is>
           <t>спасения денежных средств с льготной карты по инвалидности распространение личных данных третьим лицам.</t>
@@ -15917,7 +15761,6 @@
       <c r="C406" t="n">
         <v>5</v>
       </c>
-      <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr">
         <is>
           <t>банк хороший всегда идут клиентам на встречу</t>
@@ -15956,7 +15799,6 @@
       <c r="C407" t="n">
         <v>5</v>
       </c>
-      <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr">
         <is>
           <t>круто</t>
@@ -15995,7 +15837,7 @@
       <c r="C408" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D408" s="2" t="inlineStr"/>
+      <c r="D408" s="2" t="n"/>
       <c r="E408" s="2" t="inlineStr">
         <is>
           <t>очень плохое приложение сильно остает от каспи</t>
@@ -16034,7 +15876,6 @@
       <c r="C409" t="n">
         <v>5</v>
       </c>
-      <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -16073,7 +15914,6 @@
       <c r="C410" t="n">
         <v>5</v>
       </c>
-      <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr">
         <is>
           <t>керемет</t>
@@ -16112,7 +15952,6 @@
       <c r="C411" t="n">
         <v>5</v>
       </c>
-      <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
           <t>все отлично работает</t>
@@ -16151,7 +15990,6 @@
       <c r="C412" t="n">
         <v>5</v>
       </c>
-      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
           <t>все отлично работает</t>
@@ -16190,7 +16028,7 @@
       <c r="C413" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D413" s="2" t="inlineStr"/>
+      <c r="D413" s="2" t="n"/>
       <c r="E413" s="2" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -16229,7 +16067,7 @@
       <c r="C414" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D414" s="2" t="inlineStr"/>
+      <c r="D414" s="2" t="n"/>
       <c r="E414" s="2" t="inlineStr">
         <is>
           <t>постоянно требует обнавления че за приложения?</t>
@@ -16268,7 +16106,6 @@
       <c r="C415" t="n">
         <v>5</v>
       </c>
-      <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr">
         <is>
           <t>Отличное понятное приложение!!!</t>
@@ -16307,7 +16144,6 @@
       <c r="C416" t="n">
         <v>5</v>
       </c>
-      <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
           <t>Обязательно нужно приложение для ПК. Получение поддержки вывести более доступно.</t>
@@ -16346,7 +16182,6 @@
       <c r="C417" t="n">
         <v>5</v>
       </c>
-      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
           <t>Круто</t>
@@ -16385,7 +16220,7 @@
       <c r="C418" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D418" s="2" t="inlineStr"/>
+      <c r="D418" s="2" t="n"/>
       <c r="E418" s="2" t="inlineStr">
         <is>
           <t>после обновления не могу зайти в приложение пишет удалите текущую версию что делать</t>
@@ -16424,7 +16259,6 @@
       <c r="C419" t="n">
         <v>5</v>
       </c>
-      <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr">
         <is>
           <t>круто хо</t>
@@ -16463,7 +16297,6 @@
       <c r="C420" t="n">
         <v>5</v>
       </c>
-      <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr">
         <is>
           <t>Хорошее</t>
@@ -16502,7 +16335,7 @@
       <c r="C421" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D421" s="2" t="inlineStr"/>
+      <c r="D421" s="2" t="n"/>
       <c r="E421" s="2" t="inlineStr">
         <is>
           <t>1. Карту закрыть в приложении невозможно. 2. Выписка непонятная, неудобная.</t>
@@ -16541,7 +16374,6 @@
       <c r="C422" t="n">
         <v>5</v>
       </c>
-      <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr">
         <is>
           <t>лучшее из лучших</t>
@@ -16580,7 +16412,6 @@
       <c r="C423" t="n">
         <v>5</v>
       </c>
-      <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr">
         <is>
           <t>супер</t>
@@ -16619,7 +16450,6 @@
       <c r="C424" t="n">
         <v>5</v>
       </c>
-      <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr">
         <is>
           <t>имба</t>
@@ -16658,7 +16488,6 @@
       <c r="C425" t="n">
         <v>5</v>
       </c>
-      <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -16697,7 +16526,6 @@
       <c r="C426" t="n">
         <v>5</v>
       </c>
-      <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
           <t>👍</t>
@@ -16736,7 +16564,6 @@
       <c r="C427" t="n">
         <v>5</v>
       </c>
-      <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr">
         <is>
           <t>Одно только замечание банку, научитесь вести диалог на равне с клиентом, и если по какой то причине вы будете блокировать счета, то заранее уведомите человека.</t>
@@ -16747,7 +16574,6 @@
           <t>shimshim mucha</t>
         </is>
       </c>
-      <c r="G427" t="inlineStr"/>
       <c r="H427" t="inlineStr">
         <is>
           <t>5d33910656d0ed91639005fe</t>
@@ -16771,7 +16597,6 @@
       <c r="C428" t="n">
         <v>5</v>
       </c>
-      <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
           <t>золотую корону только верните и цены вам не будет!</t>
@@ -16810,7 +16635,7 @@
       <c r="C429" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D429" s="2" t="inlineStr"/>
+      <c r="D429" s="2" t="n"/>
       <c r="E429" s="2" t="inlineStr">
         <is>
           <t>Мне не нравиться, что оплата, к примеру, кредита в не рабочее время не возможно, депозит открыть в не рабочее время не возможно, карточку три года назад выпустила, деньги снимают каждый год,консультанты объяснить не могут, моего мнения ни спрашивают, уведомили, деньги забрали, в наглую</t>
@@ -16849,7 +16674,6 @@
       <c r="C430" t="n">
         <v>5</v>
       </c>
-      <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
           <t>Классное приложение</t>
@@ -16888,7 +16712,6 @@
       <c r="C431" t="n">
         <v>5</v>
       </c>
-      <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
           <t>ясность и понятность..........</t>
@@ -16927,7 +16750,6 @@
       <c r="C432" t="n">
         <v>5</v>
       </c>
-      <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
           <t>Отлично</t>
@@ -16966,7 +16788,6 @@
       <c r="C433" t="n">
         <v>5</v>
       </c>
-      <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
           <t>Отлично</t>
@@ -17005,7 +16826,6 @@
       <c r="C434" t="n">
         <v>5</v>
       </c>
-      <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -17044,7 +16864,6 @@
       <c r="C435" t="n">
         <v>5</v>
       </c>
-      <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
           <t>отлично спасибо</t>
@@ -17055,7 +16874,6 @@
           <t>Вадим Игумнов</t>
         </is>
       </c>
-      <c r="G435" t="inlineStr"/>
       <c r="H435" t="inlineStr">
         <is>
           <t>648ea98a22d96be4fa2889e1</t>
@@ -17079,7 +16897,6 @@
       <c r="C436" t="n">
         <v>5</v>
       </c>
-      <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
           <t>өте керемет,қолдануға өте ыңғайлы</t>
@@ -17118,7 +16935,6 @@
       <c r="C437" t="n">
         <v>5</v>
       </c>
-      <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
           <t>Лучшие</t>
@@ -17157,7 +16973,7 @@
       <c r="C438" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D438" s="2" t="inlineStr"/>
+      <c r="D438" s="2" t="n"/>
       <c r="E438" s="2" t="inlineStr">
         <is>
           <t>Түсініксіз</t>
@@ -17203,7 +17019,7 @@
       <c r="C440" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D440" s="2" t="inlineStr"/>
+      <c r="D440" s="2" t="n"/>
       <c r="E440" s="2" t="inlineStr">
         <is>
           <t>уже сутки приложение не могу установить, после ввода номера телефона продолжение авторизации не следует, и это после очередной оповещательной, что надо обновить приложение, при этом означает полный его снос с устройства и это уже продолжается больше года, но сейчас вообще ни в какие ворота, просто ужас, сотрудники проблему решить не могут, перенаправили в поддержку, жду вашего объяснения.</t>
@@ -17283,7 +17099,7 @@
       <c r="C441" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D441" s="2" t="inlineStr"/>
+      <c r="D441" s="2" t="n"/>
       <c r="E441" s="2" t="inlineStr">
         <is>
           <t>просит обновить приложение хотя стоит последняя версия и не открывается</t>
@@ -17322,7 +17138,6 @@
       <c r="C442" t="n">
         <v>4</v>
       </c>
-      <c r="D442" t="inlineStr"/>
       <c r="E442" t="inlineStr">
         <is>
           <t>Отстаете от Каспий</t>
@@ -17361,7 +17176,6 @@
       <c r="C443" t="n">
         <v>5</v>
       </c>
-      <c r="D443" t="inlineStr"/>
       <c r="E443" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -17400,7 +17214,6 @@
       <c r="C444" t="n">
         <v>5</v>
       </c>
-      <c r="D444" t="inlineStr"/>
       <c r="E444" t="inlineStr">
         <is>
           <t>очень благодарна</t>
@@ -17439,7 +17252,6 @@
       <c r="C445" t="n">
         <v>5</v>
       </c>
-      <c r="D445" t="inlineStr"/>
       <c r="E445" t="inlineStr">
         <is>
           <t>😘</t>
@@ -17478,7 +17290,6 @@
       <c r="C446" t="n">
         <v>5</v>
       </c>
-      <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
           <t>удобно</t>
@@ -17517,7 +17328,6 @@
       <c r="C447" t="n">
         <v>5</v>
       </c>
-      <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
           <t>👍👍👍</t>
@@ -17556,7 +17366,6 @@
       <c r="C448" t="n">
         <v>5</v>
       </c>
-      <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
           <t>Супер</t>
@@ -17595,7 +17404,6 @@
       <c r="C449" t="n">
         <v>5</v>
       </c>
-      <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
           <t>👏</t>
@@ -17634,7 +17442,7 @@
       <c r="C450" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D450" s="2" t="inlineStr"/>
+      <c r="D450" s="2" t="n"/>
       <c r="E450" s="2" t="inlineStr">
         <is>
           <t>За навязчивость. Пришлось зайти т.к.реклама в Janatube не позволяла смотреть фильм. А раз зашёл, то поставил единичку.</t>
@@ -17673,7 +17481,6 @@
       <c r="C451" t="n">
         <v>5</v>
       </c>
-      <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
           <t>өте жақсы</t>
@@ -17712,7 +17519,6 @@
       <c r="C452" t="n">
         <v>5</v>
       </c>
-      <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
           <t>отличное обслужование</t>
@@ -17751,7 +17557,6 @@
       <c r="C453" t="n">
         <v>5</v>
       </c>
-      <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
           <t>Удобно,доступно.</t>
@@ -17790,7 +17595,6 @@
       <c r="C454" t="n">
         <v>5</v>
       </c>
-      <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
           <t>керемет</t>
@@ -17829,7 +17633,6 @@
       <c r="C455" t="n">
         <v>5</v>
       </c>
-      <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
           <t>Жақсы</t>
@@ -17868,7 +17671,6 @@
       <c r="C456" t="n">
         <v>5</v>
       </c>
-      <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
           <t>все отлично</t>
@@ -17907,7 +17709,6 @@
       <c r="C457" t="n">
         <v>5</v>
       </c>
-      <c r="D457" t="inlineStr"/>
       <c r="E457" t="inlineStr">
         <is>
           <t>Халық банкі жақсы атқарады,өз жұмысын.Рахмет</t>
@@ -17946,7 +17747,6 @@
       <c r="C458" t="n">
         <v>5</v>
       </c>
-      <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr">
         <is>
           <t>очень хороший банк</t>
@@ -17985,7 +17785,6 @@
       <c r="C459" t="n">
         <v>5</v>
       </c>
-      <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr">
         <is>
           <t>молодцы</t>
@@ -18024,7 +17823,7 @@
       <c r="C460" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D460" s="2" t="inlineStr"/>
+      <c r="D460" s="2" t="n"/>
       <c r="E460" s="2" t="inlineStr">
         <is>
           <t>штраф ПДД давно оплачен, а приложении висит до сих пор</t>
@@ -18063,7 +17862,6 @@
       <c r="C461" t="n">
         <v>5</v>
       </c>
-      <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr">
         <is>
           <t>отлично 👍</t>
@@ -18102,7 +17900,6 @@
       <c r="C462" t="n">
         <v>5</v>
       </c>
-      <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr">
         <is>
           <t>лучший банк</t>
@@ -18141,7 +17938,6 @@
       <c r="C463" t="n">
         <v>5</v>
       </c>
-      <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr">
         <is>
           <t>молодец ,,😘👍</t>
@@ -18180,7 +17976,6 @@
       <c r="C464" t="n">
         <v>5</v>
       </c>
-      <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr">
         <is>
           <t>всё отлично и удобно</t>
@@ -18219,7 +18014,6 @@
       <c r="C465" t="n">
         <v>4</v>
       </c>
-      <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr">
         <is>
           <t>иногда тормозит</t>
@@ -18258,7 +18052,7 @@
       <c r="C466" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D466" s="2" t="inlineStr"/>
+      <c r="D466" s="2" t="n"/>
       <c r="E466" s="2" t="inlineStr">
         <is>
           <t>к сожалению застраховал а/м в данной организации, снял с учёта а/м ч/з месяц, деньги не хотят возвращать, требуют справку о снятии с учёта, несмотря на то, что в техпаспорте стоит отметка о снятии с учёта. родственник, пенсионер, при дтп не дозвонился им, пришлось самому разбираться.</t>
@@ -18297,7 +18091,6 @@
       <c r="C467" t="n">
         <v>4</v>
       </c>
-      <c r="D467" t="inlineStr"/>
       <c r="E467" t="inlineStr">
         <is>
           <t>Плохо то, что любой перевод на свои карты в другие банки взимают процент. В остальном всё хорошо.</t>
@@ -18336,7 +18129,6 @@
       <c r="C468" t="n">
         <v>5</v>
       </c>
-      <c r="D468" t="inlineStr"/>
       <c r="E468" t="inlineStr">
         <is>
           <t>отл.</t>
@@ -18375,7 +18167,6 @@
       <c r="C469" t="n">
         <v>5</v>
       </c>
-      <c r="D469" t="inlineStr"/>
       <c r="E469" t="inlineStr">
         <is>
           <t>Удобное приложение. Самое главное для меня работает SAMSUNG PAY.</t>
@@ -18414,7 +18205,6 @@
       <c r="C470" t="n">
         <v>5</v>
       </c>
-      <c r="D470" t="inlineStr"/>
       <c r="E470" t="inlineStr">
         <is>
           <t>Отлично</t>
@@ -18453,7 +18243,7 @@
       <c r="C471" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D471" s="2" t="inlineStr"/>
+      <c r="D471" s="2" t="n"/>
       <c r="E471" s="2" t="inlineStr">
         <is>
           <t>Тормозит</t>
@@ -18492,7 +18282,6 @@
       <c r="C472" t="n">
         <v>5</v>
       </c>
-      <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
           <t>👍</t>
@@ -18531,7 +18320,6 @@
       <c r="C473" t="n">
         <v>5</v>
       </c>
-      <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
           <t>өте тамаша</t>
@@ -18570,7 +18358,7 @@
       <c r="C474" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D474" s="2" t="inlineStr"/>
+      <c r="D474" s="2" t="n"/>
       <c r="E474" s="2" t="inlineStr">
         <is>
           <t>С 2021 года пользовалась приложением, и меня, более чем, всё устраивало. Вчера, в целях безопасности, потребовали удалить приложение, и скачать заново. Обновить, как раньше, в гугл плэй нет возможности (почему?).Удалила, скачала, зарегистрировалась! И ! О ЧУДО!!! Сегодня приложение требует то же самое! Вы издеваетесь? Все платежи я произвожу ч/з приложение,т.к по состоянию здоровья не могу выйти из дома. И не могу проплатить за интернет, спасибо соседям за разрешение воспользоваться их Wi-Fi.</t>
@@ -18609,7 +18397,6 @@
       <c r="C475" t="n">
         <v>5</v>
       </c>
-      <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -18648,7 +18435,6 @@
       <c r="C476" t="n">
         <v>5</v>
       </c>
-      <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
           <t>удобно</t>
@@ -18687,7 +18473,6 @@
       <c r="C477" t="n">
         <v>5</v>
       </c>
-      <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
           <t>очень удобно ещё бы кредит довели воше цены не было бы</t>
@@ -18726,7 +18511,6 @@
       <c r="C478" t="n">
         <v>5</v>
       </c>
-      <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
         <is>
           <t>приложение рабочее,функциональное, необходимое для всех</t>
@@ -18765,7 +18549,6 @@
       <c r="C479" t="n">
         <v>5</v>
       </c>
-      <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
           <t>много лет вместе! уважаю!!!</t>
@@ -18804,7 +18587,6 @@
       <c r="C480" t="n">
         <v>5</v>
       </c>
-      <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
           <t>жақсы жасап,алға ұмтылыс бар,жаңаша өмірге құштар,керемет Халық Банк!</t>
@@ -18843,7 +18625,6 @@
       <c r="C481" t="n">
         <v>5</v>
       </c>
-      <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
           <t>Добавьте пожалуйста голосовое озвучивание команд при видеопроверке личности. Людям со слабым зрением тяжело пройти проверку самостоятельно</t>
@@ -18882,7 +18663,7 @@
       <c r="C482" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D482" s="2" t="inlineStr"/>
+      <c r="D482" s="2" t="n"/>
       <c r="E482" s="2" t="inlineStr">
         <is>
           <t>Обратился через неделю после первого обращения.Предложили подойти в отделение банка для уточнения. Скажите для каких уточнений?</t>
@@ -18893,7 +18674,7 @@
           <t>Станислав Тиханов</t>
         </is>
       </c>
-      <c r="G482" s="2" t="inlineStr"/>
+      <c r="G482" s="2" t="n"/>
       <c r="H482" s="2" t="inlineStr">
         <is>
           <t>888a532c58744d45ca70c288</t>
@@ -18917,7 +18698,6 @@
       <c r="C483" t="n">
         <v>5</v>
       </c>
-      <c r="D483" t="inlineStr"/>
       <c r="E483" t="inlineStr">
         <is>
           <t>все нормально на 5 звезд</t>
@@ -18956,7 +18736,7 @@
       <c r="C484" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D484" s="2" t="inlineStr"/>
+      <c r="D484" s="2" t="n"/>
       <c r="E484" s="2" t="inlineStr">
         <is>
           <t>постоянно требует обновления удалил и установил снова через день снова не надежныи источник удалите и где тепер скачать</t>
@@ -18995,7 +18775,7 @@
       <c r="C485" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D485" s="2" t="inlineStr"/>
+      <c r="D485" s="2" t="n"/>
       <c r="E485" s="2" t="inlineStr">
         <is>
           <t>долго грузиться</t>
@@ -19034,7 +18814,6 @@
       <c r="C486" t="n">
         <v>5</v>
       </c>
-      <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr">
         <is>
           <t>👍👍👍👍</t>
@@ -19073,7 +18852,6 @@
       <c r="C487" t="n">
         <v>5</v>
       </c>
-      <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr">
         <is>
           <t>хороший банк, и само приложение хорошо оптимизирован легко использовать</t>
@@ -19112,7 +18890,7 @@
       <c r="C488" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D488" s="2" t="inlineStr"/>
+      <c r="D488" s="2" t="n"/>
       <c r="E488" s="2" t="inlineStr">
         <is>
           <t>yrodi сделайте норм страховку без брокера....</t>
@@ -19151,7 +18929,6 @@
       <c r="C489" t="n">
         <v>5</v>
       </c>
-      <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -19190,7 +18967,6 @@
       <c r="C490" t="n">
         <v>5</v>
       </c>
-      <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
           <t>Верните Золотую корону.</t>
@@ -19229,7 +19005,6 @@
       <c r="C491" t="n">
         <v>5</v>
       </c>
-      <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr">
         <is>
           <t>молодцы</t>
@@ -19268,7 +19043,7 @@
       <c r="C492" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D492" s="2" t="inlineStr"/>
+      <c r="D492" s="2" t="n"/>
       <c r="E492" s="2" t="inlineStr">
         <is>
           <t>нельяз сделать заказ на озон</t>
@@ -19314,7 +19089,7 @@
       <c r="C494" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D494" s="2" t="inlineStr"/>
+      <c r="D494" s="2" t="n"/>
       <c r="E494" s="2" t="inlineStr">
         <is>
           <t>Приложениемен жұмыс істеу қиын боп жатыр,депозитіме ақша салайын десем аудара алмай отырмын уже 3 кун болды</t>
@@ -19394,7 +19169,6 @@
       <c r="C495" t="n">
         <v>5</v>
       </c>
-      <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr">
         <is>
           <t>Всё очень хорошо и удобно пользоваться приложением</t>
@@ -19474,7 +19248,6 @@
       <c r="C496" t="n">
         <v>5</v>
       </c>
-      <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr">
         <is>
           <t>Всё информативно и понятно.</t>
@@ -19554,7 +19327,6 @@
       <c r="C497" t="n">
         <v>5</v>
       </c>
-      <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
           <t>просто мне не одобряются рассрочки</t>
@@ -19593,7 +19365,6 @@
       <c r="C498" t="n">
         <v>5</v>
       </c>
-      <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr">
         <is>
           <t>удобно и понятно</t>
@@ -19632,7 +19403,6 @@
       <c r="C499" t="n">
         <v>5</v>
       </c>
-      <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
           <t>кушти</t>
@@ -19671,7 +19441,6 @@
       <c r="C500" t="n">
         <v>5</v>
       </c>
-      <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
           <t>супер</t>
@@ -19710,7 +19479,7 @@
       <c r="C501" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D501" s="2" t="inlineStr"/>
+      <c r="D501" s="2" t="n"/>
       <c r="E501" s="2" t="inlineStr">
         <is>
           <t>19ыншы гасырда калган банк сиякты перевод узак туседи ишинде тусиниксиз операторлар оз жумыстарын билмейди обратный связь жок обслуживание шамалы</t>
@@ -19749,7 +19518,7 @@
       <c r="C502" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D502" s="2" t="inlineStr"/>
+      <c r="D502" s="2" t="n"/>
       <c r="E502" s="2" t="inlineStr">
         <is>
           <t>третий день уже не могу изменить страховой полис приложение не работает, через сайт тоже пробовал бесполезно,</t>
@@ -19788,7 +19557,7 @@
       <c r="C503" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D503" s="2" t="inlineStr"/>
+      <c r="D503" s="2" t="n"/>
       <c r="E503" s="2" t="inlineStr">
         <is>
           <t>С RuStore после очередного обновления перестало работать. пришлось переустанавливать, после чего вылезла та же ошибка. заново пришлось удалять и скачивать от сюда. если ваше приложение можно скачивать только из одного источника - Google play, то пожалуйста не выкладывайте его в других магазинах и напишите это в описании приложения здесь. просмотрел первые 100-150 оценок и создалось впечатление, что рейтинг в 4,7 скорее всего чрезмерно накручен.</t>
@@ -19827,7 +19596,6 @@
       <c r="C504" t="n">
         <v>5</v>
       </c>
-      <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr">
         <is>
           <t>да нравится, удобно стало🤩</t>
@@ -19866,7 +19634,6 @@
       <c r="C505" t="n">
         <v>5</v>
       </c>
-      <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
           <t>Соңғы кезде жақсы өзгерістер болды қызметтермен пайдалану ыңғайлы</t>
@@ -19905,7 +19672,6 @@
       <c r="C506" t="n">
         <v>5</v>
       </c>
-      <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr">
         <is>
           <t>хорошо</t>
@@ -19944,7 +19710,6 @@
       <c r="C507" t="n">
         <v>5</v>
       </c>
-      <c r="D507" t="inlineStr"/>
       <c r="E507" t="inlineStr">
         <is>
           <t>күшті жақсы</t>
@@ -19983,7 +19748,6 @@
       <c r="C508" t="n">
         <v>5</v>
       </c>
-      <c r="D508" t="inlineStr"/>
       <c r="E508" t="inlineStr">
         <is>
           <t>Спасибо вам, всё быстро и оперативно! Держите марку!</t>
@@ -20022,7 +19786,7 @@
       <c r="C509" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D509" s="2" t="inlineStr"/>
+      <c r="D509" s="2" t="n"/>
       <c r="E509" s="2" t="inlineStr">
         <is>
           <t>самое отсталое приложение</t>
@@ -20061,7 +19825,6 @@
       <c r="C510" t="n">
         <v>5</v>
       </c>
-      <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr">
         <is>
           <t>отличное</t>
@@ -20100,7 +19863,6 @@
       <c r="C511" t="n">
         <v>5</v>
       </c>
-      <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr">
         <is>
           <t>удобно практично и качество отличное самого приложения</t>
@@ -20139,7 +19901,6 @@
       <c r="C512" t="n">
         <v>4</v>
       </c>
-      <c r="D512" t="inlineStr"/>
       <c r="E512" t="inlineStr">
         <is>
           <t>При оформлении договора обязательного страхования авто автоматически оформляется Каско лайт и помощь на дорогах, нужно это вынести так, что-бы было видно что выбираешь, а не прятать куда-то глубоко, что-бы отказаться от этой функции.</t>
@@ -20178,7 +19939,6 @@
       <c r="C513" t="n">
         <v>5</v>
       </c>
-      <c r="D513" t="inlineStr"/>
       <c r="E513" t="inlineStr">
         <is>
           <t>Барі жақсы күшті</t>
@@ -20217,7 +19977,6 @@
       <c r="C514" t="n">
         <v>5</v>
       </c>
-      <c r="D514" t="inlineStr"/>
       <c r="E514" t="inlineStr">
         <is>
           <t>Очень довольна приложением♥️</t>
@@ -20256,7 +20015,6 @@
       <c r="C515" t="n">
         <v>5</v>
       </c>
-      <c r="D515" t="inlineStr"/>
       <c r="E515" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -20295,7 +20053,6 @@
       <c r="C516" t="n">
         <v>5</v>
       </c>
-      <c r="D516" t="inlineStr"/>
       <c r="E516" t="inlineStr">
         <is>
           <t>Очень понравиться мне когда ступит деньги</t>
@@ -20334,7 +20091,6 @@
       <c r="C517" t="n">
         <v>5</v>
       </c>
-      <c r="D517" t="inlineStr"/>
       <c r="E517" t="inlineStr">
         <is>
           <t>спасибо вам Халык банк!!!</t>
@@ -20373,7 +20129,6 @@
       <c r="C518" t="n">
         <v>5</v>
       </c>
-      <c r="D518" t="inlineStr"/>
       <c r="E518" t="inlineStr">
         <is>
           <t>оте мыкты банк</t>
@@ -20412,7 +20167,6 @@
       <c r="C519" t="n">
         <v>5</v>
       </c>
-      <c r="D519" t="inlineStr"/>
       <c r="E519" t="inlineStr">
         <is>
           <t>керемет</t>
@@ -20451,7 +20205,6 @@
       <c r="C520" t="n">
         <v>5</v>
       </c>
-      <c r="D520" t="inlineStr"/>
       <c r="E520" t="inlineStr">
         <is>
           <t>Отлично</t>
@@ -20490,7 +20243,7 @@
       <c r="C521" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D521" s="2" t="inlineStr"/>
+      <c r="D521" s="2" t="n"/>
       <c r="E521" s="2" t="inlineStr">
         <is>
           <t>Сиздердин банктарынызда болганыма 15 жылдан асты 1,5 жыл бурын до срочна кредит жауып едим, енди кредит бермиди маган, сондыктан баска банке ауыссамба деп отырмын.</t>
@@ -20529,7 +20282,6 @@
       <c r="C522" t="n">
         <v>5</v>
       </c>
-      <c r="D522" t="inlineStr"/>
       <c r="E522" t="inlineStr">
         <is>
           <t>Halyk банк Супер!!!</t>
@@ -20568,7 +20320,6 @@
       <c r="C523" t="n">
         <v>5</v>
       </c>
-      <c r="D523" t="inlineStr"/>
       <c r="E523" t="inlineStr">
         <is>
           <t>хорошо</t>
@@ -20607,7 +20358,6 @@
       <c r="C524" t="n">
         <v>5</v>
       </c>
-      <c r="D524" t="inlineStr"/>
       <c r="E524" t="inlineStr">
         <is>
           <t>классно !!! удобно!!!</t>
@@ -20646,7 +20396,7 @@
       <c r="C525" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D525" s="2" t="inlineStr"/>
+      <c r="D525" s="2" t="n"/>
       <c r="E525" s="2" t="inlineStr">
         <is>
           <t>куда делась функция снятия денег по коду? раньше была сейчас этой функции нет в приложении</t>
@@ -20657,7 +20407,7 @@
           <t>Алина Шиленок</t>
         </is>
       </c>
-      <c r="G525" s="2" t="inlineStr"/>
+      <c r="G525" s="2" t="n"/>
       <c r="H525" s="2" t="inlineStr">
         <is>
           <t>15613e387ee08c90d98f6938</t>
@@ -20681,7 +20431,6 @@
       <c r="C526" t="n">
         <v>5</v>
       </c>
-      <c r="D526" t="inlineStr"/>
       <c r="E526" t="inlineStr">
         <is>
           <t>Халық банк тамаша жұмыс істейді</t>
@@ -20720,7 +20469,6 @@
       <c r="C527" t="n">
         <v>5</v>
       </c>
-      <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr">
         <is>
           <t>отличное приложение спасибо</t>
@@ -20759,7 +20507,6 @@
       <c r="C528" t="n">
         <v>5</v>
       </c>
-      <c r="D528" t="inlineStr"/>
       <c r="E528" t="inlineStr">
         <is>
           <t>Супер</t>
@@ -20798,7 +20545,6 @@
       <c r="C529" t="n">
         <v>5</v>
       </c>
-      <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr">
         <is>
           <t>Керемет</t>
@@ -20837,7 +20583,6 @@
       <c r="C530" t="n">
         <v>5</v>
       </c>
-      <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr">
         <is>
           <t>Очень хорошо</t>
@@ -20876,7 +20621,6 @@
       <c r="C531" t="n">
         <v>5</v>
       </c>
-      <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr">
         <is>
           <t>Халык банк супер</t>
@@ -20915,7 +20659,6 @@
       <c r="C532" t="n">
         <v>5</v>
       </c>
-      <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr">
         <is>
           <t>Всё удобно и хорошо</t>
@@ -20954,7 +20697,6 @@
       <c r="C533" t="n">
         <v>5</v>
       </c>
-      <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr">
         <is>
           <t>хорошое приложение, всё можно посмотреть,сколько на счету, и все справки, спасибо.</t>
@@ -20993,7 +20735,6 @@
       <c r="C534" t="n">
         <v>5</v>
       </c>
-      <c r="D534" t="inlineStr"/>
       <c r="E534" t="inlineStr">
         <is>
           <t>каждым днём луще</t>
@@ -21032,7 +20773,6 @@
       <c r="C535" t="n">
         <v>4</v>
       </c>
-      <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr">
         <is>
           <t>Банк хороший ! Но есть минус- комиссия за переводы на другие банки.</t>
@@ -21071,7 +20811,6 @@
       <c r="C536" t="n">
         <v>5</v>
       </c>
-      <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr">
         <is>
           <t>удобное приложение</t>
@@ -21110,7 +20849,6 @@
       <c r="C537" t="n">
         <v>5</v>
       </c>
-      <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr">
         <is>
           <t>быстро,удобно мен нравится</t>
@@ -21149,7 +20887,6 @@
       <c r="C538" t="n">
         <v>5</v>
       </c>
-      <c r="D538" t="inlineStr"/>
       <c r="E538" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -21188,7 +20925,6 @@
       <c r="C539" t="n">
         <v>5</v>
       </c>
-      <c r="D539" t="inlineStr"/>
       <c r="E539" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -21227,7 +20963,6 @@
       <c r="C540" t="n">
         <v>5</v>
       </c>
-      <c r="D540" t="inlineStr"/>
       <c r="E540" t="inlineStr">
         <is>
           <t>Всё как надо. Благодарю.</t>
@@ -21266,7 +21001,6 @@
       <c r="C541" t="n">
         <v>5</v>
       </c>
-      <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr">
         <is>
           <t>отличное приложение, все быстро и четко</t>
@@ -21305,7 +21039,6 @@
       <c r="C542" t="n">
         <v>5</v>
       </c>
-      <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr">
         <is>
           <t>имбуличка</t>
@@ -21344,7 +21077,6 @@
       <c r="C543" t="n">
         <v>5</v>
       </c>
-      <c r="D543" t="inlineStr"/>
       <c r="E543" t="inlineStr">
         <is>
           <t>отлично!</t>
@@ -21383,7 +21115,6 @@
       <c r="C544" t="n">
         <v>4</v>
       </c>
-      <c r="D544" t="inlineStr"/>
       <c r="E544" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -21422,7 +21153,6 @@
       <c r="C545" t="n">
         <v>5</v>
       </c>
-      <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr">
         <is>
           <t>Барлық төлемдерді төлеймін. өте жақсы.</t>
@@ -21461,7 +21191,7 @@
       <c r="C546" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D546" s="2" t="inlineStr"/>
+      <c r="D546" s="2" t="n"/>
       <c r="E546" s="2" t="inlineStr">
         <is>
           <t>сегодня хотел сделать страховку на авто,после обновы сделали хуже.просят не существующие документы,не смог сделать на 6 месяцев.а служба поддержки у них вообще отстой вацап отвечает через полдня,а звонить вообще бестолку.</t>
@@ -21500,7 +21230,6 @@
       <c r="C547" t="n">
         <v>5</v>
       </c>
-      <c r="D547" t="inlineStr"/>
       <c r="E547" t="inlineStr">
         <is>
           <t>хорошо</t>
@@ -21539,7 +21268,6 @@
       <c r="C548" t="n">
         <v>5</v>
       </c>
-      <c r="D548" t="inlineStr"/>
       <c r="E548" t="inlineStr">
         <is>
           <t>неделают ренфеносирование((((</t>
@@ -21578,7 +21306,7 @@
       <c r="C549" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D549" s="2" t="inlineStr"/>
+      <c r="D549" s="2" t="n"/>
       <c r="E549" s="2" t="inlineStr">
         <is>
           <t>плаха работает банк</t>
@@ -21617,7 +21345,6 @@
       <c r="C550" t="n">
         <v>5</v>
       </c>
-      <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr">
         <is>
           <t>Өте кушті</t>
@@ -21628,7 +21355,6 @@
           <t>Nursultan</t>
         </is>
       </c>
-      <c r="G550" t="inlineStr"/>
       <c r="H550" t="inlineStr">
         <is>
           <t>ad603c34c1c0f80ce62a6334</t>
@@ -21652,7 +21378,6 @@
       <c r="C551" t="n">
         <v>5</v>
       </c>
-      <c r="D551" t="inlineStr"/>
       <c r="E551" t="inlineStr">
         <is>
           <t>вот и кридит дал мне вообще супер будет</t>
@@ -21691,7 +21416,6 @@
       <c r="C552" t="n">
         <v>5</v>
       </c>
-      <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr">
         <is>
           <t>отлично работаете что я могу сказать особенно в инвест приложении</t>
@@ -21730,7 +21454,6 @@
       <c r="C553" t="n">
         <v>5</v>
       </c>
-      <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
           <t>отличное приложение, очень удобно, доступно, постоянно пользуюсь Спасибо банку!!!!</t>
@@ -21769,7 +21492,6 @@
       <c r="C554" t="n">
         <v>5</v>
       </c>
-      <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
         <is>
           <t>Отлично все работает</t>
@@ -21808,7 +21530,6 @@
       <c r="C555" t="n">
         <v>5</v>
       </c>
-      <c r="D555" t="inlineStr"/>
       <c r="E555" t="inlineStr">
         <is>
           <t>быстро, удобно и надежно.</t>
@@ -21847,7 +21568,6 @@
       <c r="C556" t="n">
         <v>4</v>
       </c>
-      <c r="D556" t="inlineStr"/>
       <c r="E556" t="inlineStr">
         <is>
           <t>все бы так хорошо. но без спроса с карты деньги снимать не праведьно</t>
@@ -21886,7 +21606,7 @@
       <c r="C557" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D557" s="2" t="inlineStr"/>
+      <c r="D557" s="2" t="n"/>
       <c r="E557" s="2" t="inlineStr">
         <is>
           <t>Очень дорогА стоимость пересылки средств в другие банки. И вообще много бюрократических проволОчек, увы, сталкивалась с этим.</t>
@@ -21925,7 +21645,6 @@
       <c r="C558" t="n">
         <v>5</v>
       </c>
-      <c r="D558" t="inlineStr"/>
       <c r="E558" t="inlineStr">
         <is>
           <t>Бәрі өте жақсы,қызмет көрсету жұмысына көңіліміз толады.</t>
@@ -21964,7 +21683,7 @@
       <c r="C559" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D559" s="2" t="inlineStr"/>
+      <c r="D559" s="2" t="n"/>
       <c r="E559" s="2" t="inlineStr">
         <is>
           <t>после обновления приложение не работает, просит удалить старое приложение и установить новое с официального сайта</t>
@@ -22003,7 +21722,6 @@
       <c r="C560" t="n">
         <v>5</v>
       </c>
-      <c r="D560" t="inlineStr"/>
       <c r="E560" t="inlineStr">
         <is>
           <t>Очень полезное приложение.Облегчает жизнь и экономит время.</t>
@@ -22042,7 +21760,6 @@
       <c r="C561" t="n">
         <v>4</v>
       </c>
-      <c r="D561" t="inlineStr"/>
       <c r="E561" t="inlineStr">
         <is>
           <t>🙋‍♂️ На сегодня всё устраивает 🤝</t>
@@ -22081,7 +21798,6 @@
       <c r="C562" t="n">
         <v>5</v>
       </c>
-      <c r="D562" t="inlineStr"/>
       <c r="E562" t="inlineStr">
         <is>
           <t>Отлично 10/10</t>
@@ -22120,7 +21836,6 @@
       <c r="C563" t="n">
         <v>5</v>
       </c>
-      <c r="D563" t="inlineStr"/>
       <c r="E563" t="inlineStr">
         <is>
           <t>Отличное приложение</t>
@@ -22159,7 +21874,6 @@
       <c r="C564" t="n">
         <v>5</v>
       </c>
-      <c r="D564" t="inlineStr"/>
       <c r="E564" t="inlineStr">
         <is>
           <t>отлично 👍</t>
@@ -22198,7 +21912,6 @@
       <c r="C565" t="n">
         <v>5</v>
       </c>
-      <c r="D565" t="inlineStr"/>
       <c r="E565" t="inlineStr">
         <is>
           <t>Народный Банк номер 1 в Казахстане!!!</t>
@@ -22237,7 +21950,6 @@
       <c r="C566" t="n">
         <v>5</v>
       </c>
-      <c r="D566" t="inlineStr"/>
       <c r="E566" t="inlineStr">
         <is>
           <t>Отличное приложение, удобно и быстро можно проверить поступление на карту и проверить свои расходы без посещения банка! Спасибо,Халык банку! Успехов и процветания!</t>
@@ -22276,7 +21988,6 @@
       <c r="C567" t="n">
         <v>5</v>
       </c>
-      <c r="D567" t="inlineStr"/>
       <c r="E567" t="inlineStr">
         <is>
           <t>Приложение очень удобное, понятное и быстро выполняет необходимые функции</t>
@@ -22315,7 +22026,6 @@
       <c r="C568" t="n">
         <v>5</v>
       </c>
-      <c r="D568" t="inlineStr"/>
       <c r="E568" t="inlineStr">
         <is>
           <t>Жаксы банк</t>
@@ -22354,7 +22064,6 @@
       <c r="C569" t="n">
         <v>5</v>
       </c>
-      <c r="D569" t="inlineStr"/>
       <c r="E569" t="inlineStr">
         <is>
           <t>сейчас стало удобно пользоваться</t>
@@ -22393,7 +22102,6 @@
       <c r="C570" t="n">
         <v>5</v>
       </c>
-      <c r="D570" t="inlineStr"/>
       <c r="E570" t="inlineStr">
         <is>
           <t>хорошее приложение</t>
@@ -22432,7 +22140,6 @@
       <c r="C571" t="n">
         <v>5</v>
       </c>
-      <c r="D571" t="inlineStr"/>
       <c r="E571" t="inlineStr">
         <is>
           <t>Спасибо большое очень удобно. переводить по номеру телефона.</t>
@@ -22471,7 +22178,6 @@
       <c r="C572" t="n">
         <v>5</v>
       </c>
-      <c r="D572" t="inlineStr"/>
       <c r="E572" t="inlineStr">
         <is>
           <t>super!</t>
@@ -22510,7 +22216,6 @@
       <c r="C573" t="n">
         <v>5</v>
       </c>
-      <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr">
         <is>
           <t>хорошее приложение</t>
@@ -22549,7 +22254,6 @@
       <c r="C574" t="n">
         <v>5</v>
       </c>
-      <c r="D574" t="inlineStr"/>
       <c r="E574" t="inlineStr">
         <is>
           <t>класс</t>
@@ -22560,7 +22264,6 @@
           <t>Жаннат Искон</t>
         </is>
       </c>
-      <c r="G574" t="inlineStr"/>
       <c r="H574" t="inlineStr">
         <is>
           <t>a723c7d1e9b99e7361a5f235</t>
@@ -22584,7 +22287,6 @@
       <c r="C575" t="n">
         <v>5</v>
       </c>
-      <c r="D575" t="inlineStr"/>
       <c r="E575" t="inlineStr">
         <is>
           <t>Ұнайды, дұрыс қызмет жасайды</t>
@@ -22623,7 +22325,6 @@
       <c r="C576" t="n">
         <v>5</v>
       </c>
-      <c r="D576" t="inlineStr"/>
       <c r="E576" t="inlineStr">
         <is>
           <t>отличное</t>
@@ -22662,7 +22363,7 @@
       <c r="C577" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D577" s="2" t="inlineStr"/>
+      <c r="D577" s="2" t="n"/>
       <c r="E577" s="2" t="inlineStr">
         <is>
           <t>Хорошо</t>
@@ -22701,7 +22402,6 @@
       <c r="C578" t="n">
         <v>5</v>
       </c>
-      <c r="D578" t="inlineStr"/>
       <c r="E578" t="inlineStr">
         <is>
           <t>супер</t>
@@ -22740,7 +22440,6 @@
       <c r="C579" t="n">
         <v>5</v>
       </c>
-      <c r="D579" t="inlineStr"/>
       <c r="E579" t="inlineStr">
         <is>
           <t>Ыңғайлы қолдану,жылдам төлеу. Бәрі түсінікті.</t>
@@ -22779,7 +22478,6 @@
       <c r="C580" t="n">
         <v>5</v>
       </c>
-      <c r="D580" t="inlineStr"/>
       <c r="E580" t="inlineStr">
         <is>
           <t>приложение очень удобное, понятное, проста и доступна. Настоящий Halyk-Народный, созданный для людей.</t>
@@ -22818,7 +22516,6 @@
       <c r="C581" t="n">
         <v>5</v>
       </c>
-      <c r="D581" t="inlineStr"/>
       <c r="E581" t="inlineStr">
         <is>
           <t>хорошего приложение</t>
@@ -22857,7 +22554,7 @@
       <c r="C582" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D582" s="2" t="inlineStr"/>
+      <c r="D582" s="2" t="n"/>
       <c r="E582" s="2" t="inlineStr">
         <is>
           <t>почему не уходит сообщение когда посмотришь выходишь из приложения, а значок показывает что непрочитано</t>
@@ -22896,7 +22593,7 @@
       <c r="C583" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D583" s="2" t="inlineStr"/>
+      <c r="D583" s="2" t="n"/>
       <c r="E583" s="2" t="inlineStr">
         <is>
           <t>зависает приложение почти каждый день технические работы</t>
@@ -22935,7 +22632,6 @@
       <c r="C584" t="n">
         <v>5</v>
       </c>
-      <c r="D584" t="inlineStr"/>
       <c r="E584" t="inlineStr">
         <is>
           <t>интересно и отлично</t>
@@ -22974,7 +22670,6 @@
       <c r="C585" t="n">
         <v>5</v>
       </c>
-      <c r="D585" t="inlineStr"/>
       <c r="E585" t="inlineStr">
         <is>
           <t>вам тоже спасибо большое</t>
@@ -23013,7 +22708,6 @@
       <c r="C586" t="n">
         <v>5</v>
       </c>
-      <c r="D586" t="inlineStr"/>
       <c r="E586" t="inlineStr">
         <is>
           <t>Круто</t>
@@ -23052,7 +22746,6 @@
       <c r="C587" t="n">
         <v>5</v>
       </c>
-      <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr">
         <is>
           <t>өте керемет</t>
@@ -23091,7 +22784,6 @@
       <c r="C588" t="n">
         <v>5</v>
       </c>
-      <c r="D588" t="inlineStr"/>
       <c r="E588" t="inlineStr">
         <is>
           <t>всё отлично</t>
@@ -23130,7 +22822,6 @@
       <c r="C589" t="n">
         <v>5</v>
       </c>
-      <c r="D589" t="inlineStr"/>
       <c r="E589" t="inlineStr">
         <is>
           <t>Удобно, понятно. Спасибо.</t>
@@ -23169,7 +22860,6 @@
       <c r="C590" t="n">
         <v>5</v>
       </c>
-      <c r="D590" t="inlineStr"/>
       <c r="E590" t="inlineStr">
         <is>
           <t>Ұнайды</t>
@@ -23208,7 +22898,6 @@
       <c r="C591" t="n">
         <v>5</v>
       </c>
-      <c r="D591" t="inlineStr"/>
       <c r="E591" t="inlineStr">
         <is>
           <t>Удобно, доступно и надежно.</t>
@@ -23247,7 +22936,7 @@
       <c r="C592" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D592" s="2" t="inlineStr"/>
+      <c r="D592" s="2" t="n"/>
       <c r="E592" s="2" t="inlineStr">
         <is>
           <t>Постоянно тормозит, медленно платежи проходят, переводы в другой банк идут больше 10 минут, а между своими счетами вынуждает выходить из программы - иначе денег на счёте не видно.</t>
@@ -23286,7 +22975,6 @@
       <c r="C593" t="n">
         <v>5</v>
       </c>
-      <c r="D593" t="inlineStr"/>
       <c r="E593" t="inlineStr">
         <is>
           <t>очень нравится 👍</t>
@@ -23325,7 +23013,6 @@
       <c r="C594" t="n">
         <v>5</v>
       </c>
-      <c r="D594" t="inlineStr"/>
       <c r="E594" t="inlineStr">
         <is>
           <t>отлично!👍👍👍👍</t>
@@ -23364,7 +23051,6 @@
       <c r="C595" t="n">
         <v>5</v>
       </c>
-      <c r="D595" t="inlineStr"/>
       <c r="E595" t="inlineStr">
         <is>
           <t>Всё отлично работает, спасибо!</t>
@@ -23403,7 +23089,6 @@
       <c r="C596" t="n">
         <v>5</v>
       </c>
-      <c r="D596" t="inlineStr"/>
       <c r="E596" t="inlineStr">
         <is>
           <t>квитанции по коммунальным платежам в Kaspibank оформлены лучше</t>
@@ -23442,7 +23127,6 @@
       <c r="C597" t="n">
         <v>5</v>
       </c>
-      <c r="D597" t="inlineStr"/>
       <c r="E597" t="inlineStr">
         <is>
           <t>Спасибо за вашу работу!</t>
@@ -23481,7 +23165,6 @@
       <c r="C598" t="n">
         <v>5</v>
       </c>
-      <c r="D598" t="inlineStr"/>
       <c r="E598" t="inlineStr">
         <is>
           <t>отлично ,</t>
@@ -23520,7 +23203,6 @@
       <c r="C599" t="n">
         <v>5</v>
       </c>
-      <c r="D599" t="inlineStr"/>
       <c r="E599" t="inlineStr">
         <is>
           <t>хорошее приложение удобное</t>
@@ -23559,7 +23241,6 @@
       <c r="C600" t="n">
         <v>5</v>
       </c>
-      <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr">
         <is>
           <t>Отличная работа!</t>
@@ -23598,7 +23279,6 @@
       <c r="C601" t="n">
         <v>5</v>
       </c>
-      <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr">
         <is>
           <t>очень удобно</t>
@@ -23637,7 +23317,7 @@
       <c r="C602" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D602" s="2" t="inlineStr"/>
+      <c r="D602" s="2" t="n"/>
       <c r="E602" s="2" t="inlineStr">
         <is>
           <t>норм</t>
@@ -23648,7 +23328,7 @@
           <t>Suleimen Abdramanov</t>
         </is>
       </c>
-      <c r="G602" s="2" t="inlineStr"/>
+      <c r="G602" s="2" t="n"/>
       <c r="H602" s="2" t="inlineStr">
         <is>
           <t>bead104f49d18eec36a1f4af</t>
@@ -23672,7 +23352,7 @@
       <c r="C603" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D603" s="2" t="inlineStr"/>
+      <c r="D603" s="2" t="n"/>
       <c r="E603" s="2" t="inlineStr">
         <is>
           <t>молоцы</t>
@@ -23711,7 +23391,6 @@
       <c r="C604" t="n">
         <v>5</v>
       </c>
-      <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr">
         <is>
           <t>мне нравиться халық банк</t>
@@ -23750,7 +23429,7 @@
       <c r="C605" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D605" s="2" t="inlineStr"/>
+      <c r="D605" s="2" t="n"/>
       <c r="E605" s="2" t="inlineStr">
         <is>
           <t>При просмотре выписок, не указано кому отправил. Просто время и какой то номер, который нам не понятно.</t>
@@ -23789,7 +23468,6 @@
       <c r="C606" t="n">
         <v>5</v>
       </c>
-      <c r="D606" t="inlineStr"/>
       <c r="E606" t="inlineStr">
         <is>
           <t>удобно</t>
@@ -23828,7 +23506,6 @@
       <c r="C607" t="n">
         <v>5</v>
       </c>
-      <c r="D607" t="inlineStr"/>
       <c r="E607" t="inlineStr">
         <is>
           <t>всё отлично!!!</t>
@@ -23867,7 +23544,6 @@
       <c r="C608" t="n">
         <v>5</v>
       </c>
-      <c r="D608" t="inlineStr"/>
       <c r="E608" t="inlineStr">
         <is>
           <t>керемет</t>
@@ -23906,7 +23582,6 @@
       <c r="C609" t="n">
         <v>5</v>
       </c>
-      <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr">
         <is>
           <t>внем все отлично</t>
@@ -23945,7 +23620,6 @@
       <c r="C610" t="n">
         <v>5</v>
       </c>
-      <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr">
         <is>
           <t>the best</t>
@@ -23984,7 +23658,6 @@
       <c r="C611" t="n">
         <v>5</v>
       </c>
-      <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr">
         <is>
           <t>отличная приложения пользуюсь ею очень давно эти две приложения самые лучшие для меня Халык и Каспи я ими полььзуюсь очень и очень давно можно сказать из первых новерное изночально желаю чтобв дальше развивались еще лучшее</t>
@@ -24023,7 +23696,6 @@
       <c r="C612" t="n">
         <v>5</v>
       </c>
-      <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr">
         <is>
           <t>Очень удобно и всё быстро</t>
@@ -24062,7 +23734,6 @@
       <c r="C613" t="n">
         <v>5</v>
       </c>
-      <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr">
         <is>
           <t>удобное</t>
@@ -24073,7 +23744,6 @@
           <t>Oleg</t>
         </is>
       </c>
-      <c r="G613" t="inlineStr"/>
       <c r="H613" t="inlineStr">
         <is>
           <t>1a0d961218b0e7e5dec11f45</t>
@@ -24097,7 +23767,6 @@
       <c r="C614" t="n">
         <v>5</v>
       </c>
-      <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr">
         <is>
           <t>не давали кредит ни где, а тут - дали, 100.000 правда только взял, а отдавать 160.000 как - то не особо приятно конечно, но они выручили. Спасибо</t>
@@ -24136,7 +23805,6 @@
       <c r="C615" t="n">
         <v>5</v>
       </c>
-      <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr">
         <is>
           <t>обновление системы Хренова</t>
@@ -24175,7 +23843,6 @@
       <c r="C616" t="n">
         <v>5</v>
       </c>
-      <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -24214,7 +23881,6 @@
       <c r="C617" t="n">
         <v>5</v>
       </c>
-      <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr">
         <is>
           <t>все отлично</t>
@@ -24253,7 +23919,6 @@
       <c r="C618" t="n">
         <v>5</v>
       </c>
-      <c r="D618" t="inlineStr"/>
       <c r="E618" t="inlineStr">
         <is>
           <t>Не в полном объёме использую приложения, пока разбираться времени нет. А так все что мне надо есть 👍</t>
@@ -24292,7 +23957,6 @@
       <c r="C619" t="n">
         <v>5</v>
       </c>
-      <c r="D619" t="inlineStr"/>
       <c r="E619" t="inlineStr">
         <is>
           <t>Лучший банк</t>
@@ -24331,7 +23995,6 @@
       <c r="C620" t="n">
         <v>5</v>
       </c>
-      <c r="D620" t="inlineStr"/>
       <c r="E620" t="inlineStr">
         <is>
           <t>удобный</t>
@@ -24370,7 +24033,6 @@
       <c r="C621" t="n">
         <v>5</v>
       </c>
-      <c r="D621" t="inlineStr"/>
       <c r="E621" t="inlineStr">
         <is>
           <t>Спасибо большое за отличную работу банка!</t>
@@ -24409,7 +24071,6 @@
       <c r="C622" t="n">
         <v>5</v>
       </c>
-      <c r="D622" t="inlineStr"/>
       <c r="E622" t="inlineStr">
         <is>
           <t>очен приятно</t>
@@ -24448,7 +24109,6 @@
       <c r="C623" t="n">
         <v>4</v>
       </c>
-      <c r="D623" t="inlineStr"/>
       <c r="E623" t="inlineStr">
         <is>
           <t>все хорошо. но инвестициях мало валютных пар. например, нет франков. почти нет облигаций.</t>
@@ -24487,7 +24147,6 @@
       <c r="C624" t="n">
         <v>5</v>
       </c>
-      <c r="D624" t="inlineStr"/>
       <c r="E624" t="inlineStr">
         <is>
           <t>хорошая 👍</t>
@@ -24526,7 +24185,7 @@
       <c r="C625" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D625" s="2" t="inlineStr"/>
+      <c r="D625" s="2" t="n"/>
       <c r="E625" s="2" t="inlineStr">
         <is>
           <t>зарплата поступает получаем через пол чиса</t>
@@ -24565,7 +24224,6 @@
       <c r="C626" t="n">
         <v>5</v>
       </c>
-      <c r="D626" t="inlineStr"/>
       <c r="E626" t="inlineStr">
         <is>
           <t>керемет</t>
@@ -24611,7 +24269,7 @@
       <c r="C628" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D628" s="2" t="inlineStr"/>
+      <c r="D628" s="2" t="n"/>
       <c r="E628" s="2" t="inlineStr">
         <is>
           <t>ненравится</t>
@@ -24691,7 +24349,7 @@
       <c r="C629" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D629" s="2" t="inlineStr"/>
+      <c r="D629" s="2" t="n"/>
       <c r="E629" s="2" t="inlineStr">
         <is>
           <t>Вываливается окно с требованием обновить приложение, хотя обновлений нет. Зато оценку попросили. Ну раз так, то держите</t>
@@ -24730,7 +24388,6 @@
       <c r="C630" t="n">
         <v>5</v>
       </c>
-      <c r="D630" t="inlineStr"/>
       <c r="E630" t="inlineStr">
         <is>
           <t>мне все нравится</t>
@@ -24769,7 +24426,6 @@
       <c r="C631" t="n">
         <v>5</v>
       </c>
-      <c r="D631" t="inlineStr"/>
       <c r="E631" t="inlineStr">
         <is>
           <t>Хороший банк удобный 👍</t>
@@ -24808,7 +24464,6 @@
       <c r="C632" t="n">
         <v>5</v>
       </c>
-      <c r="D632" t="inlineStr"/>
       <c r="E632" t="inlineStr">
         <is>
           <t>Удобное ,интуитивно понятное приложение.</t>
@@ -24847,7 +24502,6 @@
       <c r="C633" t="n">
         <v>5</v>
       </c>
-      <c r="D633" t="inlineStr"/>
       <c r="E633" t="inlineStr">
         <is>
           <t>класс</t>
@@ -24886,7 +24540,6 @@
       <c r="C634" t="n">
         <v>5</v>
       </c>
-      <c r="D634" t="inlineStr"/>
       <c r="E634" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -24925,7 +24578,6 @@
       <c r="C635" t="n">
         <v>5</v>
       </c>
-      <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr">
         <is>
           <t>очень классный и удобный</t>
@@ -24964,7 +24616,6 @@
       <c r="C636" t="n">
         <v>5</v>
       </c>
-      <c r="D636" t="inlineStr"/>
       <c r="E636" t="inlineStr">
         <is>
           <t>харошо</t>
@@ -25003,7 +24654,6 @@
       <c r="C637" t="n">
         <v>5</v>
       </c>
-      <c r="D637" t="inlineStr"/>
       <c r="E637" t="inlineStr">
         <is>
           <t>супер</t>
@@ -25042,7 +24692,6 @@
       <c r="C638" t="n">
         <v>5</v>
       </c>
-      <c r="D638" t="inlineStr"/>
       <c r="E638" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -25081,7 +24730,6 @@
       <c r="C639" t="n">
         <v>5</v>
       </c>
-      <c r="D639" t="inlineStr"/>
       <c r="E639" t="inlineStr">
         <is>
           <t>самый лучший</t>
@@ -25120,7 +24768,6 @@
       <c r="C640" t="n">
         <v>5</v>
       </c>
-      <c r="D640" t="inlineStr"/>
       <c r="E640" t="inlineStr">
         <is>
           <t>Мне нравится.</t>
@@ -25159,7 +24806,6 @@
       <c r="C641" t="n">
         <v>4</v>
       </c>
-      <c r="D641" t="inlineStr"/>
       <c r="E641" t="inlineStr">
         <is>
           <t>не нравится комиссия между банками РК</t>
@@ -25198,7 +24844,6 @@
       <c r="C642" t="n">
         <v>5</v>
       </c>
-      <c r="D642" t="inlineStr"/>
       <c r="E642" t="inlineStr">
         <is>
           <t>Очень вежливый персонал. Все операции проводяться быстро и все разъяснения понятны и приемлемы. Спасибо</t>
@@ -25237,7 +24882,6 @@
       <c r="C643" t="n">
         <v>5</v>
       </c>
-      <c r="D643" t="inlineStr"/>
       <c r="E643" t="inlineStr">
         <is>
           <t>Молодцы! Приложение стало намного лучше!</t>
@@ -25276,7 +24920,6 @@
       <c r="C644" t="n">
         <v>5</v>
       </c>
-      <c r="D644" t="inlineStr"/>
       <c r="E644" t="inlineStr">
         <is>
           <t>нормик</t>
@@ -25315,7 +24958,6 @@
       <c r="C645" t="n">
         <v>4</v>
       </c>
-      <c r="D645" t="inlineStr"/>
       <c r="E645" t="inlineStr">
         <is>
           <t>Приложение часто и густо подтормаживает</t>
@@ -25354,7 +24996,6 @@
       <c r="C646" t="n">
         <v>5</v>
       </c>
-      <c r="D646" t="inlineStr"/>
       <c r="E646" t="inlineStr">
         <is>
           <t>все очень удобно</t>
@@ -25393,7 +25034,6 @@
       <c r="C647" t="n">
         <v>5</v>
       </c>
-      <c r="D647" t="inlineStr"/>
       <c r="E647" t="inlineStr">
         <is>
           <t>ok</t>
@@ -25432,7 +25072,6 @@
       <c r="C648" t="n">
         <v>5</v>
       </c>
-      <c r="D648" t="inlineStr"/>
       <c r="E648" t="inlineStr">
         <is>
           <t>ещё бы кшбк за оплату картой былбы было-бы вобще отлично</t>
@@ -25471,7 +25110,6 @@
       <c r="C649" t="n">
         <v>5</v>
       </c>
-      <c r="D649" t="inlineStr"/>
       <c r="E649" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -25510,7 +25148,6 @@
       <c r="C650" t="n">
         <v>5</v>
       </c>
-      <c r="D650" t="inlineStr"/>
       <c r="E650" t="inlineStr">
         <is>
           <t>өте ыңғайлы</t>
@@ -25549,7 +25186,7 @@
       <c r="C651" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D651" s="2" t="inlineStr"/>
+      <c r="D651" s="2" t="n"/>
       <c r="E651" s="2" t="inlineStr">
         <is>
           <t>Добрый день! благодарю за такое доверие, но хотелось бы отметить приложение при открытии долго грузиться, и снимает деньги за обслуживание ежемесячное не смотря что зарплатные проект</t>
@@ -25588,7 +25225,7 @@
       <c r="C652" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D652" s="2" t="inlineStr"/>
+      <c r="D652" s="2" t="n"/>
       <c r="E652" s="2" t="inlineStr">
         <is>
           <t>ужасное ,все виснет! каждая операция занимает время,просто нервы сдают ,приходиться выходить и опять все повторять,идут наслоение одной строчки на другую,особенно в марките при выборе доставки,промучилвсь ,ели вышла из приложения и купила на каспий</t>
@@ -25627,7 +25264,6 @@
       <c r="C653" t="n">
         <v>5</v>
       </c>
-      <c r="D653" t="inlineStr"/>
       <c r="E653" t="inlineStr">
         <is>
           <t>оте жаксы</t>
@@ -25666,7 +25302,6 @@
       <c r="C654" t="n">
         <v>5</v>
       </c>
-      <c r="D654" t="inlineStr"/>
       <c r="E654" t="inlineStr">
         <is>
           <t>Ыңғайлы және қарапайым сосын комиссия аз алынады. Бір сөзбен айтқанда "Супер"</t>
@@ -25705,7 +25340,6 @@
       <c r="C655" t="n">
         <v>5</v>
       </c>
-      <c r="D655" t="inlineStr"/>
       <c r="E655" t="inlineStr">
         <is>
           <t>отличный</t>
@@ -25744,7 +25378,6 @@
       <c r="C656" t="n">
         <v>5</v>
       </c>
-      <c r="D656" t="inlineStr"/>
       <c r="E656" t="inlineStr">
         <is>
           <t>Здоровья всем вашим сотрудникам! Благодарю за прекрасную работу!</t>
@@ -25783,7 +25416,6 @@
       <c r="C657" t="n">
         <v>5</v>
       </c>
-      <c r="D657" t="inlineStr"/>
       <c r="E657" t="inlineStr">
         <is>
           <t>супер</t>
@@ -25822,7 +25454,6 @@
       <c r="C658" t="n">
         <v>5</v>
       </c>
-      <c r="D658" t="inlineStr"/>
       <c r="E658" t="inlineStr">
         <is>
           <t>Өте қаты үнайды</t>
@@ -25861,7 +25492,7 @@
       <c r="C659" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D659" s="2" t="inlineStr"/>
+      <c r="D659" s="2" t="n"/>
       <c r="E659" s="2" t="inlineStr">
         <is>
           <t>комисия слишком большая. почему ? не должно быть комисии при пепеводе. все банки же казакстана!!!</t>
@@ -25900,7 +25531,6 @@
       <c r="C660" t="n">
         <v>5</v>
       </c>
-      <c r="D660" t="inlineStr"/>
       <c r="E660" t="inlineStr">
         <is>
           <t>Ынғайлы қолданғанға</t>
@@ -25939,7 +25569,7 @@
       <c r="C661" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D661" s="2" t="inlineStr"/>
+      <c r="D661" s="2" t="n"/>
       <c r="E661" s="2" t="inlineStr">
         <is>
           <t>Хочу удалить</t>
@@ -25978,7 +25608,6 @@
       <c r="C662" t="n">
         <v>5</v>
       </c>
-      <c r="D662" t="inlineStr"/>
       <c r="E662" t="inlineStr">
         <is>
           <t>самый лучше банк халык банк</t>
@@ -26017,7 +25646,6 @@
       <c r="C663" t="n">
         <v>5</v>
       </c>
-      <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr">
         <is>
           <t>Очень удобно, спасибо</t>
@@ -26056,7 +25684,6 @@
       <c r="C664" t="n">
         <v>5</v>
       </c>
-      <c r="D664" t="inlineStr"/>
       <c r="E664" t="inlineStr">
         <is>
           <t>спасибо за услугу 🤝</t>
@@ -26095,7 +25722,6 @@
       <c r="C665" t="n">
         <v>5</v>
       </c>
-      <c r="D665" t="inlineStr"/>
       <c r="E665" t="inlineStr">
         <is>
           <t>качество отличное молодци</t>
@@ -26134,7 +25760,6 @@
       <c r="C666" t="n">
         <v>5</v>
       </c>
-      <c r="D666" t="inlineStr"/>
       <c r="E666" t="inlineStr">
         <is>
           <t>все отлично.</t>
@@ -26173,7 +25798,7 @@
       <c r="C667" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D667" s="2" t="inlineStr"/>
+      <c r="D667" s="2" t="n"/>
       <c r="E667" s="2" t="inlineStr">
         <is>
           <t>Здравствуйте, я плохо вижу.Аосле нескольких попыток входа. Не могу больше зайти в личный кабинет. Удалил приложение, установил заново. Прохожу регистрацию, номер, дата рождения. НАЖИМАЮ Далее не активно. Как мне восстановить доступ?</t>
@@ -26212,7 +25837,7 @@
       <c r="C668" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D668" s="2" t="inlineStr"/>
+      <c r="D668" s="2" t="n"/>
       <c r="E668" s="2" t="inlineStr">
         <is>
           <t>как надоело постоянно что-то придумает чтобы деньги удержать. сегодня 1000 тенге удержалась за что думаешь))) 2024 году карту меняли за это говорят 2 года прошло они как ракеты ворует</t>
@@ -26251,7 +25876,6 @@
       <c r="C669" t="n">
         <v>5</v>
       </c>
-      <c r="D669" t="inlineStr"/>
       <c r="E669" t="inlineStr">
         <is>
           <t>отлично да</t>
@@ -26290,7 +25914,6 @@
       <c r="C670" t="n">
         <v>5</v>
       </c>
-      <c r="D670" t="inlineStr"/>
       <c r="E670" t="inlineStr">
         <is>
           <t>хорошо 👍</t>
@@ -26301,7 +25924,6 @@
           <t>Madi Нуриденулы</t>
         </is>
       </c>
-      <c r="G670" t="inlineStr"/>
       <c r="H670" t="inlineStr">
         <is>
           <t>57482bdc9df7cfa02c5dd22d</t>
@@ -26325,7 +25947,6 @@
       <c r="C671" t="n">
         <v>5</v>
       </c>
-      <c r="D671" t="inlineStr"/>
       <c r="E671" t="inlineStr">
         <is>
           <t>💪💪💪💪💪💪</t>
@@ -26364,7 +25985,6 @@
       <c r="C672" t="n">
         <v>5</v>
       </c>
-      <c r="D672" t="inlineStr"/>
       <c r="E672" t="inlineStr">
         <is>
           <t>отличная работа</t>
@@ -26403,7 +26023,6 @@
       <c r="C673" t="n">
         <v>5</v>
       </c>
-      <c r="D673" t="inlineStr"/>
       <c r="E673" t="inlineStr">
         <is>
           <t>хорош вовсем</t>
@@ -26442,7 +26061,6 @@
       <c r="C674" t="n">
         <v>5</v>
       </c>
-      <c r="D674" t="inlineStr"/>
       <c r="E674" t="inlineStr">
         <is>
           <t>хороший банк, удобное приложение, единственный минус для иностранцев - это жёсткие лимиты на суточные переводы и снятие наличных. Тут 50 на 50, с одной стороны безопасность с другой стороны сильно подставляет, когда условно ты должен заплатить за аренду квартиры, а тебе лимиты не позволяют снять больше денег.</t>
@@ -26488,7 +26106,6 @@
       <c r="C676" t="n">
         <v>5</v>
       </c>
-      <c r="D676" t="inlineStr"/>
       <c r="E676" t="inlineStr">
         <is>
           <t>спасибо</t>
@@ -26568,7 +26185,6 @@
       <c r="C677" t="n">
         <v>5</v>
       </c>
-      <c r="D677" t="inlineStr"/>
       <c r="E677" t="inlineStr">
         <is>
           <t>Мне нравится очень нравится!</t>
@@ -26579,7 +26195,6 @@
           <t>Гулнур Аманбаева</t>
         </is>
       </c>
-      <c r="G677" t="inlineStr"/>
       <c r="H677" t="inlineStr">
         <is>
           <t>b2d89c04eabdcc8a79864d03</t>
@@ -26603,7 +26218,6 @@
       <c r="C678" t="n">
         <v>5</v>
       </c>
-      <c r="D678" t="inlineStr"/>
       <c r="E678" t="inlineStr">
         <is>
           <t>ок</t>
@@ -26642,7 +26256,7 @@
       <c r="C679" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D679" s="2" t="inlineStr"/>
+      <c r="D679" s="2" t="n"/>
       <c r="E679" s="2" t="inlineStr">
         <is>
           <t>дурацкое приложение. пробовал совершить перевод со своего счета на свой счет в зарубежном банке - пишет "счет арестован". поехал в отделение - сказали нет ниикаких арестов, попробуйе снять лимиты. снял лимиты пробую перевести на зарубежную карту всего лишь 700$- пишет "операция не возможна - обратитесь в колл-центр". Звоню туда - там ступор - "ну мы не в еурсе отправим заявеу в тех поддержку - ждите ответ 3 дня..." Кто вам пишет это приложение ? Папуасы какие-то?</t>
@@ -26681,7 +26295,6 @@
       <c r="C680" t="n">
         <v>5</v>
       </c>
-      <c r="D680" t="inlineStr"/>
       <c r="E680" t="inlineStr">
         <is>
           <t>Круто</t>
@@ -26720,7 +26333,6 @@
       <c r="C681" t="n">
         <v>5</v>
       </c>
-      <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr">
         <is>
           <t>Приложение Halyk меня устраивает всё понятно и доступно. Спасибо большое разработчикам данного приложения.</t>
@@ -26759,7 +26371,6 @@
       <c r="C682" t="n">
         <v>5</v>
       </c>
-      <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr">
         <is>
           <t>Меня вполне все устраивает.</t>
@@ -26798,7 +26409,6 @@
       <c r="C683" t="n">
         <v>5</v>
       </c>
-      <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr">
         <is>
           <t>Да, нравится</t>
@@ -26837,7 +26447,6 @@
       <c r="C684" t="n">
         <v>5</v>
       </c>
-      <c r="D684" t="inlineStr"/>
       <c r="E684" t="inlineStr">
         <is>
           <t>рахмет</t>
@@ -26876,7 +26485,6 @@
       <c r="C685" t="n">
         <v>5</v>
       </c>
-      <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr">
         <is>
           <t>класно</t>
@@ -26915,7 +26523,6 @@
       <c r="C686" t="n">
         <v>4</v>
       </c>
-      <c r="D686" t="inlineStr"/>
       <c r="E686" t="inlineStr">
         <is>
           <t>Можете сделать отображение примерной стоимости металл счета в тенге? Было бы удобно</t>
@@ -26954,7 +26561,7 @@
       <c r="C687" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D687" s="2" t="inlineStr"/>
+      <c r="D687" s="2" t="n"/>
       <c r="E687" s="2" t="inlineStr">
         <is>
           <t>Чат-бот у вас не важно отвечает на вопросы</t>
@@ -26993,7 +26600,6 @@
       <c r="C688" t="n">
         <v>5</v>
       </c>
-      <c r="D688" t="inlineStr"/>
       <c r="E688" t="inlineStr">
         <is>
           <t>Все продумано и удобно в использовании</t>
@@ -27032,7 +26638,6 @@
       <c r="C689" t="n">
         <v>5</v>
       </c>
-      <c r="D689" t="inlineStr"/>
       <c r="E689" t="inlineStr">
         <is>
           <t>Сделайте открытие текущих счётов ьез карты как раньше.</t>
@@ -27078,7 +26683,6 @@
       <c r="C691" t="n">
         <v>5</v>
       </c>
-      <c r="D691" t="inlineStr"/>
       <c r="E691" t="inlineStr">
         <is>
           <t>👍</t>
@@ -27158,7 +26762,6 @@
       <c r="C692" t="n">
         <v>5</v>
       </c>
-      <c r="D692" t="inlineStr"/>
       <c r="E692" t="inlineStr">
         <is>
           <t>супер</t>
@@ -27238,7 +26841,6 @@
       <c r="C693" t="n">
         <v>5</v>
       </c>
-      <c r="D693" t="inlineStr"/>
       <c r="E693" t="inlineStr">
         <is>
           <t>Респект</t>
@@ -27277,7 +26879,6 @@
       <c r="C694" t="n">
         <v>5</v>
       </c>
-      <c r="D694" t="inlineStr"/>
       <c r="E694" t="inlineStr">
         <is>
           <t>спасибо очень нравится</t>
@@ -27316,7 +26917,7 @@
       <c r="C695" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D695" s="2" t="inlineStr"/>
+      <c r="D695" s="2" t="n"/>
       <c r="E695" s="2" t="inlineStr">
         <is>
           <t>Надоело постоянно удалять приложение, чтобы обновить его! Сколько можно проходить верификацию? Это единственное прилодение, которое требует таких танцев с бубнами :(</t>
@@ -27355,7 +26956,6 @@
       <c r="C696" t="n">
         <v>5</v>
       </c>
-      <c r="D696" t="inlineStr"/>
       <c r="E696" t="inlineStr">
         <is>
           <t>ок</t>
@@ -27394,7 +26994,6 @@
       <c r="C697" t="n">
         <v>5</v>
       </c>
-      <c r="D697" t="inlineStr"/>
       <c r="E697" t="inlineStr">
         <is>
           <t>Оте керемет</t>
@@ -27433,7 +27032,6 @@
       <c r="C698" t="n">
         <v>5</v>
       </c>
-      <c r="D698" t="inlineStr"/>
       <c r="E698" t="inlineStr">
         <is>
           <t>ұнайды өзіме. молодцы. жақсылап жұмыс істеңдер.</t>
@@ -27472,7 +27070,6 @@
       <c r="C699" t="n">
         <v>5</v>
       </c>
-      <c r="D699" t="inlineStr"/>
       <c r="E699" t="inlineStr">
         <is>
           <t>маған ұнады рахмет. колжетымды банк</t>
@@ -27511,7 +27108,6 @@
       <c r="C700" t="n">
         <v>5</v>
       </c>
-      <c r="D700" t="inlineStr"/>
       <c r="E700" t="inlineStr">
         <is>
           <t>приложения хорошое меня пока все устраивает</t>
@@ -27550,7 +27146,6 @@
       <c r="C701" t="n">
         <v>5</v>
       </c>
-      <c r="D701" t="inlineStr"/>
       <c r="E701" t="inlineStr">
         <is>
           <t>Супер прилржение! №2 в Казахстане!</t>
@@ -27589,7 +27184,6 @@
       <c r="C702" t="n">
         <v>5</v>
       </c>
-      <c r="D702" t="inlineStr"/>
       <c r="E702" t="inlineStr">
         <is>
           <t>Хорошо</t>
@@ -27628,7 +27222,6 @@
       <c r="C703" t="n">
         <v>5</v>
       </c>
-      <c r="D703" t="inlineStr"/>
       <c r="E703" t="inlineStr">
         <is>
           <t>все отлично</t>
@@ -27667,7 +27260,6 @@
       <c r="C704" t="n">
         <v>5</v>
       </c>
-      <c r="D704" t="inlineStr"/>
       <c r="E704" t="inlineStr">
         <is>
           <t>Удобно, понятно и доступно</t>
@@ -27706,7 +27298,6 @@
       <c r="C705" t="n">
         <v>5</v>
       </c>
-      <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr">
         <is>
           <t>спасибо за работу!</t>
@@ -27745,7 +27336,6 @@
       <c r="C706" t="n">
         <v>5</v>
       </c>
-      <c r="D706" t="inlineStr"/>
       <c r="E706" t="inlineStr">
         <is>
           <t>отличная приложение</t>
@@ -27784,7 +27374,6 @@
       <c r="C707" t="n">
         <v>5</v>
       </c>
-      <c r="D707" t="inlineStr"/>
       <c r="E707" t="inlineStr">
         <is>
           <t>Все хорошо, спасибо!!!</t>
@@ -27823,7 +27412,6 @@
       <c r="C708" t="n">
         <v>4</v>
       </c>
-      <c r="D708" t="inlineStr"/>
       <c r="E708" t="inlineStr">
         <is>
           <t>хороший банк но иногда долго грузится</t>
@@ -27862,7 +27450,7 @@
       <c r="C709" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D709" s="2" t="inlineStr"/>
+      <c r="D709" s="2" t="n"/>
       <c r="E709" s="2" t="inlineStr">
         <is>
           <t>постоянно требует обновления, плохо работает,</t>
@@ -27873,7 +27461,7 @@
           <t>кυмα</t>
         </is>
       </c>
-      <c r="G709" s="2" t="inlineStr"/>
+      <c r="G709" s="2" t="n"/>
       <c r="H709" s="2" t="inlineStr">
         <is>
           <t>a7068a88f10561e72e133a59</t>
@@ -27904,7 +27492,7 @@
       <c r="C711" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D711" s="2" t="inlineStr"/>
+      <c r="D711" s="2" t="n"/>
       <c r="E711" s="2" t="inlineStr">
         <is>
           <t>Самый отвратительный банк в стране. Сотрудники ничего не знают, приходится по сто раз уточнять. В базе не видно, ой то, ой пятое десятое. приложение вечно тупит, не заходит, долго грузит, переводы или платежи порой такие долгие. Раздражает ещё тот факт, что многие организации сотрудничают с этим банком и нужно открывать заработный счёт. Видимо комиссии за обслуживание маленькие в этом банке. Если бы не работа, никогда в жизни бы вашим банком не пользовался, такой опущенный банк, слов нет.</t>
@@ -27943,7 +27531,6 @@
       <c r="C712" t="n">
         <v>5</v>
       </c>
-      <c r="D712" t="inlineStr"/>
       <c r="E712" t="inlineStr">
         <is>
           <t>хорошо</t>
@@ -27982,7 +27569,6 @@
       <c r="C713" t="n">
         <v>5</v>
       </c>
-      <c r="D713" t="inlineStr"/>
       <c r="E713" t="inlineStr">
         <is>
           <t>хорошее обслуживание, и процентная ставка по депозитам</t>
@@ -28021,7 +27607,7 @@
       <c r="C714" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D714" s="2" t="inlineStr"/>
+      <c r="D714" s="2" t="n"/>
       <c r="E714" s="2" t="inlineStr">
         <is>
           <t>во время не приходят саобщения</t>
@@ -28060,7 +27646,6 @@
       <c r="C715" t="n">
         <v>5</v>
       </c>
-      <c r="D715" t="inlineStr"/>
       <c r="E715" t="inlineStr">
         <is>
           <t>все отлично</t>
@@ -28099,7 +27684,6 @@
       <c r="C716" t="n">
         <v>5</v>
       </c>
-      <c r="D716" t="inlineStr"/>
       <c r="E716" t="inlineStr">
         <is>
           <t>все хорошо и понятно!</t>
@@ -28138,7 +27722,6 @@
       <c r="C717" t="n">
         <v>5</v>
       </c>
-      <c r="D717" t="inlineStr"/>
       <c r="E717" t="inlineStr">
         <is>
           <t>жақсарып келеді</t>
@@ -28177,7 +27760,7 @@
       <c r="C718" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D718" s="2" t="inlineStr"/>
+      <c r="D718" s="2" t="n"/>
       <c r="E718" s="2" t="inlineStr">
         <is>
           <t>В разделе "операции по счетам" после каждой совершённой операции должен быть остаток денежных средств, чтобы можно было проконтролировать корректное списание. Также остаток денежных средств после списания должен отображаться во всплывающих уведомлениях. Раньше в вашем приложении всё это было. Почему убрали??? По этому поводу уже неоднократно звонила в ваш банк. И не только я звонила - многие клиенты жалуются на эту проблему. Вам и в отзывах об этом пишут. Когда внесёте исправления???</t>
@@ -28216,7 +27799,6 @@
       <c r="C719" t="n">
         <v>5</v>
       </c>
-      <c r="D719" t="inlineStr"/>
       <c r="E719" t="inlineStr">
         <is>
           <t>отличное приложение. Спасибо за хорошее обслуживание.</t>
@@ -28255,7 +27837,7 @@
       <c r="C720" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D720" s="2" t="inlineStr"/>
+      <c r="D720" s="2" t="n"/>
       <c r="E720" s="2" t="inlineStr">
         <is>
           <t>платёж был 34307, вы ещё 500 тенге комиссию сдержали. как так? главное если бы перевод,я через кассу платила. возмущена😔</t>
@@ -28294,7 +27876,6 @@
       <c r="C721" t="n">
         <v>5</v>
       </c>
-      <c r="D721" t="inlineStr"/>
       <c r="E721" t="inlineStr">
         <is>
           <t>Да очень удобно</t>
@@ -28333,7 +27914,6 @@
       <c r="C722" t="n">
         <v>5</v>
       </c>
-      <c r="D722" t="inlineStr"/>
       <c r="E722" t="inlineStr">
         <is>
           <t>удобно, бонусы, депозиты ещё больше усовершенствуйте будем вам благодарны, чтобы было лучше чем каспий, ведь вы народный банк</t>
@@ -28372,7 +27952,7 @@
       <c r="C723" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D723" s="2" t="inlineStr"/>
+      <c r="D723" s="2" t="n"/>
       <c r="E723" s="2" t="inlineStr">
         <is>
           <t>худшее приложение. страхование авто добавить водителя уже 2 месяца не можем. Колл центр ничего кроме как обновите приложение не решает. даже жалобу на дочернюю страховую компанию не принимают. Так как эта страховая не берет трубки. колл центр 797 платный и тоже не берет трубку. Просто беспредел.</t>
@@ -28411,7 +27991,7 @@
       <c r="C724" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D724" s="2" t="inlineStr"/>
+      <c r="D724" s="2" t="n"/>
       <c r="E724" s="2" t="inlineStr">
         <is>
           <t>приложение кривое, не могу переоформить страховку, по пол часа жду соединения с оператором они постоянно говорят попробуйте позже, зачем нужно приложение если оператор говорит попробуйте через компьютер, хотя там тоже нечего не работает</t>
@@ -28450,7 +28030,7 @@
       <c r="C725" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D725" s="2" t="inlineStr"/>
+      <c r="D725" s="2" t="n"/>
       <c r="E725" s="2" t="inlineStr">
         <is>
           <t>обслуживание на 0. До оператора не дозвониться.</t>
@@ -28489,7 +28069,6 @@
       <c r="C726" t="n">
         <v>5</v>
       </c>
-      <c r="D726" t="inlineStr"/>
       <c r="E726" t="inlineStr">
         <is>
           <t>Отлично Благодарю</t>
@@ -28528,7 +28107,7 @@
       <c r="C727" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D727" s="2" t="inlineStr"/>
+      <c r="D727" s="2" t="n"/>
       <c r="E727" s="2" t="inlineStr">
         <is>
           <t>почему кредит не дают?</t>
@@ -28567,7 +28146,6 @@
       <c r="C728" t="n">
         <v>5</v>
       </c>
-      <c r="D728" t="inlineStr"/>
       <c r="E728" t="inlineStr">
         <is>
           <t>қызмет көрсету сапасы өте жоғары.ризамын.қызметтерініз өсіп ,табыстарыныз хайырлы берекелді болсын.</t>
@@ -28606,7 +28184,6 @@
       <c r="C729" t="n">
         <v>5</v>
       </c>
-      <c r="D729" t="inlineStr"/>
       <c r="E729" t="inlineStr">
         <is>
           <t>Супер</t>
@@ -28645,7 +28222,6 @@
       <c r="C730" t="n">
         <v>5</v>
       </c>
-      <c r="D730" t="inlineStr"/>
       <c r="E730" t="inlineStr">
         <is>
           <t>удобно, информативно.</t>
@@ -28684,7 +28260,6 @@
       <c r="C731" t="n">
         <v>5</v>
       </c>
-      <c r="D731" t="inlineStr"/>
       <c r="E731" t="inlineStr">
         <is>
           <t>Нормальное приложение. По инвестициям бы обучение более подробное. Спасибо</t>
@@ -28723,7 +28298,6 @@
       <c r="C732" t="n">
         <v>5</v>
       </c>
-      <c r="D732" t="inlineStr"/>
       <c r="E732" t="inlineStr">
         <is>
           <t>всё отлично работает</t>
@@ -28762,7 +28336,6 @@
       <c r="C733" t="n">
         <v>5</v>
       </c>
-      <c r="D733" t="inlineStr"/>
       <c r="E733" t="inlineStr">
         <is>
           <t>все отлично!👍</t>
@@ -28801,7 +28374,7 @@
       <c r="C734" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D734" s="2" t="inlineStr"/>
+      <c r="D734" s="2" t="n"/>
       <c r="E734" s="2" t="inlineStr">
         <is>
           <t>Здравствуйте .Почему это приложение не патоиает на телефоне . Раньше работало приложение. Разработчик . Как можно занова установить приложение?</t>
@@ -28840,7 +28413,6 @@
       <c r="C735" t="n">
         <v>5</v>
       </c>
-      <c r="D735" t="inlineStr"/>
       <c r="E735" t="inlineStr">
         <is>
           <t>классное приложение👍💯</t>
@@ -28879,7 +28451,6 @@
       <c r="C736" t="n">
         <v>5</v>
       </c>
-      <c r="D736" t="inlineStr"/>
       <c r="E736" t="inlineStr">
         <is>
           <t>отлично все .пополнение снимание денег без проблем</t>
@@ -28918,7 +28489,6 @@
       <c r="C737" t="n">
         <v>5</v>
       </c>
-      <c r="D737" t="inlineStr"/>
       <c r="E737" t="inlineStr">
         <is>
           <t>5 отлично</t>
@@ -28957,7 +28527,6 @@
       <c r="C738" t="n">
         <v>5</v>
       </c>
-      <c r="D738" t="inlineStr"/>
       <c r="E738" t="inlineStr">
         <is>
           <t>отлично, спасибо...ещё бы кредит давали мне((</t>
@@ -28996,7 +28565,7 @@
       <c r="C739" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D739" s="2" t="inlineStr"/>
+      <c r="D739" s="2" t="n"/>
       <c r="E739" s="2" t="inlineStr">
         <is>
           <t>тормозит маркет жутко дорогой рассрочку не даёт если есть кредит хотя и нет просрочек оплачивается все вовремя переводы бывает на 3 дня теряются между своими счетами ну а если деньги идут мошенникам за границу то за секунду уходят и отменить перевод нельзя 2 звезды только из-за того что этим приложением эпизодически пользуюсь</t>
@@ -29035,7 +28604,6 @@
       <c r="C740" t="n">
         <v>5</v>
       </c>
-      <c r="D740" t="inlineStr"/>
       <c r="E740" t="inlineStr">
         <is>
           <t>всё нравиться</t>
@@ -29074,7 +28642,6 @@
       <c r="C741" t="n">
         <v>5</v>
       </c>
-      <c r="D741" t="inlineStr"/>
       <c r="E741" t="inlineStr">
         <is>
           <t>самый хорошый банк 🏦</t>
@@ -29113,7 +28680,6 @@
       <c r="C742" t="n">
         <v>5</v>
       </c>
-      <c r="D742" t="inlineStr"/>
       <c r="E742" t="inlineStr">
         <is>
           <t>Рахмееет</t>
@@ -29152,7 +28718,6 @@
       <c r="C743" t="n">
         <v>5</v>
       </c>
-      <c r="D743" t="inlineStr"/>
       <c r="E743" t="inlineStr">
         <is>
           <t>хорошее приложение .</t>
@@ -29191,7 +28756,6 @@
       <c r="C744" t="n">
         <v>5</v>
       </c>
-      <c r="D744" t="inlineStr"/>
       <c r="E744" t="inlineStr">
         <is>
           <t>хорошее приложение для всех, особенно для старшего поколения, для студентов</t>
@@ -29230,7 +28794,6 @@
       <c r="C745" t="n">
         <v>5</v>
       </c>
-      <c r="D745" t="inlineStr"/>
       <c r="E745" t="inlineStr">
         <is>
           <t>нравиться , все доступно</t>
@@ -29241,7 +28804,6 @@
           <t>Турсын Саржигитова</t>
         </is>
       </c>
-      <c r="G745" t="inlineStr"/>
       <c r="H745" t="inlineStr">
         <is>
           <t>29d165828efd29a64ccd2b92</t>
@@ -29265,7 +28827,6 @@
       <c r="C746" t="n">
         <v>5</v>
       </c>
-      <c r="D746" t="inlineStr"/>
       <c r="E746" t="inlineStr">
         <is>
           <t>супер приложение все отлично работает</t>
@@ -29304,7 +28865,7 @@
       <c r="C747" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D747" s="2" t="inlineStr"/>
+      <c r="D747" s="2" t="n"/>
       <c r="E747" s="2" t="inlineStr">
         <is>
           <t>Киюр істемеит камера ашпайды нестеуге болды</t>
@@ -29350,7 +28911,6 @@
       <c r="C749" t="n">
         <v>5</v>
       </c>
-      <c r="D749" t="inlineStr"/>
       <c r="E749" t="inlineStr">
         <is>
           <t>5 из 5</t>
@@ -29389,7 +28949,6 @@
       <c r="C750" t="n">
         <v>5</v>
       </c>
-      <c r="D750" t="inlineStr"/>
       <c r="E750" t="inlineStr">
         <is>
           <t>все классно</t>
@@ -29428,7 +28987,6 @@
       <c r="C751" t="n">
         <v>5</v>
       </c>
-      <c r="D751" t="inlineStr"/>
       <c r="E751" t="inlineStr">
         <is>
           <t>жақсы банк</t>
@@ -29467,7 +29025,6 @@
       <c r="C752" t="n">
         <v>5</v>
       </c>
-      <c r="D752" t="inlineStr"/>
       <c r="E752" t="inlineStr">
         <is>
           <t>Очень</t>
@@ -29506,7 +29063,6 @@
       <c r="C753" t="n">
         <v>5</v>
       </c>
-      <c r="D753" t="inlineStr"/>
       <c r="E753" t="inlineStr">
         <is>
           <t>Керемет!</t>
@@ -29545,7 +29101,6 @@
       <c r="C754" t="n">
         <v>5</v>
       </c>
-      <c r="D754" t="inlineStr"/>
       <c r="E754" t="inlineStr">
         <is>
           <t>Вы можете сначала по халык (например списание комиссии) предложить а потом добавить функцию каспи как списывается.</t>
@@ -29584,7 +29139,7 @@
       <c r="C755" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D755" s="2" t="inlineStr"/>
+      <c r="D755" s="2" t="n"/>
       <c r="E755" s="2" t="inlineStr">
         <is>
           <t>Добрый день,не работает кюар,куда обратиться?</t>
@@ -29623,7 +29178,6 @@
       <c r="C756" t="n">
         <v>5</v>
       </c>
-      <c r="D756" t="inlineStr"/>
       <c r="E756" t="inlineStr">
         <is>
           <t>Керемет 👍🥰</t>
@@ -29662,7 +29216,7 @@
       <c r="C757" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D757" s="2" t="inlineStr"/>
+      <c r="D757" s="2" t="n"/>
       <c r="E757" s="2" t="inlineStr">
         <is>
           <t>в приложении в автостраховании не получается обновить полюс, посоветовали обновить, но обновления тоже не выходит. вообще не возможно работать на приложении в автостраховании</t>
@@ -29701,7 +29255,7 @@
       <c r="C758" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D758" s="2" t="inlineStr"/>
+      <c r="D758" s="2" t="n"/>
       <c r="E758" s="2" t="inlineStr">
         <is>
           <t>приложение супер 👍</t>
@@ -29740,7 +29294,6 @@
       <c r="C759" t="n">
         <v>5</v>
       </c>
-      <c r="D759" t="inlineStr"/>
       <c r="E759" t="inlineStr">
         <is>
           <t>замечательно</t>
@@ -29779,7 +29332,7 @@
       <c r="C760" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D760" s="2" t="inlineStr"/>
+      <c r="D760" s="2" t="n"/>
       <c r="E760" s="2" t="inlineStr">
         <is>
           <t>Тяжёлый и медленный</t>
@@ -29818,7 +29371,6 @@
       <c r="C761" t="n">
         <v>5</v>
       </c>
-      <c r="D761" t="inlineStr"/>
       <c r="E761" t="inlineStr">
         <is>
           <t>стал намного лучше</t>
@@ -29857,7 +29409,6 @@
       <c r="C762" t="n">
         <v>5</v>
       </c>
-      <c r="D762" t="inlineStr"/>
       <c r="E762" t="inlineStr">
         <is>
           <t>надежность.культура обслуживания.</t>
@@ -29896,7 +29447,6 @@
       <c r="C763" t="n">
         <v>5</v>
       </c>
-      <c r="D763" t="inlineStr"/>
       <c r="E763" t="inlineStr">
         <is>
           <t>все устраивает,работает без проблем.</t>
@@ -29935,7 +29485,6 @@
       <c r="C764" t="n">
         <v>5</v>
       </c>
-      <c r="D764" t="inlineStr"/>
       <c r="E764" t="inlineStr">
         <is>
           <t>супер 👍</t>
@@ -29946,7 +29495,6 @@
           <t>Sayat Rahimzhanov</t>
         </is>
       </c>
-      <c r="G764" t="inlineStr"/>
       <c r="H764" t="inlineStr">
         <is>
           <t>8bb20fe15a98fa13b7a95a66</t>
@@ -29970,7 +29518,7 @@
       <c r="C765" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D765" s="2" t="inlineStr"/>
+      <c r="D765" s="2" t="n"/>
       <c r="E765" s="2" t="inlineStr">
         <is>
           <t>Без коментариев. За меня все уже сказали.</t>
@@ -30009,7 +29557,7 @@
       <c r="C766" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D766" s="2" t="inlineStr"/>
+      <c r="D766" s="2" t="n"/>
       <c r="E766" s="2" t="inlineStr">
         <is>
           <t>В чате поддержки нет уведомлений, т.е. нужно в нем сидеть постоянно, чтобы не пропустить ответ, иначе диалог закроется моментом чуть ли не за 5 секунд отсутствия ответа пользователя.</t>
@@ -30048,7 +29596,6 @@
       <c r="C767" t="n">
         <v>5</v>
       </c>
-      <c r="D767" t="inlineStr"/>
       <c r="E767" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -30087,7 +29634,6 @@
       <c r="C768" t="n">
         <v>5</v>
       </c>
-      <c r="D768" t="inlineStr"/>
       <c r="E768" t="inlineStr">
         <is>
           <t>керемет банксың</t>
@@ -30126,7 +29672,6 @@
       <c r="C769" t="n">
         <v>5</v>
       </c>
-      <c r="D769" t="inlineStr"/>
       <c r="E769" t="inlineStr">
         <is>
           <t>мне это приложение савершено независимо но хачу изучить его досканально и что он из себя представляет я тоже не знаю но всё равно спасибо есть ли он мне будет полезен то я буду рат буду ей пользоваться и вас благодарить и паменать добрым словом маи слова да богу в уши,,</t>
@@ -30165,7 +29710,6 @@
       <c r="C770" t="n">
         <v>5</v>
       </c>
-      <c r="D770" t="inlineStr"/>
       <c r="E770" t="inlineStr">
         <is>
           <t>отличный сервис</t>
@@ -30204,7 +29748,6 @@
       <c r="C771" t="n">
         <v>5</v>
       </c>
-      <c r="D771" t="inlineStr"/>
       <c r="E771" t="inlineStr">
         <is>
           <t>Рахмет</t>
@@ -30243,7 +29786,6 @@
       <c r="C772" t="n">
         <v>5</v>
       </c>
-      <c r="D772" t="inlineStr"/>
       <c r="E772" t="inlineStr">
         <is>
           <t>хорошо</t>
@@ -30289,7 +29831,6 @@
       <c r="C774" t="n">
         <v>5</v>
       </c>
-      <c r="D774" t="inlineStr"/>
       <c r="E774" t="inlineStr">
         <is>
           <t>спасибо вам большое</t>
@@ -30369,7 +29910,6 @@
       <c r="C775" t="n">
         <v>5</v>
       </c>
-      <c r="D775" t="inlineStr"/>
       <c r="E775" t="inlineStr">
         <is>
           <t>👍👍👍👍</t>
@@ -30449,7 +29989,6 @@
       <c r="C776" t="n">
         <v>5</v>
       </c>
-      <c r="D776" t="inlineStr"/>
       <c r="E776" t="inlineStr">
         <is>
           <t>👍</t>
@@ -30488,7 +30027,7 @@
       <c r="C777" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D777" s="2" t="inlineStr"/>
+      <c r="D777" s="2" t="n"/>
       <c r="E777" s="2" t="inlineStr">
         <is>
           <t>заблокировали доступ, пишет надо переустановить, переустановил, не помогло, звонок не проходит, остался без доступа к деньгам.</t>
@@ -30527,7 +30066,6 @@
       <c r="C778" t="n">
         <v>5</v>
       </c>
-      <c r="D778" t="inlineStr"/>
       <c r="E778" t="inlineStr">
         <is>
           <t>всё нравится</t>
@@ -30566,7 +30104,7 @@
       <c r="C779" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D779" s="2" t="inlineStr"/>
+      <c r="D779" s="2" t="n"/>
       <c r="E779" s="2" t="inlineStr">
         <is>
           <t>Алаяқ народный</t>
@@ -30577,7 +30115,7 @@
           <t>Алматбек Сарсембаев</t>
         </is>
       </c>
-      <c r="G779" s="2" t="inlineStr"/>
+      <c r="G779" s="2" t="n"/>
       <c r="H779" s="2" t="inlineStr">
         <is>
           <t>65e46b5539d67a5f1390ce18</t>
@@ -30601,7 +30139,6 @@
       <c r="C780" t="n">
         <v>5</v>
       </c>
-      <c r="D780" t="inlineStr"/>
       <c r="E780" t="inlineStr">
         <is>
           <t>побольше кредит одобряйте</t>
@@ -30640,7 +30177,6 @@
       <c r="C781" t="n">
         <v>4</v>
       </c>
-      <c r="D781" t="inlineStr"/>
       <c r="E781" t="inlineStr">
         <is>
           <t>В целом всё нормально, иногда подводит, когда надо зарплату получить, но не постоянно.</t>
@@ -30679,7 +30215,6 @@
       <c r="C782" t="n">
         <v>5</v>
       </c>
-      <c r="D782" t="inlineStr"/>
       <c r="E782" t="inlineStr">
         <is>
           <t>рахмет</t>
@@ -30718,7 +30253,6 @@
       <c r="C783" t="n">
         <v>5</v>
       </c>
-      <c r="D783" t="inlineStr"/>
       <c r="E783" t="inlineStr">
         <is>
           <t>унайды,,оте қарапайым ,бонус алу үшін боныс карта алу керекпе екен?</t>
@@ -30757,7 +30291,7 @@
       <c r="C784" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D784" s="2" t="inlineStr"/>
+      <c r="D784" s="2" t="n"/>
       <c r="E784" s="2" t="inlineStr">
         <is>
           <t>бонус бермейсіздер сол жағы шамалы</t>
@@ -30796,7 +30330,7 @@
       <c r="C785" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D785" s="2" t="inlineStr"/>
+      <c r="D785" s="2" t="n"/>
       <c r="E785" s="2" t="inlineStr">
         <is>
           <t>Что за приложение? Совсем неудобное. В Kaspi заходишь — всё понятно и удобно. А в этом приложении попробуй найти хотя бы карту с банкоматами.</t>
@@ -30835,7 +30369,6 @@
       <c r="C786" t="n">
         <v>5</v>
       </c>
-      <c r="D786" t="inlineStr"/>
       <c r="E786" t="inlineStr">
         <is>
           <t>Очень удобное приложение</t>
@@ -30874,7 +30407,6 @@
       <c r="C787" t="n">
         <v>5</v>
       </c>
-      <c r="D787" t="inlineStr"/>
       <c r="E787" t="inlineStr">
         <is>
           <t>хороший сервис</t>
@@ -30913,7 +30445,6 @@
       <c r="C788" t="n">
         <v>5</v>
       </c>
-      <c r="D788" t="inlineStr"/>
       <c r="E788" t="inlineStr">
         <is>
           <t>быстро и удобно снятие средств</t>
@@ -30952,7 +30483,6 @@
       <c r="C789" t="n">
         <v>5</v>
       </c>
-      <c r="D789" t="inlineStr"/>
       <c r="E789" t="inlineStr">
         <is>
           <t>хорошо желаю вам всего наилучшего</t>
@@ -30991,7 +30521,6 @@
       <c r="C790" t="n">
         <v>5</v>
       </c>
-      <c r="D790" t="inlineStr"/>
       <c r="E790" t="inlineStr">
         <is>
           <t>Депозит делайте упрощёный получение наличными в банке или банкомате</t>
@@ -31030,7 +30559,7 @@
       <c r="C791" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D791" s="2" t="inlineStr"/>
+      <c r="D791" s="2" t="n"/>
       <c r="E791" s="2" t="inlineStr">
         <is>
           <t>мало того что сам банк за каждое движение деньги снимает, ещё и проценты на кредиты грабительски дикие. не банк а ОПГ в законе</t>
@@ -31069,7 +30598,6 @@
       <c r="C792" t="n">
         <v>5</v>
       </c>
-      <c r="D792" t="inlineStr"/>
       <c r="E792" t="inlineStr">
         <is>
           <t>Хороший банк</t>
@@ -31108,7 +30636,6 @@
       <c r="C793" t="n">
         <v>4</v>
       </c>
-      <c r="D793" t="inlineStr"/>
       <c r="E793" t="inlineStr">
         <is>
           <t>если честно все хорошо, сам интерфейс и обслуживание но иногда возникает проблемы с самим приложением</t>
@@ -31147,7 +30674,7 @@
       <c r="C794" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D794" s="2" t="inlineStr"/>
+      <c r="D794" s="2" t="n"/>
       <c r="E794" s="2" t="inlineStr">
         <is>
           <t>Всю жизнь этот банк является совокупностью всего самого наихудшего</t>
@@ -31158,7 +30685,7 @@
           <t>Bai ~</t>
         </is>
       </c>
-      <c r="G794" s="2" t="inlineStr"/>
+      <c r="G794" s="2" t="n"/>
       <c r="H794" s="2" t="inlineStr">
         <is>
           <t>a9ff0cf0c4c0f212a4394b5b</t>
@@ -31182,7 +30709,6 @@
       <c r="C795" t="n">
         <v>5</v>
       </c>
-      <c r="D795" t="inlineStr"/>
       <c r="E795" t="inlineStr">
         <is>
           <t>все прекрасно работает</t>
@@ -31221,7 +30747,6 @@
       <c r="C796" t="n">
         <v>4</v>
       </c>
-      <c r="D796" t="inlineStr"/>
       <c r="E796" t="inlineStr">
         <is>
           <t>Не нравится бонусная программа (не возможно потратить даже 100000 тенге на покупках в магазинах если не делать крупных покупок (например электроника), чтобы заработать на 1 процент в следующем месяце).</t>
@@ -31260,7 +30785,6 @@
       <c r="C797" t="n">
         <v>5</v>
       </c>
-      <c r="D797" t="inlineStr"/>
       <c r="E797" t="inlineStr">
         <is>
           <t>қазақстандағы сенімді банктің бірі👍</t>
@@ -31299,7 +30823,6 @@
       <c r="C798" t="n">
         <v>5</v>
       </c>
-      <c r="D798" t="inlineStr"/>
       <c r="E798" t="inlineStr">
         <is>
           <t>💗</t>
@@ -31338,7 +30861,6 @@
       <c r="C799" t="n">
         <v>5</v>
       </c>
-      <c r="D799" t="inlineStr"/>
       <c r="E799" t="inlineStr">
         <is>
           <t>Очень удобное приложение! Недавно добавили функцию с помощью которой можно оплачивать с халыка на терминал каспи 5 звёзд!</t>
@@ -31377,7 +30899,6 @@
       <c r="C800" t="n">
         <v>5</v>
       </c>
-      <c r="D800" t="inlineStr"/>
       <c r="E800" t="inlineStr">
         <is>
           <t>просто супер</t>
@@ -31416,7 +30937,6 @@
       <c r="C801" t="n">
         <v>5</v>
       </c>
-      <c r="D801" t="inlineStr"/>
       <c r="E801" t="inlineStr">
         <is>
           <t>Ок</t>
@@ -31455,7 +30975,6 @@
       <c r="C802" t="n">
         <v>5</v>
       </c>
-      <c r="D802" t="inlineStr"/>
       <c r="E802" t="inlineStr">
         <is>
           <t>все отлично 👍</t>
@@ -31494,7 +31013,6 @@
       <c r="C803" t="n">
         <v>5</v>
       </c>
-      <c r="D803" t="inlineStr"/>
       <c r="E803" t="inlineStr">
         <is>
           <t>Очен хорошо</t>
@@ -31533,7 +31051,6 @@
       <c r="C804" t="n">
         <v>5</v>
       </c>
-      <c r="D804" t="inlineStr"/>
       <c r="E804" t="inlineStr">
         <is>
           <t>СУПЕР банк! Надеждный, серьезный . Сервис на Вышем классе!</t>
@@ -31572,7 +31089,6 @@
       <c r="C805" t="n">
         <v>4</v>
       </c>
-      <c r="D805" t="inlineStr"/>
       <c r="E805" t="inlineStr">
         <is>
           <t>хорошее приложение, удобно оплачивать.</t>
@@ -31611,7 +31127,6 @@
       <c r="C806" t="n">
         <v>4</v>
       </c>
-      <c r="D806" t="inlineStr"/>
       <c r="E806" t="inlineStr">
         <is>
           <t>рахмет</t>
@@ -31650,7 +31165,6 @@
       <c r="C807" t="n">
         <v>5</v>
       </c>
-      <c r="D807" t="inlineStr"/>
       <c r="E807" t="inlineStr">
         <is>
           <t>Отличный</t>
@@ -31689,7 +31203,6 @@
       <c r="C808" t="n">
         <v>5</v>
       </c>
-      <c r="D808" t="inlineStr"/>
       <c r="E808" t="inlineStr">
         <is>
           <t>всё прекрасно!</t>
@@ -31728,7 +31241,7 @@
       <c r="C809" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D809" s="2" t="inlineStr"/>
+      <c r="D809" s="2" t="n"/>
       <c r="E809" s="2" t="inlineStr">
         <is>
           <t>Приложение вопше не рабочая 0 отценка</t>
@@ -31767,7 +31280,6 @@
       <c r="C810" t="n">
         <v>5</v>
       </c>
-      <c r="D810" t="inlineStr"/>
       <c r="E810" t="inlineStr">
         <is>
           <t>молодцы. халык супер.</t>
@@ -31806,7 +31318,6 @@
       <c r="C811" t="n">
         <v>5</v>
       </c>
-      <c r="D811" t="inlineStr"/>
       <c r="E811" t="inlineStr">
         <is>
           <t>Все отлично</t>
@@ -31845,7 +31356,6 @@
       <c r="C812" t="n">
         <v>5</v>
       </c>
-      <c r="D812" t="inlineStr"/>
       <c r="E812" t="inlineStr">
         <is>
           <t>Халық банк әрдайым бізбен бірге🥰😍</t>
@@ -31884,7 +31394,6 @@
       <c r="C813" t="n">
         <v>5</v>
       </c>
-      <c r="D813" t="inlineStr"/>
       <c r="E813" t="inlineStr">
         <is>
           <t>Класс</t>
@@ -31923,7 +31432,6 @@
       <c r="C814" t="n">
         <v>5</v>
       </c>
-      <c r="D814" t="inlineStr"/>
       <c r="E814" t="inlineStr">
         <is>
           <t>Всё отлично работает прекрасно и надёжно!</t>
@@ -31962,7 +31470,6 @@
       <c r="C815" t="n">
         <v>5</v>
       </c>
-      <c r="D815" t="inlineStr"/>
       <c r="E815" t="inlineStr">
         <is>
           <t>Отлично</t>
@@ -32001,7 +31508,6 @@
       <c r="C816" t="n">
         <v>5</v>
       </c>
-      <c r="D816" t="inlineStr"/>
       <c r="E816" t="inlineStr">
         <is>
           <t>ВЫ СУПЕР</t>
@@ -32040,7 +31546,7 @@
       <c r="C817" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D817" s="2" t="inlineStr"/>
+      <c r="D817" s="2" t="n"/>
       <c r="E817" s="2" t="inlineStr">
         <is>
           <t>«Здравствуйте. Перевыпустил свою единственную основную карту по истечении срока действия через картомат, так как банк везде рекламировал этот способ как полностью бесплатный. 06.08.2026 с меня списали комиссию 1 000 тенге за "ранее выпущенную дополнительную карту через картомат". Никаких дополнительных карт у меня нет, а плановый перевыпуск основной карты не должен быть платным. Считаю данное списание скрытым сбором и введением в заблуждение. Требую вернуть 1 000 тенге на счет».</t>
@@ -32079,7 +31585,6 @@
       <c r="C818" t="n">
         <v>5</v>
       </c>
-      <c r="D818" t="inlineStr"/>
       <c r="E818" t="inlineStr">
         <is>
           <t>Кому же не нравиться приложение, который даёт деньги, конечно лайк</t>
@@ -32118,7 +31623,6 @@
       <c r="C819" t="n">
         <v>5</v>
       </c>
-      <c r="D819" t="inlineStr"/>
       <c r="E819" t="inlineStr">
         <is>
           <t>Да. Очень удобная</t>
@@ -32157,7 +31661,7 @@
       <c r="C820" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D820" s="2" t="inlineStr"/>
+      <c r="D820" s="2" t="n"/>
       <c r="E820" s="2" t="inlineStr">
         <is>
           <t>переводы на другие карты с комиссией,это плохо.</t>
@@ -32196,7 +31700,6 @@
       <c r="C821" t="n">
         <v>5</v>
       </c>
-      <c r="D821" t="inlineStr"/>
       <c r="E821" t="inlineStr">
         <is>
           <t>Очень нравится!</t>
@@ -32235,7 +31738,6 @@
       <c r="C822" t="n">
         <v>5</v>
       </c>
-      <c r="D822" t="inlineStr"/>
       <c r="E822" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -32274,7 +31776,6 @@
       <c r="C823" t="n">
         <v>5</v>
       </c>
-      <c r="D823" t="inlineStr"/>
       <c r="E823" t="inlineStr">
         <is>
           <t>Отличный банк.</t>
@@ -32313,7 +31814,6 @@
       <c r="C824" t="n">
         <v>5</v>
       </c>
-      <c r="D824" t="inlineStr"/>
       <c r="E824" t="inlineStr">
         <is>
           <t>өте жақсы рахмет айтамын</t>
@@ -32352,7 +31852,6 @@
       <c r="C825" t="n">
         <v>5</v>
       </c>
-      <c r="D825" t="inlineStr"/>
       <c r="E825" t="inlineStr">
         <is>
           <t>ваш банк мен нравитса девчата хорошо авслуживает</t>
@@ -32391,7 +31890,6 @@
       <c r="C826" t="n">
         <v>5</v>
       </c>
-      <c r="D826" t="inlineStr"/>
       <c r="E826" t="inlineStr">
         <is>
           <t>хороший приложение</t>
@@ -32430,7 +31928,6 @@
       <c r="C827" t="n">
         <v>5</v>
       </c>
-      <c r="D827" t="inlineStr"/>
       <c r="E827" t="inlineStr">
         <is>
           <t>Да нравится 👍</t>
@@ -32476,7 +31973,6 @@
       <c r="C829" t="n">
         <v>5</v>
       </c>
-      <c r="D829" t="inlineStr"/>
       <c r="E829" t="inlineStr">
         <is>
           <t>хорошо</t>
@@ -32556,7 +32052,6 @@
       <c r="C830" t="n">
         <v>5</v>
       </c>
-      <c r="D830" t="inlineStr"/>
       <c r="E830" t="inlineStr">
         <is>
           <t>очень удобное предложение всегда всё доступно там Я обожаю это предложение и всем рекомендую скачивать все вот эти предложения детям можно получить пособие и также можно заработную плату получать и также можно инвестировать ваши деньги</t>
@@ -32636,7 +32131,6 @@
       <c r="C831" t="n">
         <v>5</v>
       </c>
-      <c r="D831" t="inlineStr"/>
       <c r="E831" t="inlineStr">
         <is>
           <t>приложение просто супер очень понятный интерфейс и функции</t>
@@ -32675,7 +32169,6 @@
       <c r="C832" t="n">
         <v>5</v>
       </c>
-      <c r="D832" t="inlineStr"/>
       <c r="E832" t="inlineStr">
         <is>
           <t>жаксы керемет ракымет</t>
@@ -32714,7 +32207,6 @@
       <c r="C833" t="n">
         <v>5</v>
       </c>
-      <c r="D833" t="inlineStr"/>
       <c r="E833" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -32753,7 +32245,7 @@
       <c r="C834" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D834" s="2" t="inlineStr"/>
+      <c r="D834" s="2" t="n"/>
       <c r="E834" s="2" t="inlineStr">
         <is>
           <t>Өте ыңғайлы,әрі қажет дүние</t>
@@ -32792,7 +32284,6 @@
       <c r="C835" t="n">
         <v>5</v>
       </c>
-      <c r="D835" t="inlineStr"/>
       <c r="E835" t="inlineStr">
         <is>
           <t>Халык банк-надежный банк, оперативно выполняет все операции, удобное приложение. Непонятные вопросы есть возможность уточнить.</t>
@@ -32831,7 +32322,6 @@
       <c r="C836" t="n">
         <v>5</v>
       </c>
-      <c r="D836" t="inlineStr"/>
       <c r="E836" t="inlineStr">
         <is>
           <t>Өте жақсы</t>
@@ -32870,7 +32360,6 @@
       <c r="C837" t="n">
         <v>5</v>
       </c>
-      <c r="D837" t="inlineStr"/>
       <c r="E837" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -32909,7 +32398,6 @@
       <c r="C838" t="n">
         <v>5</v>
       </c>
-      <c r="D838" t="inlineStr"/>
       <c r="E838" t="inlineStr">
         <is>
           <t>все хорош😀</t>
@@ -32948,7 +32436,6 @@
       <c r="C839" t="n">
         <v>5</v>
       </c>
-      <c r="D839" t="inlineStr"/>
       <c r="E839" t="inlineStr">
         <is>
           <t>хорошо</t>
@@ -32987,7 +32474,6 @@
       <c r="C840" t="n">
         <v>5</v>
       </c>
-      <c r="D840" t="inlineStr"/>
       <c r="E840" t="inlineStr">
         <is>
           <t>молодец</t>
@@ -33026,7 +32512,6 @@
       <c r="C841" t="n">
         <v>5</v>
       </c>
-      <c r="D841" t="inlineStr"/>
       <c r="E841" t="inlineStr">
         <is>
           <t>Обслуживание вашего банка отличное! Есть операторы которые обслуживают на высшем уровне! Если желаете, могу назвать имена</t>
@@ -33065,7 +32550,6 @@
       <c r="C842" t="n">
         <v>5</v>
       </c>
-      <c r="D842" t="inlineStr"/>
       <c r="E842" t="inlineStr">
         <is>
           <t>нёән</t>
@@ -33104,7 +32588,6 @@
       <c r="C843" t="n">
         <v>5</v>
       </c>
-      <c r="D843" t="inlineStr"/>
       <c r="E843" t="inlineStr">
         <is>
           <t>всё нравится</t>
@@ -33143,7 +32626,7 @@
       <c r="C844" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D844" s="2" t="inlineStr"/>
+      <c r="D844" s="2" t="n"/>
       <c r="E844" s="2" t="inlineStr">
         <is>
           <t>не могу переводы платежи делать заграницей код подтверждения не приходит</t>
@@ -33182,7 +32665,6 @@
       <c r="C845" t="n">
         <v>5</v>
       </c>
-      <c r="D845" t="inlineStr"/>
       <c r="E845" t="inlineStr">
         <is>
           <t>отлично!</t>
@@ -33221,7 +32703,6 @@
       <c r="C846" t="n">
         <v>5</v>
       </c>
-      <c r="D846" t="inlineStr"/>
       <c r="E846" t="inlineStr">
         <is>
           <t>хорошо. спасибо.</t>
@@ -33260,7 +32741,6 @@
       <c r="C847" t="n">
         <v>5</v>
       </c>
-      <c r="D847" t="inlineStr"/>
       <c r="E847" t="inlineStr">
         <is>
           <t>Өте керемет</t>
@@ -33299,7 +32779,7 @@
       <c r="C848" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D848" s="2" t="inlineStr"/>
+      <c r="D848" s="2" t="n"/>
       <c r="E848" s="2" t="inlineStr">
         <is>
           <t>слишком медленное</t>
@@ -33338,7 +32818,6 @@
       <c r="C849" t="n">
         <v>5</v>
       </c>
-      <c r="D849" t="inlineStr"/>
       <c r="E849" t="inlineStr">
         <is>
           <t>керемет жұмыс істейді</t>
@@ -33377,7 +32856,6 @@
       <c r="C850" t="n">
         <v>5</v>
       </c>
-      <c r="D850" t="inlineStr"/>
       <c r="E850" t="inlineStr">
         <is>
           <t>хорошая работа</t>
@@ -33416,7 +32894,6 @@
       <c r="C851" t="n">
         <v>4</v>
       </c>
-      <c r="D851" t="inlineStr"/>
       <c r="E851" t="inlineStr">
         <is>
           <t>сделайте переводы между банками бесплатными</t>
@@ -33455,7 +32932,6 @@
       <c r="C852" t="n">
         <v>5</v>
       </c>
-      <c r="D852" t="inlineStr"/>
       <c r="E852" t="inlineStr">
         <is>
           <t>надёжный банк!</t>
@@ -33494,7 +32970,6 @@
       <c r="C853" t="n">
         <v>5</v>
       </c>
-      <c r="D853" t="inlineStr"/>
       <c r="E853" t="inlineStr">
         <is>
           <t>Ұнайды дегенмен перевод жасағанда пеня ұсталмаса екен осыны қолданарек бәріміз</t>
@@ -33533,7 +33008,6 @@
       <c r="C854" t="n">
         <v>5</v>
       </c>
-      <c r="D854" t="inlineStr"/>
       <c r="E854" t="inlineStr">
         <is>
           <t>Все отлично.</t>
@@ -33572,7 +33046,7 @@
       <c r="C855" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D855" s="2" t="inlineStr"/>
+      <c r="D855" s="2" t="n"/>
       <c r="E855" s="2" t="inlineStr">
         <is>
           <t>вроде обновляем ,он все равно не открывает приложение и говорит нужно обновить</t>
@@ -33611,7 +33085,6 @@
       <c r="C856" t="n">
         <v>5</v>
       </c>
-      <c r="D856" t="inlineStr"/>
       <c r="E856" t="inlineStr">
         <is>
           <t>удобное приложение для оплаты коммунальных услуг, получение зп, переводы</t>
@@ -33650,7 +33123,7 @@
       <c r="C857" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D857" s="2" t="inlineStr"/>
+      <c r="D857" s="2" t="n"/>
       <c r="E857" s="2" t="inlineStr">
         <is>
           <t>постоянно долго думает и зависает, самый плохой предложение</t>
@@ -33689,7 +33162,6 @@
       <c r="C858" t="n">
         <v>5</v>
       </c>
-      <c r="D858" t="inlineStr"/>
       <c r="E858" t="inlineStr">
         <is>
           <t>super</t>
@@ -33728,7 +33200,6 @@
       <c r="C859" t="n">
         <v>5</v>
       </c>
-      <c r="D859" t="inlineStr"/>
       <c r="E859" t="inlineStr">
         <is>
           <t>нормально</t>
@@ -33767,7 +33238,6 @@
       <c r="C860" t="n">
         <v>5</v>
       </c>
-      <c r="D860" t="inlineStr"/>
       <c r="E860" t="inlineStr">
         <is>
           <t>спасибо большое</t>
@@ -33806,7 +33276,6 @@
       <c r="C861" t="n">
         <v>5</v>
       </c>
-      <c r="D861" t="inlineStr"/>
       <c r="E861" t="inlineStr">
         <is>
           <t>супер</t>
@@ -33845,7 +33314,6 @@
       <c r="C862" t="n">
         <v>5</v>
       </c>
-      <c r="D862" t="inlineStr"/>
       <c r="E862" t="inlineStr">
         <is>
           <t>На данный момент меня всё устраивает, надеюсь, что и в дальнейшем всё будет хорошо 🙏🤗🥰, благодарю👋🤗🥰</t>
@@ -33884,7 +33352,7 @@
       <c r="C863" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D863" s="2" t="inlineStr"/>
+      <c r="D863" s="2" t="n"/>
       <c r="E863" s="2" t="inlineStr">
         <is>
           <t>ужасно</t>
@@ -33923,7 +33391,6 @@
       <c r="C864" t="n">
         <v>5</v>
       </c>
-      <c r="D864" t="inlineStr"/>
       <c r="E864" t="inlineStr">
         <is>
           <t>очень удобно и добро.</t>
@@ -33962,7 +33429,6 @@
       <c r="C865" t="n">
         <v>5</v>
       </c>
-      <c r="D865" t="inlineStr"/>
       <c r="E865" t="inlineStr">
         <is>
           <t>БЛАГОДАРЮ!</t>
@@ -34001,7 +33467,6 @@
       <c r="C866" t="n">
         <v>5</v>
       </c>
-      <c r="D866" t="inlineStr"/>
       <c r="E866" t="inlineStr">
         <is>
           <t>легкое быстое удобное супер</t>
@@ -34040,7 +33505,6 @@
       <c r="C867" t="n">
         <v>5</v>
       </c>
-      <c r="D867" t="inlineStr"/>
       <c r="E867" t="inlineStr">
         <is>
           <t>рахмет</t>
@@ -34079,7 +33543,6 @@
       <c r="C868" t="n">
         <v>5</v>
       </c>
-      <c r="D868" t="inlineStr"/>
       <c r="E868" t="inlineStr">
         <is>
           <t>спасибо за удобство и мобильность👍👍👍</t>
@@ -34118,7 +33581,6 @@
       <c r="C869" t="n">
         <v>5</v>
       </c>
-      <c r="D869" t="inlineStr"/>
       <c r="E869" t="inlineStr">
         <is>
           <t>все ок</t>
@@ -34157,7 +33619,6 @@
       <c r="C870" t="n">
         <v>5</v>
       </c>
-      <c r="D870" t="inlineStr"/>
       <c r="E870" t="inlineStr">
         <is>
           <t>нравиться</t>
@@ -34196,7 +33657,7 @@
       <c r="C871" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D871" s="2" t="inlineStr"/>
+      <c r="D871" s="2" t="n"/>
       <c r="E871" s="2" t="inlineStr">
         <is>
           <t>Приложение одного устройства.</t>
@@ -34235,7 +33696,7 @@
       <c r="C872" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D872" s="2" t="inlineStr"/>
+      <c r="D872" s="2" t="n"/>
       <c r="E872" s="2" t="inlineStr">
         <is>
           <t>постоянно на удалить и скачать сделали бы уже норм</t>
@@ -34274,7 +33735,6 @@
       <c r="C873" t="n">
         <v>5</v>
       </c>
-      <c r="D873" t="inlineStr"/>
       <c r="E873" t="inlineStr">
         <is>
           <t>барлығы ұнайды қызметтері</t>
@@ -34313,7 +33773,6 @@
       <c r="C874" t="n">
         <v>5</v>
       </c>
-      <c r="D874" t="inlineStr"/>
       <c r="E874" t="inlineStr">
         <is>
           <t>Өте жақсы 👍</t>
@@ -34352,7 +33811,7 @@
       <c r="C875" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D875" s="2" t="inlineStr"/>
+      <c r="D875" s="2" t="n"/>
       <c r="E875" s="2" t="inlineStr">
         <is>
           <t>не помогли с проблемой написано долг по налогам но оплатить не как не получается даже в банке говорят "мы ни чем помочь не можешь ваши проблемы сами решайте" и как после этого доверять банку?</t>
@@ -34391,7 +33850,6 @@
       <c r="C876" t="n">
         <v>5</v>
       </c>
-      <c r="D876" t="inlineStr"/>
       <c r="E876" t="inlineStr">
         <is>
           <t>Во-👍🏻!</t>
@@ -34430,7 +33888,6 @@
       <c r="C877" t="n">
         <v>5</v>
       </c>
-      <c r="D877" t="inlineStr"/>
       <c r="E877" t="inlineStr">
         <is>
           <t>очень удобное приложение,хороший банк .</t>
@@ -34469,7 +33926,6 @@
       <c r="C878" t="n">
         <v>5</v>
       </c>
-      <c r="D878" t="inlineStr"/>
       <c r="E878" t="inlineStr">
         <is>
           <t>Спасибо за качественную работу</t>
@@ -34508,7 +33964,6 @@
       <c r="C879" t="n">
         <v>5</v>
       </c>
-      <c r="D879" t="inlineStr"/>
       <c r="E879" t="inlineStr">
         <is>
           <t>Хорошо</t>
@@ -34547,7 +34002,6 @@
       <c r="C880" t="n">
         <v>4</v>
       </c>
-      <c r="D880" t="inlineStr"/>
       <c r="E880" t="inlineStr">
         <is>
           <t>норма</t>
@@ -34586,7 +34040,6 @@
       <c r="C881" t="n">
         <v>5</v>
       </c>
-      <c r="D881" t="inlineStr"/>
       <c r="E881" t="inlineStr">
         <is>
           <t>өте жақсы</t>
@@ -34625,7 +34078,6 @@
       <c r="C882" t="n">
         <v>5</v>
       </c>
-      <c r="D882" t="inlineStr"/>
       <c r="E882" t="inlineStr">
         <is>
           <t>являюсь пользователем карточки банка почти 30 лет, начиная со студенческой стипендии. Банк работал всегда, в любую погоду в любых ситуациях мы могли получить деньги. Народный банк всегда с народом!</t>
@@ -34664,7 +34116,7 @@
       <c r="C883" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D883" s="2" t="inlineStr"/>
+      <c r="D883" s="2" t="n"/>
       <c r="E883" s="2" t="inlineStr">
         <is>
           <t>класс</t>
@@ -34703,7 +34155,6 @@
       <c r="C884" t="n">
         <v>5</v>
       </c>
-      <c r="D884" t="inlineStr"/>
       <c r="E884" t="inlineStr">
         <is>
           <t>Благодарю Банк за их ресурсы и программы, помогают через автоматы.</t>
@@ -34742,7 +34193,6 @@
       <c r="C885" t="n">
         <v>5</v>
       </c>
-      <c r="D885" t="inlineStr"/>
       <c r="E885" t="inlineStr">
         <is>
           <t>хорошое предложение удобное</t>
@@ -34781,7 +34231,6 @@
       <c r="C886" t="n">
         <v>5</v>
       </c>
-      <c r="D886" t="inlineStr"/>
       <c r="E886" t="inlineStr">
         <is>
           <t>өте жақсы қызмет көрсетеді</t>
@@ -34820,7 +34269,6 @@
       <c r="C887" t="n">
         <v>5</v>
       </c>
-      <c r="D887" t="inlineStr"/>
       <c r="E887" t="inlineStr">
         <is>
           <t>👍</t>
@@ -34859,7 +34307,6 @@
       <c r="C888" t="n">
         <v>5</v>
       </c>
-      <c r="D888" t="inlineStr"/>
       <c r="E888" t="inlineStr">
         <is>
           <t>😍😍😍😍</t>
@@ -34898,7 +34345,6 @@
       <c r="C889" t="n">
         <v>5</v>
       </c>
-      <c r="D889" t="inlineStr"/>
       <c r="E889" t="inlineStr">
         <is>
           <t>все отлично</t>
@@ -34937,7 +34383,6 @@
       <c r="C890" t="n">
         <v>5</v>
       </c>
-      <c r="D890" t="inlineStr"/>
       <c r="E890" t="inlineStr">
         <is>
           <t>Ок</t>
@@ -34976,7 +34421,6 @@
       <c r="C891" t="n">
         <v>5</v>
       </c>
-      <c r="D891" t="inlineStr"/>
       <c r="E891" t="inlineStr">
         <is>
           <t>хорошо</t>
@@ -35015,7 +34459,6 @@
       <c r="C892" t="n">
         <v>5</v>
       </c>
-      <c r="D892" t="inlineStr"/>
       <c r="E892" t="inlineStr">
         <is>
           <t>отлично и очень быстро работаете</t>
@@ -35054,7 +34497,6 @@
       <c r="C893" t="n">
         <v>5</v>
       </c>
-      <c r="D893" t="inlineStr"/>
       <c r="E893" t="inlineStr">
         <is>
           <t>Удобно!</t>
@@ -35093,7 +34535,6 @@
       <c r="C894" t="n">
         <v>5</v>
       </c>
-      <c r="D894" t="inlineStr"/>
       <c r="E894" t="inlineStr">
         <is>
           <t>👍🏼👍🏼👍🏼👍🏼</t>
@@ -35132,7 +34573,6 @@
       <c r="C895" t="n">
         <v>5</v>
       </c>
-      <c r="D895" t="inlineStr"/>
       <c r="E895" t="inlineStr">
         <is>
           <t>Вы супер</t>
@@ -35171,7 +34611,6 @@
       <c r="C896" t="n">
         <v>5</v>
       </c>
-      <c r="D896" t="inlineStr"/>
       <c r="E896" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -35210,7 +34649,6 @@
       <c r="C897" t="n">
         <v>5</v>
       </c>
-      <c r="D897" t="inlineStr"/>
       <c r="E897" t="inlineStr">
         <is>
           <t>клас супер</t>
@@ -35249,7 +34687,6 @@
       <c r="C898" t="n">
         <v>5</v>
       </c>
-      <c r="D898" t="inlineStr"/>
       <c r="E898" t="inlineStr">
         <is>
           <t>все хорошо</t>
@@ -35288,7 +34725,6 @@
       <c r="C899" t="n">
         <v>5</v>
       </c>
-      <c r="D899" t="inlineStr"/>
       <c r="E899" t="inlineStr">
         <is>
           <t>очень классные жаль промокоды не дают за деньги</t>
@@ -35327,7 +34763,6 @@
       <c r="C900" t="n">
         <v>5</v>
       </c>
-      <c r="D900" t="inlineStr"/>
       <c r="E900" t="inlineStr">
         <is>
           <t>классно!</t>
@@ -35366,7 +34801,6 @@
       <c r="C901" t="n">
         <v>5</v>
       </c>
-      <c r="D901" t="inlineStr"/>
       <c r="E901" t="inlineStr">
         <is>
           <t>тез әрі сенімді</t>
@@ -35405,7 +34839,6 @@
       <c r="C902" t="n">
         <v>5</v>
       </c>
-      <c r="D902" t="inlineStr"/>
       <c r="E902" t="inlineStr">
         <is>
           <t>Нравятся получать бонусы за платежи</t>
@@ -35444,7 +34877,6 @@
       <c r="C903" t="n">
         <v>5</v>
       </c>
-      <c r="D903" t="inlineStr"/>
       <c r="E903" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -35483,7 +34915,6 @@
       <c r="C904" t="n">
         <v>5</v>
       </c>
-      <c r="D904" t="inlineStr"/>
       <c r="E904" t="inlineStr">
         <is>
           <t>вы лучщие . спасибо за вашу работу ..</t>
@@ -35522,7 +34953,6 @@
       <c r="C905" t="n">
         <v>5</v>
       </c>
-      <c r="D905" t="inlineStr"/>
       <c r="E905" t="inlineStr">
         <is>
           <t>классно</t>
@@ -35561,7 +34991,6 @@
       <c r="C906" t="n">
         <v>5</v>
       </c>
-      <c r="D906" t="inlineStr"/>
       <c r="E906" t="inlineStr">
         <is>
           <t>Хороший надежный банк</t>
@@ -35600,7 +35029,6 @@
       <c r="C907" t="n">
         <v>5</v>
       </c>
-      <c r="D907" t="inlineStr"/>
       <c r="E907" t="inlineStr">
         <is>
           <t>Здравствуйте. Мне нравится банк, персонал вежливый и в любую минуту помогут, если что то не понятно или защитить от мошенников. Спасибо Вам.</t>
@@ -35639,7 +35067,6 @@
       <c r="C908" t="n">
         <v>5</v>
       </c>
-      <c r="D908" t="inlineStr"/>
       <c r="E908" t="inlineStr">
         <is>
           <t>удобно</t>
@@ -35678,7 +35105,7 @@
       <c r="C909" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D909" s="2" t="inlineStr"/>
+      <c r="D909" s="2" t="n"/>
       <c r="E909" s="2" t="inlineStr">
         <is>
           <t>не могу войти на главную страницу</t>
@@ -35717,7 +35144,7 @@
       <c r="C910" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D910" s="2" t="inlineStr"/>
+      <c r="D910" s="2" t="n"/>
       <c r="E910" s="2" t="inlineStr">
         <is>
           <t>зависает функция оформления страховки, несколько дней не мог оформить страховку, в итоге оформился через посредника. Скрыли ползунок допуслуги при оформлении страховки осгпо. нельзя сохранить номер карты другого банка при переводе второй и третий раз. в магазине мало товаров.</t>
@@ -35756,7 +35183,6 @@
       <c r="C911" t="n">
         <v>5</v>
       </c>
-      <c r="D911" t="inlineStr"/>
       <c r="E911" t="inlineStr">
         <is>
           <t>Прекрасно спасибо</t>
@@ -35795,7 +35221,6 @@
       <c r="C912" t="n">
         <v>5</v>
       </c>
-      <c r="D912" t="inlineStr"/>
       <c r="E912" t="inlineStr">
         <is>
           <t>👏</t>
@@ -35834,7 +35259,6 @@
       <c r="C913" t="n">
         <v>5</v>
       </c>
-      <c r="D913" t="inlineStr"/>
       <c r="E913" t="inlineStr">
         <is>
           <t>очень хорошый</t>
@@ -35873,7 +35297,6 @@
       <c r="C914" t="n">
         <v>5</v>
       </c>
-      <c r="D914" t="inlineStr"/>
       <c r="E914" t="inlineStr">
         <is>
           <t>спасибо банку</t>
@@ -35912,7 +35335,7 @@
       <c r="C915" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D915" s="2" t="inlineStr"/>
+      <c r="D915" s="2" t="n"/>
       <c r="E915" s="2" t="inlineStr">
         <is>
           <t>не нравится</t>
@@ -35951,7 +35374,6 @@
       <c r="C916" t="n">
         <v>5</v>
       </c>
-      <c r="D916" t="inlineStr"/>
       <c r="E916" t="inlineStr">
         <is>
           <t>супер</t>
@@ -35990,7 +35412,6 @@
       <c r="C917" t="n">
         <v>5</v>
       </c>
-      <c r="D917" t="inlineStr"/>
       <c r="E917" t="inlineStr">
         <is>
           <t>отлично бонусы дарить</t>
@@ -36029,7 +35450,6 @@
       <c r="C918" t="n">
         <v>5</v>
       </c>
-      <c r="D918" t="inlineStr"/>
       <c r="E918" t="inlineStr">
         <is>
           <t>Хорошее приложение, все устраивает</t>
@@ -36068,7 +35488,6 @@
       <c r="C919" t="n">
         <v>5</v>
       </c>
-      <c r="D919" t="inlineStr"/>
       <c r="E919" t="inlineStr">
         <is>
           <t>Рахмет</t>
@@ -36107,7 +35526,6 @@
       <c r="C920" t="n">
         <v>5</v>
       </c>
-      <c r="D920" t="inlineStr"/>
       <c r="E920" t="inlineStr">
         <is>
           <t>очень нужное и своевременное приложение осбенно для пенсионеров пожилого возраста.</t>
@@ -36146,7 +35564,6 @@
       <c r="C921" t="n">
         <v>5</v>
       </c>
-      <c r="D921" t="inlineStr"/>
       <c r="E921" t="inlineStr">
         <is>
           <t>хорошо</t>
@@ -36185,7 +35602,6 @@
       <c r="C922" t="n">
         <v>5</v>
       </c>
-      <c r="D922" t="inlineStr"/>
       <c r="E922" t="inlineStr">
         <is>
           <t>очень удобна</t>
@@ -36224,7 +35640,6 @@
       <c r="C923" t="n">
         <v>5</v>
       </c>
-      <c r="D923" t="inlineStr"/>
       <c r="E923" t="inlineStr">
         <is>
           <t>өте жақсы,ыңғайлы</t>
@@ -36263,7 +35678,6 @@
       <c r="C924" t="n">
         <v>5</v>
       </c>
-      <c r="D924" t="inlineStr"/>
       <c r="E924" t="inlineStr">
         <is>
           <t>бәрі жақсы</t>
@@ -36302,7 +35716,6 @@
       <c r="C925" t="n">
         <v>5</v>
       </c>
-      <c r="D925" t="inlineStr"/>
       <c r="E925" t="inlineStr">
         <is>
           <t>Керем т</t>
@@ -36341,7 +35754,6 @@
       <c r="C926" t="n">
         <v>5</v>
       </c>
-      <c r="D926" t="inlineStr"/>
       <c r="E926" t="inlineStr">
         <is>
           <t>👍</t>
@@ -36380,7 +35792,6 @@
       <c r="C927" t="n">
         <v>5</v>
       </c>
-      <c r="D927" t="inlineStr"/>
       <c r="E927" t="inlineStr">
         <is>
           <t>супер</t>
@@ -36419,7 +35830,6 @@
       <c r="C928" t="n">
         <v>5</v>
       </c>
-      <c r="D928" t="inlineStr"/>
       <c r="E928" t="inlineStr">
         <is>
           <t>---Всё нормально, супер-классно..!!!---</t>
@@ -36458,7 +35868,6 @@
       <c r="C929" t="n">
         <v>5</v>
       </c>
-      <c r="D929" t="inlineStr"/>
       <c r="E929" t="inlineStr">
         <is>
           <t>сделайте тем кто ставить 5 звёзд хорошую кредитную историю.</t>
@@ -36497,7 +35906,6 @@
       <c r="C930" t="n">
         <v>5</v>
       </c>
-      <c r="D930" t="inlineStr"/>
       <c r="E930" t="inlineStr">
         <is>
           <t>кредит шығама маған</t>
@@ -36536,7 +35944,6 @@
       <c r="C931" t="n">
         <v>5</v>
       </c>
-      <c r="D931" t="inlineStr"/>
       <c r="E931" t="inlineStr">
         <is>
           <t>супер всё единственны момент не давайте всяким суд исполнителям блокировать счёт без нашего согласия и фактов обоснование</t>
@@ -36575,7 +35982,6 @@
       <c r="C932" t="n">
         <v>5</v>
       </c>
-      <c r="D932" t="inlineStr"/>
       <c r="E932" t="inlineStr">
         <is>
           <t>Спасибо Halyk Market! Мой вопрос был рассмотрен и успешно решен. Благодарю за профессиональный подход и внимательное отношение к партнерам. Рекомендую Halyk Market как надежную площадку для покупок и продаж.</t>
@@ -36614,7 +36020,6 @@
       <c r="C933" t="n">
         <v>4</v>
       </c>
-      <c r="D933" t="inlineStr"/>
       <c r="E933" t="inlineStr">
         <is>
           <t>нормальный банк</t>
@@ -36660,7 +36065,6 @@
       <c r="C935" t="n">
         <v>5</v>
       </c>
-      <c r="D935" t="inlineStr"/>
       <c r="E935" t="inlineStr">
         <is>
           <t>незря название НОРОДНЫЙ</t>
@@ -36740,7 +36144,6 @@
       <c r="C936" t="n">
         <v>5</v>
       </c>
-      <c r="D936" t="inlineStr"/>
       <c r="E936" t="inlineStr">
         <is>
           <t>Сәлеметсіз бе?! 🤝🏻📝 Өте ыңғайлы қолдауға және түсінікті функция, разделдері бар. Рақмет! 👍🏻💪🏻💴</t>
@@ -36820,7 +36223,7 @@
       <c r="C937" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D937" s="2" t="inlineStr"/>
+      <c r="D937" s="2" t="n"/>
       <c r="E937" s="2" t="inlineStr">
         <is>
           <t>өте жақсы</t>
@@ -36901,7 +36304,6 @@
       <c r="C938" t="n">
         <v>5</v>
       </c>
-      <c r="D938" t="inlineStr"/>
       <c r="E938" t="inlineStr">
         <is>
           <t>оте катты унайды</t>
@@ -36981,7 +36383,6 @@
       <c r="C939" t="n">
         <v>5</v>
       </c>
-      <c r="D939" t="inlineStr"/>
       <c r="E939" t="inlineStr">
         <is>
           <t>всё отлично</t>
@@ -37061,7 +36462,6 @@
       <c r="C940" t="n">
         <v>5</v>
       </c>
-      <c r="D940" t="inlineStr"/>
       <c r="E940" t="inlineStr">
         <is>
           <t>очень удобно 👍👍</t>
@@ -37141,7 +36541,7 @@
       <c r="C941" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D941" s="2" t="inlineStr"/>
+      <c r="D941" s="2" t="n"/>
       <c r="E941" s="2" t="inlineStr">
         <is>
           <t>неудобное</t>
@@ -37221,7 +36621,6 @@
       <c r="C942" t="n">
         <v>5</v>
       </c>
-      <c r="D942" t="inlineStr"/>
       <c r="E942" t="inlineStr">
         <is>
           <t>класны лучший предложения всем саветую</t>
@@ -37301,7 +36700,6 @@
       <c r="C943" t="n">
         <v>5</v>
       </c>
-      <c r="D943" t="inlineStr"/>
       <c r="E943" t="inlineStr">
         <is>
           <t>хорошо</t>
@@ -37340,7 +36738,6 @@
       <c r="C944" t="n">
         <v>5</v>
       </c>
-      <c r="D944" t="inlineStr"/>
       <c r="E944" t="inlineStr">
         <is>
           <t>Все нормально.</t>
@@ -37379,7 +36776,6 @@
       <c r="C945" t="n">
         <v>5</v>
       </c>
-      <c r="D945" t="inlineStr"/>
       <c r="E945" t="inlineStr">
         <is>
           <t>местами фонит</t>
@@ -37418,7 +36814,6 @@
       <c r="C946" t="n">
         <v>5</v>
       </c>
-      <c r="D946" t="inlineStr"/>
       <c r="E946" t="inlineStr">
         <is>
           <t>наш Халык банк очень гибкий ,мягкий дальновидный</t>
@@ -37457,7 +36852,6 @@
       <c r="C947" t="n">
         <v>5</v>
       </c>
-      <c r="D947" t="inlineStr"/>
       <c r="E947" t="inlineStr">
         <is>
           <t>👍</t>
@@ -37496,7 +36890,6 @@
       <c r="C948" t="n">
         <v>5</v>
       </c>
-      <c r="D948" t="inlineStr"/>
       <c r="E948" t="inlineStr">
         <is>
           <t>Маган оте жаксы унайды.</t>
@@ -37535,7 +36928,6 @@
       <c r="C949" t="n">
         <v>5</v>
       </c>
-      <c r="D949" t="inlineStr"/>
       <c r="E949" t="inlineStr">
         <is>
           <t>супер супер</t>
@@ -37574,7 +36966,6 @@
       <c r="C950" t="n">
         <v>5</v>
       </c>
-      <c r="D950" t="inlineStr"/>
       <c r="E950" t="inlineStr">
         <is>
           <t>спасиба</t>
@@ -37613,7 +37004,6 @@
       <c r="C951" t="n">
         <v>5</v>
       </c>
-      <c r="D951" t="inlineStr"/>
       <c r="E951" t="inlineStr">
         <is>
           <t>ок</t>
@@ -37652,7 +37042,6 @@
       <c r="C952" t="n">
         <v>5</v>
       </c>
-      <c r="D952" t="inlineStr"/>
       <c r="E952" t="inlineStr">
         <is>
           <t>керемет бәрі жақсы</t>
@@ -37691,7 +37080,6 @@
       <c r="C953" t="n">
         <v>5</v>
       </c>
-      <c r="D953" t="inlineStr"/>
       <c r="E953" t="inlineStr">
         <is>
           <t>Спасибо за то что есть Халык банк,</t>
@@ -37730,7 +37118,6 @@
       <c r="C954" t="n">
         <v>5</v>
       </c>
-      <c r="D954" t="inlineStr"/>
       <c r="E954" t="inlineStr">
         <is>
           <t>отличное приложение!!! ставлю 5</t>
@@ -37769,7 +37156,6 @@
       <c r="C955" t="n">
         <v>5</v>
       </c>
-      <c r="D955" t="inlineStr"/>
       <c r="E955" t="inlineStr">
         <is>
           <t>хорошо приложение</t>
@@ -37808,7 +37194,6 @@
       <c r="C956" t="n">
         <v>5</v>
       </c>
-      <c r="D956" t="inlineStr"/>
       <c r="E956" t="inlineStr">
         <is>
           <t>очень профессионально</t>
@@ -37847,7 +37232,6 @@
       <c r="C957" t="n">
         <v>5</v>
       </c>
-      <c r="D957" t="inlineStr"/>
       <c r="E957" t="inlineStr">
         <is>
           <t>Классно</t>
@@ -37886,7 +37270,6 @@
       <c r="C958" t="n">
         <v>5</v>
       </c>
-      <c r="D958" t="inlineStr"/>
       <c r="E958" t="inlineStr">
         <is>
           <t>хорошый банк толка кредит не даёт жаль</t>
@@ -37925,7 +37308,6 @@
       <c r="C959" t="n">
         <v>5</v>
       </c>
-      <c r="D959" t="inlineStr"/>
       <c r="E959" t="inlineStr">
         <is>
           <t>отличное приложение</t>
@@ -37964,7 +37346,6 @@
       <c r="C960" t="n">
         <v>5</v>
       </c>
-      <c r="D960" t="inlineStr"/>
       <c r="E960" t="inlineStr">
         <is>
           <t>кредиты жабылса воопще супер болар еды</t>
@@ -37975,7 +37356,6 @@
           <t>Samat Kartamanov</t>
         </is>
       </c>
-      <c r="G960" t="inlineStr"/>
       <c r="H960" t="inlineStr">
         <is>
           <t>084509e01decb2171c7446b2</t>
@@ -37999,7 +37379,7 @@
       <c r="C961" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D961" s="2" t="inlineStr"/>
+      <c r="D961" s="2" t="n"/>
       <c r="E961" s="2" t="inlineStr">
         <is>
           <t>не могу обновить</t>
@@ -38038,7 +37418,7 @@
       <c r="C962" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D962" s="2" t="inlineStr"/>
+      <c r="D962" s="2" t="n"/>
       <c r="E962" s="2" t="inlineStr">
         <is>
           <t>за обслуживание или блокировка карты снимаете деньги!</t>
@@ -38077,7 +37457,6 @@
       <c r="C963" t="n">
         <v>5</v>
       </c>
-      <c r="D963" t="inlineStr"/>
       <c r="E963" t="inlineStr">
         <is>
           <t>Спасибо, что Вы есть. От души.</t>
@@ -38116,7 +37495,6 @@
       <c r="C964" t="n">
         <v>5</v>
       </c>
-      <c r="D964" t="inlineStr"/>
       <c r="E964" t="inlineStr">
         <is>
           <t>Отличное приложение, видно что не стоят на месте, постоянно развиваются. Хочется пожелать Halyk Market побольше здоровой агрессии и пошире ассортимент</t>
@@ -38155,7 +37533,6 @@
       <c r="C965" t="n">
         <v>5</v>
       </c>
-      <c r="D965" t="inlineStr"/>
       <c r="E965" t="inlineStr">
         <is>
           <t>почему кридит не дадут</t>
@@ -38194,7 +37571,6 @@
       <c r="C966" t="n">
         <v>5</v>
       </c>
-      <c r="D966" t="inlineStr"/>
       <c r="E966" t="inlineStr">
         <is>
           <t>Да очень удобное!!!</t>
@@ -38233,7 +37609,6 @@
       <c r="C967" t="n">
         <v>5</v>
       </c>
-      <c r="D967" t="inlineStr"/>
       <c r="E967" t="inlineStr">
         <is>
           <t>очень удобное</t>
@@ -38272,7 +37647,7 @@
       <c r="C968" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D968" s="2" t="inlineStr"/>
+      <c r="D968" s="2" t="n"/>
       <c r="E968" s="2" t="inlineStr">
         <is>
           <t>Плохо, что нельзя сделать скриншот квитанций с экрана, поэтому «3».</t>
@@ -38311,7 +37686,6 @@
       <c r="C969" t="n">
         <v>5</v>
       </c>
-      <c r="D969" t="inlineStr"/>
       <c r="E969" t="inlineStr">
         <is>
           <t>жақсы</t>
@@ -38350,7 +37724,6 @@
       <c r="C970" t="n">
         <v>5</v>
       </c>
-      <c r="D970" t="inlineStr"/>
       <c r="E970" t="inlineStr">
         <is>
           <t>Сәттілік</t>
@@ -38389,7 +37762,6 @@
       <c r="C971" t="n">
         <v>5</v>
       </c>
-      <c r="D971" t="inlineStr"/>
       <c r="E971" t="inlineStr">
         <is>
           <t>рахмет сіздерге</t>
@@ -38428,7 +37800,6 @@
       <c r="C972" t="n">
         <v>5</v>
       </c>
-      <c r="D972" t="inlineStr"/>
       <c r="E972" t="inlineStr">
         <is>
           <t>Очень нравится. Отлично работайте!</t>
@@ -38467,7 +37838,7 @@
       <c r="C973" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D973" s="2" t="inlineStr"/>
+      <c r="D973" s="2" t="n"/>
       <c r="E973" s="2" t="inlineStr">
         <is>
           <t>после того как с меня недавно сняли 1000 за замену зарплатой карты два года назад, в 24 году, за пару дней до истечения срока годности карты, Я все больше задумываюсь о переходе в другой банк</t>
@@ -38506,7 +37877,6 @@
       <c r="C974" t="n">
         <v>5</v>
       </c>
-      <c r="D974" t="inlineStr"/>
       <c r="E974" t="inlineStr">
         <is>
           <t>спасибо что вы есть всё очень хорошо</t>
@@ -38545,7 +37915,6 @@
       <c r="C975" t="n">
         <v>5</v>
       </c>
-      <c r="D975" t="inlineStr"/>
       <c r="E975" t="inlineStr">
         <is>
           <t>Очень удобный. Никаких проблем с оплатой.</t>
@@ -38584,7 +37953,6 @@
       <c r="C976" t="n">
         <v>5</v>
       </c>
-      <c r="D976" t="inlineStr"/>
       <c r="E976" t="inlineStr">
         <is>
           <t>очень удобное приложение.</t>
@@ -38623,7 +37991,6 @@
       <c r="C977" t="n">
         <v>4</v>
       </c>
-      <c r="D977" t="inlineStr"/>
       <c r="E977" t="inlineStr">
         <is>
           <t>Раньше видела,сколько остаётся на счету,а теперь пишут сколько списывается,а остаток не показывает,надо каждый раз заходить в приложение....</t>
@@ -38662,7 +38029,6 @@
       <c r="C978" t="n">
         <v>5</v>
       </c>
-      <c r="D978" t="inlineStr"/>
       <c r="E978" t="inlineStr">
         <is>
           <t>қолдану өте ыңғайлы түсінікті</t>
@@ -38701,7 +38067,6 @@
       <c r="C979" t="n">
         <v>5</v>
       </c>
-      <c r="D979" t="inlineStr"/>
       <c r="E979" t="inlineStr">
         <is>
           <t>отлично, молодцы</t>
@@ -38740,7 +38105,6 @@
       <c r="C980" t="n">
         <v>5</v>
       </c>
-      <c r="D980" t="inlineStr"/>
       <c r="E980" t="inlineStr">
         <is>
           <t>👌👍Все Ok</t>
@@ -38779,7 +38143,6 @@
       <c r="C981" t="n">
         <v>5</v>
       </c>
-      <c r="D981" t="inlineStr"/>
       <c r="E981" t="inlineStr">
         <is>
           <t>отлично 👍</t>
@@ -38818,7 +38181,7 @@
       <c r="C982" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D982" s="2" t="inlineStr"/>
+      <c r="D982" s="2" t="n"/>
       <c r="E982" s="2" t="inlineStr">
         <is>
           <t>притормаживает</t>
@@ -38857,7 +38220,6 @@
       <c r="C983" t="n">
         <v>5</v>
       </c>
-      <c r="D983" t="inlineStr"/>
       <c r="E983" t="inlineStr">
         <is>
           <t>всё супер</t>
@@ -38896,7 +38258,7 @@
       <c r="C984" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D984" s="2" t="inlineStr"/>
+      <c r="D984" s="2" t="n"/>
       <c r="E984" s="2" t="inlineStr">
         <is>
           <t>В целом всё нравится, но будет отлично что при оплате налогов в квитанции Вы будете выводит код налога (как в цифровом формате, так и в буквенном), так и в какой УГД ушёл налог. Так как столкнувшись с этим, пришлось пройти 33 круга ада, что бы узнать куда были отправлены деньги, и то ответ предоставить полностью корректно так и не смогли, читаю данная информация очень актуальна. Спасибо</t>
@@ -38935,7 +38297,6 @@
       <c r="C985" t="n">
         <v>5</v>
       </c>
-      <c r="D985" t="inlineStr"/>
       <c r="E985" t="inlineStr">
         <is>
           <t>Самый лучший халык банк</t>
@@ -38974,7 +38335,7 @@
       <c r="C986" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D986" s="2" t="inlineStr"/>
+      <c r="D986" s="2" t="n"/>
       <c r="E986" s="2" t="inlineStr">
         <is>
           <t>у меня вопрос к банку по поводу беспричинной блокировки моей карты, когда я решила расторгнуть Договор только тогда её разблокировали, так и не объяснив причину. Само Приложение удобное, функционал большой, нравится.</t>
@@ -39013,7 +38374,6 @@
       <c r="C987" t="n">
         <v>5</v>
       </c>
-      <c r="D987" t="inlineStr"/>
       <c r="E987" t="inlineStr">
         <is>
           <t>Пока все нравится</t>
@@ -39052,7 +38412,6 @@
       <c r="C988" t="n">
         <v>5</v>
       </c>
-      <c r="D988" t="inlineStr"/>
       <c r="E988" t="inlineStr">
         <is>
           <t>вы лучшие</t>
@@ -39091,7 +38450,6 @@
       <c r="C989" t="n">
         <v>5</v>
       </c>
-      <c r="D989" t="inlineStr"/>
       <c r="E989" t="inlineStr">
         <is>
           <t>отлично все</t>
@@ -39130,7 +38488,6 @@
       <c r="C990" t="n">
         <v>5</v>
       </c>
-      <c r="D990" t="inlineStr"/>
       <c r="E990" t="inlineStr">
         <is>
           <t>Приложением легео пользоваться, все функция понятны и доступгы.</t>
@@ -39169,7 +38526,7 @@
       <c r="C991" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D991" s="2" t="inlineStr"/>
+      <c r="D991" s="2" t="n"/>
       <c r="E991" s="2" t="inlineStr">
         <is>
           <t>дно,не понятно за что списывают деньги</t>
@@ -39208,7 +38565,6 @@
       <c r="C992" t="n">
         <v>5</v>
       </c>
-      <c r="D992" t="inlineStr"/>
       <c r="E992" t="inlineStr">
         <is>
           <t>мы довольные</t>
@@ -39247,7 +38603,6 @@
       <c r="C993" t="n">
         <v>5</v>
       </c>
-      <c r="D993" t="inlineStr"/>
       <c r="E993" t="inlineStr">
         <is>
           <t>удобно</t>
@@ -39286,7 +38641,6 @@
       <c r="C994" t="n">
         <v>5</v>
       </c>
-      <c r="D994" t="inlineStr"/>
       <c r="E994" t="inlineStr">
         <is>
           <t>керемет</t>
@@ -39325,7 +38679,6 @@
       <c r="C995" t="n">
         <v>5</v>
       </c>
-      <c r="D995" t="inlineStr"/>
       <c r="E995" t="inlineStr">
         <is>
           <t>да всё понятно нравится</t>
@@ -39364,7 +38717,6 @@
       <c r="C996" t="n">
         <v>5</v>
       </c>
-      <c r="D996" t="inlineStr"/>
       <c r="E996" t="inlineStr">
         <is>
           <t>удобно, быстро.</t>
@@ -39403,7 +38755,6 @@
       <c r="C997" t="n">
         <v>5</v>
       </c>
-      <c r="D997" t="inlineStr"/>
       <c r="E997" t="inlineStr">
         <is>
           <t>Спасибо Вам.</t>
@@ -39442,7 +38793,6 @@
       <c r="C998" t="n">
         <v>5</v>
       </c>
-      <c r="D998" t="inlineStr"/>
       <c r="E998" t="inlineStr">
         <is>
           <t>Нравится. С этим банком я с 2001 года. как только появилось приложение, сразу стал пользоваться. Единственная просьба ускорить отображение переводов со счёта на депозит и обратно, плюс: расширить линейку товаров в маркете</t>
@@ -39481,7 +38831,6 @@
       <c r="C999" t="n">
         <v>5</v>
       </c>
-      <c r="D999" t="inlineStr"/>
       <c r="E999" t="inlineStr">
         <is>
           <t>улкен Рахмет жумыстарына саттилик тилеймин</t>
@@ -39520,7 +38869,6 @@
       <c r="C1000" t="n">
         <v>5</v>
       </c>
-      <c r="D1000" t="inlineStr"/>
       <c r="E1000" t="inlineStr">
         <is>
           <t>удобно</t>
@@ -39559,7 +38907,7 @@
       <c r="C1001" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D1001" s="2" t="inlineStr"/>
+      <c r="D1001" s="2" t="n"/>
       <c r="E1001" s="2" t="inlineStr">
         <is>
           <t>очень неудобное приложение</t>
@@ -39598,7 +38946,6 @@
       <c r="C1002" t="n">
         <v>5</v>
       </c>
-      <c r="D1002" t="inlineStr"/>
       <c r="E1002" t="inlineStr">
         <is>
           <t>доступно. удобно</t>
@@ -39637,7 +38984,6 @@
       <c r="C1003" t="n">
         <v>5</v>
       </c>
-      <c r="D1003" t="inlineStr"/>
       <c r="E1003" t="inlineStr">
         <is>
           <t>халық банк ең жақсы банк.</t>
@@ -39676,7 +39022,6 @@
       <c r="C1004" t="n">
         <v>5</v>
       </c>
-      <c r="D1004" t="inlineStr"/>
       <c r="E1004" t="inlineStr">
         <is>
           <t>отличное</t>
@@ -39715,7 +39060,7 @@
       <c r="C1005" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D1005" s="2" t="inlineStr"/>
+      <c r="D1005" s="2" t="n"/>
       <c r="E1005" s="2" t="inlineStr">
         <is>
           <t>29. 6авг2026: в invest невозможно отфильтровать все операции по одному предприятию. приходиться выкачивать все полностью. 24.Нельзя онлайн заказать съем валюты с депозита 25мар2025 21.При пополнении отбасы не выходит имя получателя.21дек24 17.Нет справок на английском.</t>
@@ -39726,7 +39071,7 @@
           <t>Mark Avrely</t>
         </is>
       </c>
-      <c r="G1005" s="2" t="inlineStr"/>
+      <c r="G1005" s="2" t="n"/>
       <c r="H1005" s="2" t="inlineStr">
         <is>
           <t>bc8a4bd3e03e5568bff53044</t>
@@ -39750,7 +39095,6 @@
       <c r="C1006" t="n">
         <v>5</v>
       </c>
-      <c r="D1006" t="inlineStr"/>
       <c r="E1006" t="inlineStr">
         <is>
           <t>спасибо Наlyk</t>
@@ -39789,7 +39133,6 @@
       <c r="C1007" t="n">
         <v>5</v>
       </c>
-      <c r="D1007" t="inlineStr"/>
       <c r="E1007" t="inlineStr">
         <is>
           <t>👍👍👍</t>
@@ -39828,7 +39171,6 @@
       <c r="C1008" t="n">
         <v>5</v>
       </c>
-      <c r="D1008" t="inlineStr"/>
       <c r="E1008" t="inlineStr">
         <is>
           <t>Всё нравится</t>
@@ -39867,7 +39209,6 @@
       <c r="C1009" t="n">
         <v>5</v>
       </c>
-      <c r="D1009" t="inlineStr"/>
       <c r="E1009" t="inlineStr">
         <is>
           <t>🤘</t>
@@ -39906,7 +39247,6 @@
       <c r="C1010" t="n">
         <v>5</v>
       </c>
-      <c r="D1010" t="inlineStr"/>
       <c r="E1010" t="inlineStr">
         <is>
           <t>хорошо</t>
@@ -39945,7 +39285,6 @@
       <c r="C1011" t="n">
         <v>5</v>
       </c>
-      <c r="D1011" t="inlineStr"/>
       <c r="E1011" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -39984,7 +39323,6 @@
       <c r="C1012" t="n">
         <v>5</v>
       </c>
-      <c r="D1012" t="inlineStr"/>
       <c r="E1012" t="inlineStr">
         <is>
           <t>почему каждые три дня надо обновлять приложение ?</t>
@@ -40023,7 +39361,6 @@
       <c r="C1013" t="n">
         <v>5</v>
       </c>
-      <c r="D1013" t="inlineStr"/>
       <c r="E1013" t="inlineStr">
         <is>
           <t>Удобно</t>
@@ -40062,7 +39399,6 @@
       <c r="C1014" t="n">
         <v>5</v>
       </c>
-      <c r="D1014" t="inlineStr"/>
       <c r="E1014" t="inlineStr">
         <is>
           <t>удобное приложение. Спасибо.</t>
@@ -40101,7 +39437,6 @@
       <c r="C1015" t="n">
         <v>5</v>
       </c>
-      <c r="D1015" t="inlineStr"/>
       <c r="E1015" t="inlineStr">
         <is>
           <t>супер</t>
@@ -40140,7 +39475,6 @@
       <c r="C1016" t="n">
         <v>5</v>
       </c>
-      <c r="D1016" t="inlineStr"/>
       <c r="E1016" t="inlineStr">
         <is>
           <t>Нам с народным банком повезло ,спасибо большое</t>
@@ -40151,7 +39485,6 @@
           <t>Тамара Нурабаева</t>
         </is>
       </c>
-      <c r="G1016" t="inlineStr"/>
       <c r="H1016" t="inlineStr">
         <is>
           <t>799e102aaa99a6a11aca4680</t>
@@ -40175,7 +39508,6 @@
       <c r="C1017" t="n">
         <v>5</v>
       </c>
-      <c r="D1017" t="inlineStr"/>
       <c r="E1017" t="inlineStr">
         <is>
           <t>Все отлично, но сайт Маркет это что то ужасное, один раз решил воспользоваться, больше ни за что на свете.</t>
@@ -40214,7 +39546,6 @@
       <c r="C1018" t="n">
         <v>5</v>
       </c>
-      <c r="D1018" t="inlineStr"/>
       <c r="E1018" t="inlineStr">
         <is>
           <t>Күшті</t>
@@ -40253,7 +39584,6 @@
       <c r="C1019" t="n">
         <v>5</v>
       </c>
-      <c r="D1019" t="inlineStr"/>
       <c r="E1019" t="inlineStr">
         <is>
           <t>спасибо за приложение</t>
@@ -40292,7 +39622,6 @@
       <c r="C1020" t="n">
         <v>5</v>
       </c>
-      <c r="D1020" t="inlineStr"/>
       <c r="E1020" t="inlineStr">
         <is>
           <t>здравствуйте ! очень нравится благодарю за приложения .</t>
@@ -40331,7 +39660,6 @@
       <c r="C1021" t="n">
         <v>4</v>
       </c>
-      <c r="D1021" t="inlineStr"/>
       <c r="E1021" t="inlineStr">
         <is>
           <t>Немного замудрённее, Каспи легче прямо для динозавров. мне лично нравится🙌🏻. Сроки предоставления выписок движения финансов✊🏻 желательно бы за последние 2 года</t>
@@ -40370,7 +39698,6 @@
       <c r="C1022" t="n">
         <v>5</v>
       </c>
-      <c r="D1022" t="inlineStr"/>
       <c r="E1022" t="inlineStr">
         <is>
           <t>круто!</t>
@@ -40409,7 +39736,6 @@
       <c r="C1023" t="n">
         <v>5</v>
       </c>
-      <c r="D1023" t="inlineStr"/>
       <c r="E1023" t="inlineStr">
         <is>
           <t>почему оплата квитанции не уходит?</t>
@@ -40448,7 +39774,6 @@
       <c r="C1024" t="n">
         <v>5</v>
       </c>
-      <c r="D1024" t="inlineStr"/>
       <c r="E1024" t="inlineStr">
         <is>
           <t>очень хорошее приложение</t>
@@ -40487,7 +39812,6 @@
       <c r="C1025" t="n">
         <v>5</v>
       </c>
-      <c r="D1025" t="inlineStr"/>
       <c r="E1025" t="inlineStr">
         <is>
           <t>ок</t>
@@ -40526,7 +39850,6 @@
       <c r="C1026" t="n">
         <v>5</v>
       </c>
-      <c r="D1026" t="inlineStr"/>
       <c r="E1026" t="inlineStr">
         <is>
           <t>я ұнайды, үлкен рахмет</t>
@@ -40565,7 +39888,6 @@
       <c r="C1027" t="n">
         <v>5</v>
       </c>
-      <c r="D1027" t="inlineStr"/>
       <c r="E1027" t="inlineStr">
         <is>
           <t>хорошо</t>
@@ -40604,7 +39926,6 @@
       <c r="C1028" t="n">
         <v>5</v>
       </c>
-      <c r="D1028" t="inlineStr"/>
       <c r="E1028" t="inlineStr">
         <is>
           <t>удобно, комфортно и почти без глюков!</t>
@@ -40643,7 +39964,6 @@
       <c r="C1029" t="n">
         <v>5</v>
       </c>
-      <c r="D1029" t="inlineStr"/>
       <c r="E1029" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -40682,7 +40002,7 @@
       <c r="C1030" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D1030" s="2" t="inlineStr"/>
+      <c r="D1030" s="2" t="n"/>
       <c r="E1030" s="2" t="inlineStr">
         <is>
           <t>Что с приложением? Постоянно нужно удалять, заново устанавливать. И это только с халыком. Ужас!</t>
@@ -40721,7 +40041,6 @@
       <c r="C1031" t="n">
         <v>5</v>
       </c>
-      <c r="D1031" t="inlineStr"/>
       <c r="E1031" t="inlineStr">
         <is>
           <t>удобное приложение 👍</t>
@@ -40760,7 +40079,6 @@
       <c r="C1032" t="n">
         <v>4</v>
       </c>
-      <c r="D1032" t="inlineStr"/>
       <c r="E1032" t="inlineStr">
         <is>
           <t>все доступно и понятно, единственный минус чтоб ушло уведомление надо каждый раз нажимать на сообщения, даже если ты просмотрел в приложении</t>
@@ -40799,7 +40117,6 @@
       <c r="C1033" t="n">
         <v>5</v>
       </c>
-      <c r="D1033" t="inlineStr"/>
       <c r="E1033" t="inlineStr">
         <is>
           <t>вы супер</t>
@@ -40838,7 +40155,6 @@
       <c r="C1034" t="n">
         <v>5</v>
       </c>
-      <c r="D1034" t="inlineStr"/>
       <c r="E1034" t="inlineStr">
         <is>
           <t>хорошее приложение</t>
@@ -40877,7 +40193,6 @@
       <c r="C1035" t="n">
         <v>5</v>
       </c>
-      <c r="D1035" t="inlineStr"/>
       <c r="E1035" t="inlineStr">
         <is>
           <t>ххалык банк тин хыззмет корсету сапасы оте тийимди ари жаксы</t>
@@ -40916,7 +40231,6 @@
       <c r="C1036" t="n">
         <v>4</v>
       </c>
-      <c r="D1036" t="inlineStr"/>
       <c r="E1036" t="inlineStr">
         <is>
           <t>почему не приходят СМС о пополнении счета и переводе денег?</t>
@@ -40955,7 +40269,6 @@
       <c r="C1037" t="n">
         <v>5</v>
       </c>
-      <c r="D1037" t="inlineStr"/>
       <c r="E1037" t="inlineStr">
         <is>
           <t>Все доступно,понятно.</t>
@@ -40994,7 +40307,7 @@
       <c r="C1038" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D1038" s="2" t="inlineStr"/>
+      <c r="D1038" s="2" t="n"/>
       <c r="E1038" s="2" t="inlineStr">
         <is>
           <t>здравствуйте,приложение не плохое, но, при оплате коммунальных услуг, долго выходит квитанция,</t>
@@ -41033,7 +40346,6 @@
       <c r="C1039" t="n">
         <v>5</v>
       </c>
-      <c r="D1039" t="inlineStr"/>
       <c r="E1039" t="inlineStr">
         <is>
           <t>надежный банк, удобное приложение</t>
@@ -41072,7 +40384,6 @@
       <c r="C1040" t="n">
         <v>5</v>
       </c>
-      <c r="D1040" t="inlineStr"/>
       <c r="E1040" t="inlineStr">
         <is>
           <t>удобно делать переводы и платежи</t>
@@ -41111,7 +40422,6 @@
       <c r="C1041" t="n">
         <v>5</v>
       </c>
-      <c r="D1041" t="inlineStr"/>
       <c r="E1041" t="inlineStr">
         <is>
           <t>Рахмет.</t>
@@ -41150,7 +40460,6 @@
       <c r="C1042" t="n">
         <v>5</v>
       </c>
-      <c r="D1042" t="inlineStr"/>
       <c r="E1042" t="inlineStr">
         <is>
           <t>Все удобно</t>
@@ -41189,7 +40498,6 @@
       <c r="C1043" t="n">
         <v>5</v>
       </c>
-      <c r="D1043" t="inlineStr"/>
       <c r="E1043" t="inlineStr">
         <is>
           <t>Приложение Супер</t>
@@ -41228,7 +40536,6 @@
       <c r="C1044" t="n">
         <v>5</v>
       </c>
-      <c r="D1044" t="inlineStr"/>
       <c r="E1044" t="inlineStr">
         <is>
           <t>Өте жақсы!!!</t>
@@ -41267,7 +40574,6 @@
       <c r="C1045" t="n">
         <v>5</v>
       </c>
-      <c r="D1045" t="inlineStr"/>
       <c r="E1045" t="inlineStr">
         <is>
           <t>нормально,жаль по Каспий куару нельзя оплатить</t>
@@ -41306,7 +40612,6 @@
       <c r="C1046" t="n">
         <v>5</v>
       </c>
-      <c r="D1046" t="inlineStr"/>
       <c r="E1046" t="inlineStr">
         <is>
           <t>норм👌</t>
@@ -41317,7 +40622,6 @@
           <t>Баян Асанова</t>
         </is>
       </c>
-      <c r="G1046" t="inlineStr"/>
       <c r="H1046" t="inlineStr">
         <is>
           <t>898a34e28cbf642d4d48dd2f</t>
@@ -41341,7 +40645,6 @@
       <c r="C1047" t="n">
         <v>5</v>
       </c>
-      <c r="D1047" t="inlineStr"/>
       <c r="E1047" t="inlineStr">
         <is>
           <t>супер</t>
@@ -41380,7 +40683,6 @@
       <c r="C1048" t="n">
         <v>5</v>
       </c>
-      <c r="D1048" t="inlineStr"/>
       <c r="E1048" t="inlineStr">
         <is>
           <t>очень крутой Банк</t>
@@ -41419,7 +40721,6 @@
       <c r="C1049" t="n">
         <v>5</v>
       </c>
-      <c r="D1049" t="inlineStr"/>
       <c r="E1049" t="inlineStr">
         <is>
           <t>нравится абсолютно всё</t>
@@ -41458,7 +40759,6 @@
       <c r="C1050" t="n">
         <v>5</v>
       </c>
-      <c r="D1050" t="inlineStr"/>
       <c r="E1050" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -41497,7 +40797,6 @@
       <c r="C1051" t="n">
         <v>5</v>
       </c>
-      <c r="D1051" t="inlineStr"/>
       <c r="E1051" t="inlineStr">
         <is>
           <t>хорошее приложение, удобно и понятно</t>
@@ -41536,7 +40835,6 @@
       <c r="C1052" t="n">
         <v>4</v>
       </c>
-      <c r="D1052" t="inlineStr"/>
       <c r="E1052" t="inlineStr">
         <is>
           <t>начал глючить фейс пей, пару раз в прошлом переставал работать, но последние пару недель -чуть ли не каждые три четыре дня - снимите головной убор, служба поддержки говорит: отключайте и снова включайте, официально сбоев нет. поправка: вчера отключил, восстановил - сегодня опять - снимите головной убор - мне налысо постричься чтобы опознавать начал?</t>
@@ -41575,7 +40873,6 @@
       <c r="C1053" t="n">
         <v>5</v>
       </c>
-      <c r="D1053" t="inlineStr"/>
       <c r="E1053" t="inlineStr">
         <is>
           <t>Удобно, практично, все действия понятны</t>
@@ -41614,7 +40911,6 @@
       <c r="C1054" t="n">
         <v>5</v>
       </c>
-      <c r="D1054" t="inlineStr"/>
       <c r="E1054" t="inlineStr">
         <is>
           <t>Очень удобно!</t>
@@ -41653,7 +40949,6 @@
       <c r="C1055" t="n">
         <v>5</v>
       </c>
-      <c r="D1055" t="inlineStr"/>
       <c r="E1055" t="inlineStr">
         <is>
           <t>хотелось бы чтобы оповещения приходили</t>
@@ -41692,7 +40987,6 @@
       <c r="C1056" t="n">
         <v>5</v>
       </c>
-      <c r="D1056" t="inlineStr"/>
       <c r="E1056" t="inlineStr">
         <is>
           <t>Все отлично</t>
@@ -41731,7 +41025,7 @@
       <c r="C1057" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D1057" s="2" t="inlineStr"/>
+      <c r="D1057" s="2" t="n"/>
       <c r="E1057" s="2" t="inlineStr">
         <is>
           <t>не удобно перечислять ,в др.банки РК. Не справедливо сняли за выпуск карты.</t>
@@ -41770,7 +41064,6 @@
       <c r="C1058" t="n">
         <v>5</v>
       </c>
-      <c r="D1058" t="inlineStr"/>
       <c r="E1058" t="inlineStr">
         <is>
           <t>отлично 👍</t>
@@ -41809,7 +41102,6 @@
       <c r="C1059" t="n">
         <v>5</v>
       </c>
-      <c r="D1059" t="inlineStr"/>
       <c r="E1059" t="inlineStr">
         <is>
           <t>Рахмет</t>
@@ -41848,7 +41140,6 @@
       <c r="C1060" t="n">
         <v>4</v>
       </c>
-      <c r="D1060" t="inlineStr"/>
       <c r="E1060" t="inlineStr">
         <is>
           <t>зачем сообщать о моих тратах</t>
@@ -41887,7 +41178,6 @@
       <c r="C1061" t="n">
         <v>5</v>
       </c>
-      <c r="D1061" t="inlineStr"/>
       <c r="E1061" t="inlineStr">
         <is>
           <t>Бывает подвисает приложение,а так нормально</t>
@@ -41926,7 +41216,6 @@
       <c r="C1062" t="n">
         <v>5</v>
       </c>
-      <c r="D1062" t="inlineStr"/>
       <c r="E1062" t="inlineStr">
         <is>
           <t>супер приложение</t>
@@ -41965,7 +41254,7 @@
       <c r="C1063" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1063" s="2" t="inlineStr"/>
+      <c r="D1063" s="2" t="n"/>
       <c r="E1063" s="2" t="inlineStr">
         <is>
           <t>включается сам сабай лимит на снятие денег</t>
@@ -42004,7 +41293,6 @@
       <c r="C1064" t="n">
         <v>5</v>
       </c>
-      <c r="D1064" t="inlineStr"/>
       <c r="E1064" t="inlineStr">
         <is>
           <t>почему кридит не даёте с зарплатные картай всегда выходит нет</t>
@@ -42043,7 +41331,6 @@
       <c r="C1065" t="n">
         <v>5</v>
       </c>
-      <c r="D1065" t="inlineStr"/>
       <c r="E1065" t="inlineStr">
         <is>
           <t>Удобный банк маркет страховка самый дешовый но в маркете есть минус там сбрасовает при просмотре</t>
@@ -42082,7 +41369,6 @@
       <c r="C1066" t="n">
         <v>5</v>
       </c>
-      <c r="D1066" t="inlineStr"/>
       <c r="E1066" t="inlineStr">
         <is>
           <t>рахмет</t>
@@ -42121,7 +41407,6 @@
       <c r="C1067" t="n">
         <v>5</v>
       </c>
-      <c r="D1067" t="inlineStr"/>
       <c r="E1067" t="inlineStr">
         <is>
           <t>нормално.тек кредит ал деп смс жібере бермесеңдер болды.</t>
@@ -42160,7 +41445,6 @@
       <c r="C1068" t="n">
         <v>5</v>
       </c>
-      <c r="D1068" t="inlineStr"/>
       <c r="E1068" t="inlineStr">
         <is>
           <t>отличное приложение</t>
@@ -42199,7 +41483,6 @@
       <c r="C1069" t="n">
         <v>5</v>
       </c>
-      <c r="D1069" t="inlineStr"/>
       <c r="E1069" t="inlineStr">
         <is>
           <t>жақсы</t>
@@ -42210,7 +41493,6 @@
           <t>Erbolat Mahanov</t>
         </is>
       </c>
-      <c r="G1069" t="inlineStr"/>
       <c r="H1069" t="inlineStr">
         <is>
           <t>46918770baa0c487d702b79f</t>
@@ -42234,7 +41516,6 @@
       <c r="C1070" t="n">
         <v>5</v>
       </c>
-      <c r="D1070" t="inlineStr"/>
       <c r="E1070" t="inlineStr">
         <is>
           <t>я нечаянно нажала неправильно 2 цифры своего номера теперь не могу войти в свой халык помогите</t>
@@ -42273,7 +41554,6 @@
       <c r="C1071" t="n">
         <v>5</v>
       </c>
-      <c r="D1071" t="inlineStr"/>
       <c r="E1071" t="inlineStr">
         <is>
           <t>тема</t>
@@ -42312,7 +41592,7 @@
       <c r="C1072" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1072" s="2" t="inlineStr"/>
+      <c r="D1072" s="2" t="n"/>
       <c r="E1072" s="2" t="inlineStr">
         <is>
           <t>При переходе в мой банк вкладку, доходы, расходы отражаются коряво, приложение лагучее, какие вкладки вообще бывают не работают, картинки наименований отображаются некорректно, не понимаю самый крупный банк, и не могут в порядок привести свое приложение.</t>
@@ -42351,7 +41631,6 @@
       <c r="C1073" t="n">
         <v>5</v>
       </c>
-      <c r="D1073" t="inlineStr"/>
       <c r="E1073" t="inlineStr">
         <is>
           <t>удобно</t>
@@ -42390,7 +41669,7 @@
       <c r="C1074" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D1074" s="2" t="inlineStr"/>
+      <c r="D1074" s="2" t="n"/>
       <c r="E1074" s="2" t="inlineStr">
         <is>
           <t>перевод 200 это много.</t>
@@ -42429,7 +41708,6 @@
       <c r="C1075" t="n">
         <v>5</v>
       </c>
-      <c r="D1075" t="inlineStr"/>
       <c r="E1075" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -42468,7 +41746,6 @@
       <c r="C1076" t="n">
         <v>5</v>
       </c>
-      <c r="D1076" t="inlineStr"/>
       <c r="E1076" t="inlineStr">
         <is>
           <t>керемет</t>
@@ -42507,7 +41784,6 @@
       <c r="C1077" t="n">
         <v>4</v>
       </c>
-      <c r="D1077" t="inlineStr"/>
       <c r="E1077" t="inlineStr">
         <is>
           <t>отсутствует оповещение и связь с егов после проведения операций, неонятно на какой стадии запрос</t>
@@ -42546,7 +41822,6 @@
       <c r="C1078" t="n">
         <v>5</v>
       </c>
-      <c r="D1078" t="inlineStr"/>
       <c r="E1078" t="inlineStr">
         <is>
           <t>супер!</t>
@@ -42585,7 +41860,6 @@
       <c r="C1079" t="n">
         <v>5</v>
       </c>
-      <c r="D1079" t="inlineStr"/>
       <c r="E1079" t="inlineStr">
         <is>
           <t>👍</t>
@@ -42624,7 +41898,7 @@
       <c r="C1080" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1080" s="2" t="inlineStr"/>
+      <c r="D1080" s="2" t="n"/>
       <c r="E1080" s="2" t="inlineStr">
         <is>
           <t>никогда не пользуйтесь приложением Халык маркет. там продавцы продают бракованные товары.и проблемы с возратом ,вы сами за всё платите только через Каспи.через Халык не вздумайте</t>
@@ -42663,7 +41937,6 @@
       <c r="C1081" t="n">
         <v>5</v>
       </c>
-      <c r="D1081" t="inlineStr"/>
       <c r="E1081" t="inlineStr">
         <is>
           <t>Супер</t>
@@ -42702,7 +41975,6 @@
       <c r="C1082" t="n">
         <v>5</v>
       </c>
-      <c r="D1082" t="inlineStr"/>
       <c r="E1082" t="inlineStr">
         <is>
           <t>благодарю за вашу работу.</t>
@@ -42741,7 +42013,6 @@
       <c r="C1083" t="n">
         <v>5</v>
       </c>
-      <c r="D1083" t="inlineStr"/>
       <c r="E1083" t="inlineStr">
         <is>
           <t>Всё в помощь клиенту</t>
@@ -42780,7 +42051,6 @@
       <c r="C1084" t="n">
         <v>5</v>
       </c>
-      <c r="D1084" t="inlineStr"/>
       <c r="E1084" t="inlineStr">
         <is>
           <t>пока всё отлично</t>
@@ -42819,7 +42089,6 @@
       <c r="C1085" t="n">
         <v>5</v>
       </c>
-      <c r="D1085" t="inlineStr"/>
       <c r="E1085" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -42858,7 +42127,7 @@
       <c r="C1086" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1086" s="2" t="inlineStr"/>
+      <c r="D1086" s="2" t="n"/>
       <c r="E1086" s="2" t="inlineStr">
         <is>
           <t>Отлично</t>
@@ -42897,7 +42166,6 @@
       <c r="C1087" t="n">
         <v>5</v>
       </c>
-      <c r="D1087" t="inlineStr"/>
       <c r="E1087" t="inlineStr">
         <is>
           <t>Ништяк!</t>
@@ -42936,7 +42204,6 @@
       <c r="C1088" t="n">
         <v>5</v>
       </c>
-      <c r="D1088" t="inlineStr"/>
       <c r="E1088" t="inlineStr">
         <is>
           <t>классное приложение хороший банк</t>
@@ -42975,7 +42242,6 @@
       <c r="C1089" t="n">
         <v>5</v>
       </c>
-      <c r="D1089" t="inlineStr"/>
       <c r="E1089" t="inlineStr">
         <is>
           <t>Өте керемет</t>
@@ -43014,7 +42280,6 @@
       <c r="C1090" t="n">
         <v>5</v>
       </c>
-      <c r="D1090" t="inlineStr"/>
       <c r="E1090" t="inlineStr">
         <is>
           <t>,👍✊</t>
@@ -43053,7 +42318,6 @@
       <c r="C1091" t="n">
         <v>5</v>
       </c>
-      <c r="D1091" t="inlineStr"/>
       <c r="E1091" t="inlineStr">
         <is>
           <t>хотелось бы получать больше кэшбеков)</t>
@@ -43092,7 +42356,7 @@
       <c r="C1092" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D1092" s="2" t="inlineStr"/>
+      <c r="D1092" s="2" t="n"/>
       <c r="E1092" s="2" t="inlineStr">
         <is>
           <t>перевод долго приходит</t>
@@ -43131,7 +42395,6 @@
       <c r="C1093" t="n">
         <v>5</v>
       </c>
-      <c r="D1093" t="inlineStr"/>
       <c r="E1093" t="inlineStr">
         <is>
           <t>приложение очень удобно</t>
@@ -43170,7 +42433,6 @@
       <c r="C1094" t="n">
         <v>5</v>
       </c>
-      <c r="D1094" t="inlineStr"/>
       <c r="E1094" t="inlineStr">
         <is>
           <t>Очень удобно!</t>
@@ -43216,7 +42478,6 @@
       <c r="C1096" t="n">
         <v>5</v>
       </c>
-      <c r="D1096" t="inlineStr"/>
       <c r="E1096" t="inlineStr">
         <is>
           <t>Отлично</t>
@@ -43296,7 +42557,6 @@
       <c r="C1097" t="n">
         <v>5</v>
       </c>
-      <c r="D1097" t="inlineStr"/>
       <c r="E1097" t="inlineStr">
         <is>
           <t>спасибо</t>
@@ -43376,7 +42636,6 @@
       <c r="C1098" t="n">
         <v>5</v>
       </c>
-      <c r="D1098" t="inlineStr"/>
       <c r="E1098" t="inlineStr">
         <is>
           <t>всё на высшем уровне</t>
@@ -43456,7 +42715,6 @@
       <c r="C1099" t="n">
         <v>5</v>
       </c>
-      <c r="D1099" t="inlineStr"/>
       <c r="E1099" t="inlineStr">
         <is>
           <t>👍</t>
@@ -43536,7 +42794,6 @@
       <c r="C1100" t="n">
         <v>5</v>
       </c>
-      <c r="D1100" t="inlineStr"/>
       <c r="E1100" t="inlineStr">
         <is>
           <t>Мне кажется что приложение очень удобное и функциональное, покрайней мере возможностей достаточно. Особенное спасибо за бонусы, которые получаешь при оплате через терминал. Очень лёгкое и понятное, думаю что даже пожилым клиентам будет комфортно. Могу рекомендовать.</t>
@@ -43575,7 +42832,6 @@
       <c r="C1101" t="n">
         <v>5</v>
       </c>
-      <c r="D1101" t="inlineStr"/>
       <c r="E1101" t="inlineStr">
         <is>
           <t>отлично работает</t>
@@ -43614,7 +42870,7 @@
       <c r="C1102" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D1102" s="2" t="inlineStr"/>
+      <c r="D1102" s="2" t="n"/>
       <c r="E1102" s="2" t="inlineStr">
         <is>
           <t>Сервис Каспий работает намного быстрее чем ваш, платежи проходят быстро, у вас даже комиссия вжимается за пополнение детского депозита, часто переводы и оплата зависает</t>
@@ -43653,7 +42909,6 @@
       <c r="C1103" t="n">
         <v>5</v>
       </c>
-      <c r="D1103" t="inlineStr"/>
       <c r="E1103" t="inlineStr">
         <is>
           <t>одобрили бы денежный кредит на 5000000 ,вообще поставил бы 10 звёзд.</t>
@@ -43692,7 +42947,6 @@
       <c r="C1104" t="n">
         <v>5</v>
       </c>
-      <c r="D1104" t="inlineStr"/>
       <c r="E1104" t="inlineStr">
         <is>
           <t>супер</t>
@@ -43731,7 +42985,7 @@
       <c r="C1105" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1105" s="2" t="inlineStr"/>
+      <c r="D1105" s="2" t="n"/>
       <c r="E1105" s="2" t="inlineStr">
         <is>
           <t>Отлично</t>
@@ -43770,7 +43024,6 @@
       <c r="C1106" t="n">
         <v>5</v>
       </c>
-      <c r="D1106" t="inlineStr"/>
       <c r="E1106" t="inlineStr">
         <is>
           <t>Отлично очень хорошо 5+5</t>
@@ -43809,7 +43062,6 @@
       <c r="C1107" t="n">
         <v>5</v>
       </c>
-      <c r="D1107" t="inlineStr"/>
       <c r="E1107" t="inlineStr">
         <is>
           <t>Отличное приложение 👍👍👍💯</t>
@@ -43848,7 +43100,6 @@
       <c r="C1108" t="n">
         <v>5</v>
       </c>
-      <c r="D1108" t="inlineStr"/>
       <c r="E1108" t="inlineStr">
         <is>
           <t>удачи вам, процветания и успехов!!!</t>
@@ -43887,7 +43138,6 @@
       <c r="C1109" t="n">
         <v>5</v>
       </c>
-      <c r="D1109" t="inlineStr"/>
       <c r="E1109" t="inlineStr">
         <is>
           <t>жалко нет золотой короны</t>
@@ -43926,7 +43176,6 @@
       <c r="C1110" t="n">
         <v>5</v>
       </c>
-      <c r="D1110" t="inlineStr"/>
       <c r="E1110" t="inlineStr">
         <is>
           <t>вас люблю</t>
@@ -43937,7 +43186,6 @@
           <t>Гульнур Есенкулова</t>
         </is>
       </c>
-      <c r="G1110" t="inlineStr"/>
       <c r="H1110" t="inlineStr">
         <is>
           <t>1b68443221b3a3679d143354</t>
@@ -43961,7 +43209,7 @@
       <c r="C1111" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1111" s="2" t="inlineStr"/>
+      <c r="D1111" s="2" t="n"/>
       <c r="E1111" s="2" t="inlineStr">
         <is>
           <t>ужасный банк ,если может избежать общения с банком ,не используйте приложение, блокирует все переводы, операторы некомпетентны, как работает система никто не знает!</t>
@@ -44000,7 +43248,6 @@
       <c r="C1112" t="n">
         <v>5</v>
       </c>
-      <c r="D1112" t="inlineStr"/>
       <c r="E1112" t="inlineStr">
         <is>
           <t>самый лутчый банк в мире</t>
@@ -44039,7 +43286,6 @@
       <c r="C1113" t="n">
         <v>5</v>
       </c>
-      <c r="D1113" t="inlineStr"/>
       <c r="E1113" t="inlineStr">
         <is>
           <t>Меня всё устраивает,мне нравиться.</t>
@@ -44078,7 +43324,7 @@
       <c r="C1114" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D1114" s="2" t="inlineStr"/>
+      <c r="D1114" s="2" t="n"/>
       <c r="E1114" s="2" t="inlineStr">
         <is>
           <t>очень-очень неудобный халык-магазин, сервисы халык аптека. в остальном нареканий нет</t>
@@ -44117,7 +43363,6 @@
       <c r="C1115" t="n">
         <v>5</v>
       </c>
-      <c r="D1115" t="inlineStr"/>
       <c r="E1115" t="inlineStr">
         <is>
           <t>очень нравиться</t>
@@ -44156,7 +43401,6 @@
       <c r="C1116" t="n">
         <v>5</v>
       </c>
-      <c r="D1116" t="inlineStr"/>
       <c r="E1116" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -44195,7 +43439,6 @@
       <c r="C1117" t="n">
         <v>5</v>
       </c>
-      <c r="D1117" t="inlineStr"/>
       <c r="E1117" t="inlineStr">
         <is>
           <t>я довольно с Халык банком</t>
@@ -44234,7 +43477,6 @@
       <c r="C1118" t="n">
         <v>5</v>
       </c>
-      <c r="D1118" t="inlineStr"/>
       <c r="E1118" t="inlineStr">
         <is>
           <t>великолепный</t>
@@ -44273,7 +43515,6 @@
       <c r="C1119" t="n">
         <v>5</v>
       </c>
-      <c r="D1119" t="inlineStr"/>
       <c r="E1119" t="inlineStr">
         <is>
           <t>удобно</t>
@@ -44312,7 +43553,6 @@
       <c r="C1120" t="n">
         <v>5</v>
       </c>
-      <c r="D1120" t="inlineStr"/>
       <c r="E1120" t="inlineStr">
         <is>
           <t>супер</t>
@@ -44351,7 +43591,6 @@
       <c r="C1121" t="n">
         <v>5</v>
       </c>
-      <c r="D1121" t="inlineStr"/>
       <c r="E1121" t="inlineStr">
         <is>
           <t>Благодарю за сервис👌👍👍👍</t>
@@ -44390,7 +43629,6 @@
       <c r="C1122" t="n">
         <v>5</v>
       </c>
-      <c r="D1122" t="inlineStr"/>
       <c r="E1122" t="inlineStr">
         <is>
           <t>великолепное приложение</t>
@@ -44429,7 +43667,6 @@
       <c r="C1123" t="n">
         <v>5</v>
       </c>
-      <c r="D1123" t="inlineStr"/>
       <c r="E1123" t="inlineStr">
         <is>
           <t>спасибо</t>
@@ -44440,7 +43677,6 @@
           <t>Айгуль Айгуль</t>
         </is>
       </c>
-      <c r="G1123" t="inlineStr"/>
       <c r="H1123" t="inlineStr">
         <is>
           <t>ca339496efdeaa9f54ea7e17</t>
@@ -44464,7 +43700,6 @@
       <c r="C1124" t="n">
         <v>5</v>
       </c>
-      <c r="D1124" t="inlineStr"/>
       <c r="E1124" t="inlineStr">
         <is>
           <t>рақмет сізге халық банк</t>
@@ -44503,7 +43738,6 @@
       <c r="C1125" t="n">
         <v>5</v>
       </c>
-      <c r="D1125" t="inlineStr"/>
       <c r="E1125" t="inlineStr">
         <is>
           <t>всегда в доступе и возможность выполнять широкий спектр действий</t>
@@ -44542,7 +43776,6 @@
       <c r="C1126" t="n">
         <v>5</v>
       </c>
-      <c r="D1126" t="inlineStr"/>
       <c r="E1126" t="inlineStr">
         <is>
           <t>надо добавить в магазин рейтинговую систему а в целом очень хорошее приложение</t>
@@ -44581,7 +43814,6 @@
       <c r="C1127" t="n">
         <v>5</v>
       </c>
-      <c r="D1127" t="inlineStr"/>
       <c r="E1127" t="inlineStr">
         <is>
           <t>өте кушти</t>
@@ -44620,7 +43852,6 @@
       <c r="C1128" t="n">
         <v>5</v>
       </c>
-      <c r="D1128" t="inlineStr"/>
       <c r="E1128" t="inlineStr">
         <is>
           <t>касппй ашыныз</t>
@@ -44659,7 +43890,6 @@
       <c r="C1129" t="n">
         <v>5</v>
       </c>
-      <c r="D1129" t="inlineStr"/>
       <c r="E1129" t="inlineStr">
         <is>
           <t>очень</t>
@@ -44698,7 +43928,6 @@
       <c r="C1130" t="n">
         <v>4</v>
       </c>
-      <c r="D1130" t="inlineStr"/>
       <c r="E1130" t="inlineStr">
         <is>
           <t>все удобно, кроме того что не приходит уведомление о зарплате. июль 2026, после обноаления рекомендует обновить и не запускается</t>
@@ -44737,7 +43966,7 @@
       <c r="C1131" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1131" s="2" t="inlineStr"/>
+      <c r="D1131" s="2" t="n"/>
       <c r="E1131" s="2" t="inlineStr">
         <is>
           <t>не могу переводить крупную сумму денег со своего счета в НБ в РБК, сразу блокируют счёт, всё смахивают на ИИ бардак!!!</t>
@@ -44776,7 +44005,6 @@
       <c r="C1132" t="n">
         <v>5</v>
       </c>
-      <c r="D1132" t="inlineStr"/>
       <c r="E1132" t="inlineStr">
         <is>
           <t>отличная работа ,теперь ни один мошенник не захочет сюда зайти</t>
@@ -44815,7 +44043,6 @@
       <c r="C1133" t="n">
         <v>5</v>
       </c>
-      <c r="D1133" t="inlineStr"/>
       <c r="E1133" t="inlineStr">
         <is>
           <t>хорошо</t>
@@ -44854,7 +44081,6 @@
       <c r="C1134" t="n">
         <v>5</v>
       </c>
-      <c r="D1134" t="inlineStr"/>
       <c r="E1134" t="inlineStr">
         <is>
           <t>ХОРОШО !</t>
@@ -44893,7 +44119,7 @@
       <c r="C1135" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1135" s="2" t="inlineStr"/>
+      <c r="D1135" s="2" t="n"/>
       <c r="E1135" s="2" t="inlineStr">
         <is>
           <t>Не могу войти в приложение, говорит что на моем устройстве неофициальная ОС</t>
@@ -44932,7 +44158,6 @@
       <c r="C1136" t="n">
         <v>5</v>
       </c>
-      <c r="D1136" t="inlineStr"/>
       <c r="E1136" t="inlineStr">
         <is>
           <t>все отлично</t>
@@ -44971,7 +44196,6 @@
       <c r="C1137" t="n">
         <v>5</v>
       </c>
-      <c r="D1137" t="inlineStr"/>
       <c r="E1137" t="inlineStr">
         <is>
           <t>Добрый день,всё отлично.</t>
@@ -45010,7 +44234,6 @@
       <c r="C1138" t="n">
         <v>5</v>
       </c>
-      <c r="D1138" t="inlineStr"/>
       <c r="E1138" t="inlineStr">
         <is>
           <t>отличное приложение</t>
@@ -45049,7 +44272,7 @@
       <c r="C1139" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D1139" s="2" t="inlineStr"/>
+      <c r="D1139" s="2" t="n"/>
       <c r="E1139" s="2" t="inlineStr">
         <is>
           <t>Очень долго</t>
@@ -45060,7 +44283,7 @@
           <t>Комерция</t>
         </is>
       </c>
-      <c r="G1139" s="2" t="inlineStr"/>
+      <c r="G1139" s="2" t="n"/>
       <c r="H1139" s="2" t="inlineStr">
         <is>
           <t>e0ac670da04668c28bcd0465</t>
@@ -45084,7 +44307,7 @@
       <c r="C1140" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1140" s="2" t="inlineStr"/>
+      <c r="D1140" s="2" t="n"/>
       <c r="E1140" s="2" t="inlineStr">
         <is>
           <t>Бесконечная переустановка лагающего приложения</t>
@@ -45095,7 +44318,7 @@
           <t>филя</t>
         </is>
       </c>
-      <c r="G1140" s="2" t="inlineStr"/>
+      <c r="G1140" s="2" t="n"/>
       <c r="H1140" s="2" t="inlineStr">
         <is>
           <t>f58cbb600c0143c24ac367fd</t>
@@ -45126,7 +44349,7 @@
       <c r="C1142" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1142" s="2" t="inlineStr"/>
+      <c r="D1142" s="2" t="n"/>
       <c r="E1142" s="2" t="inlineStr">
         <is>
           <t>При каждом запуске приложения оно просит его обновить и сразу же закрывается, даже несмотря на то что приложение уже обновлено.</t>
@@ -45137,7 +44360,7 @@
           <t>Ольга Ковалёва</t>
         </is>
       </c>
-      <c r="G1142" s="2" t="inlineStr"/>
+      <c r="G1142" s="2" t="n"/>
       <c r="H1142" s="2" t="inlineStr">
         <is>
           <t>6fe754a40eba29654bdcbb77</t>
@@ -45202,7 +44425,6 @@
       <c r="C1143" t="n">
         <v>5</v>
       </c>
-      <c r="D1143" t="inlineStr"/>
       <c r="E1143" t="inlineStr">
         <is>
           <t>все хорошо</t>
@@ -45241,7 +44463,7 @@
       <c r="C1144" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1144" s="2" t="inlineStr"/>
+      <c r="D1144" s="2" t="n"/>
       <c r="E1144" s="2" t="inlineStr">
         <is>
           <t>Приложение долго грузится, а сам банк до ужаса не удобный. Раньше мне он нравился, но после некоторых обстоятельств полностью упал в моих глаза. Как и приложение, в которой приходится проходить видео проверку по 100 раз, но по итогу ничего не выходит. Желание пользоваться приложением и банком отпало</t>
@@ -45280,7 +44502,6 @@
       <c r="C1145" t="n">
         <v>5</v>
       </c>
-      <c r="D1145" t="inlineStr"/>
       <c r="E1145" t="inlineStr">
         <is>
           <t>бомба</t>
@@ -45319,7 +44540,6 @@
       <c r="C1146" t="n">
         <v>5</v>
       </c>
-      <c r="D1146" t="inlineStr"/>
       <c r="E1146" t="inlineStr">
         <is>
           <t>супер</t>
@@ -45358,7 +44578,7 @@
       <c r="C1147" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1147" s="2" t="inlineStr"/>
+      <c r="D1147" s="2" t="n"/>
       <c r="E1147" s="2" t="inlineStr">
         <is>
           <t>Почему, чтобы войти в приложение, я должен идентифицироваться, я не могу без входа посмотреть как на Каспий товары?</t>
@@ -45397,7 +44617,6 @@
       <c r="C1148" t="n">
         <v>5</v>
       </c>
-      <c r="D1148" t="inlineStr"/>
       <c r="E1148" t="inlineStr">
         <is>
           <t>всегда мобильно</t>
@@ -45436,7 +44655,6 @@
       <c r="C1149" t="n">
         <v>5</v>
       </c>
-      <c r="D1149" t="inlineStr"/>
       <c r="E1149" t="inlineStr">
         <is>
           <t>хорошо 👍</t>
@@ -45475,7 +44693,6 @@
       <c r="C1150" t="n">
         <v>5</v>
       </c>
-      <c r="D1150" t="inlineStr"/>
       <c r="E1150" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -45514,7 +44731,6 @@
       <c r="C1151" t="n">
         <v>5</v>
       </c>
-      <c r="D1151" t="inlineStr"/>
       <c r="E1151" t="inlineStr">
         <is>
           <t>А мне всё нравиться! Да, чат бот как то не понятно работает))) ну это не особо важный момент. По финансовым движением всё прозрачно, и понятно. Я доволен на всё 💯 PS очень хотелось хоть раз выиграть бонусы 🙈 всем хорошего настроения , и здоровья!</t>
@@ -45553,7 +44769,6 @@
       <c r="C1152" t="n">
         <v>5</v>
       </c>
-      <c r="D1152" t="inlineStr"/>
       <c r="E1152" t="inlineStr">
         <is>
           <t>Спасибо</t>
@@ -45592,7 +44807,6 @@
       <c r="C1153" t="n">
         <v>5</v>
       </c>
-      <c r="D1153" t="inlineStr"/>
       <c r="E1153" t="inlineStr">
         <is>
           <t>спасибо что с нами</t>
@@ -45631,7 +44845,6 @@
       <c r="C1154" t="n">
         <v>5</v>
       </c>
-      <c r="D1154" t="inlineStr"/>
       <c r="E1154" t="inlineStr">
         <is>
           <t>Всё нравится. Интерфейс удобный. Ничего лишнего</t>
@@ -45670,7 +44883,6 @@
       <c r="C1155" t="n">
         <v>5</v>
       </c>
-      <c r="D1155" t="inlineStr"/>
       <c r="E1155" t="inlineStr">
         <is>
           <t>керемет 👍👍👍 жақсы, рахмет</t>
@@ -45716,7 +44928,7 @@
       <c r="C1157" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1157" s="2" t="inlineStr"/>
+      <c r="D1157" s="2" t="n"/>
       <c r="E1157" s="2" t="inlineStr">
         <is>
           <t>1.Кредит- Одобрено!!! пока до 9 утра нельзя подтвердить. 2.Маркет виснет 2026г. 3.Доставка нет-никто не знает- Когда?!! 4.Продавец не отвечает - нет системы с продавцами - деньги вернули! 5. нет логистики при возврате от покупателя. 6 .Сделайте Календарь платежей для людей по месяцам-сколько платежей по Каждому кредиту. 7. Почему последний платеж выставляется,на день оформление кредита 8. чтобы открыть депозит 6 меч не выгодно. чтобы снять свои деньги надо платить 1%. ужасно условия для кого.</t>
@@ -45755,7 +44967,7 @@
       <c r="C1158" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1158" s="2" t="inlineStr"/>
+      <c r="D1158" s="2" t="n"/>
       <c r="E1158" s="2" t="inlineStr">
         <is>
           <t>ай-яй-яй, делал страховку на авто, получил довеском услуги и вторую страховку каско. совесть есть? риторический вопрос.</t>
@@ -45794,7 +45006,7 @@
       <c r="C1159" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1159" s="2" t="inlineStr"/>
+      <c r="D1159" s="2" t="n"/>
       <c r="E1159" s="2" t="inlineStr">
         <is>
           <t>никакой стабильности. Кикнуло с кабинета и не получается войти обратно уже полгода. Даже поддержка не помогла, просто бесконечная загрузка при проверке данных для входа</t>
@@ -45805,7 +45017,7 @@
           <t>Åmir</t>
         </is>
       </c>
-      <c r="G1159" s="2" t="inlineStr"/>
+      <c r="G1159" s="2" t="n"/>
       <c r="H1159" s="2" t="inlineStr">
         <is>
           <t>6d2597dc603a0af06aa1d7c8</t>
@@ -45829,7 +45041,6 @@
       <c r="C1160" t="n">
         <v>5</v>
       </c>
-      <c r="D1160" t="inlineStr"/>
       <c r="E1160" t="inlineStr">
         <is>
           <t>оперативный банк! отличная работа операторов</t>
@@ -45868,7 +45079,6 @@
       <c r="C1161" t="n">
         <v>4</v>
       </c>
-      <c r="D1161" t="inlineStr"/>
       <c r="E1161" t="inlineStr">
         <is>
           <t>Тяжёлое приложение. Долго грузится.</t>
@@ -45907,7 +45117,7 @@
       <c r="C1162" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1162" s="2" t="inlineStr"/>
+      <c r="D1162" s="2" t="n"/>
       <c r="E1162" s="2" t="inlineStr">
         <is>
           <t>в неделю 2раза удаляю приложение народного банка,это походу издевательство,сделайте что нибудь</t>
@@ -45946,7 +45156,6 @@
       <c r="C1163" t="n">
         <v>5</v>
       </c>
-      <c r="D1163" t="inlineStr"/>
       <c r="E1163" t="inlineStr">
         <is>
           <t>молодцы</t>
@@ -45985,7 +45194,6 @@
       <c r="C1164" t="n">
         <v>5</v>
       </c>
-      <c r="D1164" t="inlineStr"/>
       <c r="E1164" t="inlineStr">
         <is>
           <t>Супер</t>
@@ -46024,7 +45232,7 @@
       <c r="C1165" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1165" s="2" t="inlineStr"/>
+      <c r="D1165" s="2" t="n"/>
       <c r="E1165" s="2" t="inlineStr">
         <is>
           <t>Автоматически включены дополниельные платные услуги, отказ явно не показан.</t>
@@ -46063,7 +45271,7 @@
       <c r="C1166" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D1166" s="2" t="inlineStr"/>
+      <c r="D1166" s="2" t="n"/>
       <c r="E1166" s="2" t="inlineStr">
         <is>
           <t>сильно зависает, каспи работает стабильнее</t>
@@ -46102,7 +45310,6 @@
       <c r="C1167" t="n">
         <v>5</v>
       </c>
-      <c r="D1167" t="inlineStr"/>
       <c r="E1167" t="inlineStr">
         <is>
           <t>еще чуть чуть доработать придожение ибудет супер очень удобно</t>
@@ -46141,7 +45348,7 @@
       <c r="C1168" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D1168" s="2" t="inlineStr"/>
+      <c r="D1168" s="2" t="n"/>
       <c r="E1168" s="2" t="inlineStr">
         <is>
           <t>не могу войти в приложение. просят до обновить до заново пройти регистрацию. начинаешь это делать всё равно не проходит теперь опять говорят едте в банк а мой ближайший банк в 100 км.от моего села. вообщем и это уже не первый случай.</t>
@@ -46152,7 +45359,7 @@
           <t>Рустам Оспанов</t>
         </is>
       </c>
-      <c r="G1168" s="2" t="inlineStr"/>
+      <c r="G1168" s="2" t="n"/>
       <c r="H1168" s="2" t="inlineStr">
         <is>
           <t>aa4a356b215d7688a4626398</t>
@@ -46176,7 +45383,6 @@
       <c r="C1169" t="n">
         <v>5</v>
       </c>
-      <c r="D1169" t="inlineStr"/>
       <c r="E1169" t="inlineStr">
         <is>
           <t>жаксы</t>
@@ -46215,7 +45421,6 @@
       <c r="C1170" t="n">
         <v>5</v>
       </c>
-      <c r="D1170" t="inlineStr"/>
       <c r="E1170" t="inlineStr">
         <is>
           <t>очень хорошо</t>
@@ -46254,7 +45459,7 @@
       <c r="C1171" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1171" s="2" t="inlineStr"/>
+      <c r="D1171" s="2" t="n"/>
       <c r="E1171" s="2" t="inlineStr">
         <is>
           <t>мне не дают кредит</t>
@@ -46293,7 +45498,6 @@
       <c r="C1172" t="n">
         <v>5</v>
       </c>
-      <c r="D1172" t="inlineStr"/>
       <c r="E1172" t="inlineStr">
         <is>
           <t>жаксы</t>
@@ -46332,7 +45536,7 @@
       <c r="C1173" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1173" s="2" t="inlineStr"/>
+      <c r="D1173" s="2" t="n"/>
       <c r="E1173" s="2" t="inlineStr">
         <is>
           <t>не запускает просит удалит и скачать новое обновление</t>
@@ -46371,7 +45575,6 @@
       <c r="C1174" t="n">
         <v>4</v>
       </c>
-      <c r="D1174" t="inlineStr"/>
       <c r="E1174" t="inlineStr">
         <is>
           <t>нет сообщений, нет бонусов вообще</t>
@@ -46410,7 +45613,6 @@
       <c r="C1175" t="n">
         <v>5</v>
       </c>
-      <c r="D1175" t="inlineStr"/>
       <c r="E1175" t="inlineStr">
         <is>
           <t>мен ушін номер бірінші банк</t>
@@ -46449,7 +45651,6 @@
       <c r="C1176" t="n">
         <v>5</v>
       </c>
-      <c r="D1176" t="inlineStr"/>
       <c r="E1176" t="inlineStr">
         <is>
           <t>Халық банк ең сенімді банк</t>
@@ -46488,7 +45689,6 @@
       <c r="C1177" t="n">
         <v>5</v>
       </c>
-      <c r="D1177" t="inlineStr"/>
       <c r="E1177" t="inlineStr">
         <is>
           <t>супер</t>
@@ -46527,7 +45727,6 @@
       <c r="C1178" t="n">
         <v>5</v>
       </c>
-      <c r="D1178" t="inlineStr"/>
       <c r="E1178" t="inlineStr">
         <is>
           <t>Очень удобно</t>
@@ -46566,7 +45765,7 @@
       <c r="C1179" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1179" s="2" t="inlineStr"/>
+      <c r="D1179" s="2" t="n"/>
       <c r="E1179" s="2" t="inlineStr">
         <is>
           <t>не могу зарегистрироваться</t>
@@ -46577,7 +45776,7 @@
           <t>Екатерина Байжуминова</t>
         </is>
       </c>
-      <c r="G1179" s="2" t="inlineStr"/>
+      <c r="G1179" s="2" t="n"/>
       <c r="H1179" s="2" t="inlineStr">
         <is>
           <t>264a89942116281b17a000ee</t>
@@ -46601,7 +45800,7 @@
       <c r="C1180" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1180" s="2" t="inlineStr"/>
+      <c r="D1180" s="2" t="n"/>
       <c r="E1180" s="2" t="inlineStr">
         <is>
           <t>каждый месяц удаляю приложение и заново скачивать требуете, вот сегодня тоже требует удалить опять скачать надо и это уже четвертый месяц продолжается</t>
@@ -46640,7 +45839,6 @@
       <c r="C1181" t="n">
         <v>5</v>
       </c>
-      <c r="D1181" t="inlineStr"/>
       <c r="E1181" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -46679,7 +45877,6 @@
       <c r="C1182" t="n">
         <v>5</v>
       </c>
-      <c r="D1182" t="inlineStr"/>
       <c r="E1182" t="inlineStr">
         <is>
           <t>Желаю процветания своему банку</t>
@@ -46725,7 +45922,7 @@
       <c r="C1184" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1184" s="2" t="inlineStr"/>
+      <c r="D1184" s="2" t="n"/>
       <c r="E1184" s="2" t="inlineStr">
         <is>
           <t>Здравствуйте ваше приложение Народного банка занова запрашивает обновление я удаляю опять закачиваю и опять просит обновления вы издеваетесь, устраните пожалуйста проблему</t>
@@ -46807,7 +46004,6 @@
       <c r="C1185" t="n">
         <v>4</v>
       </c>
-      <c r="D1185" t="inlineStr"/>
       <c r="E1185" t="inlineStr">
         <is>
           <t>иногда бывают глюки в общем много удобного в приложении . больше проблем с юр приложением. там вообще все печально часто..</t>
@@ -46846,7 +46042,6 @@
       <c r="C1186" t="n">
         <v>5</v>
       </c>
-      <c r="D1186" t="inlineStr"/>
       <c r="E1186" t="inlineStr">
         <is>
           <t>спасибо большое</t>
@@ -46885,7 +46080,6 @@
       <c r="C1187" t="n">
         <v>5</v>
       </c>
-      <c r="D1187" t="inlineStr"/>
       <c r="E1187" t="inlineStr">
         <is>
           <t>удобно</t>
@@ -46924,7 +46118,7 @@
       <c r="C1188" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1188" s="2" t="inlineStr"/>
+      <c r="D1188" s="2" t="n"/>
       <c r="E1188" s="2" t="inlineStr">
         <is>
           <t>приложение перестала работать не могу зайти обновите приложение написано захожу чтобы обновить а там обновление нету исправьте пожалуйста.Пришлось удалить приложение и заново установить.</t>
@@ -46963,7 +46157,7 @@
       <c r="C1189" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1189" s="2" t="inlineStr"/>
+      <c r="D1189" s="2" t="n"/>
       <c r="E1189" s="2" t="inlineStr">
         <is>
           <t>очень разочарован банком и как закрою кредит удалю это приложение</t>
@@ -47002,7 +46196,7 @@
       <c r="C1190" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D1190" s="2" t="inlineStr"/>
+      <c r="D1190" s="2" t="n"/>
       <c r="E1190" s="2" t="inlineStr">
         <is>
           <t>жұмыстарыңызға береке берсін</t>
@@ -47041,7 +46235,6 @@
       <c r="C1191" t="n">
         <v>5</v>
       </c>
-      <c r="D1191" t="inlineStr"/>
       <c r="E1191" t="inlineStr">
         <is>
           <t>срасибо</t>
@@ -47080,7 +46273,6 @@
       <c r="C1192" t="n">
         <v>5</v>
       </c>
-      <c r="D1192" t="inlineStr"/>
       <c r="E1192" t="inlineStr">
         <is>
           <t>приятно работать с вашим банком</t>
@@ -47119,7 +46311,6 @@
       <c r="C1193" t="n">
         <v>5</v>
       </c>
-      <c r="D1193" t="inlineStr"/>
       <c r="E1193" t="inlineStr">
         <is>
           <t>мне нравится. удобно</t>
@@ -47158,7 +46349,6 @@
       <c r="C1194" t="n">
         <v>5</v>
       </c>
-      <c r="D1194" t="inlineStr"/>
       <c r="E1194" t="inlineStr">
         <is>
           <t>отличное приложение</t>
@@ -47197,7 +46387,6 @@
       <c r="C1195" t="n">
         <v>5</v>
       </c>
-      <c r="D1195" t="inlineStr"/>
       <c r="E1195" t="inlineStr">
         <is>
           <t>Ыңғайлы банк</t>
@@ -47236,7 +46425,7 @@
       <c r="C1196" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1196" s="2" t="inlineStr"/>
+      <c r="D1196" s="2" t="n"/>
       <c r="E1196" s="2" t="inlineStr">
         <is>
           <t>почему с приложение выкидывает</t>
@@ -47275,7 +46464,6 @@
       <c r="C1197" t="n">
         <v>5</v>
       </c>
-      <c r="D1197" t="inlineStr"/>
       <c r="E1197" t="inlineStr">
         <is>
           <t>Как предложение, реализовать в приложении функцию просмотра графика предстоящих платежей при выборе полного или частичного досрочного погашения с отображением расчётной остаточной суммы задолженности.</t>
@@ -47314,7 +46502,6 @@
       <c r="C1198" t="n">
         <v>5</v>
       </c>
-      <c r="D1198" t="inlineStr"/>
       <c r="E1198" t="inlineStr">
         <is>
           <t>супер</t>
@@ -47353,7 +46540,6 @@
       <c r="C1199" t="n">
         <v>5</v>
       </c>
-      <c r="D1199" t="inlineStr"/>
       <c r="E1199" t="inlineStr">
         <is>
           <t>очень удобно, оплата всё и сразу быстро!!!</t>
@@ -47399,7 +46585,6 @@
       <c r="C1201" t="n">
         <v>5</v>
       </c>
-      <c r="D1201" t="inlineStr"/>
       <c r="E1201" t="inlineStr">
         <is>
           <t>Рахмет вам, все хорошо!</t>
@@ -47479,7 +46664,6 @@
       <c r="C1202" t="n">
         <v>5</v>
       </c>
-      <c r="D1202" t="inlineStr"/>
       <c r="E1202" t="inlineStr">
         <is>
           <t>всё хорошо</t>
@@ -47518,7 +46702,6 @@
       <c r="C1203" t="n">
         <v>5</v>
       </c>
-      <c r="D1203" t="inlineStr"/>
       <c r="E1203" t="inlineStr">
         <is>
           <t>клас</t>
@@ -47557,7 +46740,6 @@
       <c r="C1204" t="n">
         <v>5</v>
       </c>
-      <c r="D1204" t="inlineStr"/>
       <c r="E1204" t="inlineStr">
         <is>
           <t>Удобно, информативно, быстро. Надёжное стабильное приложение, как сам Банк.</t>
@@ -47596,7 +46778,6 @@
       <c r="C1205" t="n">
         <v>5</v>
       </c>
-      <c r="D1205" t="inlineStr"/>
       <c r="E1205" t="inlineStr">
         <is>
           <t>Удобно. Главное - надёжное приложение</t>
@@ -47635,7 +46816,6 @@
       <c r="C1206" t="n">
         <v>5</v>
       </c>
-      <c r="D1206" t="inlineStr"/>
       <c r="E1206" t="inlineStr">
         <is>
           <t>Всё отлично спасибо</t>
@@ -47674,7 +46854,6 @@
       <c r="C1207" t="n">
         <v>5</v>
       </c>
-      <c r="D1207" t="inlineStr"/>
       <c r="E1207" t="inlineStr">
         <is>
           <t>керемет</t>
@@ -47713,7 +46892,7 @@
       <c r="C1208" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D1208" s="2" t="inlineStr"/>
+      <c r="D1208" s="2" t="n"/>
       <c r="E1208" s="2" t="inlineStr">
         <is>
           <t>очень низкое интернет соединение.</t>
@@ -47752,7 +46931,6 @@
       <c r="C1209" t="n">
         <v>5</v>
       </c>
-      <c r="D1209" t="inlineStr"/>
       <c r="E1209" t="inlineStr">
         <is>
           <t>жақсы</t>
@@ -47791,7 +46969,6 @@
       <c r="C1210" t="n">
         <v>5</v>
       </c>
-      <c r="D1210" t="inlineStr"/>
       <c r="E1210" t="inlineStr">
         <is>
           <t>всегда понятно и внятно</t>
@@ -47830,7 +47007,6 @@
       <c r="C1211" t="n">
         <v>5</v>
       </c>
-      <c r="D1211" t="inlineStr"/>
       <c r="E1211" t="inlineStr">
         <is>
           <t>всё отлично,люблю халык банк</t>
@@ -47876,7 +47052,6 @@
       <c r="C1213" t="n">
         <v>5</v>
       </c>
-      <c r="D1213" t="inlineStr"/>
       <c r="E1213" t="inlineStr">
         <is>
           <t>спасибо что Вы по человечески отнеслись ко мне !</t>
@@ -47915,7 +47090,6 @@
       <c r="C1214" t="n">
         <v>5</v>
       </c>
-      <c r="D1214" t="inlineStr"/>
       <c r="E1214" t="inlineStr">
         <is>
           <t>Доверяю этому банку 👍</t>
@@ -47954,7 +47128,6 @@
       <c r="C1215" t="n">
         <v>5</v>
       </c>
-      <c r="D1215" t="inlineStr"/>
       <c r="E1215" t="inlineStr">
         <is>
           <t>лучший</t>
@@ -47993,7 +47166,7 @@
       <c r="C1216" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1216" s="2" t="inlineStr"/>
+      <c r="D1216" s="2" t="n"/>
       <c r="E1216" s="2" t="inlineStr">
         <is>
           <t>самое медленное и тормознутое приложение</t>
@@ -48032,7 +47205,6 @@
       <c r="C1217" t="n">
         <v>5</v>
       </c>
-      <c r="D1217" t="inlineStr"/>
       <c r="E1217" t="inlineStr">
         <is>
           <t>👍</t>
@@ -48071,7 +47243,6 @@
       <c r="C1218" t="n">
         <v>4</v>
       </c>
-      <c r="D1218" t="inlineStr"/>
       <c r="E1218" t="inlineStr">
         <is>
           <t>Распечатка квитанции по ком.платежам получается слишком длинная.Надо чтоб на одном листе по форме квитанции АЛСЕКО</t>
@@ -48110,7 +47281,6 @@
       <c r="C1219" t="n">
         <v>5</v>
       </c>
-      <c r="D1219" t="inlineStr"/>
       <c r="E1219" t="inlineStr">
         <is>
           <t>приложение супер</t>
@@ -48149,7 +47319,6 @@
       <c r="C1220" t="n">
         <v>5</v>
       </c>
-      <c r="D1220" t="inlineStr"/>
       <c r="E1220" t="inlineStr">
         <is>
           <t>Все опции приложения удобные</t>
@@ -48188,7 +47357,6 @@
       <c r="C1221" t="n">
         <v>5</v>
       </c>
-      <c r="D1221" t="inlineStr"/>
       <c r="E1221" t="inlineStr">
         <is>
           <t>Ұнайды</t>
@@ -48227,7 +47395,6 @@
       <c r="C1222" t="n">
         <v>5</v>
       </c>
-      <c r="D1222" t="inlineStr"/>
       <c r="E1222" t="inlineStr">
         <is>
           <t>супер!!!</t>
@@ -48266,7 +47433,6 @@
       <c r="C1223" t="n">
         <v>5</v>
       </c>
-      <c r="D1223" t="inlineStr"/>
       <c r="E1223" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -48305,7 +47471,7 @@
       <c r="C1224" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1224" s="2" t="inlineStr"/>
+      <c r="D1224" s="2" t="n"/>
       <c r="E1224" s="2" t="inlineStr">
         <is>
           <t>не работает био идентификация на смартфоне vivo x300 pro. смартфон официальный, никаких проблем с другими банкингами, именно в халыке так</t>
@@ -48344,7 +47510,6 @@
       <c r="C1225" t="n">
         <v>5</v>
       </c>
-      <c r="D1225" t="inlineStr"/>
       <c r="E1225" t="inlineStr">
         <is>
           <t>отличное приложение , удобное , понятное .</t>
@@ -48383,7 +47548,7 @@
       <c r="C1226" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1226" s="2" t="inlineStr"/>
+      <c r="D1226" s="2" t="n"/>
       <c r="E1226" s="2" t="inlineStr">
         <is>
           <t>Разработка приложения ужасное. При оформления товарной рассрочки в Халык маркет высвечивается сразу отказ в рассрочке, это понятно. Но через три рабочих дня приходит уведомление что "кредитный договор АННУЛИРОВАН" и поэтому заявка не оформлена". Хочу понять что это значит, отвечают что мне отказали и это уведомление поздно пришло. Но как могут отказ аннулировать мне не понятно. В службе поддержки не могут это обьяснить.Как они могут не видеть содержания уведомления своих клиентов</t>
@@ -48422,7 +47587,6 @@
       <c r="C1227" t="n">
         <v>5</v>
       </c>
-      <c r="D1227" t="inlineStr"/>
       <c r="E1227" t="inlineStr">
         <is>
           <t>💯👍</t>
@@ -48461,7 +47625,6 @@
       <c r="C1228" t="n">
         <v>4</v>
       </c>
-      <c r="D1228" t="inlineStr"/>
       <c r="E1228" t="inlineStr">
         <is>
           <t>в сообщениях при движении средств по счетам не показывается остаток средств. раньше это было удобно</t>
@@ -48500,7 +47663,6 @@
       <c r="C1229" t="n">
         <v>5</v>
       </c>
-      <c r="D1229" t="inlineStr"/>
       <c r="E1229" t="inlineStr">
         <is>
           <t>здравствуйте! мне всё нравится в Вашем приложении! чётко, понятно, ничего лишнего. я использую спец.программу, несмотря на это, функционирует прекрасно! Благодарю!</t>
@@ -48539,7 +47701,6 @@
       <c r="C1230" t="n">
         <v>5</v>
       </c>
-      <c r="D1230" t="inlineStr"/>
       <c r="E1230" t="inlineStr">
         <is>
           <t>бар! жаксы</t>
@@ -48578,7 +47739,6 @@
       <c r="C1231" t="n">
         <v>4</v>
       </c>
-      <c r="D1231" t="inlineStr"/>
       <c r="E1231" t="inlineStr">
         <is>
           <t>Қосымша жақсы, бірақ кредит алуға берген тапсырысқа не үшін қарсвлық білдіргенін түсіндірмейді. Тек осы жағдайды білу үшін банкке бару керек пе! 7171 өле қалсаңда жауап бермейді.</t>
@@ -48617,7 +47777,7 @@
       <c r="C1232" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D1232" s="2" t="inlineStr"/>
+      <c r="D1232" s="2" t="n"/>
       <c r="E1232" s="2" t="inlineStr">
         <is>
           <t>в целом все не плохо с каждым разом улучшения есть но по юзерфрендли по дизайну и по расположению немножко теряешся как в каспи надо сделать все интуитивно понятно.</t>
@@ -48656,7 +47816,6 @@
       <c r="C1233" t="n">
         <v>5</v>
       </c>
-      <c r="D1233" t="inlineStr"/>
       <c r="E1233" t="inlineStr">
         <is>
           <t>да поидет</t>
@@ -48667,7 +47826,6 @@
           <t>Куат Тулеубеков</t>
         </is>
       </c>
-      <c r="G1233" t="inlineStr"/>
       <c r="H1233" t="inlineStr">
         <is>
           <t>5b07c3afc18a40e7dadba9b3</t>
@@ -48691,7 +47849,6 @@
       <c r="C1234" t="n">
         <v>5</v>
       </c>
-      <c r="D1234" t="inlineStr"/>
       <c r="E1234" t="inlineStr">
         <is>
           <t>приложение и банк Halyk супер спасибо за все.</t>
@@ -48730,7 +47887,6 @@
       <c r="C1235" t="n">
         <v>5</v>
       </c>
-      <c r="D1235" t="inlineStr"/>
       <c r="E1235" t="inlineStr">
         <is>
           <t>керемет</t>
@@ -48769,7 +47925,7 @@
       <c r="C1236" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1236" s="2" t="inlineStr"/>
+      <c r="D1236" s="2" t="n"/>
       <c r="E1236" s="2" t="inlineStr">
         <is>
           <t>Не открывается приложение. Зависает постоянно</t>
@@ -48808,7 +47964,6 @@
       <c r="C1237" t="n">
         <v>5</v>
       </c>
-      <c r="D1237" t="inlineStr"/>
       <c r="E1237" t="inlineStr">
         <is>
           <t>Ұнайды</t>
@@ -48847,7 +48002,6 @@
       <c r="C1238" t="n">
         <v>5</v>
       </c>
-      <c r="D1238" t="inlineStr"/>
       <c r="E1238" t="inlineStr">
         <is>
           <t>надёжный банк!</t>
@@ -48886,7 +48040,6 @@
       <c r="C1239" t="n">
         <v>4</v>
       </c>
-      <c r="D1239" t="inlineStr"/>
       <c r="E1239" t="inlineStr">
         <is>
           <t>приложение работает корректно, на трердые 4 звезды, ошибок не было замечено, однако почему переводы отображаются не сразу, а через некоторое время, это вводит в заблуждение, на мой взгляд это нужно скорректировать</t>
@@ -48925,7 +48078,6 @@
       <c r="C1240" t="n">
         <v>5</v>
       </c>
-      <c r="D1240" t="inlineStr"/>
       <c r="E1240" t="inlineStr">
         <is>
           <t>халық банк өте ыңғайлы жаксы банк</t>
@@ -48964,7 +48116,6 @@
       <c r="C1241" t="n">
         <v>5</v>
       </c>
-      <c r="D1241" t="inlineStr"/>
       <c r="E1241" t="inlineStr">
         <is>
           <t>ок</t>
@@ -49003,7 +48154,7 @@
       <c r="C1242" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1242" s="2" t="inlineStr"/>
+      <c r="D1242" s="2" t="n"/>
       <c r="E1242" s="2" t="inlineStr">
         <is>
           <t>Худший банк Казахстана. Банк требует 1% комиссии с уже истекшего по сроку депозита! И это ещё не все! За операцию, по которой другие банки не берут ничего, содрали почти 20 тысяч тенге. При попытке перевода денег на свой счет в другом банке блокируют доступ к приложению и к счетам. За полдня они вытворяют такое 4 раза! Остается теперь только закрыть все депозиты, внести банк в черный список. PS: прочитал другие отзывы и убедился, что я принял верное решение!</t>
@@ -49042,7 +48193,7 @@
       <c r="C1243" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1243" s="2" t="inlineStr"/>
+      <c r="D1243" s="2" t="n"/>
       <c r="E1243" s="2" t="inlineStr">
         <is>
           <t>Ассалаумағалейкум бұрынгысын кетирип кайта жүктеу керек обновит етип үнеми солай не сұмдык мынау</t>
@@ -49053,7 +48204,7 @@
           <t>Еламан Канатов</t>
         </is>
       </c>
-      <c r="G1243" s="2" t="inlineStr"/>
+      <c r="G1243" s="2" t="n"/>
       <c r="H1243" s="2" t="inlineStr">
         <is>
           <t>2ada9ef0f75a1eb83891fc77</t>
@@ -49077,7 +48228,6 @@
       <c r="C1244" t="n">
         <v>4</v>
       </c>
-      <c r="D1244" t="inlineStr"/>
       <c r="E1244" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -49116,7 +48266,6 @@
       <c r="C1245" t="n">
         <v>5</v>
       </c>
-      <c r="D1245" t="inlineStr"/>
       <c r="E1245" t="inlineStr">
         <is>
           <t>приложение на оценку отлично</t>
@@ -49155,7 +48304,6 @@
       <c r="C1246" t="n">
         <v>5</v>
       </c>
-      <c r="D1246" t="inlineStr"/>
       <c r="E1246" t="inlineStr">
         <is>
           <t>удобно</t>
@@ -49194,7 +48342,6 @@
       <c r="C1247" t="n">
         <v>5</v>
       </c>
-      <c r="D1247" t="inlineStr"/>
       <c r="E1247" t="inlineStr">
         <is>
           <t>супер банк</t>
@@ -49240,7 +48387,6 @@
       <c r="C1249" t="n">
         <v>5</v>
       </c>
-      <c r="D1249" t="inlineStr"/>
       <c r="E1249" t="inlineStr">
         <is>
           <t>нравится в простоте</t>
@@ -49279,7 +48425,7 @@
       <c r="C1250" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D1250" s="2" t="inlineStr"/>
+      <c r="D1250" s="2" t="n"/>
       <c r="E1250" s="2" t="inlineStr">
         <is>
           <t>туповатое по сравнению с каспи</t>
@@ -49318,7 +48464,6 @@
       <c r="C1251" t="n">
         <v>5</v>
       </c>
-      <c r="D1251" t="inlineStr"/>
       <c r="E1251" t="inlineStr">
         <is>
           <t>Жақсы</t>
@@ -49357,7 +48502,6 @@
       <c r="C1252" t="n">
         <v>5</v>
       </c>
-      <c r="D1252" t="inlineStr"/>
       <c r="E1252" t="inlineStr">
         <is>
           <t>надёжный банк 😇</t>
@@ -49396,7 +48540,7 @@
       <c r="C1253" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D1253" s="2" t="inlineStr"/>
+      <c r="D1253" s="2" t="n"/>
       <c r="E1253" s="2" t="inlineStr">
         <is>
           <t>Сервис стоит доработать - скорость приложения, зависает халык магазин, долго обрабатывается сумма</t>
@@ -49435,7 +48579,6 @@
       <c r="C1254" t="n">
         <v>5</v>
       </c>
-      <c r="D1254" t="inlineStr"/>
       <c r="E1254" t="inlineStr">
         <is>
           <t>Мне нравится многофункцианальность приложения, очень удобно в повседневной жизни. Как человеку старшего поколения, избавиться от необходимости в любую погоду выходить из дома для оплаты коммунальных услуг, с отстаиванием очередей это огромный шаг вперёд, который молодое поколение принимает как нечто мифическое. Спасибо вам за то, что двигаетесь вместе с прогрессом.</t>
@@ -49474,7 +48617,6 @@
       <c r="C1255" t="n">
         <v>5</v>
       </c>
-      <c r="D1255" t="inlineStr"/>
       <c r="E1255" t="inlineStr">
         <is>
           <t>👍👍👍</t>
@@ -49513,7 +48655,6 @@
       <c r="C1256" t="n">
         <v>5</v>
       </c>
-      <c r="D1256" t="inlineStr"/>
       <c r="E1256" t="inlineStr">
         <is>
           <t>Өте жақсы.Қолдану тәсіліде оңай әрі жеңіл.Кредитке одобрение берсе нұр үстіне нұр болар еді.</t>
@@ -49552,7 +48693,6 @@
       <c r="C1257" t="n">
         <v>5</v>
       </c>
-      <c r="D1257" t="inlineStr"/>
       <c r="E1257" t="inlineStr">
         <is>
           <t>удобно</t>
@@ -49591,7 +48731,6 @@
       <c r="C1258" t="n">
         <v>5</v>
       </c>
-      <c r="D1258" t="inlineStr"/>
       <c r="E1258" t="inlineStr">
         <is>
           <t>все качественно</t>
@@ -49630,7 +48769,6 @@
       <c r="C1259" t="n">
         <v>5</v>
       </c>
-      <c r="D1259" t="inlineStr"/>
       <c r="E1259" t="inlineStr">
         <is>
           <t>өте жақсы</t>
@@ -49641,7 +48779,6 @@
           <t>Абиева Мадина Абиева Мадина</t>
         </is>
       </c>
-      <c r="G1259" t="inlineStr"/>
       <c r="H1259" t="inlineStr">
         <is>
           <t>3b252ff689e682f7adbe55b0</t>
@@ -49665,7 +48802,6 @@
       <c r="C1260" t="n">
         <v>5</v>
       </c>
-      <c r="D1260" t="inlineStr"/>
       <c r="E1260" t="inlineStr">
         <is>
           <t>отличный приложение, только на свою карту другого банка перевод денег стоит есть возможность сделать эту операцию бесплатно?</t>
@@ -49704,7 +48840,6 @@
       <c r="C1261" t="n">
         <v>5</v>
       </c>
-      <c r="D1261" t="inlineStr"/>
       <c r="E1261" t="inlineStr">
         <is>
           <t>отличный банк</t>
@@ -49743,7 +48878,7 @@
       <c r="C1262" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D1262" s="2" t="inlineStr"/>
+      <c r="D1262" s="2" t="n"/>
       <c r="E1262" s="2" t="inlineStr">
         <is>
           <t>ну не знаю денги перевести без комисии нельзя</t>
@@ -49782,7 +48917,6 @@
       <c r="C1263" t="n">
         <v>5</v>
       </c>
-      <c r="D1263" t="inlineStr"/>
       <c r="E1263" t="inlineStr">
         <is>
           <t>Отличные работы, всегда доступные</t>
@@ -49821,7 +48955,7 @@
       <c r="C1264" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1264" s="2" t="inlineStr"/>
+      <c r="D1264" s="2" t="n"/>
       <c r="E1264" s="2" t="inlineStr">
         <is>
           <t>Постоянно надо удалять и заново устанавливать</t>
@@ -49860,7 +48994,6 @@
       <c r="C1265" t="n">
         <v>5</v>
       </c>
-      <c r="D1265" t="inlineStr"/>
       <c r="E1265" t="inlineStr">
         <is>
           <t>Профессиальное обслуживание, Халык лучшие👍</t>
@@ -49899,7 +49032,7 @@
       <c r="C1266" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D1266" s="2" t="inlineStr"/>
+      <c r="D1266" s="2" t="n"/>
       <c r="E1266" s="2" t="inlineStr">
         <is>
           <t>Каждый раз после обновления приложение надо заново скачивать</t>
@@ -49938,7 +49071,6 @@
       <c r="C1267" t="n">
         <v>5</v>
       </c>
-      <c r="D1267" t="inlineStr"/>
       <c r="E1267" t="inlineStr">
         <is>
           <t>хорошо все</t>
@@ -49977,7 +49109,6 @@
       <c r="C1268" t="n">
         <v>5</v>
       </c>
-      <c r="D1268" t="inlineStr"/>
       <c r="E1268" t="inlineStr">
         <is>
           <t>да хорошо работает но потупает медленно переводе</t>
@@ -50016,7 +49147,7 @@
       <c r="C1269" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D1269" s="2" t="inlineStr"/>
+      <c r="D1269" s="2" t="n"/>
       <c r="E1269" s="2" t="inlineStr">
         <is>
           <t>Я не могу понять что случилось но я осталась без приложения. И в тех поддержку звонила и к менеджерам ходила никто не может установить приложение. Мне остаётся только одно расстаться с банком и уйти в другой менее капризный. Хотя тут и пенсия и зарплата поступали. Хочу знать что мне делать? Как установить приложение. Или уходить из банка?</t>
@@ -50055,7 +49186,6 @@
       <c r="C1270" t="n">
         <v>5</v>
       </c>
-      <c r="D1270" t="inlineStr"/>
       <c r="E1270" t="inlineStr">
         <is>
           <t>ия унайды оте керемет</t>
@@ -50094,7 +49224,6 @@
       <c r="C1271" t="n">
         <v>5</v>
       </c>
-      <c r="D1271" t="inlineStr"/>
       <c r="E1271" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -50133,7 +49262,6 @@
       <c r="C1272" t="n">
         <v>5</v>
       </c>
-      <c r="D1272" t="inlineStr"/>
       <c r="E1272" t="inlineStr">
         <is>
           <t>вы самые классные</t>
@@ -50172,7 +49300,6 @@
       <c r="C1273" t="n">
         <v>5</v>
       </c>
-      <c r="D1273" t="inlineStr"/>
       <c r="E1273" t="inlineStr">
         <is>
           <t>отлтчно</t>
@@ -50211,7 +49338,6 @@
       <c r="C1274" t="n">
         <v>4</v>
       </c>
-      <c r="D1274" t="inlineStr"/>
       <c r="E1274" t="inlineStr">
         <is>
           <t>Информация по акциям приходит не поздновато, служба поддержки слабая</t>
@@ -50250,7 +49376,6 @@
       <c r="C1275" t="n">
         <v>5</v>
       </c>
-      <c r="D1275" t="inlineStr"/>
       <c r="E1275" t="inlineStr">
         <is>
           <t>очень удобные и хорошее приложение</t>
@@ -50289,7 +49414,6 @@
       <c r="C1276" t="n">
         <v>5</v>
       </c>
-      <c r="D1276" t="inlineStr"/>
       <c r="E1276" t="inlineStr">
         <is>
           <t>все ясно и понятно, спасибо разработчикам и халык банку</t>
@@ -50328,7 +49452,6 @@
       <c r="C1277" t="n">
         <v>5</v>
       </c>
-      <c r="D1277" t="inlineStr"/>
       <c r="E1277" t="inlineStr">
         <is>
           <t>оперативно</t>
@@ -50367,7 +49490,6 @@
       <c r="C1278" t="n">
         <v>5</v>
       </c>
-      <c r="D1278" t="inlineStr"/>
       <c r="E1278" t="inlineStr">
         <is>
           <t>удобный, подробный, аккуратный аккаунт</t>
@@ -50406,7 +49528,7 @@
       <c r="C1279" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1279" s="2" t="inlineStr"/>
+      <c r="D1279" s="2" t="n"/>
       <c r="E1279" s="2" t="inlineStr">
         <is>
           <t>ужасное содердание, неуважение к клиентам</t>
@@ -50445,7 +49567,6 @@
       <c r="C1280" t="n">
         <v>4</v>
       </c>
-      <c r="D1280" t="inlineStr"/>
       <c r="E1280" t="inlineStr">
         <is>
           <t>Подскажите пож почему на смартфонах Huawei сканер QR не работает?</t>
@@ -50484,7 +49605,6 @@
       <c r="C1281" t="n">
         <v>5</v>
       </c>
-      <c r="D1281" t="inlineStr"/>
       <c r="E1281" t="inlineStr">
         <is>
           <t>отлично спасибо 👍👍👍</t>
@@ -50523,7 +49643,6 @@
       <c r="C1282" t="n">
         <v>5</v>
       </c>
-      <c r="D1282" t="inlineStr"/>
       <c r="E1282" t="inlineStr">
         <is>
           <t>супер</t>
@@ -50562,7 +49681,6 @@
       <c r="C1283" t="n">
         <v>5</v>
       </c>
-      <c r="D1283" t="inlineStr"/>
       <c r="E1283" t="inlineStr">
         <is>
           <t>Грамотно жауап алдым</t>
@@ -50601,7 +49719,6 @@
       <c r="C1284" t="n">
         <v>5</v>
       </c>
-      <c r="D1284" t="inlineStr"/>
       <c r="E1284" t="inlineStr">
         <is>
           <t>самый надежный банк</t>
@@ -50640,7 +49757,6 @@
       <c r="C1285" t="n">
         <v>5</v>
       </c>
-      <c r="D1285" t="inlineStr"/>
       <c r="E1285" t="inlineStr">
         <is>
           <t>отлично все работает</t>
@@ -50679,7 +49795,6 @@
       <c r="C1286" t="n">
         <v>5</v>
       </c>
-      <c r="D1286" t="inlineStr"/>
       <c r="E1286" t="inlineStr">
         <is>
           <t>ия,ұнайды</t>
@@ -50718,7 +49833,6 @@
       <c r="C1287" t="n">
         <v>5</v>
       </c>
-      <c r="D1287" t="inlineStr"/>
       <c r="E1287" t="inlineStr">
         <is>
           <t>керемет</t>
@@ -50757,7 +49871,6 @@
       <c r="C1288" t="n">
         <v>5</v>
       </c>
-      <c r="D1288" t="inlineStr"/>
       <c r="E1288" t="inlineStr">
         <is>
           <t>Работает отлично 👍</t>
@@ -50796,7 +49909,6 @@
       <c r="C1289" t="n">
         <v>5</v>
       </c>
-      <c r="D1289" t="inlineStr"/>
       <c r="E1289" t="inlineStr">
         <is>
           <t>👍👏🙏</t>
@@ -50835,7 +49947,6 @@
       <c r="C1290" t="n">
         <v>5</v>
       </c>
-      <c r="D1290" t="inlineStr"/>
       <c r="E1290" t="inlineStr">
         <is>
           <t>спасибо за удобство</t>
@@ -50874,7 +49985,6 @@
       <c r="C1291" t="n">
         <v>5</v>
       </c>
-      <c r="D1291" t="inlineStr"/>
       <c r="E1291" t="inlineStr">
         <is>
           <t>очень удобный</t>
@@ -50913,7 +50023,7 @@
       <c r="C1292" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1292" s="2" t="inlineStr"/>
+      <c r="D1292" s="2" t="n"/>
       <c r="E1292" s="2" t="inlineStr">
         <is>
           <t>слишком поздно приходят квитанции за коммуналку.</t>
@@ -50952,7 +50062,6 @@
       <c r="C1293" t="n">
         <v>5</v>
       </c>
-      <c r="D1293" t="inlineStr"/>
       <c r="E1293" t="inlineStr">
         <is>
           <t>Норм рекомендую</t>
@@ -50991,7 +50100,6 @@
       <c r="C1294" t="n">
         <v>5</v>
       </c>
-      <c r="D1294" t="inlineStr"/>
       <c r="E1294" t="inlineStr">
         <is>
           <t>очень удобно и легко.</t>
@@ -51030,7 +50138,7 @@
       <c r="C1295" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D1295" s="2" t="inlineStr"/>
+      <c r="D1295" s="2" t="n"/>
       <c r="E1295" s="2" t="inlineStr">
         <is>
           <t>жақсы</t>
@@ -51069,7 +50177,6 @@
       <c r="C1296" t="n">
         <v>5</v>
       </c>
-      <c r="D1296" t="inlineStr"/>
       <c r="E1296" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -51108,7 +50215,6 @@
       <c r="C1297" t="n">
         <v>5</v>
       </c>
-      <c r="D1297" t="inlineStr"/>
       <c r="E1297" t="inlineStr">
         <is>
           <t>Өте жақсы өте ыңғайлы күшті</t>
@@ -51154,7 +50260,6 @@
       <c r="C1299" t="n">
         <v>5</v>
       </c>
-      <c r="D1299" t="inlineStr"/>
       <c r="E1299" t="inlineStr">
         <is>
           <t>жақсы</t>
@@ -51193,7 +50298,7 @@
       <c r="C1300" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1300" s="2" t="inlineStr"/>
+      <c r="D1300" s="2" t="n"/>
       <c r="E1300" s="2" t="inlineStr">
         <is>
           <t>ылги жанарту керек</t>
@@ -51204,7 +50309,7 @@
           <t>Сымбат Тойгулова</t>
         </is>
       </c>
-      <c r="G1300" s="2" t="inlineStr"/>
+      <c r="G1300" s="2" t="n"/>
       <c r="H1300" s="2" t="inlineStr">
         <is>
           <t>f9bfffba8be2748c4629a6c0</t>
@@ -51228,7 +50333,6 @@
       <c r="C1301" t="n">
         <v>5</v>
       </c>
-      <c r="D1301" t="inlineStr"/>
       <c r="E1301" t="inlineStr">
         <is>
           <t>удобно ,круто</t>
@@ -51267,7 +50371,6 @@
       <c r="C1302" t="n">
         <v>4</v>
       </c>
-      <c r="D1302" t="inlineStr"/>
       <c r="E1302" t="inlineStr">
         <is>
           <t>все норм. однако пароль дважды просит. неудобно</t>
@@ -51306,7 +50409,6 @@
       <c r="C1303" t="n">
         <v>5</v>
       </c>
-      <c r="D1303" t="inlineStr"/>
       <c r="E1303" t="inlineStr">
         <is>
           <t>5 звезд</t>
@@ -51345,7 +50447,6 @@
       <c r="C1304" t="n">
         <v>5</v>
       </c>
-      <c r="D1304" t="inlineStr"/>
       <c r="E1304" t="inlineStr">
         <is>
           <t>отично</t>
@@ -51384,7 +50485,6 @@
       <c r="C1305" t="n">
         <v>5</v>
       </c>
-      <c r="D1305" t="inlineStr"/>
       <c r="E1305" t="inlineStr">
         <is>
           <t>мне всё нравится!!!</t>
@@ -51423,7 +50523,6 @@
       <c r="C1306" t="n">
         <v>5</v>
       </c>
-      <c r="D1306" t="inlineStr"/>
       <c r="E1306" t="inlineStr">
         <is>
           <t>Все работает хорошо</t>
@@ -51462,7 +50561,7 @@
       <c r="C1307" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1307" s="2" t="inlineStr"/>
+      <c r="D1307" s="2" t="n"/>
       <c r="E1307" s="2" t="inlineStr">
         <is>
           <t>плохо работает зависает</t>
@@ -51501,7 +50600,7 @@
       <c r="C1308" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1308" s="2" t="inlineStr"/>
+      <c r="D1308" s="2" t="n"/>
       <c r="E1308" s="2" t="inlineStr">
         <is>
           <t>почему на запрос каторые я оставила было написано погашения через 7 дней, рассмотрено, а деньги так и не паступила а дата погашения уже через 6 дней 04.07-го????????????</t>
@@ -51540,7 +50639,6 @@
       <c r="C1309" t="n">
         <v>4</v>
       </c>
-      <c r="D1309" t="inlineStr"/>
       <c r="E1309" t="inlineStr">
         <is>
           <t>очень часто подвисает ускорьте обработку процессов</t>
@@ -51579,7 +50677,6 @@
       <c r="C1310" t="n">
         <v>5</v>
       </c>
-      <c r="D1310" t="inlineStr"/>
       <c r="E1310" t="inlineStr">
         <is>
           <t>оперативно, чётко, ничего лишнего, доступно в любое время</t>
@@ -51618,7 +50715,6 @@
       <c r="C1311" t="n">
         <v>5</v>
       </c>
-      <c r="D1311" t="inlineStr"/>
       <c r="E1311" t="inlineStr">
         <is>
           <t>👍👍👍</t>
@@ -51657,7 +50753,6 @@
       <c r="C1312" t="n">
         <v>4</v>
       </c>
-      <c r="D1312" t="inlineStr"/>
       <c r="E1312" t="inlineStr">
         <is>
           <t>Всё хорошо 👍🏾</t>
@@ -51696,7 +50791,6 @@
       <c r="C1313" t="n">
         <v>5</v>
       </c>
-      <c r="D1313" t="inlineStr"/>
       <c r="E1313" t="inlineStr">
         <is>
           <t>Рахмет</t>
@@ -51735,7 +50829,6 @@
       <c r="C1314" t="n">
         <v>5</v>
       </c>
-      <c r="D1314" t="inlineStr"/>
       <c r="E1314" t="inlineStr">
         <is>
           <t>удобство и оперативность</t>
@@ -51774,7 +50867,6 @@
       <c r="C1315" t="n">
         <v>5</v>
       </c>
-      <c r="D1315" t="inlineStr"/>
       <c r="E1315" t="inlineStr">
         <is>
           <t>Всё отлично. Спасибо ОГРОМНОЕ Halyk.</t>
@@ -51813,7 +50905,7 @@
       <c r="C1316" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1316" s="2" t="inlineStr"/>
+      <c r="D1316" s="2" t="n"/>
       <c r="E1316" s="2" t="inlineStr">
         <is>
           <t>плохо потому что убрали переводы с halyk wallet</t>
@@ -51824,7 +50916,7 @@
           <t>Қалқаман Амангелді</t>
         </is>
       </c>
-      <c r="G1316" s="2" t="inlineStr"/>
+      <c r="G1316" s="2" t="n"/>
       <c r="H1316" s="2" t="inlineStr">
         <is>
           <t>9f4ce5c7b5ff381e0a9e61bc</t>
@@ -51848,7 +50940,6 @@
       <c r="C1317" t="n">
         <v>5</v>
       </c>
-      <c r="D1317" t="inlineStr"/>
       <c r="E1317" t="inlineStr">
         <is>
           <t>вы лучшие</t>
@@ -51887,7 +50978,6 @@
       <c r="C1318" t="n">
         <v>5</v>
       </c>
-      <c r="D1318" t="inlineStr"/>
       <c r="E1318" t="inlineStr">
         <is>
           <t>👍</t>
@@ -51926,7 +51016,6 @@
       <c r="C1319" t="n">
         <v>4</v>
       </c>
-      <c r="D1319" t="inlineStr"/>
       <c r="E1319" t="inlineStr">
         <is>
           <t>супер</t>
@@ -51965,7 +51054,7 @@
       <c r="C1320" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1320" s="2" t="inlineStr"/>
+      <c r="D1320" s="2" t="n"/>
       <c r="E1320" s="2" t="inlineStr">
         <is>
           <t>қайта қайта жабылып қала береді...өте шамалы..Қайта қайта жүктеуден шаршадым.Ең шамалы банк,ең жебір банк.Филиалға барсаң бәрі ақылы, анықтама алу үшін 2000т төлеуім керек екен.Масқара</t>
@@ -52004,7 +51093,6 @@
       <c r="C1321" t="n">
         <v>5</v>
       </c>
-      <c r="D1321" t="inlineStr"/>
       <c r="E1321" t="inlineStr">
         <is>
           <t>отлично 👍</t>
@@ -52043,7 +51131,6 @@
       <c r="C1322" t="n">
         <v>5</v>
       </c>
-      <c r="D1322" t="inlineStr"/>
       <c r="E1322" t="inlineStr">
         <is>
           <t>оК</t>
@@ -52082,7 +51169,7 @@
       <c r="C1323" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1323" s="2" t="inlineStr"/>
+      <c r="D1323" s="2" t="n"/>
       <c r="E1323" s="2" t="inlineStr">
         <is>
           <t>Қайырлыаы</t>
@@ -52121,7 +51208,7 @@
       <c r="C1324" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1324" s="2" t="inlineStr"/>
+      <c r="D1324" s="2" t="n"/>
       <c r="E1324" s="2" t="inlineStr">
         <is>
           <t>обновления не приходят , приходится удалять и установить заново приложение</t>
@@ -52160,7 +51247,6 @@
       <c r="C1325" t="n">
         <v>5</v>
       </c>
-      <c r="D1325" t="inlineStr"/>
       <c r="E1325" t="inlineStr">
         <is>
           <t>Приложение Хорошое</t>
@@ -52199,7 +51285,6 @@
       <c r="C1326" t="n">
         <v>5</v>
       </c>
-      <c r="D1326" t="inlineStr"/>
       <c r="E1326" t="inlineStr">
         <is>
           <t>хороший прилодения</t>
@@ -52238,7 +51323,7 @@
       <c r="C1327" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1327" s="2" t="inlineStr"/>
+      <c r="D1327" s="2" t="n"/>
       <c r="E1327" s="2" t="inlineStr">
         <is>
           <t>Внимание.... вы нам должны 10xxx тенге мы якобы не успели их ранее списать когда вы выпускали карту...Все ясно с вами перехожу в другой банк...</t>
@@ -52249,7 +51334,7 @@
           <t>иван макаров</t>
         </is>
       </c>
-      <c r="G1327" s="2" t="inlineStr"/>
+      <c r="G1327" s="2" t="n"/>
       <c r="H1327" s="2" t="inlineStr">
         <is>
           <t>5d5e0da7fb58d8ac4dd584c3</t>
@@ -52273,7 +51358,6 @@
       <c r="C1328" t="n">
         <v>5</v>
       </c>
-      <c r="D1328" t="inlineStr"/>
       <c r="E1328" t="inlineStr">
         <is>
           <t>просьба к разработчикам. вы либо уберите приложение с других app store либо отключите свою проверку на источник обновления.... у меня тел китайский со своим магазином который работает по умолчанию не смотря на наличие Плай маркета от Гугла. и ваше приложение загружено изначально от китайцев и обновления отслеживает китаец. после каждого обновления вынужден сносить ваше приложение и заново ставить из Гугла.</t>
@@ -52312,7 +51396,7 @@
       <c r="C1329" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D1329" s="2" t="inlineStr"/>
+      <c r="D1329" s="2" t="n"/>
       <c r="E1329" s="2" t="inlineStr">
         <is>
           <t>Почему постоянные проблемы с приложением на телефоне хуавей? И когда это прекратится? То есть постоянно просит обновление, а обновить невозможно, кюаром тоже не оплатить😒</t>
@@ -52358,7 +51442,7 @@
       <c r="C1331" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1331" s="2" t="inlineStr"/>
+      <c r="D1331" s="2" t="n"/>
       <c r="E1331" s="2" t="inlineStr">
         <is>
           <t>что за БРЕД?!?!??? я открыл своей дочери , которой всего 1 год вклад Акыл на ее имя для будущей работы программы Келешек.. но теперь за пополнения вклада с меня требуют комиссию... за что?!?! вы там совсем от жадности офонарели ? это мои деньги для моего ребенка... он сам не может пополнить свой депозит... почему вы берете а меня комиссию??? отмените этот абсурд и привяжите этот вклад к моему счету , т.к. это я коплю.. не чужой человек .. какой позор.. крохоборы..</t>
@@ -52397,7 +51481,6 @@
       <c r="C1332" t="n">
         <v>5</v>
       </c>
-      <c r="D1332" t="inlineStr"/>
       <c r="E1332" t="inlineStr">
         <is>
           <t>очень хорошо</t>
@@ -52436,7 +51519,6 @@
       <c r="C1333" t="n">
         <v>5</v>
       </c>
-      <c r="D1333" t="inlineStr"/>
       <c r="E1333" t="inlineStr">
         <is>
           <t>нравится👍</t>
@@ -52475,7 +51557,6 @@
       <c r="C1334" t="n">
         <v>5</v>
       </c>
-      <c r="D1334" t="inlineStr"/>
       <c r="E1334" t="inlineStr">
         <is>
           <t>я рад с халык банком пенсию получаю</t>
@@ -52514,7 +51595,6 @@
       <c r="C1335" t="n">
         <v>5</v>
       </c>
-      <c r="D1335" t="inlineStr"/>
       <c r="E1335" t="inlineStr">
         <is>
           <t>Отлично 👍</t>
@@ -52553,7 +51633,7 @@
       <c r="C1336" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D1336" s="2" t="inlineStr"/>
+      <c r="D1336" s="2" t="n"/>
       <c r="E1336" s="2" t="inlineStr">
         <is>
           <t>Очень часто зависает, особенно при оплате в магазине и т.д.</t>
@@ -52592,7 +51672,7 @@
       <c r="C1337" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D1337" s="2" t="inlineStr"/>
+      <c r="D1337" s="2" t="n"/>
       <c r="E1337" s="2" t="inlineStr">
         <is>
           <t>Почему прикаждом обновлении нужно удалять приложение и устанавливать новое? Почему нужно опять проходить идентификацию? Вы не понимаете что это лишняя работа для ваших клиентов? Рядовой обновление превращается в танцы с бубном. Я разочарована и считаю что это безобразие!!</t>
@@ -52631,7 +51711,6 @@
       <c r="C1338" t="n">
         <v>4</v>
       </c>
-      <c r="D1338" t="inlineStr"/>
       <c r="E1338" t="inlineStr">
         <is>
           <t>тема 👌</t>
@@ -52670,7 +51749,6 @@
       <c r="C1339" t="n">
         <v>5</v>
       </c>
-      <c r="D1339" t="inlineStr"/>
       <c r="E1339" t="inlineStr">
         <is>
           <t>тиымды</t>
@@ -52709,7 +51787,6 @@
       <c r="C1340" t="n">
         <v>5</v>
       </c>
-      <c r="D1340" t="inlineStr"/>
       <c r="E1340" t="inlineStr">
         <is>
           <t>Отлично</t>
@@ -52748,7 +51825,6 @@
       <c r="C1341" t="n">
         <v>5</v>
       </c>
-      <c r="D1341" t="inlineStr"/>
       <c r="E1341" t="inlineStr">
         <is>
           <t>ок</t>
@@ -52787,7 +51863,6 @@
       <c r="C1342" t="n">
         <v>5</v>
       </c>
-      <c r="D1342" t="inlineStr"/>
       <c r="E1342" t="inlineStr">
         <is>
           <t>Отлична</t>
@@ -52826,7 +51901,6 @@
       <c r="C1343" t="n">
         <v>5</v>
       </c>
-      <c r="D1343" t="inlineStr"/>
       <c r="E1343" t="inlineStr">
         <is>
           <t>Очень нравится,удобное,понятное,лучшее!</t>
@@ -52872,7 +51946,6 @@
       <c r="C1345" t="n">
         <v>5</v>
       </c>
-      <c r="D1345" t="inlineStr"/>
       <c r="E1345" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -52911,7 +51984,7 @@
       <c r="C1346" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1346" s="2" t="inlineStr"/>
+      <c r="D1346" s="2" t="n"/>
       <c r="E1346" s="2" t="inlineStr">
         <is>
           <t>После обновлений в Halyk Homebank убрали возможность видеть остаток средств сразу после оплаты. Это сильно ухудшило контроль за деньгами. Теперь невозможно оперативно проверить корректность списания. Обращения в Halyk Bank не дают результата. Приходят только формальные ответы без сроков решения. Верните функцию отображения остатка.</t>
@@ -52950,7 +52023,6 @@
       <c r="C1347" t="n">
         <v>5</v>
       </c>
-      <c r="D1347" t="inlineStr"/>
       <c r="E1347" t="inlineStr">
         <is>
           <t>супер</t>
@@ -52989,7 +52061,7 @@
       <c r="C1348" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1348" s="2" t="inlineStr"/>
+      <c r="D1348" s="2" t="n"/>
       <c r="E1348" s="2" t="inlineStr">
         <is>
           <t>конченая шарага приложение такое же звонишь в поддержку операторы заняты минут 10 ждёшь нет ответа пишу в поддержку на ватсап сутки не отвечают наберите значит больше штат сотрудников если не справляетесь</t>
@@ -53028,7 +52100,6 @@
       <c r="C1349" t="n">
         <v>5</v>
       </c>
-      <c r="D1349" t="inlineStr"/>
       <c r="E1349" t="inlineStr">
         <is>
           <t>очень удобно, хорошо.</t>
@@ -53067,7 +52138,7 @@
       <c r="C1350" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1350" s="2" t="inlineStr"/>
+      <c r="D1350" s="2" t="n"/>
       <c r="E1350" s="2" t="inlineStr">
         <is>
           <t>перевод по номеру телефона постоянно выходит ошибка,халык не отвечает сделать перевод не возможно.</t>
@@ -53078,7 +52149,7 @@
           <t>Пернехан Ажигабылов</t>
         </is>
       </c>
-      <c r="G1350" s="2" t="inlineStr"/>
+      <c r="G1350" s="2" t="n"/>
       <c r="H1350" s="2" t="inlineStr">
         <is>
           <t>3bfb9096cdfe5d276aef2b42</t>
@@ -53102,7 +52173,6 @@
       <c r="C1351" t="n">
         <v>5</v>
       </c>
-      <c r="D1351" t="inlineStr"/>
       <c r="E1351" t="inlineStr">
         <is>
           <t>супер</t>
@@ -53141,7 +52211,7 @@
       <c r="C1352" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1352" s="2" t="inlineStr"/>
+      <c r="D1352" s="2" t="n"/>
       <c r="E1352" s="2" t="inlineStr">
         <is>
           <t>не могу зайти написано заблокировано</t>
@@ -53180,7 +52250,6 @@
       <c r="C1353" t="n">
         <v>5</v>
       </c>
-      <c r="D1353" t="inlineStr"/>
       <c r="E1353" t="inlineStr">
         <is>
           <t>всё просто супер</t>
@@ -53219,7 +52288,7 @@
       <c r="C1354" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1354" s="2" t="inlineStr"/>
+      <c r="D1354" s="2" t="n"/>
       <c r="E1354" s="2" t="inlineStr">
         <is>
           <t>не могу оформить рассрочку по qr выходит (Вам отказано в получении заима. в связи с проведением проверки внесеных вами изменениями, попробуйте через 7дней, хотя я нечего не делал, ни 7111 ни в банке не смогли решить проблему, заявка даже не формируется то есть в банки не видят что я подаю заявку</t>
@@ -53258,7 +52327,7 @@
       <c r="C1355" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1355" s="2" t="inlineStr"/>
+      <c r="D1355" s="2" t="n"/>
       <c r="E1355" s="2" t="inlineStr">
         <is>
           <t>не открывается после обновления. Очень не удобно.</t>
@@ -53297,7 +52366,6 @@
       <c r="C1356" t="n">
         <v>5</v>
       </c>
-      <c r="D1356" t="inlineStr"/>
       <c r="E1356" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -53336,7 +52404,6 @@
       <c r="C1357" t="n">
         <v>5</v>
       </c>
-      <c r="D1357" t="inlineStr"/>
       <c r="E1357" t="inlineStr">
         <is>
           <t>класс</t>
@@ -53375,7 +52442,6 @@
       <c r="C1358" t="n">
         <v>5</v>
       </c>
-      <c r="D1358" t="inlineStr"/>
       <c r="E1358" t="inlineStr">
         <is>
           <t>отлично всё удобно и понятно</t>
@@ -53414,7 +52480,6 @@
       <c r="C1359" t="n">
         <v>5</v>
       </c>
-      <c r="D1359" t="inlineStr"/>
       <c r="E1359" t="inlineStr">
         <is>
           <t>вы классный банк</t>
@@ -53453,7 +52518,7 @@
       <c r="C1360" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1360" s="2" t="inlineStr"/>
+      <c r="D1360" s="2" t="n"/>
       <c r="E1360" s="2" t="inlineStr">
         <is>
           <t>Выпустите обновление для Huawei</t>
@@ -53492,7 +52557,7 @@
       <c r="C1361" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1361" s="2" t="inlineStr"/>
+      <c r="D1361" s="2" t="n"/>
       <c r="E1361" s="2" t="inlineStr">
         <is>
           <t>Звоните в 7111 и вас до смерти за..ет наитупейший бот который просит что то сформулировать чего я сам не понимаю. Я звоню чтобы об этом поговорить и узнать у оператора. Бот просит оценить от 1 до 5 и бросает трубку. Спасибо за очень плохое обслуживание и за бота из каменного века которая походу только у Халық банка</t>
@@ -53531,7 +52596,6 @@
       <c r="C1362" t="n">
         <v>5</v>
       </c>
-      <c r="D1362" t="inlineStr"/>
       <c r="E1362" t="inlineStr">
         <is>
           <t>всё удобно. особенно для пенсионеров. Благодарю</t>
@@ -53570,7 +52634,6 @@
       <c r="C1363" t="n">
         <v>5</v>
       </c>
-      <c r="D1363" t="inlineStr"/>
       <c r="E1363" t="inlineStr">
         <is>
           <t>Кейде қатып қалатыны болмаса, бәрі жақсы</t>
@@ -53609,7 +52672,6 @@
       <c r="C1364" t="n">
         <v>5</v>
       </c>
-      <c r="D1364" t="inlineStr"/>
       <c r="E1364" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -53648,7 +52710,6 @@
       <c r="C1365" t="n">
         <v>5</v>
       </c>
-      <c r="D1365" t="inlineStr"/>
       <c r="E1365" t="inlineStr">
         <is>
           <t>Когда заработает это приложение??? Авторизация не возможна. Почему?</t>
@@ -53687,7 +52748,7 @@
       <c r="C1366" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1366" s="2" t="inlineStr"/>
+      <c r="D1366" s="2" t="n"/>
       <c r="E1366" s="2" t="inlineStr">
         <is>
           <t>самое ужасное приложение. страховку уже 10 дней не можем изменить. приложение не работает. Всё отстой у вас. ужасссс</t>
@@ -53726,7 +52787,6 @@
       <c r="C1367" t="n">
         <v>5</v>
       </c>
-      <c r="D1367" t="inlineStr"/>
       <c r="E1367" t="inlineStr">
         <is>
           <t>👍👍👍</t>
@@ -53772,7 +52832,6 @@
       <c r="C1369" t="n">
         <v>5</v>
       </c>
-      <c r="D1369" t="inlineStr"/>
       <c r="E1369" t="inlineStr">
         <is>
           <t>всё прекрасно, Я доволен.</t>
@@ -53811,7 +52870,6 @@
       <c r="C1370" t="n">
         <v>5</v>
       </c>
-      <c r="D1370" t="inlineStr"/>
       <c r="E1370" t="inlineStr">
         <is>
           <t>сәттілік тілеймін жұмыс тарыңызға.</t>
@@ -53850,7 +52908,6 @@
       <c r="C1371" t="n">
         <v>5</v>
       </c>
-      <c r="D1371" t="inlineStr"/>
       <c r="E1371" t="inlineStr">
         <is>
           <t>Спасибо Халық , всегда выручает</t>
@@ -53889,7 +52946,6 @@
       <c r="C1372" t="n">
         <v>5</v>
       </c>
-      <c r="D1372" t="inlineStr"/>
       <c r="E1372" t="inlineStr">
         <is>
           <t>нравиться</t>
@@ -53928,7 +52984,6 @@
       <c r="C1373" t="n">
         <v>5</v>
       </c>
-      <c r="D1373" t="inlineStr"/>
       <c r="E1373" t="inlineStr">
         <is>
           <t>Отлично</t>
@@ -53967,7 +53022,6 @@
       <c r="C1374" t="n">
         <v>5</v>
       </c>
-      <c r="D1374" t="inlineStr"/>
       <c r="E1374" t="inlineStr">
         <is>
           <t>Удобно и отлично</t>
@@ -54006,7 +53060,7 @@
       <c r="C1375" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D1375" s="2" t="inlineStr"/>
+      <c r="D1375" s="2" t="n"/>
       <c r="E1375" s="2" t="inlineStr">
         <is>
           <t>Удобно рассчитываться по QR коду, но не нравится, что вы не начисляете бонусы. Программа, которую вы предлагаете, просто ужасная и не выполнимая для меня. Почему то муж всегда получает бонусы по оплате через QR код в любом магазине и на любую сумму.А я плачу солидные суммы, и даже 1 тенге не заслужила . Наверное уйду от вас</t>
@@ -54045,7 +53099,6 @@
       <c r="C1376" t="n">
         <v>4</v>
       </c>
-      <c r="D1376" t="inlineStr"/>
       <c r="E1376" t="inlineStr">
         <is>
           <t>деньги не бесконечные 4 звезды</t>
@@ -54084,7 +53137,6 @@
       <c r="C1377" t="n">
         <v>5</v>
       </c>
-      <c r="D1377" t="inlineStr"/>
       <c r="E1377" t="inlineStr">
         <is>
           <t>керемет қосымша</t>
@@ -54123,7 +53175,6 @@
       <c r="C1378" t="n">
         <v>5</v>
       </c>
-      <c r="D1378" t="inlineStr"/>
       <c r="E1378" t="inlineStr">
         <is>
           <t>отлично</t>
@@ -54162,7 +53213,6 @@
       <c r="C1379" t="n">
         <v>5</v>
       </c>
-      <c r="D1379" t="inlineStr"/>
       <c r="E1379" t="inlineStr">
         <is>
           <t>керемет</t>
@@ -54201,7 +53251,6 @@
       <c r="C1380" t="n">
         <v>5</v>
       </c>
-      <c r="D1380" t="inlineStr"/>
       <c r="E1380" t="inlineStr">
         <is>
           <t>вы супер</t>
@@ -54240,7 +53289,6 @@
       <c r="C1381" t="n">
         <v>5</v>
       </c>
-      <c r="D1381" t="inlineStr"/>
       <c r="E1381" t="inlineStr">
         <is>
           <t>доверяю</t>
@@ -54279,7 +53327,6 @@
       <c r="C1382" t="n">
         <v>5</v>
       </c>
-      <c r="D1382" t="inlineStr"/>
       <c r="E1382" t="inlineStr">
         <is>
           <t>всё отлично!!!</t>
@@ -54318,7 +53365,6 @@
       <c r="C1383" t="n">
         <v>5</v>
       </c>
-      <c r="D1383" t="inlineStr"/>
       <c r="E1383" t="inlineStr">
         <is>
           <t>Очень нравиться</t>
@@ -54357,7 +53403,6 @@
       <c r="C1384" t="n">
         <v>5</v>
       </c>
-      <c r="D1384" t="inlineStr"/>
       <c r="E1384" t="inlineStr">
         <is>
           <t>отлично спасибо за такую приложение</t>
@@ -54403,7 +53448,6 @@
       <c r="C1386" t="n">
         <v>5</v>
       </c>
-      <c r="D1386" t="inlineStr"/>
       <c r="E1386" t="inlineStr">
         <is>
           <t>Отлично</t>
@@ -54442,7 +53486,6 @@
       <c r="C1387" t="n">
         <v>5</v>
       </c>
-      <c r="D1387" t="inlineStr"/>
       <c r="E1387" t="inlineStr">
         <is>
           <t>Все Отлично</t>
@@ -54481,7 +53524,6 @@
       <c r="C1388" t="n">
         <v>5</v>
       </c>
-      <c r="D1388" t="inlineStr"/>
       <c r="E1388" t="inlineStr">
         <is>
           <t>👍👍👍</t>
@@ -54520,7 +53562,6 @@
       <c r="C1389" t="n">
         <v>5</v>
       </c>
-      <c r="D1389" t="inlineStr"/>
       <c r="E1389" t="inlineStr">
         <is>
           <t>супер</t>
@@ -54559,7 +53600,6 @@
       <c r="C1390" t="n">
         <v>5</v>
       </c>
-      <c r="D1390" t="inlineStr"/>
       <c r="E1390" t="inlineStr">
         <is>
           <t>удобно,доступно всегда</t>
@@ -54598,7 +53638,7 @@
       <c r="C1391" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1391" s="2" t="inlineStr"/>
+      <c r="D1391" s="2" t="n"/>
       <c r="E1391" s="2" t="inlineStr">
         <is>
           <t>Устал каждый раз переустановить! Один раз заходишь и опять требует обновление и закрыть приложение, а обновление нет! И как быть?!</t>
@@ -54637,7 +53677,6 @@
       <c r="C1392" t="n">
         <v>5</v>
       </c>
-      <c r="D1392" t="inlineStr"/>
       <c r="E1392" t="inlineStr">
         <is>
           <t>спасибо очень удобно</t>
@@ -54676,7 +53715,6 @@
       <c r="C1393" t="n">
         <v>5</v>
       </c>
-      <c r="D1393" t="inlineStr"/>
       <c r="E1393" t="inlineStr">
         <is>
           <t>Рақмет!</t>
@@ -54715,7 +53753,6 @@
       <c r="C1394" t="n">
         <v>5</v>
       </c>
-      <c r="D1394" t="inlineStr"/>
       <c r="E1394" t="inlineStr">
         <is>
           <t>отлично мне нравится</t>
@@ -54748,8 +53785,9 @@
     <mergeCell ref="A675:S675"/>
     <mergeCell ref="A1095:S1095"/>
     <mergeCell ref="A1200:S1200"/>
+    <mergeCell ref="A828:S828"/>
+    <mergeCell ref="A303:S303"/>
     <mergeCell ref="A1344:S1344"/>
-    <mergeCell ref="A303:S303"/>
     <mergeCell ref="A234:S234"/>
     <mergeCell ref="A439:S439"/>
     <mergeCell ref="A140:S140"/>
@@ -54757,24 +53795,23 @@
     <mergeCell ref="A1368:S1368"/>
     <mergeCell ref="A1330:S1330"/>
     <mergeCell ref="A67:S67"/>
+    <mergeCell ref="A1183:S1183"/>
+    <mergeCell ref="A627:S627"/>
     <mergeCell ref="A337:S337"/>
-    <mergeCell ref="A627:S627"/>
-    <mergeCell ref="A1183:S1183"/>
+    <mergeCell ref="A304:S304"/>
     <mergeCell ref="A710:S710"/>
     <mergeCell ref="A1385:S1385"/>
-    <mergeCell ref="A304:S304"/>
     <mergeCell ref="A1212:S1212"/>
     <mergeCell ref="A1141:S1141"/>
     <mergeCell ref="A25:S25"/>
     <mergeCell ref="A1298:S1298"/>
+    <mergeCell ref="A1156:S1156"/>
     <mergeCell ref="A690:S690"/>
-    <mergeCell ref="A1156:S1156"/>
     <mergeCell ref="A493:S493"/>
+    <mergeCell ref="A773:S773"/>
+    <mergeCell ref="A385:S385"/>
     <mergeCell ref="A3:S3"/>
-    <mergeCell ref="A385:S385"/>
-    <mergeCell ref="A773:S773"/>
     <mergeCell ref="A934:S934"/>
-    <mergeCell ref="A828:S828"/>
     <mergeCell ref="A748:S748"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/otzyvy_halyk.xlsx
+++ b/otzyvy_halyk.xlsx
@@ -73206,9 +73206,9 @@
     <mergeCell ref="A648:S648"/>
     <mergeCell ref="A270:S270"/>
     <mergeCell ref="A1059:S1059"/>
-    <mergeCell ref="A546:S546"/>
     <mergeCell ref="A986:S986"/>
     <mergeCell ref="A615:S615"/>
+    <mergeCell ref="A546:S546"/>
     <mergeCell ref="A207:S207"/>
     <mergeCell ref="A1139:S1139"/>
     <mergeCell ref="A1511:S1511"/>

--- a/otzyvy_halyk.xlsx
+++ b/otzyvy_halyk.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1519"/>
+  <dimension ref="A1:S1518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -73141,54 +73141,6 @@
       <c r="Q1518" s="14" t="n"/>
       <c r="R1518" s="14" t="n"/>
       <c r="S1518" s="14" t="n"/>
-    </row>
-    <row r="1519">
-      <c r="A1519" s="17" t="n">
-        <v>46235.51386574074</v>
-      </c>
-      <c r="B1519" s="18" t="inlineStr">
-        <is>
-          <t>kz</t>
-        </is>
-      </c>
-      <c r="C1519" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D1519" s="18" t="n"/>
-      <c r="E1519" s="11" t="inlineStr">
-        <is>
-          <t>очень низкое интернет соединение.</t>
-        </is>
-      </c>
-      <c r="F1519" s="20" t="inlineStr">
-        <is>
-          <t>Александр Дружков</t>
-        </is>
-      </c>
-      <c r="G1519" s="18" t="inlineStr">
-        <is>
-          <t>7.13.0</t>
-        </is>
-      </c>
-      <c r="H1519" s="18" t="inlineStr">
-        <is>
-          <t>2c1f83a453a36ad6e7885411</t>
-        </is>
-      </c>
-      <c r="I1519" s="18" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="K1519" s="14" t="n"/>
-      <c r="L1519" s="14" t="n"/>
-      <c r="M1519" s="14" t="n"/>
-      <c r="N1519" s="16" t="n"/>
-      <c r="O1519" s="10" t="n"/>
-      <c r="P1519" s="15" t="n"/>
-      <c r="Q1519" s="14" t="n"/>
-      <c r="R1519" s="14" t="n"/>
-      <c r="S1519" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="33">
